--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -2180,7 +2180,7 @@
     <t>Follow-up status</t>
   </si>
   <si>
-    <t>Under follow-up: The follow-up process is running. Follow-up completed: The follow-up has been completed. Follow-up canceled: The follow-up process has been canceled, e.g. because the person died or the contact became irrelevant. Lost to follow-up: The follow-up process could not be continued because the person was not available. No follow-up: No contact follow-up is being done.</t>
+    <t>&lt;ul&gt;&lt;li&gt;Under follow-up: The follow-up process is running.&lt;/li&gt;&lt;li&gt;Follow-up completed: The follow-up has been completed.&lt;/li&gt;&lt;li&gt;Follow-up canceled: The follow-up process has been canceled, e.g. because the person died or the contact became irrelevant.&lt;/li&gt;&lt;li&gt;Lost to follow-up: The follow-up process could not be continued, e.g. because the person could not be found.&lt;/li&gt;&lt;li&gt;No follow-up: No contact follow-up is being done.&lt;/li&gt;&lt;/ul&gt;</t>
   </si>
   <si>
     <t>EVD, Lassa, Cholera, Monkeypox, Plague, Other</t>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -3383,7 +3383,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.8.0-SNAPSHOT</t>
+    <t>1.9.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="1118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="1120">
   <si>
     <t>Field</t>
   </si>
@@ -2696,6 +2696,9 @@
     <t>Histopathology</t>
   </si>
   <si>
+    <t>ISOLATION</t>
+  </si>
+  <si>
     <t>IGM_SERUM_ANTIBODY</t>
   </si>
   <si>
@@ -2714,15 +2717,18 @@
     <t>Microscopy</t>
   </si>
   <si>
+    <t>NEUTRALIZING_ANTIBODIES</t>
+  </si>
+  <si>
+    <t>Neutralizing antibodies</t>
+  </si>
+  <si>
     <t>PCR_RT_PCR</t>
   </si>
   <si>
     <t>PCR / RT-PCR</t>
   </si>
   <si>
-    <t>VIRUS_ISOLATION</t>
-  </si>
-  <si>
     <t>WEST_NILE_FEVER_IGM</t>
   </si>
   <si>
@@ -3383,7 +3389,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.9.0-SNAPSHOT</t>
+    <t>1.10.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -4031,7 +4037,7 @@
 </file>
 
 <file path=xl/tables/table44.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="SampleSampleTestType" displayName="SampleSampleTestType" ref="A48:E65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="SampleSampleTestType" displayName="SampleSampleTestType" ref="A48:E66">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4061,7 +4067,7 @@
 </file>
 
 <file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="Sample_testSampleTestType" displayName="Sample_testSampleTestType" ref="A14:E31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="Sample_testSampleTestType" displayName="Sample_testSampleTestType" ref="A14:E32">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4075,7 +4081,7 @@
 </file>
 
 <file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="Sample_testSampleTestResultType" displayName="Sample_testSampleTestResultType" ref="A33:E37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="Sample_testSampleTestResultType" displayName="Sample_testSampleTestResultType" ref="A34:E38">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4355,7 +4361,7 @@
 </file>
 
 <file path=xl/tables/table64.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="User" displayName="User" ref="A1:G14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="User" displayName="User" ref="A1:G15">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -5781,7 +5787,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -5818,7 +5824,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>843</v>
@@ -5839,13 +5845,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>840</v>
       </c>
       <c r="C3" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>17</v>
@@ -5860,13 +5866,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>17</v>
@@ -5879,16 +5885,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -5940,7 +5946,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>206</v>
@@ -5961,13 +5967,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C9" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>17</v>
@@ -5982,13 +5988,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>17</v>
@@ -6003,13 +6009,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>341</v>
       </c>
       <c r="C11" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>17</v>
@@ -6022,16 +6028,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>341</v>
       </c>
       <c r="C12" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="10" t="s">
@@ -6154,7 +6160,7 @@
         <v>888</v>
       </c>
       <c r="C21" t="s">
-        <v>889</v>
+        <v>332</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
@@ -6166,10 +6172,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
+        <v>889</v>
+      </c>
+      <c r="C22" t="s">
         <v>890</v>
-      </c>
-      <c r="C22" t="s">
-        <v>891</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6181,10 +6187,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
+        <v>891</v>
+      </c>
+      <c r="C23" t="s">
         <v>892</v>
-      </c>
-      <c r="C23" t="s">
-        <v>893</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6196,10 +6202,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
+        <v>893</v>
+      </c>
+      <c r="C24" t="s">
         <v>894</v>
-      </c>
-      <c r="C24" t="s">
-        <v>895</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6211,10 +6217,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
+        <v>895</v>
+      </c>
+      <c r="C25" t="s">
         <v>896</v>
-      </c>
-      <c r="C25" t="s">
-        <v>332</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6301,59 +6307,59 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
+        <v>907</v>
+      </c>
+      <c r="C31" t="s">
+        <v>908</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32"/>
+      <c r="B32" t="s">
         <v>133</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>135</v>
       </c>
-      <c r="D31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D33" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>91</v>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>917</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>926</v>
+        <v>90</v>
       </c>
       <c r="C34" t="s">
-        <v>927</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35"/>
+      <c r="A35" t="s">
+        <v>919</v>
+      </c>
       <c r="B35" t="s">
-        <v>295</v>
+        <v>928</v>
       </c>
       <c r="C35" t="s">
-        <v>297</v>
+        <v>929</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -6365,10 +6371,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>928</v>
+        <v>295</v>
       </c>
       <c r="C36" t="s">
-        <v>929</v>
+        <v>297</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -6389,6 +6395,21 @@
         <v>17</v>
       </c>
       <c r="E37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38"/>
+      <c r="B38" t="s">
+        <v>932</v>
+      </c>
+      <c r="C38" t="s">
+        <v>933</v>
+      </c>
+      <c r="D38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E38" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6441,13 +6462,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>17</v>
@@ -6481,13 +6502,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C4" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>17</v>
@@ -6500,13 +6521,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C5" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>17</v>
@@ -6519,16 +6540,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="C6" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -6540,13 +6561,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="C7" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>17</v>
@@ -6559,13 +6580,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>17</v>
@@ -6580,13 +6601,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>17</v>
@@ -6599,13 +6620,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C10" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>17</v>
@@ -6618,13 +6639,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>17</v>
@@ -6637,13 +6658,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
@@ -6656,13 +6677,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>17</v>
@@ -6675,13 +6696,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -6694,13 +6715,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>17</v>
@@ -6715,13 +6736,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>
@@ -6734,7 +6755,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>25</v>
@@ -6753,7 +6774,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -6772,7 +6793,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>25</v>
@@ -6808,13 +6829,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B22" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="C22" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6826,10 +6847,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C23" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6841,10 +6862,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="C24" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6856,10 +6877,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C25" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6887,13 +6908,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B28" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="C28" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -6905,10 +6926,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C29" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -6920,10 +6941,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="C30" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -6935,10 +6956,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C31" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -6950,10 +6971,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C32" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -6965,10 +6986,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C33" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -6980,10 +7001,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="C34" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -6995,10 +7016,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C35" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7010,10 +7031,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="C36" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -7025,10 +7046,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C37" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -7040,10 +7061,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="C38" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -7055,10 +7076,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C39" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -7070,10 +7091,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="C40" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -7085,10 +7106,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C41" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -7100,10 +7121,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="C42" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -7115,10 +7136,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="C43" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -7130,10 +7151,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="C44" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -7148,7 +7169,7 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -7160,10 +7181,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C46" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -7175,10 +7196,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C47" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -7190,10 +7211,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C48" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -7221,13 +7242,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B51" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C51" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -7239,10 +7260,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C52" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -7254,10 +7275,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C53" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -7285,13 +7306,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B56" t="s">
         <v>295</v>
       </c>
       <c r="C56" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -7306,7 +7327,7 @@
         <v>298</v>
       </c>
       <c r="C57" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -7318,10 +7339,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C58" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -7333,10 +7354,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C59" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -7396,13 +7417,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="C2" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>17</v>
@@ -7417,16 +7438,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C3" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -7438,16 +7459,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -7459,16 +7480,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
@@ -7520,13 +7541,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>17</v>
@@ -7539,16 +7560,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C9" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="12" t="s">
@@ -7558,16 +7579,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="12" t="s">
@@ -7577,16 +7598,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="12" t="s">
@@ -7596,16 +7617,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="12" t="s">
@@ -7615,16 +7636,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="12" t="s">
@@ -7691,13 +7712,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>17</v>
@@ -7784,13 +7805,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B23" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="C23" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -7802,10 +7823,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="C24" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -7833,19 +7854,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B27" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C27" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="28">
@@ -7854,7 +7875,7 @@
         <v>289</v>
       </c>
       <c r="C28" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -7866,16 +7887,16 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C29" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="31">
@@ -7897,13 +7918,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="B32" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C32" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -7915,10 +7936,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C33" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -7945,10 +7966,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C35" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7960,10 +7981,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C36" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -8237,13 +8258,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C2" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>17</v>
@@ -8261,10 +8282,10 @@
         <v>198</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C3" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>17</v>
@@ -8279,13 +8300,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>17</v>
@@ -8362,13 +8383,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>17</v>
@@ -8463,7 +8484,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>17</v>
@@ -8482,7 +8503,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>17</v>
@@ -8495,10 +8516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -8514,7 +8535,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>341</v>
@@ -8550,13 +8571,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B13" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C13" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -8568,10 +8589,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="C14" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -8583,10 +8604,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C15" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -8598,10 +8619,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -8658,13 +8679,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>17</v>
@@ -8677,13 +8698,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>17</v>
@@ -8696,13 +8717,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>17</v>
@@ -8715,13 +8736,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>17</v>
@@ -8779,13 +8800,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>17</v>
@@ -8798,13 +8819,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>17</v>
@@ -8817,13 +8838,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>17</v>
@@ -8836,13 +8857,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>17</v>
@@ -8919,13 +8940,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>17</v>
@@ -8965,7 +8986,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -9002,13 +9023,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>17</v>
@@ -9021,13 +9042,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>17</v>
@@ -9078,13 +9099,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>17</v>
@@ -9135,11 +9156,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>17</v>
@@ -9190,13 +9211,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>17</v>
@@ -9209,13 +9230,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1113</v>
+        <v>230</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>820</v>
+        <v>231</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>17</v>
@@ -9228,13 +9249,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>206</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>1115</v>
+        <v>820</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>17</v>
@@ -9244,6 +9265,25 @@
         <v>11</v>
       </c>
       <c r="G14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15"/>
+      <c r="F15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -9260,12 +9300,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>
@@ -15753,7 +15793,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -16653,7 +16693,7 @@
         <v>888</v>
       </c>
       <c r="C55" t="s">
-        <v>889</v>
+        <v>332</v>
       </c>
       <c r="D55" t="s">
         <v>17</v>
@@ -16665,10 +16705,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
+        <v>889</v>
+      </c>
+      <c r="C56" t="s">
         <v>890</v>
-      </c>
-      <c r="C56" t="s">
-        <v>891</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -16680,10 +16720,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
+        <v>891</v>
+      </c>
+      <c r="C57" t="s">
         <v>892</v>
-      </c>
-      <c r="C57" t="s">
-        <v>893</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -16695,10 +16735,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
+        <v>893</v>
+      </c>
+      <c r="C58" t="s">
         <v>894</v>
-      </c>
-      <c r="C58" t="s">
-        <v>895</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -16710,10 +16750,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
+        <v>895</v>
+      </c>
+      <c r="C59" t="s">
         <v>896</v>
-      </c>
-      <c r="C59" t="s">
-        <v>332</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -16800,15 +16840,30 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
+        <v>907</v>
+      </c>
+      <c r="C65" t="s">
+        <v>908</v>
+      </c>
+      <c r="D65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66"/>
+      <c r="B66" t="s">
         <v>133</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>135</v>
       </c>
-      <c r="D65" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" t="s">
         <v>17</v>
       </c>
     </row>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="1117">
   <si>
     <t>Field</t>
   </si>
@@ -341,7 +341,7 @@
     <t>DEAD</t>
   </si>
   <si>
-    <t xml:space="preserve">Dead </t>
+    <t>Dead</t>
   </si>
   <si>
     <t>BURIED</t>
@@ -491,7 +491,7 @@
     <t>RELIGIOUS_LEADER</t>
   </si>
   <si>
-    <t xml:space="preserve">Religious leader </t>
+    <t>Religious leader</t>
   </si>
   <si>
     <t>HOUSEWIFE</t>
@@ -1007,7 +1007,7 @@
     <t>admittedToHealthFacility</t>
   </si>
   <si>
-    <t>Was patient admitted at the health facility?</t>
+    <t>Was patient admitted at the health facility as an inpatient?</t>
   </si>
   <si>
     <t>admissionDate</t>
@@ -1451,7 +1451,7 @@
     <t>Pain behind eyes/Sensitivity to light</t>
   </si>
   <si>
-    <t>Pain behind eyes or eyes sensitive to light</t>
+    <t>ain behind eyes or eyes sensitive to light</t>
   </si>
   <si>
     <t>EVD, Lassa, New flu, CSM, Measles, Dengue, Monkeypox, Other</t>
@@ -1736,9 +1736,6 @@
     <t>patientIllLocation</t>
   </si>
   <si>
-    <t>Name of the village (and country) where the patient got ill</t>
-  </si>
-  <si>
     <t>AXILLARY</t>
   </si>
   <si>
@@ -1757,9 +1754,6 @@
     <t>rectal</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes </t>
-  </si>
-  <si>
     <t>burialAttended</t>
   </si>
   <si>
@@ -2102,9 +2096,6 @@
     <t>Stream</t>
   </si>
   <si>
-    <t>Dead</t>
-  </si>
-  <si>
     <t>PROCESSED</t>
   </si>
   <si>
@@ -3389,7 +3380,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.10.0-SNAPSHOT</t>
+    <t>1.11.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -5824,10 +5815,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -5845,13 +5836,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C3" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>17</v>
@@ -5866,13 +5857,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>17</v>
@@ -5885,16 +5876,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -5906,13 +5897,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>17</v>
@@ -5927,13 +5918,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>17</v>
@@ -5946,7 +5937,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>206</v>
@@ -5967,13 +5958,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="C9" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>17</v>
@@ -5988,13 +5979,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>921</v>
+        <v>918</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>17</v>
@@ -6009,13 +6000,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>341</v>
       </c>
       <c r="C11" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>17</v>
@@ -6028,16 +6019,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>341</v>
       </c>
       <c r="C12" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="10" t="s">
@@ -6064,13 +6055,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B15" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C15" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -6082,10 +6073,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C16" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -6097,10 +6088,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C17" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -6112,10 +6103,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C18" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -6127,10 +6118,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C19" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -6142,10 +6133,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C20" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -6157,7 +6148,7 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C21" t="s">
         <v>332</v>
@@ -6172,10 +6163,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C22" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6187,10 +6178,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C23" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6202,10 +6193,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="C24" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6217,10 +6208,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="C25" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6232,10 +6223,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="C26" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -6247,10 +6238,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="C27" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -6262,10 +6253,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C28" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -6277,10 +6268,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C29" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -6292,10 +6283,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C30" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -6307,10 +6298,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C31" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -6353,13 +6344,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
       <c r="B35" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
       <c r="C35" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -6386,10 +6377,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="C37" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -6401,10 +6392,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="C38" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -6462,13 +6453,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="C2" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>17</v>
@@ -6483,13 +6474,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C3" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>17</v>
@@ -6502,13 +6493,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C4" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>17</v>
@@ -6521,13 +6512,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="C5" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>17</v>
@@ -6540,16 +6531,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>940</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>941</v>
+      </c>
+      <c r="C6" t="s">
+        <v>942</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>943</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>944</v>
-      </c>
-      <c r="C6" t="s">
-        <v>945</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>946</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -6561,13 +6552,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C7" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>17</v>
@@ -6580,13 +6571,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>17</v>
@@ -6601,13 +6592,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>17</v>
@@ -6620,13 +6611,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="C10" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>17</v>
@@ -6639,13 +6630,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>958</v>
+        <v>955</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>17</v>
@@ -6658,13 +6649,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
@@ -6677,13 +6668,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>17</v>
@@ -6696,13 +6687,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>964</v>
+        <v>961</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -6715,13 +6706,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>17</v>
@@ -6736,13 +6727,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>967</v>
+        <v>964</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>
@@ -6755,7 +6746,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>25</v>
@@ -6774,7 +6765,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -6793,7 +6784,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>25</v>
@@ -6829,13 +6820,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="B22" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="C22" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6847,10 +6838,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="C23" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6862,10 +6853,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="C24" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6877,10 +6868,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="C25" t="s">
-        <v>979</v>
+        <v>976</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6908,13 +6899,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="B28" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="C28" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -6926,10 +6917,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="C29" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -6941,10 +6932,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="C30" t="s">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -6956,10 +6947,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>986</v>
+        <v>983</v>
       </c>
       <c r="C31" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -6971,10 +6962,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="C32" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -6986,10 +6977,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="C33" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -7001,10 +6992,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="C34" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -7016,10 +7007,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="C35" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7031,10 +7022,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="C36" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -7046,10 +7037,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C37" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -7061,10 +7052,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C38" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -7076,10 +7067,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="C39" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -7091,10 +7082,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="C40" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -7106,10 +7097,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="C41" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -7121,10 +7112,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="C42" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -7136,10 +7127,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C43" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -7151,10 +7142,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C44" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -7169,7 +7160,7 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -7181,10 +7172,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="C46" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -7196,10 +7187,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C47" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -7211,10 +7202,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="C48" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -7242,13 +7233,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="B51" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="C51" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -7260,10 +7251,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C52" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -7275,10 +7266,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C53" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -7306,13 +7297,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>955</v>
+        <v>952</v>
       </c>
       <c r="B56" t="s">
         <v>295</v>
       </c>
       <c r="C56" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -7327,7 +7318,7 @@
         <v>298</v>
       </c>
       <c r="C57" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -7339,10 +7330,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C58" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -7354,10 +7345,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C59" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -7417,13 +7408,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="C2" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>17</v>
@@ -7438,16 +7429,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>1036</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>1039</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -7459,16 +7450,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -7480,16 +7471,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
@@ -7499,7 +7490,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>39</v>
@@ -7541,13 +7532,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>17</v>
@@ -7560,16 +7551,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>1048</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>1049</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>1051</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="12" t="s">
@@ -7579,16 +7570,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="12" t="s">
@@ -7598,16 +7589,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="12" t="s">
@@ -7617,16 +7608,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="12" t="s">
@@ -7636,16 +7627,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="12" t="s">
@@ -7712,13 +7703,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>17</v>
@@ -7805,13 +7796,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="B23" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C23" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -7823,10 +7814,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C24" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -7854,19 +7845,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="B27" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C27" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="28">
@@ -7875,7 +7866,7 @@
         <v>289</v>
       </c>
       <c r="C28" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -7887,16 +7878,16 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C29" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="31">
@@ -7918,13 +7909,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="B32" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="C32" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -7936,10 +7927,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="C33" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -7966,10 +7957,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="C35" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7981,10 +7972,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="C36" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -8258,13 +8249,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="C2" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>17</v>
@@ -8282,10 +8273,10 @@
         <v>198</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="C3" t="s">
-        <v>1085</v>
+        <v>1082</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>17</v>
@@ -8300,13 +8291,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>17</v>
@@ -8319,10 +8310,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8383,13 +8374,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>17</v>
@@ -8484,7 +8475,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>17</v>
@@ -8503,7 +8494,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>17</v>
@@ -8516,10 +8507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -8535,7 +8526,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>341</v>
@@ -8571,13 +8562,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C13" t="s">
         <v>1093</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1095</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1096</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -8589,10 +8580,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="C14" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -8604,10 +8595,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="C15" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -8619,10 +8610,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="C16" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -8679,13 +8670,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>17</v>
@@ -8698,13 +8689,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>17</v>
@@ -8717,13 +8708,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>17</v>
@@ -8736,13 +8727,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>17</v>
@@ -8800,13 +8791,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>17</v>
@@ -8819,13 +8810,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>17</v>
@@ -8838,13 +8829,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>17</v>
@@ -8857,13 +8848,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>17</v>
@@ -8940,13 +8931,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>17</v>
@@ -9023,13 +9014,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>341</v>
       </c>
       <c r="C2" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>17</v>
@@ -9042,13 +9033,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>17</v>
@@ -9099,13 +9090,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>17</v>
@@ -9156,11 +9147,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>17</v>
@@ -9249,13 +9240,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>17</v>
@@ -9268,13 +9259,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>17</v>
@@ -9300,12 +9291,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
     </row>
   </sheetData>
@@ -13096,7 +13087,7 @@
         <v>8</v>
       </c>
       <c r="C90" t="s">
-        <v>568</v>
+        <v>17</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>17</v>
@@ -13129,10 +13120,10 @@
         <v>355</v>
       </c>
       <c r="B93" t="s">
+        <v>568</v>
+      </c>
+      <c r="C93" t="s">
         <v>569</v>
-      </c>
-      <c r="C93" t="s">
-        <v>570</v>
       </c>
       <c r="D93" t="s">
         <v>17</v>
@@ -13144,10 +13135,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
+        <v>570</v>
+      </c>
+      <c r="C94" t="s">
         <v>571</v>
-      </c>
-      <c r="C94" t="s">
-        <v>572</v>
       </c>
       <c r="D94" t="s">
         <v>17</v>
@@ -13159,10 +13150,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
+        <v>572</v>
+      </c>
+      <c r="C95" t="s">
         <v>573</v>
-      </c>
-      <c r="C95" t="s">
-        <v>574</v>
       </c>
       <c r="D95" t="s">
         <v>17</v>
@@ -13196,7 +13187,7 @@
         <v>312</v>
       </c>
       <c r="C98" t="s">
-        <v>575</v>
+        <v>313</v>
       </c>
       <c r="D98" t="s">
         <v>17</v>
@@ -13284,16 +13275,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E2"/>
       <c r="F2" s="6" t="s">
@@ -13303,35 +13294,35 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E3"/>
       <c r="F3" s="6" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E4"/>
       <c r="F4" s="6" t="s">
@@ -13341,11 +13332,11 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>17</v>
@@ -13358,11 +13349,11 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>17</v>
@@ -13375,11 +13366,11 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>17</v>
@@ -13392,89 +13383,89 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C8" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" s="6" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="6" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C10" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C11" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="6" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>17</v>
@@ -13487,13 +13478,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C13" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>17</v>
@@ -13506,13 +13497,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>17</v>
@@ -13525,206 +13516,206 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C15" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C21" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C22" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C24" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="6" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C25" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E25"/>
       <c r="F25" s="6" t="s">
@@ -13734,35 +13725,35 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C26" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E26"/>
       <c r="F26" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C27" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E27"/>
       <c r="F27" s="6" t="s">
@@ -13772,35 +13763,35 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C28" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E28"/>
       <c r="F28" s="6" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C29" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E29"/>
       <c r="F29" s="6" t="s">
@@ -13810,130 +13801,130 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C30" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E30"/>
       <c r="F30" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>653</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="C32" t="s">
         <v>655</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="D32" s="6" t="s">
         <v>656</v>
-      </c>
-      <c r="C32" t="s">
-        <v>657</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>658</v>
       </c>
       <c r="E32"/>
       <c r="F32" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C34" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E34"/>
       <c r="F34" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C36" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E36"/>
       <c r="F36" s="6" t="s">
@@ -13943,16 +13934,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C37" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="6" t="s">
@@ -13962,13 +13953,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>17</v>
@@ -13981,13 +13972,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>17</v>
@@ -14000,13 +13991,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>677</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="C40" t="s">
         <v>679</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>680</v>
-      </c>
-      <c r="C40" t="s">
-        <v>681</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>17</v>
@@ -14100,13 +14091,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B48" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C48" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -14118,10 +14109,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C49" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -14133,10 +14124,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C50" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -14148,10 +14139,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C51" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -14194,7 +14185,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B55" t="s">
         <v>100</v>
@@ -14215,7 +14206,7 @@
         <v>102</v>
       </c>
       <c r="C56" t="s">
-        <v>690</v>
+        <v>103</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -14227,10 +14218,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C57" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -14304,13 +14295,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -14409,7 +14400,7 @@
         <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>17</v>
@@ -14424,13 +14415,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C8" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>17</v>
@@ -14445,13 +14436,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>17</v>
@@ -14464,13 +14455,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>17</v>
@@ -14483,16 +14474,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>700</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>701</v>
+      </c>
+      <c r="C11" t="s">
+        <v>702</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>703</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>704</v>
-      </c>
-      <c r="C11" t="s">
-        <v>705</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>706</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="7" t="s">
@@ -14502,13 +14493,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C12" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>17</v>
@@ -14521,13 +14512,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C13" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>17</v>
@@ -14540,89 +14531,89 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>710</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>711</v>
+      </c>
+      <c r="C14" t="s">
+        <v>712</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>713</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>714</v>
-      </c>
-      <c r="C14" t="s">
-        <v>715</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>716</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="7" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>17</v>
@@ -14635,16 +14626,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>723</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="C19" t="s">
+        <v>725</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>726</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="C19" t="s">
-        <v>728</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>729</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="7" t="s">
@@ -14654,13 +14645,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C20" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>17</v>
@@ -14673,13 +14664,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>17</v>
@@ -14893,13 +14884,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B37" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C37" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -14911,10 +14902,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C38" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -14926,10 +14917,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C39" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -14941,10 +14932,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C40" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -14956,10 +14947,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C41" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -14987,19 +14978,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B44" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C44" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="45">
@@ -15008,7 +14999,7 @@
         <v>289</v>
       </c>
       <c r="C45" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -15020,16 +15011,16 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C46" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="48">
@@ -15051,13 +15042,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B49" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C49" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -15069,10 +15060,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C50" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -15084,10 +15075,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C51" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -15115,76 +15106,76 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B54" t="s">
+        <v>754</v>
+      </c>
+      <c r="C54" t="s">
+        <v>755</v>
+      </c>
+      <c r="D54" t="s">
+        <v>756</v>
+      </c>
+      <c r="E54" t="s">
         <v>757</v>
-      </c>
-      <c r="C54" t="s">
-        <v>758</v>
-      </c>
-      <c r="D54" t="s">
-        <v>759</v>
-      </c>
-      <c r="E54" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
+        <v>758</v>
+      </c>
+      <c r="C55" t="s">
+        <v>759</v>
+      </c>
+      <c r="D55" t="s">
+        <v>760</v>
+      </c>
+      <c r="E55" t="s">
         <v>761</v>
-      </c>
-      <c r="C55" t="s">
-        <v>762</v>
-      </c>
-      <c r="D55" t="s">
-        <v>763</v>
-      </c>
-      <c r="E55" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
+        <v>762</v>
+      </c>
+      <c r="C56" t="s">
+        <v>763</v>
+      </c>
+      <c r="D56" t="s">
+        <v>764</v>
+      </c>
+      <c r="E56" t="s">
         <v>765</v>
-      </c>
-      <c r="C56" t="s">
-        <v>766</v>
-      </c>
-      <c r="D56" t="s">
-        <v>767</v>
-      </c>
-      <c r="E56" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
+        <v>766</v>
+      </c>
+      <c r="C57" t="s">
+        <v>767</v>
+      </c>
+      <c r="D57" t="s">
+        <v>768</v>
+      </c>
+      <c r="E57" t="s">
         <v>769</v>
-      </c>
-      <c r="C57" t="s">
-        <v>770</v>
-      </c>
-      <c r="D57" t="s">
-        <v>771</v>
-      </c>
-      <c r="E57" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C58" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D58" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
@@ -15209,13 +15200,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B61" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C61" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
@@ -15227,10 +15218,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C62" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
@@ -15242,10 +15233,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C63" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D63" t="s">
         <v>17</v>
@@ -15257,10 +15248,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C64" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
@@ -15343,7 +15334,7 @@
         <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>17</v>
@@ -15377,16 +15368,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -15398,13 +15389,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>17</v>
@@ -15419,16 +15410,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>787</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>788</v>
+      </c>
+      <c r="C6" t="s">
+        <v>789</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>790</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>791</v>
-      </c>
-      <c r="C6" t="s">
-        <v>792</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>793</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -15440,16 +15431,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="E7"/>
       <c r="F7" s="8" t="s">
@@ -15736,13 +15727,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="B27" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C27" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -15754,31 +15745,31 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C28" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C29" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
   </sheetData>
@@ -15830,13 +15821,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C2" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>17</v>
@@ -15851,13 +15842,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>17</v>
@@ -15870,13 +15861,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>17</v>
@@ -15889,16 +15880,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -15910,7 +15901,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>39</v>
@@ -16009,13 +16000,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C11" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>17</v>
@@ -16030,13 +16021,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>17</v>
@@ -16049,13 +16040,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>17</v>
@@ -16070,13 +16061,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>17</v>
@@ -16089,13 +16080,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>17</v>
@@ -16108,13 +16099,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>17</v>
@@ -16127,13 +16118,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>17</v>
@@ -16146,13 +16137,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C18" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>17</v>
@@ -16165,13 +16156,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>17</v>
@@ -16184,13 +16175,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>17</v>
@@ -16203,13 +16194,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C21" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>17</v>
@@ -16222,13 +16213,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C22" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>17</v>
@@ -16241,10 +16232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -16260,13 +16251,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>341</v>
       </c>
       <c r="C24" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>17</v>
@@ -16279,13 +16270,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>341</v>
       </c>
       <c r="C25" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>17</v>
@@ -16315,13 +16306,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="B28" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C28" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -16333,10 +16324,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C29" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -16348,10 +16339,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="C30" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -16363,10 +16354,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C31" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -16378,10 +16369,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C32" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -16393,10 +16384,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C33" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -16408,10 +16399,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C34" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -16423,10 +16414,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C35" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -16438,10 +16429,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C36" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -16484,13 +16475,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="B40" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C40" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -16502,10 +16493,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="C41" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -16533,13 +16524,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B44" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C44" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -16551,10 +16542,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C45" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -16566,10 +16557,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C46" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -16597,13 +16588,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B49" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C49" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -16615,10 +16606,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C50" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -16630,10 +16621,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C51" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -16645,10 +16636,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C52" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -16660,10 +16651,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C53" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -16675,10 +16666,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C54" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="D54" t="s">
         <v>17</v>
@@ -16690,7 +16681,7 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C55" t="s">
         <v>332</v>
@@ -16705,10 +16696,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C56" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -16720,10 +16711,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="C57" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -16735,10 +16726,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="C58" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -16750,10 +16741,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="C59" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -16765,10 +16756,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="C60" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="D60" t="s">
         <v>17</v>
@@ -16780,10 +16771,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="C61" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
@@ -16795,10 +16786,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C62" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
@@ -16810,10 +16801,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="C63" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="D63" t="s">
         <v>17</v>
@@ -16825,10 +16816,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="C64" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
@@ -16840,10 +16831,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C65" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D65" t="s">
         <v>17</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -2915,7 +2915,7 @@
     <t>creatorComment</t>
   </si>
   <si>
-    <t>Supervisor comment</t>
+    <t>Comments on task</t>
   </si>
   <si>
     <t>assigneeUser</t>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3178" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3183" uniqueCount="1119">
   <si>
     <t>Field</t>
   </si>
@@ -839,6 +839,12 @@
     <t>Epidemiological data</t>
   </si>
   <si>
+    <t>therapy</t>
+  </si>
+  <si>
+    <t>Therapy</t>
+  </si>
+  <si>
     <t>BUBONIC</t>
   </si>
   <si>
@@ -3380,7 +3386,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.11.0-SNAPSHOT</t>
+    <t>1.12.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -3510,7 +3516,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Case" displayName="Case" ref="A1:G38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Case" displayName="Case" ref="A1:G39">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -3526,7 +3532,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="CaseDisease" displayName="CaseDisease" ref="A40:E51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="CaseDisease" displayName="CaseDisease" ref="A41:E52">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3540,7 +3546,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="CasePlagueType" displayName="CasePlagueType" ref="A53:E56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="CasePlagueType" displayName="CasePlagueType" ref="A54:E57">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3554,7 +3560,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="CaseDengueFeverType" displayName="CaseDengueFeverType" ref="A58:E61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="CaseDengueFeverType" displayName="CaseDengueFeverType" ref="A59:E62">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3568,7 +3574,7 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="CaseCaseClassification" displayName="CaseCaseClassification" ref="A63:E68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="CaseCaseClassification" displayName="CaseCaseClassification" ref="A64:E69">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3582,7 +3588,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="CaseInvestigationStatus" displayName="CaseInvestigationStatus" ref="A70:E73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="CaseInvestigationStatus" displayName="CaseInvestigationStatus" ref="A71:E74">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3596,7 +3602,7 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="CaseCaseOutcome" displayName="CaseCaseOutcome" ref="A75:E79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="CaseCaseOutcome" displayName="CaseCaseOutcome" ref="A76:E80">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3610,7 +3616,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="CaseYesNoUnknown" displayName="CaseYesNoUnknown" ref="A81:E84">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="CaseYesNoUnknown" displayName="CaseYesNoUnknown" ref="A82:E85">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3624,7 +3630,7 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="CaseVaccination" displayName="CaseVaccination" ref="A86:E89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="CaseVaccination" displayName="CaseVaccination" ref="A87:E90">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -3652,7 +3658,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="CaseVaccinationInfoSource" displayName="CaseVaccinationInfoSource" ref="A91:E93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="CaseVaccinationInfoSource" displayName="CaseVaccinationInfoSource" ref="A92:E94">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -5815,10 +5821,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -5836,13 +5842,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C3" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>17</v>
@@ -5857,13 +5863,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>17</v>
@@ -5876,16 +5882,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -5897,13 +5903,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>17</v>
@@ -5918,13 +5924,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>17</v>
@@ -5937,7 +5943,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>206</v>
@@ -5958,13 +5964,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C9" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>17</v>
@@ -5979,13 +5985,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>17</v>
@@ -6000,13 +6006,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C11" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>17</v>
@@ -6019,16 +6025,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C12" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="10" t="s">
@@ -6055,13 +6061,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B15" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C15" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -6073,10 +6079,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C16" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -6088,10 +6094,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C17" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -6103,10 +6109,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C18" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -6118,10 +6124,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -6133,10 +6139,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C20" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -6148,10 +6154,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C21" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D21" t="s">
         <v>17</v>
@@ -6163,10 +6169,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C22" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6178,10 +6184,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C23" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6193,10 +6199,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C24" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6208,10 +6214,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C25" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6223,10 +6229,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C26" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -6238,10 +6244,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C27" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -6253,10 +6259,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C28" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -6268,10 +6274,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C29" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -6283,10 +6289,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C30" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -6298,10 +6304,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C31" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -6344,13 +6350,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B35" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C35" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -6362,10 +6368,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -6377,10 +6383,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C37" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -6392,10 +6398,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C38" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -6453,13 +6459,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C2" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>17</v>
@@ -6474,13 +6480,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>17</v>
@@ -6493,13 +6499,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>17</v>
@@ -6512,13 +6518,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C5" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>17</v>
@@ -6531,16 +6537,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C6" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -6552,13 +6558,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C7" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>17</v>
@@ -6571,13 +6577,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>17</v>
@@ -6592,13 +6598,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>17</v>
@@ -6611,13 +6617,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="C10" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>17</v>
@@ -6630,13 +6636,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>17</v>
@@ -6649,13 +6655,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
@@ -6668,13 +6674,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>206</v>
       </c>
       <c r="C13" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>17</v>
@@ -6687,13 +6693,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -6706,13 +6712,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>17</v>
@@ -6727,13 +6733,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>
@@ -6746,7 +6752,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>25</v>
@@ -6765,7 +6771,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -6784,7 +6790,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>25</v>
@@ -6820,13 +6826,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B22" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C22" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6838,10 +6844,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C23" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6853,10 +6859,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C24" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6868,10 +6874,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C25" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6899,13 +6905,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B28" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C28" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -6917,10 +6923,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C29" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -6932,10 +6938,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C30" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -6947,10 +6953,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C31" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -6962,10 +6968,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C32" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -6977,10 +6983,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C33" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -6992,10 +6998,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C34" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -7007,10 +7013,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C35" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7022,10 +7028,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C36" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -7037,10 +7043,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C37" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -7052,10 +7058,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C38" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -7067,10 +7073,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C39" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -7082,10 +7088,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C40" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -7097,10 +7103,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C41" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -7112,10 +7118,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C42" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -7127,10 +7133,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C43" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -7142,10 +7148,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C44" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -7160,7 +7166,7 @@
         <v>133</v>
       </c>
       <c r="C45" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -7172,10 +7178,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="C46" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -7187,10 +7193,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="C47" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -7202,10 +7208,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="C48" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -7233,13 +7239,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B51" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="C51" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -7251,10 +7257,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="C52" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -7266,10 +7272,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="C53" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -7297,13 +7303,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B56" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C56" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -7315,10 +7321,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C57" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -7330,10 +7336,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="C58" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -7345,10 +7351,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="C59" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -7408,13 +7414,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C2" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>17</v>
@@ -7429,16 +7435,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C3" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -7450,16 +7456,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -7471,16 +7477,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
@@ -7490,7 +7496,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>39</v>
@@ -7532,13 +7538,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>17</v>
@@ -7551,16 +7557,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C9" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="12" t="s">
@@ -7570,16 +7576,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="12" t="s">
@@ -7589,16 +7595,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="12" t="s">
@@ -7608,16 +7614,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="12" t="s">
@@ -7627,16 +7633,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="12" t="s">
@@ -7703,13 +7709,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>17</v>
@@ -7796,13 +7802,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="B23" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C23" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -7814,10 +7820,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C24" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -7845,49 +7851,49 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B27" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C27" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C28" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C29" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="31">
@@ -7909,13 +7915,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B32" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C32" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -7927,10 +7933,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="C33" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -7957,10 +7963,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C35" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7972,10 +7978,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C36" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -7987,10 +7993,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C37" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -8249,13 +8255,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C2" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>17</v>
@@ -8273,10 +8279,10 @@
         <v>198</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C3" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>17</v>
@@ -8291,13 +8297,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>17</v>
@@ -8310,10 +8316,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8374,13 +8380,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>17</v>
@@ -8475,7 +8481,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>17</v>
@@ -8494,7 +8500,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>17</v>
@@ -8507,10 +8513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -8526,10 +8532,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -8562,13 +8568,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B13" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C13" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -8580,10 +8586,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C14" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="D14" t="s">
         <v>17</v>
@@ -8595,10 +8601,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C15" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -8610,10 +8616,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C16" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -8670,13 +8676,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>17</v>
@@ -8689,13 +8695,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>17</v>
@@ -8708,13 +8714,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>17</v>
@@ -8727,13 +8733,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>17</v>
@@ -8791,13 +8797,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>17</v>
@@ -8810,13 +8816,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>17</v>
@@ -8829,13 +8835,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>17</v>
@@ -8848,13 +8854,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>17</v>
@@ -8931,13 +8937,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>17</v>
@@ -9014,13 +9020,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C2" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>17</v>
@@ -9033,13 +9039,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>17</v>
@@ -9090,13 +9096,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>17</v>
@@ -9147,11 +9153,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>17</v>
@@ -9240,13 +9246,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>17</v>
@@ -9259,13 +9265,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>206</v>
       </c>
       <c r="C15" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>17</v>
@@ -9291,12 +9297,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
   </sheetData>
@@ -9522,7 +9528,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -10328,107 +10334,111 @@
       </c>
       <c r="G38"/>
     </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>90</v>
-      </c>
-      <c r="C40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" t="s">
-        <v>91</v>
-      </c>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>269</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C39" t="s">
+        <v>270</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
         <v>46</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>110</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>111</v>
       </c>
-      <c r="D41" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42"/>
-      <c r="B42" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" t="s">
-        <v>113</v>
-      </c>
       <c r="D42" t="s">
         <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>112</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -10440,10 +10450,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -10455,99 +10465,99 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C48" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
       </c>
       <c r="E48" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
       </c>
       <c r="E49" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C50" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
       </c>
       <c r="E50" t="s">
-        <v>132</v>
+        <v>17</v>
       </c>
     </row>
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52"/>
+      <c r="B52" t="s">
         <v>133</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>134</v>
       </c>
-      <c r="D51" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="D52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>1</v>
-      </c>
-      <c r="B53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C53" t="s">
-        <v>2</v>
-      </c>
-      <c r="D53" t="s">
-        <v>3</v>
-      </c>
-      <c r="E53" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
         <v>193</v>
       </c>
-      <c r="B54" t="s">
-        <v>269</v>
-      </c>
-      <c r="C54" t="s">
-        <v>270</v>
-      </c>
-      <c r="D54" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55"/>
       <c r="B55" t="s">
         <v>271</v>
       </c>
@@ -10576,47 +10586,47 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>1</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" t="s">
-        <v>91</v>
+    <row r="57">
+      <c r="A57"/>
+      <c r="B57" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" t="s">
+        <v>276</v>
+      </c>
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>196</v>
       </c>
-      <c r="B59" t="s">
-        <v>275</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="B60" t="s">
+        <v>277</v>
+      </c>
+      <c r="C60" t="s">
         <v>115</v>
-      </c>
-      <c r="D59" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60"/>
-      <c r="B60" t="s">
-        <v>276</v>
-      </c>
-      <c r="C60" t="s">
-        <v>277</v>
       </c>
       <c r="D60" t="s">
         <v>17</v>
@@ -10640,200 +10650,200 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>1</v>
-      </c>
-      <c r="B63" t="s">
-        <v>90</v>
-      </c>
-      <c r="C63" t="s">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
-        <v>3</v>
-      </c>
-      <c r="E63" t="s">
-        <v>91</v>
+    <row r="62">
+      <c r="A62"/>
+      <c r="B62" t="s">
+        <v>280</v>
+      </c>
+      <c r="C62" t="s">
+        <v>281</v>
+      </c>
+      <c r="D62" t="s">
+        <v>17</v>
+      </c>
+      <c r="E62" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
         <v>212</v>
       </c>
-      <c r="B64" t="s">
-        <v>280</v>
-      </c>
-      <c r="C64" t="s">
-        <v>281</v>
-      </c>
-      <c r="D64" t="s">
-        <v>17</v>
-      </c>
-      <c r="E64" t="s">
+      <c r="B65" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65"/>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>283</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" t="s">
         <v>284</v>
-      </c>
-      <c r="D65" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
+        <v>285</v>
+      </c>
+      <c r="C66" t="s">
         <v>286</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" t="s">
         <v>287</v>
-      </c>
-      <c r="D66" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
+        <v>288</v>
+      </c>
+      <c r="C67" t="s">
         <v>289</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" t="s">
         <v>290</v>
-      </c>
-      <c r="D67" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
+        <v>291</v>
+      </c>
+      <c r="C68" t="s">
         <v>292</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" t="s">
         <v>293</v>
       </c>
-      <c r="D68" t="s">
-        <v>17</v>
-      </c>
-      <c r="E68" t="s">
+    </row>
+    <row r="69">
+      <c r="A69"/>
+      <c r="B69" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>1</v>
-      </c>
-      <c r="B70" t="s">
-        <v>90</v>
-      </c>
-      <c r="C70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D70" t="s">
-        <v>3</v>
-      </c>
-      <c r="E70" t="s">
-        <v>91</v>
+      <c r="C69" t="s">
+        <v>295</v>
+      </c>
+      <c r="D69" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>1</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
         <v>221</v>
       </c>
-      <c r="B71" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" t="s">
-        <v>296</v>
-      </c>
-      <c r="D71" t="s">
-        <v>17</v>
-      </c>
-      <c r="E71" t="s">
+      <c r="B72" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72"/>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>298</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" t="s">
         <v>299</v>
-      </c>
-      <c r="D72" t="s">
-        <v>17</v>
-      </c>
-      <c r="E72" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
+        <v>300</v>
+      </c>
+      <c r="C73" t="s">
         <v>301</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73" t="s">
         <v>302</v>
       </c>
-      <c r="D73" t="s">
-        <v>17</v>
-      </c>
-      <c r="E73" t="s">
+    </row>
+    <row r="74">
+      <c r="A74"/>
+      <c r="B74" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B75" t="s">
-        <v>90</v>
-      </c>
-      <c r="C75" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" t="s">
-        <v>3</v>
-      </c>
-      <c r="E75" t="s">
-        <v>91</v>
+      <c r="C74" t="s">
+        <v>304</v>
+      </c>
+      <c r="D74" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>1</v>
+      </c>
+      <c r="B76" t="s">
+        <v>90</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
         <v>226</v>
       </c>
-      <c r="B76" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" t="s">
-        <v>305</v>
-      </c>
-      <c r="D76" t="s">
-        <v>17</v>
-      </c>
-      <c r="E76" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77"/>
       <c r="B77" t="s">
         <v>306</v>
       </c>
@@ -10877,42 +10887,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>1</v>
-      </c>
-      <c r="B81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C81" t="s">
-        <v>2</v>
-      </c>
-      <c r="D81" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" t="s">
-        <v>91</v>
+    <row r="80">
+      <c r="A80"/>
+      <c r="B80" t="s">
+        <v>312</v>
+      </c>
+      <c r="C80" t="s">
+        <v>313</v>
+      </c>
+      <c r="D80" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
+        <v>1</v>
+      </c>
+      <c r="B82" t="s">
+        <v>90</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" t="s">
+        <v>3</v>
+      </c>
+      <c r="E82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
         <v>235</v>
       </c>
-      <c r="B82" t="s">
-        <v>312</v>
-      </c>
-      <c r="C82" t="s">
-        <v>313</v>
-      </c>
-      <c r="D82" t="s">
-        <v>17</v>
-      </c>
-      <c r="E82" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83"/>
       <c r="B83" t="s">
         <v>314</v>
       </c>
@@ -10929,10 +10939,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C84" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D84" t="s">
         <v>17</v>
@@ -10941,42 +10951,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>1</v>
-      </c>
-      <c r="B86" t="s">
-        <v>90</v>
-      </c>
-      <c r="C86" t="s">
-        <v>2</v>
-      </c>
-      <c r="D86" t="s">
-        <v>3</v>
-      </c>
-      <c r="E86" t="s">
-        <v>91</v>
+    <row r="85">
+      <c r="A85"/>
+      <c r="B85" t="s">
+        <v>312</v>
+      </c>
+      <c r="C85" t="s">
+        <v>313</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>90</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" t="s">
+        <v>3</v>
+      </c>
+      <c r="E87" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
         <v>239</v>
       </c>
-      <c r="B87" t="s">
-        <v>316</v>
-      </c>
-      <c r="C87" t="s">
-        <v>317</v>
-      </c>
-      <c r="D87" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88"/>
       <c r="B88" t="s">
         <v>318</v>
       </c>
@@ -10993,10 +11003,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C89" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="D89" t="s">
         <v>17</v>
@@ -11005,42 +11015,42 @@
         <v>17</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>1</v>
-      </c>
-      <c r="B91" t="s">
-        <v>90</v>
-      </c>
-      <c r="C91" t="s">
-        <v>2</v>
-      </c>
-      <c r="D91" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" t="s">
-        <v>91</v>
+    <row r="90">
+      <c r="A90"/>
+      <c r="B90" t="s">
+        <v>312</v>
+      </c>
+      <c r="C90" t="s">
+        <v>313</v>
+      </c>
+      <c r="D90" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" t="s">
+        <v>90</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
         <v>249</v>
       </c>
-      <c r="B92" t="s">
-        <v>320</v>
-      </c>
-      <c r="C92" t="s">
-        <v>321</v>
-      </c>
-      <c r="D92" t="s">
-        <v>17</v>
-      </c>
-      <c r="E92" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93"/>
       <c r="B93" t="s">
         <v>322</v>
       </c>
@@ -11051,6 +11061,21 @@
         <v>17</v>
       </c>
       <c r="E93" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94"/>
+      <c r="B94" t="s">
+        <v>324</v>
+      </c>
+      <c r="C94" t="s">
+        <v>325</v>
+      </c>
+      <c r="D94" t="s">
+        <v>17</v>
+      </c>
+      <c r="E94" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11110,13 +11135,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>17</v>
@@ -11131,16 +11156,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E3"/>
       <c r="F3" s="4" t="s">
@@ -11150,13 +11175,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>17</v>
@@ -11169,16 +11194,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>235</v>
       </c>
       <c r="C5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="4" t="s">
@@ -11188,13 +11213,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>17</v>
@@ -11207,13 +11232,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>235</v>
       </c>
       <c r="C7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>17</v>
@@ -11226,11 +11251,11 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
@@ -11263,10 +11288,10 @@
         <v>235</v>
       </c>
       <c r="B11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -11278,10 +11303,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D12" t="s">
         <v>17</v>
@@ -11293,10 +11318,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C13" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D13" t="s">
         <v>17</v>
@@ -11353,16 +11378,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E2"/>
       <c r="F2" s="5" t="s">
@@ -11372,16 +11397,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E3"/>
       <c r="F3" s="5" t="s">
@@ -11393,16 +11418,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E4"/>
       <c r="F4" s="5" t="s">
@@ -11412,20 +11437,20 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -11433,20 +11458,20 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E6"/>
       <c r="F6" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -11454,20 +11479,20 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E7"/>
       <c r="F7" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -11475,20 +11500,20 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -11496,20 +11521,20 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -11517,77 +11542,77 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C12" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C13" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -11595,20 +11620,20 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -11616,39 +11641,39 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C16" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -11656,20 +11681,20 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -11677,20 +11702,20 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C18" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -11698,191 +11723,191 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C19" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C20" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C21" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C22" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C23" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C24" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C25" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E25"/>
       <c r="F25" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C26" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E26"/>
       <c r="F26" s="5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C27" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E27"/>
       <c r="F27" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C28" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E28"/>
       <c r="F28" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -11890,115 +11915,115 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C29" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E29"/>
       <c r="F29" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C30" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E30"/>
       <c r="F30" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C31" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C32" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E32"/>
       <c r="F32" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C34" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E34"/>
       <c r="F34" s="5" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G34" t="b">
         <v>1</v>
@@ -12006,20 +12031,20 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C35" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G35" t="b">
         <v>1</v>
@@ -12027,20 +12052,20 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C36" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E36"/>
       <c r="F36" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G36" t="b">
         <v>1</v>
@@ -12048,39 +12073,39 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C37" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C38" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E38"/>
       <c r="F38" s="5" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G38" t="b">
         <v>1</v>
@@ -12088,58 +12113,58 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C39" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E39"/>
       <c r="F39" s="5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C40" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E40"/>
       <c r="F40" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G40"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C41" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E41"/>
       <c r="F41" s="5" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G41" t="b">
         <v>1</v>
@@ -12147,20 +12172,20 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C42" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E42"/>
       <c r="F42" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G42" t="b">
         <v>1</v>
@@ -12168,20 +12193,20 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C43" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E43"/>
       <c r="F43" s="5" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G43" t="b">
         <v>1</v>
@@ -12189,20 +12214,20 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C44" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E44"/>
       <c r="F44" s="5" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G44" t="b">
         <v>1</v>
@@ -12210,39 +12235,39 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C45" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E45"/>
       <c r="F45" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C46" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E46"/>
       <c r="F46" s="5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G46" t="b">
         <v>1</v>
@@ -12250,115 +12275,115 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C47" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E47"/>
       <c r="F47" s="5" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C48" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E48"/>
       <c r="F48" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C49" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E49"/>
       <c r="F49" s="5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C50" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E50"/>
       <c r="F50" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C51" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E51"/>
       <c r="F51" s="5" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C52" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E52"/>
       <c r="F52" s="5" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G52" t="b">
         <v>1</v>
@@ -12366,39 +12391,39 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C53" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E53"/>
       <c r="F53" s="5" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C54" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E54"/>
       <c r="F54" s="5" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="G54" t="b">
         <v>1</v>
@@ -12406,20 +12431,20 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C55" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E55"/>
       <c r="F55" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G55" t="b">
         <v>1</v>
@@ -12427,16 +12452,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C56" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E56"/>
       <c r="F56" s="5" t="s">
@@ -12446,336 +12471,336 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C57" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E57"/>
       <c r="F57" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C58" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E58"/>
       <c r="F58" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C59" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E59"/>
       <c r="F59" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C60" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E60"/>
       <c r="F60" s="5" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C61" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E61"/>
       <c r="F61" s="5" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C62" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E62"/>
       <c r="F62" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C63" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E63"/>
       <c r="F63" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C64" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E64"/>
       <c r="F64" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C65" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E65"/>
       <c r="F65" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C66" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E66"/>
       <c r="F66" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C67" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E67"/>
       <c r="F67" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C68" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E68"/>
       <c r="F68" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C69" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E69"/>
       <c r="F69" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G69"/>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C70" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E70"/>
       <c r="F70" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C71" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E71"/>
       <c r="F71" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G71"/>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C72" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E72"/>
       <c r="F72" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G72"/>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C73" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E73"/>
       <c r="F73" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G73"/>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C74" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>17</v>
@@ -12788,13 +12813,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C75" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>17</v>
@@ -12807,13 +12832,13 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
+        <v>542</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C76" t="s">
         <v>540</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="C76" t="s">
-        <v>538</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>17</v>
@@ -12826,13 +12851,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C77" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>17</v>
@@ -12845,13 +12870,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C78" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>17</v>
@@ -12864,77 +12889,77 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C79" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E79"/>
       <c r="F79" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C80" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E80"/>
       <c r="F80" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C81" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D81" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E81"/>
       <c r="F81" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C82" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E82"/>
       <c r="F82" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G82" t="b">
         <v>1</v>
@@ -12942,20 +12967,20 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C83" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E83"/>
       <c r="F83" s="5" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="G83" t="b">
         <v>1</v>
@@ -12963,77 +12988,77 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C84" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E84"/>
       <c r="F84" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C85" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E85"/>
       <c r="F85" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G85"/>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C86" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E86"/>
       <c r="F86" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C87" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E87"/>
       <c r="F87" s="5" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G87" t="b">
         <v>1</v>
@@ -13041,20 +13066,20 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E88"/>
       <c r="F88" s="5" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G88" t="b">
         <v>1</v>
@@ -13062,26 +13087,26 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C89" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E89"/>
       <c r="F89" s="5" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>8</v>
@@ -13094,7 +13119,7 @@
       </c>
       <c r="E90"/>
       <c r="F90" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G90"/>
     </row>
@@ -13117,13 +13142,13 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B93" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C93" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D93" t="s">
         <v>17</v>
@@ -13135,10 +13160,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C94" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D94" t="s">
         <v>17</v>
@@ -13150,10 +13175,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C95" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D95" t="s">
         <v>17</v>
@@ -13181,13 +13206,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B98" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C98" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D98" t="s">
         <v>17</v>
@@ -13199,10 +13224,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C99" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D99" t="s">
         <v>17</v>
@@ -13214,10 +13239,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C100" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D100" t="s">
         <v>17</v>
@@ -13275,68 +13300,68 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E2"/>
       <c r="F2" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E3"/>
       <c r="F3" s="6" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="G3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C4" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E4"/>
       <c r="F4" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="G4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>17</v>
@@ -13349,11 +13374,11 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>17</v>
@@ -13366,11 +13391,11 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>17</v>
@@ -13383,89 +13408,89 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C8" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" s="6" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="G8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C9" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="6" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C10" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C11" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="6" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C12" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>17</v>
@@ -13478,13 +13503,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C13" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>17</v>
@@ -13497,13 +13522,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>17</v>
@@ -13516,495 +13541,495 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C15" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C17" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C21" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C22" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="G23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C24" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="6" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="G24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C25" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="E25"/>
       <c r="F25" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C26" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="E26"/>
       <c r="F26" s="6" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C27" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="E27"/>
       <c r="F27" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C28" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E28"/>
       <c r="F28" s="6" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C29" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="E29"/>
       <c r="F29" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C30" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E30"/>
       <c r="F30" s="6" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="6" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C32" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="E32"/>
       <c r="F32" s="6" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="6" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C34" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="E34"/>
       <c r="F34" s="6" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="6" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C36" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="E36"/>
       <c r="F36" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>235</v>
       </c>
       <c r="C37" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E38"/>
       <c r="F38" s="6" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G38"/>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E39"/>
       <c r="F39" s="6" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C40" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E40"/>
       <c r="F40" s="6" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="G40"/>
     </row>
@@ -14030,10 +14055,10 @@
         <v>235</v>
       </c>
       <c r="B43" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C43" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -14045,10 +14070,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C44" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -14060,10 +14085,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C45" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -14091,13 +14116,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B48" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C48" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -14109,10 +14134,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C49" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -14124,10 +14149,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C50" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -14139,10 +14164,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C51" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -14185,7 +14210,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B55" t="s">
         <v>100</v>
@@ -14218,10 +14243,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C57" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -14233,10 +14258,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C58" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -14295,13 +14320,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -14400,7 +14425,7 @@
         <v>199</v>
       </c>
       <c r="C7" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>17</v>
@@ -14415,13 +14440,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C8" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>17</v>
@@ -14436,13 +14461,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>17</v>
@@ -14455,13 +14480,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>17</v>
@@ -14474,16 +14499,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C11" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="7" t="s">
@@ -14493,13 +14518,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C12" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>17</v>
@@ -14512,13 +14537,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C13" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>17</v>
@@ -14531,89 +14556,89 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C14" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="7" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="7" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="7" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="7" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>17</v>
@@ -14626,16 +14651,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C19" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="7" t="s">
@@ -14645,13 +14670,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C20" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>17</v>
@@ -14664,13 +14689,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>206</v>
       </c>
       <c r="C21" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>17</v>
@@ -14884,13 +14909,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B37" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C37" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -14902,10 +14927,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C38" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -14917,10 +14942,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C39" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -14932,10 +14957,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C40" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -14947,10 +14972,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C41" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -14978,49 +15003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B44" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C44" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C45" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
       </c>
       <c r="E45" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="C46" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
     </row>
     <row r="48">
@@ -15042,13 +15067,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B49" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C49" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -15060,10 +15085,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C50" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -15075,10 +15100,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C51" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -15106,76 +15131,76 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B54" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C54" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D54" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E54" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C55" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D55" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="E55" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C56" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D56" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="E56" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C57" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D57" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="E57" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C58" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D58" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
@@ -15200,13 +15225,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B61" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C61" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
@@ -15218,10 +15243,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C62" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
@@ -15233,10 +15258,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C63" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D63" t="s">
         <v>17</v>
@@ -15248,10 +15273,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C64" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
@@ -15334,7 +15359,7 @@
         <v>199</v>
       </c>
       <c r="C2" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>17</v>
@@ -15368,16 +15393,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -15389,13 +15414,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>17</v>
@@ -15410,16 +15435,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -15431,16 +15456,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E7"/>
       <c r="F7" s="8" t="s">
@@ -15727,13 +15752,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B27" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C27" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -15745,31 +15770,31 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C28" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C29" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
     </row>
   </sheetData>
@@ -15821,13 +15846,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C2" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>17</v>
@@ -15842,13 +15867,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>17</v>
@@ -15861,13 +15886,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>17</v>
@@ -15880,16 +15905,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -15901,7 +15926,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>39</v>
@@ -16000,13 +16025,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="C11" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>17</v>
@@ -16021,13 +16046,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>17</v>
@@ -16040,13 +16065,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>17</v>
@@ -16061,13 +16086,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>17</v>
@@ -16080,13 +16105,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>17</v>
@@ -16099,13 +16124,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>17</v>
@@ -16118,13 +16143,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>17</v>
@@ -16137,13 +16162,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C18" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>17</v>
@@ -16156,13 +16181,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>17</v>
@@ -16175,13 +16200,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>17</v>
@@ -16194,13 +16219,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C21" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>17</v>
@@ -16213,13 +16238,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C22" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>17</v>
@@ -16232,10 +16257,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C23" t="s">
         <v>17</v>
@@ -16251,13 +16276,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C24" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>17</v>
@@ -16270,13 +16295,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>17</v>
@@ -16306,13 +16331,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B28" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C28" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -16324,10 +16349,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C29" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -16339,10 +16364,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C30" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -16354,10 +16379,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C31" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -16369,10 +16394,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C32" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -16384,10 +16409,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C33" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -16399,10 +16424,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C34" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -16414,10 +16439,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C35" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -16429,10 +16454,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C36" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -16475,13 +16500,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B40" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C40" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -16493,10 +16518,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C41" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -16524,13 +16549,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B44" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C44" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -16542,10 +16567,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C45" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -16557,10 +16582,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C46" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -16588,13 +16613,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B49" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C49" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -16606,10 +16631,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C50" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -16621,10 +16646,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C51" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -16636,10 +16661,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C52" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -16651,10 +16676,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C53" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -16666,10 +16691,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C54" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D54" t="s">
         <v>17</v>
@@ -16681,10 +16706,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C55" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D55" t="s">
         <v>17</v>
@@ -16696,10 +16721,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="C56" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -16711,10 +16736,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C57" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -16726,10 +16751,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="C58" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -16741,10 +16766,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C59" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -16756,10 +16781,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="C60" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="D60" t="s">
         <v>17</v>
@@ -16771,10 +16796,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C61" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
@@ -16786,10 +16811,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="C62" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
@@ -16801,10 +16826,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C63" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D63" t="s">
         <v>17</v>
@@ -16816,10 +16841,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="C64" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
@@ -16831,10 +16856,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C65" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D65" t="s">
         <v>17</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="1208">
   <si>
     <t>Field</t>
   </si>
@@ -1232,7 +1232,7 @@
     <t>midUpperArmCircumference</t>
   </si>
   <si>
-    <t>Mid-upper arm circumference (cm)</t>
+    <t>Mid-upper arm circumf. (cm)</t>
   </si>
   <si>
     <t>respiratoryRate</t>
@@ -2009,6 +2009,12 @@
     <t>rectal</t>
   </si>
   <si>
+    <t>NON_CONTACT</t>
+  </si>
+  <si>
+    <t>Non-contact (infrared)</t>
+  </si>
+  <si>
     <t>burialAttended</t>
   </si>
   <si>
@@ -2711,7 +2717,7 @@
     <t>sampleDateTime</t>
   </si>
   <si>
-    <t>Date of sampling</t>
+    <t>Date sample was collected</t>
   </si>
   <si>
     <t>When the sample was taken (enter a date)?</t>
@@ -2810,6 +2816,15 @@
     <t>Received</t>
   </si>
   <si>
+    <t>pathogenTestResult</t>
+  </si>
+  <si>
+    <t>PathogenTestResultType</t>
+  </si>
+  <si>
+    <t>Pathogen test result</t>
+  </si>
+  <si>
     <t>pathogenTestingRequested</t>
   </si>
   <si>
@@ -2831,6 +2846,18 @@
     <t>requestedAdditionalTests</t>
   </si>
   <si>
+    <t>requestedOtherPathogenTests</t>
+  </si>
+  <si>
+    <t>Other requested pathogen tests</t>
+  </si>
+  <si>
+    <t>requestedOtherAdditionalTests</t>
+  </si>
+  <si>
+    <t>Other requested additional tests</t>
+  </si>
+  <si>
     <t>BLOOD</t>
   </si>
   <si>
@@ -2921,6 +2948,24 @@
     <t>Environment</t>
   </si>
   <si>
+    <t>INDETERMINATE</t>
+  </si>
+  <si>
+    <t>Indeterminate</t>
+  </si>
+  <si>
+    <t>NEGATIVE</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>POSITIVE</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
     <t>sample</t>
   </si>
   <si>
@@ -2951,9 +2996,6 @@
     <t>testResult</t>
   </si>
   <si>
-    <t>PathogenTestResultType</t>
-  </si>
-  <si>
     <t>Test result</t>
   </si>
   <si>
@@ -2966,7 +3008,7 @@
     <t>testResultVerified</t>
   </si>
   <si>
-    <t>Result verified by supervisor</t>
+    <t>Result verified by lab supervisor</t>
   </si>
   <si>
     <t>fourFoldIncreaseAntibodyTiter</t>
@@ -3074,24 +3116,6 @@
     <t>Yersinia pestis antigen test</t>
   </si>
   <si>
-    <t>INDETERMINATE</t>
-  </si>
-  <si>
-    <t>Indeterminate</t>
-  </si>
-  <si>
-    <t>NEGATIVE</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>POSITIVE</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
     <t>taskContext</t>
   </si>
   <si>
@@ -3629,7 +3653,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.14.0-SNAPSHOT</t>
+    <t>1.15.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -3989,7 +4013,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="SymptomsTemperatureSource" displayName="SymptomsTemperatureSource" ref="A116:E119">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="SymptomsTemperatureSource" displayName="SymptomsTemperatureSource" ref="A116:E120">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4003,7 +4027,7 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="SymptomsSymptomState" displayName="SymptomsSymptomState" ref="A121:E124">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="SymptomsSymptomState" displayName="SymptomsSymptomState" ref="A122:E125">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4247,7 +4271,7 @@
 </file>
 
 <file path=xl/tables/table42.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="Sample" displayName="Sample" ref="A1:G28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="42" name="Sample" displayName="Sample" ref="A1:G31">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -4263,7 +4287,7 @@
 </file>
 
 <file path=xl/tables/table43.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="SampleSampleMaterial" displayName="SampleSampleMaterial" ref="A30:E41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="43" name="SampleSampleMaterial" displayName="SampleSampleMaterial" ref="A33:E44">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4277,7 +4301,7 @@
 </file>
 
 <file path=xl/tables/table44.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="SampleSpecimenCondition" displayName="SampleSpecimenCondition" ref="A43:E45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="44" name="SampleSpecimenCondition" displayName="SampleSpecimenCondition" ref="A46:E48">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4291,7 +4315,7 @@
 </file>
 
 <file path=xl/tables/table45.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="SampleSampleSource" displayName="SampleSampleSource" ref="A47:E50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="45" name="SampleSampleSource" displayName="SampleSampleSource" ref="A50:E53">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4305,7 +4329,21 @@
 </file>
 
 <file path=xl/tables/table46.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="Pathogen_test" displayName="Pathogen_test" ref="A1:G12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="46" name="SamplePathogenTestResultType" displayName="SamplePathogenTestResultType" ref="A55:E59">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="Pathogen_test" displayName="Pathogen_test" ref="A1:G12">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -4320,22 +4358,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table47.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="47" name="Pathogen_testPathogenTestType" displayName="Pathogen_testPathogenTestType" ref="A14:E32">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
 <file path=xl/tables/table48.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="Pathogen_testPathogenTestResultType" displayName="Pathogen_testPathogenTestResultType" ref="A34:E38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="48" name="Pathogen_testPathogenTestType" displayName="Pathogen_testPathogenTestType" ref="A14:E32">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4349,18 +4373,16 @@
 </file>
 
 <file path=xl/tables/table49.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="Task" displayName="Task" ref="A1:G19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="49" name="Pathogen_testPathogenTestResultType" displayName="Pathogen_testPathogenTestResultType" ref="A34:E38">
   <autoFilter/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Type"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
     <tableColumn id="3" name="Caption"/>
     <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Required"/>
-    <tableColumn id="6" name="Diseases"/>
-    <tableColumn id="7" name="Outbreaks"/>
+    <tableColumn id="5" name="Short"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
@@ -4379,63 +4401,7 @@
 </file>
 
 <file path=xl/tables/table50.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="TaskTaskContext" displayName="TaskTaskContext" ref="A21:E25">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table51.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="TaskTaskType" displayName="TaskTaskType" ref="A27:E48">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table52.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="TaskTaskPriority" displayName="TaskTaskPriority" ref="A50:E53">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table53.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="TaskTaskStatus" displayName="TaskTaskStatus" ref="A55:E59">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table54.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="Event" displayName="Event" ref="A1:G20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="50" name="Task" displayName="Task" ref="A1:G19">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -4450,8 +4416,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="EventEventType" displayName="EventEventType" ref="A22:E24">
+<file path=xl/tables/table51.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="TaskTaskContext" displayName="TaskTaskContext" ref="A21:E25">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4464,8 +4430,66 @@
 </table>
 </file>
 
+<file path=xl/tables/table52.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="TaskTaskType" displayName="TaskTaskType" ref="A27:E48">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table53.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="TaskTaskPriority" displayName="TaskTaskPriority" ref="A50:E53">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table54.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="TaskTaskStatus" displayName="TaskTaskStatus" ref="A55:E59">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="Event" displayName="Event" ref="A1:G20">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Type"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
 <file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="EventEventStatus" displayName="EventEventStatus" ref="A26:E29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="EventEventType" displayName="EventEventType" ref="A22:E24">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4479,7 +4503,7 @@
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="EventTypeOfPlace" displayName="EventTypeOfPlace" ref="A31:E38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="EventEventStatus" displayName="EventEventStatus" ref="A26:E29">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4493,7 +4517,7 @@
 </file>
 
 <file path=xl/tables/table58.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="EventDisease" displayName="EventDisease" ref="A40:E51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="EventTypeOfPlace" displayName="EventTypeOfPlace" ref="A31:E38">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4507,18 +4531,16 @@
 </file>
 
 <file path=xl/tables/table59.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="Person_involved" displayName="Person_involved" ref="A1:G5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="EventDisease" displayName="EventDisease" ref="A40:E51">
   <autoFilter/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Type"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
     <tableColumn id="3" name="Caption"/>
     <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Required"/>
-    <tableColumn id="6" name="Diseases"/>
-    <tableColumn id="7" name="Outbreaks"/>
+    <tableColumn id="5" name="Short"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
@@ -4537,7 +4559,7 @@
 </file>
 
 <file path=xl/tables/table60.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="Facility" displayName="Facility" ref="A1:G10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="Person_involved" displayName="Person_involved" ref="A1:G5">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -4553,21 +4575,7 @@
 </file>
 
 <file path=xl/tables/table61.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="FacilityFacilityType" displayName="FacilityFacilityType" ref="A12:E16">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table62.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="Region" displayName="Region" ref="A1:G5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="Facility" displayName="Facility" ref="A1:G10">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -4582,8 +4590,22 @@
 </table>
 </file>
 
+<file path=xl/tables/table62.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="FacilityFacilityType" displayName="FacilityFacilityType" ref="A12:E16">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
 <file path=xl/tables/table63.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="63" name="District" displayName="District" ref="A1:G6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="63" name="Region" displayName="Region" ref="A1:G5">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -4599,7 +4621,7 @@
 </file>
 
 <file path=xl/tables/table64.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="Community" displayName="Community" ref="A1:G4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="District" displayName="District" ref="A1:G6">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -4615,7 +4637,23 @@
 </file>
 
 <file path=xl/tables/table65.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="User" displayName="User" ref="A1:G15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="Community" displayName="Community" ref="A1:G4">
+  <autoFilter/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Type"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="Diseases"/>
+    <tableColumn id="7" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table66.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="66" name="User" displayName="User" ref="A1:G15">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -6247,10 +6285,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C2" t="s">
         <v>17</v>
@@ -6268,13 +6306,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C3" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>17</v>
@@ -6289,13 +6327,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>17</v>
@@ -6308,13 +6346,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>17</v>
@@ -6329,13 +6367,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>17</v>
@@ -6350,13 +6388,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>17</v>
@@ -6369,7 +6407,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>222</v>
@@ -6390,13 +6428,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>973</v>
+        <v>929</v>
       </c>
       <c r="C9" t="s">
-        <v>974</v>
+        <v>988</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>17</v>
@@ -6411,13 +6449,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>975</v>
+        <v>989</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>17</v>
@@ -6432,13 +6470,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>977</v>
+        <v>991</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>376</v>
       </c>
       <c r="C11" t="s">
-        <v>978</v>
+        <v>992</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>17</v>
@@ -6451,13 +6489,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>979</v>
+        <v>993</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>376</v>
       </c>
       <c r="C12" t="s">
-        <v>980</v>
+        <v>994</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>17</v>
@@ -6487,13 +6525,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="B15" t="s">
-        <v>981</v>
+        <v>995</v>
       </c>
       <c r="C15" t="s">
-        <v>982</v>
+        <v>996</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -6505,10 +6543,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="C16" t="s">
-        <v>984</v>
+        <v>998</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -6520,10 +6558,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>985</v>
+        <v>999</v>
       </c>
       <c r="C17" t="s">
-        <v>986</v>
+        <v>1000</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -6535,10 +6573,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>987</v>
+        <v>1001</v>
       </c>
       <c r="C18" t="s">
-        <v>988</v>
+        <v>1002</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -6550,10 +6588,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>989</v>
+        <v>1003</v>
       </c>
       <c r="C19" t="s">
-        <v>990</v>
+        <v>1004</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -6565,10 +6603,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>991</v>
+        <v>1005</v>
       </c>
       <c r="C20" t="s">
-        <v>992</v>
+        <v>1006</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -6580,7 +6618,7 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>993</v>
+        <v>1007</v>
       </c>
       <c r="C21" t="s">
         <v>361</v>
@@ -6595,10 +6633,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>994</v>
+        <v>1008</v>
       </c>
       <c r="C22" t="s">
-        <v>995</v>
+        <v>1009</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6610,10 +6648,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>996</v>
+        <v>1010</v>
       </c>
       <c r="C23" t="s">
-        <v>997</v>
+        <v>1011</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6625,10 +6663,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>998</v>
+        <v>1012</v>
       </c>
       <c r="C24" t="s">
-        <v>999</v>
+        <v>1013</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6640,10 +6678,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1000</v>
+        <v>1014</v>
       </c>
       <c r="C25" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6655,10 +6693,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>1002</v>
+        <v>1016</v>
       </c>
       <c r="C26" t="s">
-        <v>1003</v>
+        <v>1017</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -6670,10 +6708,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1004</v>
+        <v>1018</v>
       </c>
       <c r="C27" t="s">
-        <v>1005</v>
+        <v>1019</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -6685,10 +6723,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>1006</v>
+        <v>1020</v>
       </c>
       <c r="C28" t="s">
-        <v>1007</v>
+        <v>1021</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -6700,10 +6738,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1008</v>
+        <v>1022</v>
       </c>
       <c r="C29" t="s">
-        <v>1009</v>
+        <v>1023</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -6715,10 +6753,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1010</v>
+        <v>1024</v>
       </c>
       <c r="C30" t="s">
-        <v>1011</v>
+        <v>1025</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -6730,10 +6768,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1012</v>
+        <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>1013</v>
+        <v>1027</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -6776,13 +6814,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>929</v>
+      </c>
+      <c r="B35" t="s">
+        <v>972</v>
+      </c>
+      <c r="C35" t="s">
         <v>973</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1015</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -6809,10 +6847,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1016</v>
+        <v>974</v>
       </c>
       <c r="C37" t="s">
-        <v>1017</v>
+        <v>975</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -6824,10 +6862,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1018</v>
+        <v>976</v>
       </c>
       <c r="C38" t="s">
-        <v>1019</v>
+        <v>977</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -6885,13 +6923,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="C2" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>17</v>
@@ -6906,13 +6944,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C3" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>17</v>
@@ -6925,13 +6963,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="C4" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>17</v>
@@ -6944,13 +6982,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="C5" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>17</v>
@@ -6963,16 +7001,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="C6" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -6984,13 +7022,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="C7" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>17</v>
@@ -7003,13 +7041,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>17</v>
@@ -7024,13 +7062,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>17</v>
@@ -7043,13 +7081,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="C10" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>17</v>
@@ -7062,13 +7100,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>17</v>
@@ -7081,13 +7119,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
@@ -7100,13 +7138,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>17</v>
@@ -7119,13 +7157,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -7138,13 +7176,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>17</v>
@@ -7159,13 +7197,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>
@@ -7178,7 +7216,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>25</v>
@@ -7197,7 +7235,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -7216,7 +7254,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>25</v>
@@ -7252,13 +7290,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="B22" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="C22" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -7270,10 +7308,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="C23" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -7285,10 +7323,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="C24" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -7300,10 +7338,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="C25" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -7331,13 +7369,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="B28" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="C28" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -7349,10 +7387,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="C29" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -7364,10 +7402,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="C30" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -7379,10 +7417,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="C31" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -7394,10 +7432,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="C32" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -7409,10 +7447,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="C33" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -7424,10 +7462,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="C34" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -7439,10 +7477,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="C35" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7454,10 +7492,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="C36" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -7469,10 +7507,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="C37" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -7484,10 +7522,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="C38" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -7499,10 +7537,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="C39" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -7514,10 +7552,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="C40" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -7529,10 +7567,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="C41" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -7544,10 +7582,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="C42" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -7559,10 +7597,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="C43" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -7574,10 +7612,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="C44" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -7592,7 +7630,7 @@
         <v>142</v>
       </c>
       <c r="C45" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -7604,10 +7642,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="C46" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -7619,10 +7657,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="C47" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -7634,10 +7672,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
       <c r="C48" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -7665,13 +7703,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="B51" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="C51" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -7683,10 +7721,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="C52" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -7698,10 +7736,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="C53" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -7729,13 +7767,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="B56" t="s">
         <v>321</v>
       </c>
       <c r="C56" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -7750,7 +7788,7 @@
         <v>324</v>
       </c>
       <c r="C57" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -7762,10 +7800,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="C58" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -7777,10 +7815,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="C59" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -7840,13 +7878,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="C2" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>17</v>
@@ -7861,16 +7899,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="C3" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -7882,16 +7920,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -7903,16 +7941,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
@@ -7922,7 +7960,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>35</v>
@@ -7964,13 +8002,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>17</v>
@@ -7983,16 +8021,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="C9" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="12" t="s">
@@ -8002,16 +8040,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1138</v>
+        <v>1146</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>1139</v>
+        <v>1147</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1140</v>
+        <v>1148</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="12" t="s">
@@ -8021,16 +8059,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1141</v>
+        <v>1149</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>1142</v>
+        <v>1150</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1143</v>
+        <v>1151</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="12" t="s">
@@ -8040,16 +8078,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1144</v>
+        <v>1152</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>1145</v>
+        <v>1153</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1146</v>
+        <v>1154</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="12" t="s">
@@ -8059,16 +8097,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1147</v>
+        <v>1155</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1149</v>
+        <v>1157</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="12" t="s">
@@ -8135,13 +8173,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1150</v>
+        <v>1158</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>1151</v>
+        <v>1159</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>17</v>
@@ -8228,13 +8266,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="B23" t="s">
-        <v>1152</v>
+        <v>1160</v>
       </c>
       <c r="C23" t="s">
-        <v>1153</v>
+        <v>1161</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -8246,10 +8284,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1154</v>
+        <v>1162</v>
       </c>
       <c r="C24" t="s">
-        <v>1155</v>
+        <v>1163</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -8277,19 +8315,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="B27" t="s">
-        <v>1156</v>
+        <v>1164</v>
       </c>
       <c r="C27" t="s">
-        <v>1157</v>
+        <v>1165</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>1158</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="28">
@@ -8298,7 +8336,7 @@
         <v>315</v>
       </c>
       <c r="C28" t="s">
-        <v>1159</v>
+        <v>1167</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -8310,16 +8348,16 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1160</v>
+        <v>1168</v>
       </c>
       <c r="C29" t="s">
-        <v>1161</v>
+        <v>1169</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>1162</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="31">
@@ -8341,13 +8379,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="B32" t="s">
-        <v>1163</v>
+        <v>1171</v>
       </c>
       <c r="C32" t="s">
-        <v>1164</v>
+        <v>1172</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -8359,10 +8397,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1165</v>
+        <v>1173</v>
       </c>
       <c r="C33" t="s">
-        <v>1166</v>
+        <v>1174</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -8389,10 +8427,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1167</v>
+        <v>1175</v>
       </c>
       <c r="C35" t="s">
-        <v>1168</v>
+        <v>1176</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -8404,10 +8442,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1169</v>
+        <v>1177</v>
       </c>
       <c r="C36" t="s">
-        <v>1170</v>
+        <v>1178</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -8681,13 +8719,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="C2" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>17</v>
@@ -8705,10 +8743,10 @@
         <v>214</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="C3" t="s">
-        <v>1171</v>
+        <v>1179</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>17</v>
@@ -8723,13 +8761,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1172</v>
+        <v>1180</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1173</v>
+        <v>1181</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>17</v>
@@ -8742,10 +8780,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -8806,13 +8844,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>17</v>
@@ -8907,7 +8945,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>1176</v>
+        <v>1184</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>17</v>
@@ -8926,7 +8964,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>1177</v>
+        <v>1185</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>17</v>
@@ -8939,10 +8977,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1178</v>
+        <v>1186</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -8958,7 +8996,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1180</v>
+        <v>1188</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>376</v>
@@ -8994,7 +9032,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1179</v>
+        <v>1187</v>
       </c>
       <c r="B13" t="s">
         <v>155</v>
@@ -9042,10 +9080,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="C16" t="s">
-        <v>1181</v>
+        <v>1189</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -9102,13 +9140,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>17</v>
@@ -9121,13 +9159,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>17</v>
@@ -9140,13 +9178,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>17</v>
@@ -9159,13 +9197,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>17</v>
@@ -9223,13 +9261,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>17</v>
@@ -9242,13 +9280,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1182</v>
+        <v>1190</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1183</v>
+        <v>1191</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>17</v>
@@ -9261,13 +9299,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1184</v>
+        <v>1192</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1185</v>
+        <v>1193</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>17</v>
@@ -9280,13 +9318,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1186</v>
+        <v>1194</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1187</v>
+        <v>1195</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>17</v>
@@ -9363,13 +9401,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1174</v>
+        <v>1182</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1175</v>
+        <v>1183</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>17</v>
@@ -9465,13 +9503,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1188</v>
+        <v>1196</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>376</v>
       </c>
       <c r="C2" t="s">
-        <v>1189</v>
+        <v>1197</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>17</v>
@@ -9484,13 +9522,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1190</v>
+        <v>1198</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1191</v>
+        <v>1199</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>17</v>
@@ -9541,13 +9579,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>1148</v>
+        <v>1156</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>17</v>
@@ -9598,11 +9636,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1193</v>
+        <v>1201</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" t="s">
-        <v>1194</v>
+        <v>1202</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>17</v>
@@ -9691,13 +9729,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1195</v>
+        <v>1203</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>17</v>
@@ -9710,13 +9748,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1196</v>
+        <v>1204</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>1197</v>
+        <v>1205</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>17</v>
@@ -9742,12 +9780,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1198</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1199</v>
+        <v>1207</v>
       </c>
     </row>
   </sheetData>
@@ -11931,7 +11969,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -14241,47 +14279,47 @@
         <v>17</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>1</v>
-      </c>
-      <c r="B121" t="s">
-        <v>97</v>
-      </c>
-      <c r="C121" t="s">
-        <v>2</v>
-      </c>
-      <c r="D121" t="s">
-        <v>3</v>
-      </c>
-      <c r="E121" t="s">
-        <v>98</v>
+    <row r="120">
+      <c r="A120"/>
+      <c r="B120" t="s">
+        <v>659</v>
+      </c>
+      <c r="C120" t="s">
+        <v>660</v>
+      </c>
+      <c r="D120" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>1</v>
+      </c>
+      <c r="B122" t="s">
+        <v>97</v>
+      </c>
+      <c r="C122" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>3</v>
+      </c>
+      <c r="E122" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
         <v>410</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B123" t="s">
         <v>338</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C123" t="s">
         <v>339</v>
-      </c>
-      <c r="D122" t="s">
-        <v>17</v>
-      </c>
-      <c r="E122" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123"/>
-      <c r="B123" t="s">
-        <v>340</v>
-      </c>
-      <c r="C123" t="s">
-        <v>341</v>
       </c>
       <c r="D123" t="s">
         <v>17</v>
@@ -14293,15 +14331,30 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
+        <v>340</v>
+      </c>
+      <c r="C124" t="s">
+        <v>341</v>
+      </c>
+      <c r="D124" t="s">
+        <v>17</v>
+      </c>
+      <c r="E124" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125"/>
+      <c r="B125" t="s">
         <v>336</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C125" t="s">
         <v>337</v>
       </c>
-      <c r="D124" t="s">
-        <v>17</v>
-      </c>
-      <c r="E124" t="s">
+      <c r="D125" t="s">
+        <v>17</v>
+      </c>
+      <c r="E125" t="s">
         <v>17</v>
       </c>
     </row>
@@ -14354,16 +14407,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="E2"/>
       <c r="F2" s="6" t="s">
@@ -14373,35 +14426,35 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="E3"/>
       <c r="F3" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C4" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E4"/>
       <c r="F4" s="6" t="s">
@@ -14411,11 +14464,11 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>17</v>
@@ -14428,11 +14481,11 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>17</v>
@@ -14445,11 +14498,11 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>17</v>
@@ -14462,32 +14515,32 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E8"/>
       <c r="F8" s="6" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C9" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>17</v>
@@ -14500,51 +14553,51 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="6" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="G11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C12" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>17</v>
@@ -14557,13 +14610,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>17</v>
@@ -14576,13 +14629,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C14" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>17</v>
@@ -14595,206 +14648,206 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C15" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C16" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C17" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C21" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C22" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="6" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C24" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="6" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C25" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="E25"/>
       <c r="F25" s="6" t="s">
@@ -14804,35 +14857,35 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C26" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="E26"/>
       <c r="F26" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="G26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C27" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E27"/>
       <c r="F27" s="6" t="s">
@@ -14842,35 +14895,35 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C28" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E28"/>
       <c r="F28" s="6" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C29" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="E29"/>
       <c r="F29" s="6" t="s">
@@ -14880,130 +14933,130 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C30" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E30"/>
       <c r="F30" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="G30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="G31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C32" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="E32"/>
       <c r="F32" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C34" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="E34"/>
       <c r="F34" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="G35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C36" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E36"/>
       <c r="F36" s="6" t="s">
@@ -15013,16 +15066,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>248</v>
       </c>
       <c r="C37" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="6" t="s">
@@ -15032,13 +15085,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>17</v>
@@ -15051,13 +15104,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>17</v>
@@ -15070,13 +15123,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C40" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>17</v>
@@ -15170,13 +15223,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B48" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C48" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -15188,10 +15241,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C49" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -15203,10 +15256,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C50" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -15218,10 +15271,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C51" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -15264,7 +15317,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B55" t="s">
         <v>109</v>
@@ -15297,10 +15350,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C57" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -15374,13 +15427,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>17</v>
@@ -15479,7 +15532,7 @@
         <v>215</v>
       </c>
       <c r="C7" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>17</v>
@@ -15494,13 +15547,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C8" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>17</v>
@@ -15515,13 +15568,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>17</v>
@@ -15534,13 +15587,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>17</v>
@@ -15553,16 +15606,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C11" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="7" t="s">
@@ -15572,13 +15625,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C12" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>17</v>
@@ -15591,13 +15644,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C13" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>17</v>
@@ -15610,89 +15663,89 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C14" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="7" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="7" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="7" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>222</v>
       </c>
       <c r="C17" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="7" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>17</v>
@@ -15705,16 +15758,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C19" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="7" t="s">
@@ -15724,13 +15777,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C20" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>17</v>
@@ -15743,13 +15796,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>222</v>
       </c>
       <c r="C21" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>17</v>
@@ -15963,13 +16016,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B37" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C37" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -15981,10 +16034,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C38" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -15996,10 +16049,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C39" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -16011,10 +16064,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C40" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -16026,10 +16079,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C41" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -16057,19 +16110,19 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B44" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C44" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
       </c>
       <c r="E44" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
     </row>
     <row r="45">
@@ -16078,7 +16131,7 @@
         <v>315</v>
       </c>
       <c r="C45" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -16090,16 +16143,16 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C46" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
       </c>
       <c r="E46" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="48">
@@ -16121,13 +16174,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B49" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C49" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="D49" t="s">
         <v>17</v>
@@ -16139,10 +16192,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C50" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D50" t="s">
         <v>17</v>
@@ -16154,10 +16207,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C51" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -16185,76 +16238,76 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B54" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C54" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D54" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="E54" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C55" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D55" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="E55" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C56" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D56" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E56" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C57" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="D57" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="E57" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="C58" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="D58" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E58" t="s">
         <v>17</v>
@@ -16279,13 +16332,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B61" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C61" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="D61" t="s">
         <v>17</v>
@@ -16297,10 +16350,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C62" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="D62" t="s">
         <v>17</v>
@@ -16312,10 +16365,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C63" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="D63" t="s">
         <v>17</v>
@@ -16327,10 +16380,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C64" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="D64" t="s">
         <v>17</v>
@@ -16413,7 +16466,7 @@
         <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>17</v>
@@ -16447,16 +16500,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -16468,13 +16521,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>222</v>
       </c>
       <c r="C5" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>17</v>
@@ -16489,16 +16542,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C6" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -16510,16 +16563,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E7"/>
       <c r="F7" s="8" t="s">
@@ -16806,13 +16859,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B27" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="C27" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -16824,31 +16877,31 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C28" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C29" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -16863,7 +16916,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -16900,13 +16953,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C2" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="D2" s="9" t="s">
         <v>17</v>
@@ -16921,13 +16974,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>17</v>
@@ -16940,13 +16993,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>17</v>
@@ -16959,16 +17012,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -16980,7 +17033,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>35</v>
@@ -17079,13 +17132,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C11" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>17</v>
@@ -17100,13 +17153,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>17</v>
@@ -17119,13 +17172,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>17</v>
@@ -17140,13 +17193,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>17</v>
@@ -17159,13 +17212,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>17</v>
@@ -17178,13 +17231,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>17</v>
@@ -17197,13 +17250,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>17</v>
@@ -17216,13 +17269,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C18" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>17</v>
@@ -17235,13 +17288,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>17</v>
@@ -17254,13 +17307,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>17</v>
@@ -17273,13 +17326,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="C21" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="D21" s="9" t="s">
         <v>17</v>
@@ -17292,10 +17345,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C22" t="s">
         <v>17</v>
@@ -17311,13 +17364,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>376</v>
       </c>
       <c r="C23" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>17</v>
@@ -17330,13 +17383,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>376</v>
       </c>
       <c r="C24" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="D24" s="9" t="s">
         <v>17</v>
@@ -17349,13 +17402,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>376</v>
+        <v>929</v>
       </c>
       <c r="C25" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>17</v>
@@ -17368,13 +17421,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>376</v>
       </c>
       <c r="C26" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>17</v>
@@ -17387,11 +17440,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>930</v>
-      </c>
-      <c r="B27" s="9"/>
+        <v>933</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>376</v>
+      </c>
       <c r="C27" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>17</v>
@@ -17404,11 +17459,11 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>936</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>17</v>
@@ -17419,77 +17474,87 @@
       </c>
       <c r="G28"/>
     </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>937</v>
+      </c>
+      <c r="B29" s="9"/>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29"/>
+      <c r="F29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29"/>
+    </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B30" t="s">
-        <v>97</v>
+        <v>938</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>2</v>
-      </c>
-      <c r="D30" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>98</v>
-      </c>
+        <v>939</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>896</v>
-      </c>
-      <c r="B31" t="s">
-        <v>933</v>
+        <v>940</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>934</v>
-      </c>
-      <c r="D31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32"/>
-      <c r="B32" t="s">
-        <v>935</v>
-      </c>
-      <c r="C32" t="s">
-        <v>936</v>
-      </c>
-      <c r="D32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" t="s">
-        <v>17</v>
-      </c>
+        <v>941</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31"/>
+      <c r="F31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31"/>
     </row>
     <row r="33">
-      <c r="A33"/>
+      <c r="A33" t="s">
+        <v>1</v>
+      </c>
       <c r="B33" t="s">
-        <v>937</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>938</v>
+        <v>2</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34"/>
+      <c r="A34" t="s">
+        <v>898</v>
+      </c>
       <c r="B34" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C34" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -17501,10 +17566,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C35" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -17516,10 +17581,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C36" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -17531,10 +17596,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="C37" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -17546,10 +17611,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C38" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -17561,10 +17626,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="C39" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -17576,10 +17641,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C40" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -17591,128 +17656,252 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
+        <v>956</v>
+      </c>
+      <c r="C41" t="s">
+        <v>957</v>
+      </c>
+      <c r="D41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42"/>
+      <c r="B42" t="s">
+        <v>958</v>
+      </c>
+      <c r="C42" t="s">
+        <v>959</v>
+      </c>
+      <c r="D42" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43"/>
+      <c r="B43" t="s">
+        <v>960</v>
+      </c>
+      <c r="C43" t="s">
+        <v>961</v>
+      </c>
+      <c r="D43" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44"/>
+      <c r="B44" t="s">
         <v>142</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C44" t="s">
         <v>144</v>
       </c>
-      <c r="D41" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
         <v>1</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B46" t="s">
         <v>97</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C46" t="s">
         <v>2</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D46" t="s">
         <v>3</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E46" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>911</v>
-      </c>
-      <c r="B44" t="s">
-        <v>953</v>
-      </c>
-      <c r="C44" t="s">
-        <v>954</v>
-      </c>
-      <c r="D44" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45"/>
-      <c r="B45" t="s">
-        <v>955</v>
-      </c>
-      <c r="C45" t="s">
-        <v>956</v>
-      </c>
-      <c r="D45" t="s">
-        <v>17</v>
-      </c>
-      <c r="E45" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>913</v>
+      </c>
+      <c r="B47" t="s">
+        <v>962</v>
+      </c>
+      <c r="C47" t="s">
+        <v>963</v>
+      </c>
+      <c r="D47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48"/>
+      <c r="B48" t="s">
+        <v>964</v>
+      </c>
+      <c r="C48" t="s">
+        <v>965</v>
+      </c>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
         <v>1</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B50" t="s">
         <v>97</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C50" t="s">
         <v>2</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D50" t="s">
         <v>3</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E50" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>918</v>
-      </c>
-      <c r="B48" t="s">
-        <v>957</v>
-      </c>
-      <c r="C48" t="s">
-        <v>958</v>
-      </c>
-      <c r="D48" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49"/>
-      <c r="B49" t="s">
-        <v>959</v>
-      </c>
-      <c r="C49" t="s">
-        <v>960</v>
-      </c>
-      <c r="D49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50"/>
-      <c r="B50" t="s">
-        <v>961</v>
-      </c>
-      <c r="C50" t="s">
-        <v>962</v>
-      </c>
-      <c r="D50" t="s">
-        <v>17</v>
-      </c>
-      <c r="E50" t="s">
+    <row r="51">
+      <c r="A51" t="s">
+        <v>920</v>
+      </c>
+      <c r="B51" t="s">
+        <v>966</v>
+      </c>
+      <c r="C51" t="s">
+        <v>967</v>
+      </c>
+      <c r="D51" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52"/>
+      <c r="B52" t="s">
+        <v>968</v>
+      </c>
+      <c r="C52" t="s">
+        <v>969</v>
+      </c>
+      <c r="D52" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53"/>
+      <c r="B53" t="s">
+        <v>970</v>
+      </c>
+      <c r="C53" t="s">
+        <v>971</v>
+      </c>
+      <c r="D53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>929</v>
+      </c>
+      <c r="B56" t="s">
+        <v>972</v>
+      </c>
+      <c r="C56" t="s">
+        <v>973</v>
+      </c>
+      <c r="D56" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57"/>
+      <c r="B57" t="s">
+        <v>321</v>
+      </c>
+      <c r="C57" t="s">
+        <v>323</v>
+      </c>
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58"/>
+      <c r="B58" t="s">
+        <v>974</v>
+      </c>
+      <c r="C58" t="s">
+        <v>975</v>
+      </c>
+      <c r="D58" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59"/>
+      <c r="B59" t="s">
+        <v>976</v>
+      </c>
+      <c r="C59" t="s">
+        <v>977</v>
+      </c>
+      <c r="D59" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17723,6 +17912,7 @@
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -3653,7 +3653,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.15.0-SNAPSHOT</t>
+    <t>1.16.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3372" uniqueCount="1209">
   <si>
     <t>Field</t>
   </si>
@@ -2846,6 +2846,9 @@
     <t>requestedAdditionalTests</t>
   </si>
   <si>
+    <t>Please tick every type of additional test you would like to be performed on this sample</t>
+  </si>
+  <si>
     <t>requestedOtherPathogenTests</t>
   </si>
   <si>
@@ -3653,7 +3656,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.16.0-SNAPSHOT</t>
+    <t>1.17.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -6285,7 +6288,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>923</v>
@@ -6306,13 +6309,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>17</v>
@@ -6327,13 +6330,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>17</v>
@@ -6346,13 +6349,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>17</v>
@@ -6407,7 +6410,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>222</v>
@@ -6428,13 +6431,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>929</v>
       </c>
       <c r="C9" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>17</v>
@@ -6449,13 +6452,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>17</v>
@@ -6470,13 +6473,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>376</v>
       </c>
       <c r="C11" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>17</v>
@@ -6489,13 +6492,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>376</v>
       </c>
       <c r="C12" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>17</v>
@@ -6525,13 +6528,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B15" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C15" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D15" t="s">
         <v>17</v>
@@ -6543,10 +6546,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C16" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -6558,10 +6561,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="D17" t="s">
         <v>17</v>
@@ -6573,10 +6576,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C18" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -6588,10 +6591,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C19" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="D19" t="s">
         <v>17</v>
@@ -6603,10 +6606,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C20" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D20" t="s">
         <v>17</v>
@@ -6618,7 +6621,7 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C21" t="s">
         <v>361</v>
@@ -6633,10 +6636,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C22" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -6648,10 +6651,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C23" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -6663,10 +6666,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="C24" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -6678,10 +6681,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C25" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -6693,10 +6696,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="C26" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D26" t="s">
         <v>17</v>
@@ -6708,10 +6711,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C27" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
@@ -6723,10 +6726,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C28" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -6738,10 +6741,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C29" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -6753,10 +6756,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -6768,10 +6771,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C31" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -6817,10 +6820,10 @@
         <v>929</v>
       </c>
       <c r="B35" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C35" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -6847,10 +6850,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C37" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -6862,10 +6865,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C38" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -6923,13 +6926,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>17</v>
@@ -6963,13 +6966,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>17</v>
@@ -6982,13 +6985,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C5" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>17</v>
@@ -7001,16 +7004,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C6" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -7022,13 +7025,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C7" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>17</v>
@@ -7041,13 +7044,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>17</v>
@@ -7062,13 +7065,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>17</v>
@@ -7081,13 +7084,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C10" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>17</v>
@@ -7100,13 +7103,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>17</v>
@@ -7119,13 +7122,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>35</v>
       </c>
       <c r="C12" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
@@ -7138,13 +7141,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>222</v>
       </c>
       <c r="C13" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>17</v>
@@ -7157,13 +7160,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>17</v>
@@ -7176,13 +7179,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>17</v>
@@ -7197,13 +7200,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>17</v>
@@ -7216,7 +7219,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>25</v>
@@ -7235,7 +7238,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>25</v>
@@ -7254,7 +7257,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>25</v>
@@ -7290,13 +7293,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B22" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C22" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D22" t="s">
         <v>17</v>
@@ -7308,10 +7311,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C23" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -7323,10 +7326,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="C24" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -7338,10 +7341,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="C25" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
@@ -7369,13 +7372,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B28" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C28" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -7387,10 +7390,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C29" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
@@ -7402,10 +7405,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C30" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D30" t="s">
         <v>17</v>
@@ -7417,10 +7420,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C31" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D31" t="s">
         <v>17</v>
@@ -7432,10 +7435,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="C32" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -7447,10 +7450,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C33" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -7462,10 +7465,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C34" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -7477,10 +7480,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C35" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -7492,10 +7495,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C36" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -7507,10 +7510,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C37" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -7522,10 +7525,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="C38" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -7537,10 +7540,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C39" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -7552,10 +7555,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C40" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -7567,10 +7570,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="C41" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -7582,10 +7585,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C42" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -7597,10 +7600,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C43" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -7612,10 +7615,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C44" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D44" t="s">
         <v>17</v>
@@ -7630,7 +7633,7 @@
         <v>142</v>
       </c>
       <c r="C45" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D45" t="s">
         <v>17</v>
@@ -7642,10 +7645,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C46" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D46" t="s">
         <v>17</v>
@@ -7657,10 +7660,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C47" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -7672,10 +7675,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C48" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -7703,13 +7706,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B51" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C51" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -7721,10 +7724,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C52" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -7736,10 +7739,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C53" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -7767,13 +7770,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B56" t="s">
         <v>321</v>
       </c>
       <c r="C56" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -7788,7 +7791,7 @@
         <v>324</v>
       </c>
       <c r="C57" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D57" t="s">
         <v>17</v>
@@ -7800,10 +7803,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C58" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -7815,10 +7818,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C59" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>
@@ -7878,13 +7881,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>17</v>
@@ -7899,16 +7902,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -7920,16 +7923,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -7941,16 +7944,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="12" t="s">
@@ -8002,13 +8005,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>17</v>
@@ -8021,16 +8024,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C9" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="12" t="s">
@@ -8040,16 +8043,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="E10"/>
       <c r="F10" s="12" t="s">
@@ -8059,16 +8062,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="E11"/>
       <c r="F11" s="12" t="s">
@@ -8078,16 +8081,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="12" t="s">
@@ -8097,16 +8100,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="12" t="s">
@@ -8173,13 +8176,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>17</v>
@@ -8266,13 +8269,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B23" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C23" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D23" t="s">
         <v>17</v>
@@ -8284,10 +8287,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C24" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D24" t="s">
         <v>17</v>
@@ -8315,19 +8318,19 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B27" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C27" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D27" t="s">
         <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="28">
@@ -8336,7 +8339,7 @@
         <v>315</v>
       </c>
       <c r="C28" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D28" t="s">
         <v>17</v>
@@ -8348,16 +8351,16 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C29" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D29" t="s">
         <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="31">
@@ -8379,13 +8382,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B32" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C32" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D32" t="s">
         <v>17</v>
@@ -8397,10 +8400,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C33" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D33" t="s">
         <v>17</v>
@@ -8427,10 +8430,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C35" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -8442,10 +8445,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C36" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -8719,13 +8722,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="C2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>17</v>
@@ -8743,10 +8746,10 @@
         <v>214</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="C3" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>17</v>
@@ -8761,13 +8764,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>17</v>
@@ -8844,13 +8847,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>17</v>
@@ -8945,7 +8948,7 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="D7" s="14" t="s">
         <v>17</v>
@@ -8964,7 +8967,7 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>17</v>
@@ -8977,10 +8980,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="C9" t="s">
         <v>17</v>
@@ -8996,7 +8999,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>376</v>
@@ -9032,7 +9035,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B13" t="s">
         <v>155</v>
@@ -9080,10 +9083,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C16" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="D16" t="s">
         <v>17</v>
@@ -9140,13 +9143,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>17</v>
@@ -9159,13 +9162,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>17</v>
@@ -9178,13 +9181,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>17</v>
@@ -9197,13 +9200,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>17</v>
@@ -9261,13 +9264,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>17</v>
@@ -9280,13 +9283,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>17</v>
@@ -9299,13 +9302,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>17</v>
@@ -9318,13 +9321,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>17</v>
@@ -9401,13 +9404,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="D2" s="17" t="s">
         <v>17</v>
@@ -9503,13 +9506,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B2" s="18" t="s">
         <v>376</v>
       </c>
       <c r="C2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>17</v>
@@ -9522,13 +9525,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>17</v>
@@ -9579,13 +9582,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>17</v>
@@ -9636,11 +9639,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>17</v>
@@ -9729,7 +9732,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>93</v>
@@ -9748,13 +9751,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>222</v>
       </c>
       <c r="C15" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>17</v>
@@ -9780,12 +9783,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
   </sheetData>
@@ -17480,7 +17483,7 @@
       </c>
       <c r="B29" s="9"/>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>938</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>17</v>
@@ -17493,13 +17496,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>17</v>
@@ -17512,13 +17515,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>17</v>
@@ -17551,10 +17554,10 @@
         <v>898</v>
       </c>
       <c r="B34" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C34" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D34" t="s">
         <v>17</v>
@@ -17566,10 +17569,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="C35" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D35" t="s">
         <v>17</v>
@@ -17581,10 +17584,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="C36" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -17596,10 +17599,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C37" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D37" t="s">
         <v>17</v>
@@ -17611,10 +17614,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C38" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D38" t="s">
         <v>17</v>
@@ -17626,10 +17629,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="C39" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D39" t="s">
         <v>17</v>
@@ -17641,10 +17644,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="C40" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D40" t="s">
         <v>17</v>
@@ -17656,10 +17659,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C41" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="D41" t="s">
         <v>17</v>
@@ -17671,10 +17674,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C42" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -17686,10 +17689,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="C43" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -17735,10 +17738,10 @@
         <v>913</v>
       </c>
       <c r="B47" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="C47" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D47" t="s">
         <v>17</v>
@@ -17750,10 +17753,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C48" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D48" t="s">
         <v>17</v>
@@ -17784,10 +17787,10 @@
         <v>920</v>
       </c>
       <c r="B51" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C51" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D51" t="s">
         <v>17</v>
@@ -17799,10 +17802,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C52" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="D52" t="s">
         <v>17</v>
@@ -17814,10 +17817,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C53" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D53" t="s">
         <v>17</v>
@@ -17848,10 +17851,10 @@
         <v>929</v>
       </c>
       <c r="B56" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C56" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D56" t="s">
         <v>17</v>
@@ -17878,10 +17881,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C58" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="D58" t="s">
         <v>17</v>
@@ -17893,10 +17896,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C59" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D59" t="s">
         <v>17</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -1157,48 +1157,792 @@
     <t>Intensive Care Unit</t>
   </si>
   <si>
+    <t>abdominalPain</t>
+  </si>
+  <si>
+    <t>SymptomState</t>
+  </si>
+  <si>
+    <t>Abdominal pain</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, Cholera, Yellow fever, Dengue, Plague, Other</t>
+  </si>
+  <si>
+    <t>alteredConsciousness</t>
+  </si>
+  <si>
+    <t>Altered level of consciousness</t>
+  </si>
+  <si>
+    <t>Altered level of consciousness, e.g. lethargy, stuporous, coma</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Other</t>
+  </si>
+  <si>
+    <t>anorexiaAppetiteLoss</t>
+  </si>
+  <si>
+    <t>Anorexia/loss of appetite</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, CSM, Cholera, Yellow fever, Other</t>
+  </si>
+  <si>
+    <t>backache</t>
+  </si>
+  <si>
+    <t>Backache</t>
+  </si>
+  <si>
+    <t>Yellow fever, Other</t>
+  </si>
+  <si>
+    <t>bedridden</t>
+  </si>
+  <si>
+    <t>Is the patient bedridden?</t>
+  </si>
+  <si>
+    <t>Monkeypox, Other</t>
+  </si>
+  <si>
+    <t>blackeningDeathOfTissue</t>
+  </si>
+  <si>
+    <t>Blackening and death of tissue in extremities</t>
+  </si>
+  <si>
+    <t>Plague, Other</t>
+  </si>
+  <si>
+    <t>bleedingVagina</t>
+  </si>
+  <si>
+    <t>Bleeding from vagina, other than menstruation</t>
+  </si>
+  <si>
+    <t>bloodInStool</t>
+  </si>
+  <si>
+    <t>Blood in stool</t>
+  </si>
+  <si>
+    <t>Visible blood in stool</t>
+  </si>
+  <si>
+    <t>Cholera, Yellow fever, Other</t>
+  </si>
+  <si>
+    <t>bloodPressureDiastolic</t>
+  </si>
+  <si>
+    <t>Blood pressure (diastolic)</t>
+  </si>
+  <si>
+    <t>bloodPressureSystolic</t>
+  </si>
+  <si>
+    <t>Blood pressure (systolic)</t>
+  </si>
+  <si>
+    <t>bloodUrine</t>
+  </si>
+  <si>
+    <t>Blood in urine (hematuria)</t>
+  </si>
+  <si>
+    <t>bloodyBlackStool</t>
+  </si>
+  <si>
+    <t>Bloody or black stools (melena)</t>
+  </si>
+  <si>
+    <t>buboesGroinArmpitNeck</t>
+  </si>
+  <si>
+    <t>Buboes in the groin, armpit or neck</t>
+  </si>
+  <si>
+    <t>bulgingFontanelle</t>
+  </si>
+  <si>
+    <t>Bulging fontanelle</t>
+  </si>
+  <si>
+    <t>CSM, Other</t>
+  </si>
+  <si>
+    <t>chestPain</t>
+  </si>
+  <si>
+    <t>Chest pain</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, Plague, Other</t>
+  </si>
+  <si>
+    <t>chillsSweats</t>
+  </si>
+  <si>
+    <t>Chills or sweats</t>
+  </si>
+  <si>
+    <t>Monkeypox, Plague, Other</t>
+  </si>
+  <si>
+    <t>confusedDisoriented</t>
+  </si>
+  <si>
+    <t>Confused or disoriented</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Plague, Other</t>
+  </si>
+  <si>
+    <t>conjunctivitis</t>
+  </si>
+  <si>
+    <t>Conjunctivitis (red eyes)</t>
+  </si>
+  <si>
+    <t>Conjunctivitis, redness of the eyes</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, Measles, Monkeypox, Other</t>
+  </si>
+  <si>
+    <t>cough</t>
+  </si>
+  <si>
+    <t>Cough</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, Measles, Monkeypox, Plague, Other</t>
+  </si>
+  <si>
+    <t>coughingBlood</t>
+  </si>
+  <si>
+    <t>Coughing up blood (haemoptysis)</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, Plague, Other</t>
+  </si>
+  <si>
+    <t>darkUrine</t>
+  </si>
+  <si>
+    <t>Dark Urine</t>
+  </si>
+  <si>
+    <t>dehydration</t>
+  </si>
+  <si>
+    <t>Dehydration</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, Cholera, Other</t>
+  </si>
+  <si>
+    <t>diarrhea</t>
+  </si>
+  <si>
+    <t>Diarrhea</t>
+  </si>
+  <si>
+    <t>&gt;= 3 loose stools within 24h</t>
+  </si>
+  <si>
+    <t>difficultyBreathing</t>
+  </si>
+  <si>
+    <t>Difficulty breathing</t>
+  </si>
+  <si>
+    <t>Difficulty breathing or shortness of breath</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, Measles, Plague, Other</t>
+  </si>
+  <si>
+    <t>digestedBloodVomit</t>
+  </si>
+  <si>
+    <t>Digested blood/"coffee grounds" in vomit</t>
+  </si>
+  <si>
+    <t>eyePainLightSensitive</t>
+  </si>
+  <si>
+    <t>Pain behind eyes/Sensitivity to light</t>
+  </si>
+  <si>
+    <t>ain behind eyes or eyes sensitive to light</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Measles, Dengue, Monkeypox, Other</t>
+  </si>
+  <si>
+    <t>eyesBleeding</t>
+  </si>
+  <si>
+    <t>Bleeding from the eyes</t>
+  </si>
+  <si>
+    <t>fatigueWeakness</t>
+  </si>
+  <si>
+    <t>Fatigue/general weakness</t>
+  </si>
+  <si>
+    <t>Fatigue or general weakness</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Yellow fever, Dengue, Monkeypox, Plague, Other</t>
+  </si>
+  <si>
+    <t>fever</t>
+  </si>
+  <si>
+    <t>Fever</t>
+  </si>
+  <si>
+    <t>&gt;= 38°C</t>
+  </si>
+  <si>
+    <t>fluidInLungCavity</t>
+  </si>
+  <si>
+    <t>Fluid in the lung cavity</t>
+  </si>
+  <si>
+    <t>Lassa, Other</t>
+  </si>
+  <si>
+    <t>glasgowComaScale</t>
+  </si>
+  <si>
+    <t>Glasgow coma scale</t>
+  </si>
+  <si>
+    <t>gumsBleeding</t>
+  </si>
+  <si>
+    <t>Bleeding of the gums</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, Yellow fever, Dengue, Other</t>
+  </si>
+  <si>
+    <t>headache</t>
+  </si>
+  <si>
+    <t>Headache</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Yellow fever, Dengue, Monkeypox, Plague, Other</t>
+  </si>
+  <si>
+    <t>hearingloss</t>
+  </si>
+  <si>
+    <t>Acute hearing loss</t>
+  </si>
+  <si>
+    <t>Acute hearing loss not related to an injury</t>
+  </si>
+  <si>
+    <t>heartRate</t>
+  </si>
+  <si>
+    <t>Heart rate (bpm)</t>
+  </si>
+  <si>
+    <t>height</t>
+  </si>
+  <si>
+    <t>Height (cm)</t>
+  </si>
+  <si>
+    <t>hemorrhagicSyndrome</t>
+  </si>
+  <si>
+    <t>Hemorrhagic syndrome</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, Yellow fever, Dengue, Plague, Other</t>
+  </si>
+  <si>
+    <t>hiccups</t>
+  </si>
+  <si>
+    <t>Hiccups</t>
+  </si>
+  <si>
+    <t>hyperglycemia</t>
+  </si>
+  <si>
+    <t>Hyperglycemia</t>
+  </si>
+  <si>
+    <t>CSM, Lassa, Other</t>
+  </si>
+  <si>
+    <t>hypoglycemia</t>
+  </si>
+  <si>
+    <t>Hypoglycemia</t>
+  </si>
+  <si>
+    <t>injectionSiteBleeding</t>
+  </si>
+  <si>
+    <t>Bleeding from injection site</t>
+  </si>
+  <si>
+    <t>jaundice</t>
+  </si>
+  <si>
+    <t>Jaundice</t>
+  </si>
+  <si>
+    <t>Yellow fever, Lassa, Other</t>
+  </si>
+  <si>
+    <t>jointPain</t>
+  </si>
+  <si>
+    <t>Joint pain or arthritis</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Measles, Dengue, Other</t>
+  </si>
+  <si>
+    <t>kopliksSpots</t>
+  </si>
+  <si>
+    <t>Koplik's Spots</t>
+  </si>
+  <si>
+    <t>Measles, Other</t>
+  </si>
+  <si>
+    <t>lesions</t>
+  </si>
+  <si>
+    <t>Vesiculopustular rash</t>
+  </si>
+  <si>
+    <t>lesionsAllOverBody</t>
+  </si>
+  <si>
+    <t>true, false</t>
+  </si>
+  <si>
+    <t>All over the body</t>
+  </si>
+  <si>
+    <t>lesionsArms</t>
+  </si>
+  <si>
+    <t>Arms</t>
+  </si>
+  <si>
+    <t>lesionsDeepProfound</t>
+  </si>
+  <si>
+    <t>Rash lesions deep and profound?</t>
+  </si>
+  <si>
+    <t>lesionsFace</t>
+  </si>
+  <si>
+    <t>Face</t>
+  </si>
+  <si>
+    <t>lesionsGenitals</t>
+  </si>
+  <si>
+    <t>Genitals</t>
+  </si>
+  <si>
+    <t>lesionsLegs</t>
+  </si>
+  <si>
+    <t>Legs</t>
+  </si>
+  <si>
+    <t>lesionsOnsetDate</t>
+  </si>
+  <si>
+    <t>Date of rash onset</t>
+  </si>
+  <si>
+    <t>lesionsPalmsHands</t>
+  </si>
+  <si>
+    <t>Palms of the hands</t>
+  </si>
+  <si>
+    <t>lesionsResembleImg1</t>
+  </si>
+  <si>
+    <t>Does the rash resemble the photo below?</t>
+  </si>
+  <si>
+    <t>lesionsResembleImg2</t>
+  </si>
+  <si>
+    <t>lesionsResembleImg3</t>
+  </si>
+  <si>
+    <t>lesionsResembleImg4</t>
+  </si>
+  <si>
+    <t>lesionsSameSize</t>
+  </si>
+  <si>
+    <t>All rash lesions the same size?</t>
+  </si>
+  <si>
+    <t>lesionsSameState</t>
+  </si>
+  <si>
+    <t>All rash lesions in same state of development?</t>
+  </si>
+  <si>
+    <t>lesionsSolesFeet</t>
+  </si>
+  <si>
+    <t>Soles of the feet</t>
+  </si>
+  <si>
+    <t>lesionsThatItch</t>
+  </si>
+  <si>
+    <t>Rash that itches</t>
+  </si>
+  <si>
+    <t>lesionsThorax</t>
+  </si>
+  <si>
+    <t>Thorax</t>
+  </si>
+  <si>
+    <t>lossSkinTurgor</t>
+  </si>
+  <si>
+    <t>Loss of skin turgor</t>
+  </si>
+  <si>
+    <t>lymphadenopathyAxillary</t>
+  </si>
+  <si>
+    <t>Enlarged lymph nodes, axillary</t>
+  </si>
+  <si>
+    <t>lymphadenopathyCervical</t>
+  </si>
+  <si>
+    <t>Enlarged lymph nodes, cervical</t>
+  </si>
+  <si>
+    <t>lymphadenopathyInguinal</t>
+  </si>
+  <si>
+    <t>Enlarged lymph nodes, inguinal</t>
+  </si>
+  <si>
+    <t>malaise</t>
+  </si>
+  <si>
+    <t>Malaise</t>
+  </si>
+  <si>
+    <t>meningealSigns</t>
+  </si>
+  <si>
+    <t>Meningeal signs</t>
+  </si>
+  <si>
+    <t>midUpperArmCircumference</t>
+  </si>
+  <si>
+    <t>Mid-upper arm circumf. (cm)</t>
+  </si>
+  <si>
+    <t>musclePain</t>
+  </si>
+  <si>
+    <t>Muscle pain</t>
+  </si>
+  <si>
+    <t>Muscle pain (myalgia)</t>
+  </si>
+  <si>
+    <t>nausea</t>
+  </si>
+  <si>
+    <t>Nausea</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Cholera, Yellow fever, Dengue, Monkeypox, Plague, Other</t>
+  </si>
+  <si>
+    <t>neckStiffness</t>
+  </si>
+  <si>
+    <t>Stiff neck</t>
+  </si>
+  <si>
+    <t>Neck feels stiff</t>
+  </si>
+  <si>
+    <t>noseBleeding</t>
+  </si>
+  <si>
+    <t>Nose bleed (epistaxis)</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, Yellow fever, Other</t>
+  </si>
+  <si>
+    <t>oedemaFaceNeck</t>
+  </si>
+  <si>
+    <t>Oedema of face/neck</t>
+  </si>
+  <si>
+    <t>oedemaLowerExtremity</t>
+  </si>
+  <si>
+    <t>Oedema of lower extremities</t>
+  </si>
+  <si>
+    <t>onsetDate</t>
+  </si>
+  <si>
+    <t>Date of symptom onset</t>
+  </si>
+  <si>
+    <t>Enter the date of onset of the person's first symptom (dd/mm/yyyy)</t>
+  </si>
+  <si>
+    <t>onsetSymptom</t>
+  </si>
+  <si>
+    <t>First symptom</t>
+  </si>
+  <si>
+    <t>What was the first symptom?</t>
+  </si>
+  <si>
+    <t>oralUlcers</t>
+  </si>
+  <si>
+    <t>Oral ulcers</t>
+  </si>
+  <si>
+    <t>otherHemorrhagicSymptoms</t>
+  </si>
+  <si>
+    <t>Other hemorrhagic symptoms</t>
+  </si>
+  <si>
+    <t>otherHemorrhagicSymptomsText</t>
+  </si>
+  <si>
+    <t>Specify other symptoms</t>
+  </si>
+  <si>
+    <t>Specify other hemorrhagic symptoms</t>
+  </si>
+  <si>
+    <t>otherNonHemorrhagicSymptoms</t>
+  </si>
+  <si>
+    <t>Other clinical symptoms</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Dengue, Monkeypox, Plague, Other</t>
+  </si>
+  <si>
+    <t>otherNonHemorrhagicSymptomsText</t>
+  </si>
+  <si>
+    <t>otitisMedia</t>
+  </si>
+  <si>
+    <t>Middle ear inflammation (otitis media)</t>
+  </si>
+  <si>
+    <t>New flu, Measles, Other</t>
+  </si>
+  <si>
+    <t>painfulLymphadenitis</t>
+  </si>
+  <si>
+    <t>Painful lymphadenitis</t>
+  </si>
+  <si>
+    <t>palpableLiver</t>
+  </si>
+  <si>
+    <t>Palpable liver</t>
+  </si>
+  <si>
+    <t>palpableSpleen</t>
+  </si>
+  <si>
+    <t>Palpable spleen</t>
+  </si>
+  <si>
+    <t>patientIllLocation</t>
+  </si>
+  <si>
+    <t>pharyngealErythema</t>
+  </si>
+  <si>
+    <t>Pharyngeal erythema</t>
+  </si>
+  <si>
+    <t>pharyngealExudate</t>
+  </si>
+  <si>
+    <t>Pharyngeal exudate</t>
+  </si>
+  <si>
+    <t>rapidBreathing</t>
+  </si>
+  <si>
+    <t>Rapid breathing</t>
+  </si>
+  <si>
+    <t>Dengue, Other</t>
+  </si>
+  <si>
+    <t>redBloodVomit</t>
+  </si>
+  <si>
+    <t>Fresh/red blood in vomit (hematemesis)</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, Dengue, Other</t>
+  </si>
+  <si>
+    <t>refusalFeedorDrink</t>
+  </si>
+  <si>
+    <t>Refusal to feed or drink</t>
+  </si>
+  <si>
+    <t>EVD, Lassa, CSM, Cholera, Other</t>
+  </si>
+  <si>
+    <t>respiratoryRate</t>
+  </si>
+  <si>
+    <t>Respiratory rate (bpm)</t>
+  </si>
+  <si>
+    <t>runnyNose</t>
+  </si>
+  <si>
+    <t>Runny nose</t>
+  </si>
+  <si>
+    <t>Runny nose (rhinitis or coryza)</t>
+  </si>
+  <si>
+    <t>seizures</t>
+  </si>
+  <si>
+    <t>Convulsions or Seizures</t>
+  </si>
+  <si>
+    <t>sepsis</t>
+  </si>
+  <si>
+    <t>Sepsis</t>
+  </si>
+  <si>
+    <t>shock</t>
+  </si>
+  <si>
+    <t>Shock (Systolic bp &lt;90)</t>
+  </si>
+  <si>
+    <t>sidePain</t>
+  </si>
+  <si>
+    <t>Side pain</t>
+  </si>
+  <si>
+    <t>skinBruising</t>
+  </si>
+  <si>
+    <t>Bruising of the skin (petechiae/ecchymosis)</t>
+  </si>
+  <si>
+    <t>skinRash</t>
+  </si>
+  <si>
+    <t>Maculopapular rash</t>
+  </si>
+  <si>
+    <t>Sudden onset of skin rash</t>
+  </si>
+  <si>
+    <t>soreThroat</t>
+  </si>
+  <si>
+    <t>Sore throat/pharyngitis</t>
+  </si>
+  <si>
+    <t>stomachBleeding</t>
+  </si>
+  <si>
+    <t>Bleeding from the stomach</t>
+  </si>
+  <si>
+    <t>sunkenEyesFontanelle</t>
+  </si>
+  <si>
+    <t>Sunken eyes or fontanelle</t>
+  </si>
+  <si>
+    <t>swollenGlands</t>
+  </si>
+  <si>
+    <t>Swollen glands</t>
+  </si>
+  <si>
     <t>symptomatic</t>
   </si>
   <si>
-    <t>true, false</t>
-  </si>
-  <si>
     <t>Symptomatic</t>
   </si>
   <si>
     <t>Did the person have any symptoms or signs of illness?</t>
   </si>
   <si>
-    <t>onsetDate</t>
-  </si>
-  <si>
-    <t>Date of symptom onset</t>
-  </si>
-  <si>
-    <t>Enter the date of onset of the person's first symptom (dd/mm/yyyy)</t>
-  </si>
-  <si>
-    <t>onsetSymptom</t>
-  </si>
-  <si>
-    <t>First symptom</t>
-  </si>
-  <si>
-    <t>What was the first symptom?</t>
+    <t>symptomsComments</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
   <si>
     <t>temperature</t>
   </si>
   <si>
-    <t>Current body temperature in °C</t>
+    <t>Current body temperature in ° C</t>
   </si>
   <si>
     <t>Enter the measured body temperature</t>
   </si>
   <si>
-    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Yellow fever, Dengue, Monkeypox, Plague, Other</t>
-  </si>
-  <si>
     <t>temperatureSource</t>
   </si>
   <si>
@@ -1211,34 +1955,34 @@
     <t>Select the source of body temperature</t>
   </si>
   <si>
-    <t>bloodPressureSystolic</t>
-  </si>
-  <si>
-    <t>Blood pressure (systolic)</t>
-  </si>
-  <si>
-    <t>bloodPressureDiastolic</t>
-  </si>
-  <si>
-    <t>Blood pressure (diastolic)</t>
-  </si>
-  <si>
-    <t>heartRate</t>
-  </si>
-  <si>
-    <t>Heart rate (bpm)</t>
-  </si>
-  <si>
-    <t>midUpperArmCircumference</t>
-  </si>
-  <si>
-    <t>Mid-upper arm circumf. (cm)</t>
-  </si>
-  <si>
-    <t>respiratoryRate</t>
-  </si>
-  <si>
-    <t>Respiratory rate (bpm)</t>
+    <t>throbocytopenia</t>
+  </si>
+  <si>
+    <t>Thrombocytopenia</t>
+  </si>
+  <si>
+    <t>Decreased level of thrombocytes in the blood</t>
+  </si>
+  <si>
+    <t>tremor</t>
+  </si>
+  <si>
+    <t>Tremor</t>
+  </si>
+  <si>
+    <t>unexplainedBleeding</t>
+  </si>
+  <si>
+    <t>Bleeding or bruising</t>
+  </si>
+  <si>
+    <t>Unexplained bleeding or bruising from any site not related to an injury</t>
+  </si>
+  <si>
+    <t>vomiting</t>
+  </si>
+  <si>
+    <t>Vomiting</t>
   </si>
   <si>
     <t>weight</t>
@@ -1247,750 +1991,6 @@
     <t>Weight (kg)</t>
   </si>
   <si>
-    <t>height</t>
-  </si>
-  <si>
-    <t>Height (cm)</t>
-  </si>
-  <si>
-    <t>glasgowComaScale</t>
-  </si>
-  <si>
-    <t>Glasgow coma scale</t>
-  </si>
-  <si>
-    <t>fever</t>
-  </si>
-  <si>
-    <t>SymptomState</t>
-  </si>
-  <si>
-    <t>Fever</t>
-  </si>
-  <si>
-    <t>&gt;= 38°C</t>
-  </si>
-  <si>
-    <t>vomiting</t>
-  </si>
-  <si>
-    <t>Vomiting</t>
-  </si>
-  <si>
-    <t>diarrhea</t>
-  </si>
-  <si>
-    <t>Diarrhea</t>
-  </si>
-  <si>
-    <t>&gt;= 3 loose stools within 24h</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Plague, Other</t>
-  </si>
-  <si>
-    <t>blackeningDeathOfTissue</t>
-  </si>
-  <si>
-    <t>Blackening and death of tissue in extremities</t>
-  </si>
-  <si>
-    <t>Plague, Other</t>
-  </si>
-  <si>
-    <t>bloodInStool</t>
-  </si>
-  <si>
-    <t>Blood in stool</t>
-  </si>
-  <si>
-    <t>Visible blood in stool</t>
-  </si>
-  <si>
-    <t>Cholera, Yellow fever, Other</t>
-  </si>
-  <si>
-    <t>buboesGroinArmpitNeck</t>
-  </si>
-  <si>
-    <t>Buboes in the groin, armpit or neck</t>
-  </si>
-  <si>
-    <t>bulgingFontanelle</t>
-  </si>
-  <si>
-    <t>Bulging fontanelle</t>
-  </si>
-  <si>
-    <t>CSM, Other</t>
-  </si>
-  <si>
-    <t>nausea</t>
-  </si>
-  <si>
-    <t>Nausea</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, CSM, Cholera, Yellow fever, Dengue, Monkeypox, Plague, Other</t>
-  </si>
-  <si>
-    <t>abdominalPain</t>
-  </si>
-  <si>
-    <t>Abdominal pain</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, Cholera, Yellow fever, Dengue, Plague, Other</t>
-  </si>
-  <si>
-    <t>headache</t>
-  </si>
-  <si>
-    <t>Headache</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, CSM, Yellow fever, Dengue, Monkeypox, Plague, Other</t>
-  </si>
-  <si>
-    <t>musclePain</t>
-  </si>
-  <si>
-    <t>Muscle pain</t>
-  </si>
-  <si>
-    <t>Muscle pain (myalgia)</t>
-  </si>
-  <si>
-    <t>fatigueWeakness</t>
-  </si>
-  <si>
-    <t>Fatigue/general weakness</t>
-  </si>
-  <si>
-    <t>Fatigue or general weakness</t>
-  </si>
-  <si>
-    <t>unexplainedBleeding</t>
-  </si>
-  <si>
-    <t>Bleeding or bruising</t>
-  </si>
-  <si>
-    <t>Unexplained bleeding or bruising from any site not related to an injury</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, Yellow fever, Dengue, Plague, Other</t>
-  </si>
-  <si>
-    <t>eyesBleeding</t>
-  </si>
-  <si>
-    <t>Bleeding from the eyes</t>
-  </si>
-  <si>
-    <t>Yellow fever, Other</t>
-  </si>
-  <si>
-    <t>gumsBleeding</t>
-  </si>
-  <si>
-    <t>Bleeding of the gums</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, Yellow fever, Dengue, Other</t>
-  </si>
-  <si>
-    <t>stomachBleeding</t>
-  </si>
-  <si>
-    <t>Bleeding from the stomach</t>
-  </si>
-  <si>
-    <t>injectionSiteBleeding</t>
-  </si>
-  <si>
-    <t>Bleeding from injection site</t>
-  </si>
-  <si>
-    <t>noseBleeding</t>
-  </si>
-  <si>
-    <t>Nose bleed (epistaxis)</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, Yellow fever, Other</t>
-  </si>
-  <si>
-    <t>bloodyBlackStool</t>
-  </si>
-  <si>
-    <t>Bloody or black stools (melena)</t>
-  </si>
-  <si>
-    <t>redBloodVomit</t>
-  </si>
-  <si>
-    <t>Fresh/red blood in vomit (hematemesis)</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, Dengue, Other</t>
-  </si>
-  <si>
-    <t>digestedBloodVomit</t>
-  </si>
-  <si>
-    <t>Digested blood/"coffee grounds" in vomit</t>
-  </si>
-  <si>
-    <t>coughingBlood</t>
-  </si>
-  <si>
-    <t>Coughing up blood (haemoptysis)</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, Plague, Other</t>
-  </si>
-  <si>
-    <t>bleedingVagina</t>
-  </si>
-  <si>
-    <t>Bleeding from vagina, other than menstruation</t>
-  </si>
-  <si>
-    <t>skinBruising</t>
-  </si>
-  <si>
-    <t>Bruising of the skin (petechiae/ecchymosis)</t>
-  </si>
-  <si>
-    <t>bloodUrine</t>
-  </si>
-  <si>
-    <t>Blood in urine (hematuria)</t>
-  </si>
-  <si>
-    <t>otherHemorrhagicSymptoms</t>
-  </si>
-  <si>
-    <t>Other hemorrhagic symptoms</t>
-  </si>
-  <si>
-    <t>otherHemorrhagicSymptomsText</t>
-  </si>
-  <si>
-    <t>Specify other symptoms</t>
-  </si>
-  <si>
-    <t>Specify other hemorrhagic symptoms</t>
-  </si>
-  <si>
-    <t>skinRash</t>
-  </si>
-  <si>
-    <t>Maculopapular rash</t>
-  </si>
-  <si>
-    <t>Sudden onset of skin rash</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, CSM, Measles, Dengue, Other</t>
-  </si>
-  <si>
-    <t>neckStiffness</t>
-  </si>
-  <si>
-    <t>Stiff neck</t>
-  </si>
-  <si>
-    <t>Neck feels stiff</t>
-  </si>
-  <si>
-    <t>soreThroat</t>
-  </si>
-  <si>
-    <t>Sore throat/pharyngitis</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, Measles, Monkeypox, Other</t>
-  </si>
-  <si>
-    <t>cough</t>
-  </si>
-  <si>
-    <t>Cough</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, Measles, Monkeypox, Plague, Other</t>
-  </si>
-  <si>
-    <t>runnyNose</t>
-  </si>
-  <si>
-    <t>Runny nose</t>
-  </si>
-  <si>
-    <t>Runny nose (rhinitis or coryza)</t>
-  </si>
-  <si>
-    <t>New flu, Measles, Other</t>
-  </si>
-  <si>
-    <t>difficultyBreathing</t>
-  </si>
-  <si>
-    <t>Difficulty breathing</t>
-  </si>
-  <si>
-    <t>Difficulty breathing or shortness of breath</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, Measles, Plague, Other</t>
-  </si>
-  <si>
-    <t>chestPain</t>
-  </si>
-  <si>
-    <t>Chest pain</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, Plague, Other</t>
-  </si>
-  <si>
-    <t>conjunctivitis</t>
-  </si>
-  <si>
-    <t>Conjunctivitis (red eyes)</t>
-  </si>
-  <si>
-    <t>Conjunctivitis, redness of the eyes</t>
-  </si>
-  <si>
-    <t>eyePainLightSensitive</t>
-  </si>
-  <si>
-    <t>Pain behind eyes/Sensitivity to light</t>
-  </si>
-  <si>
-    <t>ain behind eyes or eyes sensitive to light</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, CSM, Measles, Dengue, Monkeypox, Other</t>
-  </si>
-  <si>
-    <t>kopliksSpots</t>
-  </si>
-  <si>
-    <t>Koplik's Spots</t>
-  </si>
-  <si>
-    <t>Measles, Other</t>
-  </si>
-  <si>
-    <t>throbocytopenia</t>
-  </si>
-  <si>
-    <t>Thrombocytopenia</t>
-  </si>
-  <si>
-    <t>Decreased level of thrombocytes in the blood</t>
-  </si>
-  <si>
-    <t>otitisMedia</t>
-  </si>
-  <si>
-    <t>Middle ear inflammation (otitis media)</t>
-  </si>
-  <si>
-    <t>hearingloss</t>
-  </si>
-  <si>
-    <t>Acute hearing loss</t>
-  </si>
-  <si>
-    <t>Acute hearing loss not related to an injury</t>
-  </si>
-  <si>
-    <t>dehydration</t>
-  </si>
-  <si>
-    <t>Dehydration</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, Cholera, Other</t>
-  </si>
-  <si>
-    <t>anorexiaAppetiteLoss</t>
-  </si>
-  <si>
-    <t>Anorexia/loss of appetite</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, CSM, Cholera, Yellow fever, Other</t>
-  </si>
-  <si>
-    <t>refusalFeedorDrink</t>
-  </si>
-  <si>
-    <t>Refusal to feed or drink</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, CSM, Cholera, Other</t>
-  </si>
-  <si>
-    <t>jointPain</t>
-  </si>
-  <si>
-    <t>Joint pain or arthritis</t>
-  </si>
-  <si>
-    <t>hiccups</t>
-  </si>
-  <si>
-    <t>Hiccups</t>
-  </si>
-  <si>
-    <t>backache</t>
-  </si>
-  <si>
-    <t>Backache</t>
-  </si>
-  <si>
-    <t>jaundice</t>
-  </si>
-  <si>
-    <t>Jaundice</t>
-  </si>
-  <si>
-    <t>Yellow fever, Lassa, Other</t>
-  </si>
-  <si>
-    <t>darkUrine</t>
-  </si>
-  <si>
-    <t>Dark Urine</t>
-  </si>
-  <si>
-    <t>rapidBreathing</t>
-  </si>
-  <si>
-    <t>Rapid breathing</t>
-  </si>
-  <si>
-    <t>Dengue, Other</t>
-  </si>
-  <si>
-    <t>swollenGlands</t>
-  </si>
-  <si>
-    <t>Swollen glands</t>
-  </si>
-  <si>
-    <t>lesions</t>
-  </si>
-  <si>
-    <t>Vesiculopustular rash</t>
-  </si>
-  <si>
-    <t>Monkeypox, Other</t>
-  </si>
-  <si>
-    <t>lesionsSameState</t>
-  </si>
-  <si>
-    <t>All rash lesions in same state of development?</t>
-  </si>
-  <si>
-    <t>lesionsSameSize</t>
-  </si>
-  <si>
-    <t>All rash lesions the same size?</t>
-  </si>
-  <si>
-    <t>lesionsDeepProfound</t>
-  </si>
-  <si>
-    <t>Rash lesions deep and profound?</t>
-  </si>
-  <si>
-    <t>lesionsFace</t>
-  </si>
-  <si>
-    <t>Face</t>
-  </si>
-  <si>
-    <t>lesionsLegs</t>
-  </si>
-  <si>
-    <t>Legs</t>
-  </si>
-  <si>
-    <t>lesionsSolesFeet</t>
-  </si>
-  <si>
-    <t>Soles of the feet</t>
-  </si>
-  <si>
-    <t>lesionsPalmsHands</t>
-  </si>
-  <si>
-    <t>Palms of the hands</t>
-  </si>
-  <si>
-    <t>lesionsThorax</t>
-  </si>
-  <si>
-    <t>Thorax</t>
-  </si>
-  <si>
-    <t>lesionsArms</t>
-  </si>
-  <si>
-    <t>Arms</t>
-  </si>
-  <si>
-    <t>lesionsGenitals</t>
-  </si>
-  <si>
-    <t>Genitals</t>
-  </si>
-  <si>
-    <t>lesionsAllOverBody</t>
-  </si>
-  <si>
-    <t>All over the body</t>
-  </si>
-  <si>
-    <t>lesionsResembleImg1</t>
-  </si>
-  <si>
-    <t>Does the rash resemble the photo below?</t>
-  </si>
-  <si>
-    <t>lesionsResembleImg2</t>
-  </si>
-  <si>
-    <t>lesionsResembleImg3</t>
-  </si>
-  <si>
-    <t>lesionsResembleImg4</t>
-  </si>
-  <si>
-    <t>lesionsOnsetDate</t>
-  </si>
-  <si>
-    <t>Date of rash onset</t>
-  </si>
-  <si>
-    <t>lymphadenopathyInguinal</t>
-  </si>
-  <si>
-    <t>Enlarged lymph nodes, inguinal</t>
-  </si>
-  <si>
-    <t>lymphadenopathyAxillary</t>
-  </si>
-  <si>
-    <t>Enlarged lymph nodes, axillary</t>
-  </si>
-  <si>
-    <t>lymphadenopathyCervical</t>
-  </si>
-  <si>
-    <t>Enlarged lymph nodes, cervical</t>
-  </si>
-  <si>
-    <t>painfulLymphadenitis</t>
-  </si>
-  <si>
-    <t>Painful lymphadenitis</t>
-  </si>
-  <si>
-    <t>chillsSweats</t>
-  </si>
-  <si>
-    <t>Chills or sweats</t>
-  </si>
-  <si>
-    <t>Monkeypox, Plague, Other</t>
-  </si>
-  <si>
-    <t>lesionsThatItch</t>
-  </si>
-  <si>
-    <t>Rash that itches</t>
-  </si>
-  <si>
-    <t>bedridden</t>
-  </si>
-  <si>
-    <t>Is the patient bedridden?</t>
-  </si>
-  <si>
-    <t>oralUlcers</t>
-  </si>
-  <si>
-    <t>Oral ulcers</t>
-  </si>
-  <si>
-    <t>pharyngealErythema</t>
-  </si>
-  <si>
-    <t>Pharyngeal erythema</t>
-  </si>
-  <si>
-    <t>Lassa, Other</t>
-  </si>
-  <si>
-    <t>pharyngealExudate</t>
-  </si>
-  <si>
-    <t>Pharyngeal exudate</t>
-  </si>
-  <si>
-    <t>oedemaFaceNeck</t>
-  </si>
-  <si>
-    <t>Oedema of face/neck</t>
-  </si>
-  <si>
-    <t>oedemaLowerExtremity</t>
-  </si>
-  <si>
-    <t>Oedema of lower extremities</t>
-  </si>
-  <si>
-    <t>lossSkinTurgor</t>
-  </si>
-  <si>
-    <t>Loss of skin turgor</t>
-  </si>
-  <si>
-    <t>palpableLiver</t>
-  </si>
-  <si>
-    <t>Palpable liver</t>
-  </si>
-  <si>
-    <t>palpableSpleen</t>
-  </si>
-  <si>
-    <t>Palpable spleen</t>
-  </si>
-  <si>
-    <t>malaise</t>
-  </si>
-  <si>
-    <t>Malaise</t>
-  </si>
-  <si>
-    <t>sunkenEyesFontanelle</t>
-  </si>
-  <si>
-    <t>Sunken eyes or fontanelle</t>
-  </si>
-  <si>
-    <t>sidePain</t>
-  </si>
-  <si>
-    <t>Side pain</t>
-  </si>
-  <si>
-    <t>fluidInLungCavity</t>
-  </si>
-  <si>
-    <t>Fluid in the lung cavity</t>
-  </si>
-  <si>
-    <t>tremor</t>
-  </si>
-  <si>
-    <t>Tremor</t>
-  </si>
-  <si>
-    <t>otherNonHemorrhagicSymptoms</t>
-  </si>
-  <si>
-    <t>Other clinical symptoms</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Dengue, Monkeypox, Plague, Other</t>
-  </si>
-  <si>
-    <t>otherNonHemorrhagicSymptomsText</t>
-  </si>
-  <si>
-    <t>symptomsComments</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>patientIllLocation</t>
-  </si>
-  <si>
-    <t>alteredConsciousness</t>
-  </si>
-  <si>
-    <t>Altered level of consciousness</t>
-  </si>
-  <si>
-    <t>Altered level of consciousness, e.g. lethargy, stuporous, coma</t>
-  </si>
-  <si>
-    <t>EVD, Lassa, New flu, CSM, Cholera, Measles, Other</t>
-  </si>
-  <si>
-    <t>confusedDisoriented</t>
-  </si>
-  <si>
-    <t>Confused or disoriented</t>
-  </si>
-  <si>
-    <t>hemorrhagicSyndrome</t>
-  </si>
-  <si>
-    <t>Hemorrhagic syndrome</t>
-  </si>
-  <si>
-    <t>hyperglycemia</t>
-  </si>
-  <si>
-    <t>Hyperglycemia</t>
-  </si>
-  <si>
-    <t>CSM, Lassa, Other</t>
-  </si>
-  <si>
-    <t>hypoglycemia</t>
-  </si>
-  <si>
-    <t>Hypoglycemia</t>
-  </si>
-  <si>
-    <t>meningealSigns</t>
-  </si>
-  <si>
-    <t>Meningeal signs</t>
-  </si>
-  <si>
-    <t>seizures</t>
-  </si>
-  <si>
-    <t>Convulsions or Seizures</t>
-  </si>
-  <si>
-    <t>sepsis</t>
-  </si>
-  <si>
-    <t>Sepsis</t>
-  </si>
-  <si>
-    <t>shock</t>
-  </si>
-  <si>
-    <t>Shock (Systolic bp &lt;90)</t>
-  </si>
-  <si>
     <t>AXILLARY</t>
   </si>
   <si>
@@ -3656,7 +3656,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.17.0-SNAPSHOT</t>
+    <t>1.18.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -4016,7 +4016,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="SymptomsTemperatureSource" displayName="SymptomsTemperatureSource" ref="A116:E120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="SymptomsSymptomState" displayName="SymptomsSymptomState" ref="A116:E119">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -4030,7 +4030,7 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="SymptomsSymptomState" displayName="SymptomsSymptomState" ref="A122:E125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="SymptomsTemperatureSource" displayName="SymptomsTemperatureSource" ref="A121:E125">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6476,7 +6476,7 @@
         <v>992</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C11" t="s">
         <v>993</v>
@@ -6495,7 +6495,7 @@
         <v>994</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C12" t="s">
         <v>995</v>
@@ -9002,7 +9002,7 @@
         <v>1189</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C10" t="s">
         <v>17</v>
@@ -9509,7 +9509,7 @@
         <v>1197</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C2" t="s">
         <v>1198</v>
@@ -12018,11 +12018,11 @@
         <v>377</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>378</v>
+        <v>17</v>
       </c>
       <c r="E2"/>
       <c r="F2" s="5" t="s">
-        <v>11</v>
+        <v>378</v>
       </c>
       <c r="G2"/>
     </row>
@@ -12031,7 +12031,7 @@
         <v>379</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>35</v>
+        <v>376</v>
       </c>
       <c r="C3" t="s">
         <v>380</v>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="E3"/>
       <c r="F3" s="5" t="s">
-        <v>11</v>
+        <v>382</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -12049,81 +12049,79 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>8</v>
+        <v>376</v>
       </c>
       <c r="C4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>384</v>
+        <v>17</v>
       </c>
       <c r="E4"/>
       <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4"/>
+        <v>385</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
       <c r="C5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>387</v>
+        <v>17</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
+      <c r="G5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>389</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C6" t="s">
         <v>390</v>
       </c>
-      <c r="C6" t="s">
-        <v>391</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>392</v>
+        <v>17</v>
       </c>
       <c r="E6"/>
       <c r="F6" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="G6" t="b">
-        <v>1</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="G6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>392</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" t="s">
         <v>393</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>394</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E7"/>
       <c r="F7" s="5" t="s">
-        <v>11</v>
+        <v>394</v>
       </c>
       <c r="G7"/>
     </row>
@@ -12132,7 +12130,7 @@
         <v>395</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
       <c r="C8" t="s">
         <v>396</v>
@@ -12142,7 +12140,7 @@
       </c>
       <c r="E8"/>
       <c r="F8" s="5" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G8"/>
     </row>
@@ -12151,29 +12149,29 @@
         <v>397</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
       <c r="C9" t="s">
         <v>398</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>17</v>
+        <v>399</v>
       </c>
       <c r="E9"/>
       <c r="F9" s="5" t="s">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="G9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>17</v>
@@ -12186,13 +12184,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>17</v>
@@ -12205,77 +12203,77 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
       <c r="C12" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="5" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
       <c r="C13" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E13"/>
       <c r="F13" s="5" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="G13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>25</v>
+        <v>376</v>
       </c>
       <c r="C14" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="5" t="s">
-        <v>11</v>
+        <v>394</v>
       </c>
       <c r="G14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C15" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>412</v>
+        <v>17</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="5" t="s">
-        <v>388</v>
+        <v>413</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -12283,20 +12281,20 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C16" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="5" t="s">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -12304,20 +12302,20 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C17" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>417</v>
+        <v>17</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -12325,77 +12323,81 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C18" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>17</v>
+        <v>421</v>
       </c>
       <c r="E18"/>
       <c r="F18" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="G18"/>
+        <v>422</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E20"/>
       <c r="F20" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="G20"/>
+        <v>429</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C21" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
@@ -12403,60 +12405,58 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C22" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E22"/>
       <c r="F22" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="G22" t="b">
-        <v>1</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="G22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C23" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E23"/>
       <c r="F23" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C24" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>17</v>
+        <v>440</v>
       </c>
       <c r="E24"/>
       <c r="F24" s="5" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -12464,81 +12464,79 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E25"/>
       <c r="F25" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="G25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C26" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>445</v>
+        <v>17</v>
       </c>
       <c r="E26"/>
       <c r="F26" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E27"/>
       <c r="F27" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="G27"/>
+        <v>450</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E28"/>
       <c r="F28" s="5" t="s">
-        <v>452</v>
+        <v>388</v>
       </c>
       <c r="G28"/>
     </row>
@@ -12547,127 +12545,133 @@
         <v>453</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C29" t="s">
         <v>454</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>17</v>
+        <v>455</v>
       </c>
       <c r="E29"/>
       <c r="F29" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="G29"/>
+        <v>456</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C30" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>17</v>
+        <v>459</v>
       </c>
       <c r="E30"/>
       <c r="F30" s="5" t="s">
-        <v>452</v>
-      </c>
-      <c r="G30"/>
+        <v>456</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E31"/>
       <c r="F31" s="5" t="s">
-        <v>60</v>
+        <v>462</v>
       </c>
       <c r="G31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>410</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E32"/>
       <c r="F32" s="5" t="s">
-        <v>462</v>
+        <v>11</v>
       </c>
       <c r="G32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C33" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E33"/>
       <c r="F33" s="5" t="s">
-        <v>60</v>
+        <v>467</v>
       </c>
       <c r="G33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C34" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E34"/>
       <c r="F34" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="G34"/>
+        <v>470</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C35" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>17</v>
+        <v>473</v>
       </c>
       <c r="E35"/>
       <c r="F35" s="5" t="s">
@@ -12677,218 +12681,218 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>410</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E36"/>
       <c r="F36" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G36" t="b">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>410</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E37"/>
       <c r="F37" s="5" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="G37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C38" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E38"/>
       <c r="F38" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="G38"/>
+        <v>480</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C39" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>17</v>
+        <v>482</v>
       </c>
       <c r="E39"/>
       <c r="F39" s="5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G39"/>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C40" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E40"/>
       <c r="F40" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G40"/>
+        <v>485</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>8</v>
+        <v>376</v>
       </c>
       <c r="C41" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>483</v>
+        <v>17</v>
       </c>
       <c r="E41"/>
       <c r="F41" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="G41"/>
+        <v>485</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C42" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>486</v>
+        <v>17</v>
       </c>
       <c r="E42"/>
       <c r="F42" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G42"/>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>490</v>
+        <v>17</v>
       </c>
       <c r="E43"/>
       <c r="F43" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="G43" t="b">
-        <v>1</v>
-      </c>
+        <v>492</v>
+      </c>
+      <c r="G43"/>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C44" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E44"/>
       <c r="F44" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="G44"/>
+        <v>495</v>
+      </c>
+      <c r="G44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C45" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>17</v>
+        <v>497</v>
       </c>
       <c r="E45"/>
       <c r="F45" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
+        <v>498</v>
+      </c>
+      <c r="G45"/>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C46" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>499</v>
+        <v>17</v>
       </c>
       <c r="E46"/>
       <c r="F46" s="5" t="s">
-        <v>500</v>
+        <v>391</v>
       </c>
       <c r="G46"/>
     </row>
@@ -12897,747 +12901,753 @@
         <v>501</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C47" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>503</v>
+        <v>17</v>
       </c>
       <c r="E47"/>
       <c r="F47" s="5" t="s">
-        <v>504</v>
+        <v>391</v>
       </c>
       <c r="G47"/>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>504</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="C48" t="s">
         <v>505</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C48" t="s">
-        <v>506</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E48"/>
       <c r="F48" s="5" t="s">
-        <v>507</v>
-      </c>
-      <c r="G48" t="b">
-        <v>1</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="G48"/>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C49" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>510</v>
+        <v>17</v>
       </c>
       <c r="E49"/>
       <c r="F49" s="5" t="s">
-        <v>493</v>
+        <v>391</v>
       </c>
       <c r="G49"/>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C50" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>513</v>
+        <v>17</v>
       </c>
       <c r="E50"/>
       <c r="F50" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G50" t="b">
-        <v>1</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="G50"/>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C51" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>516</v>
+        <v>17</v>
       </c>
       <c r="E51"/>
       <c r="F51" s="5" t="s">
-        <v>517</v>
+        <v>391</v>
       </c>
       <c r="G51"/>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C52" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>520</v>
+        <v>17</v>
       </c>
       <c r="E52"/>
       <c r="F52" s="5" t="s">
-        <v>60</v>
+        <v>391</v>
       </c>
       <c r="G52"/>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>410</v>
+        <v>35</v>
       </c>
       <c r="C53" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E53"/>
       <c r="F53" s="5" t="s">
-        <v>500</v>
+        <v>133</v>
       </c>
       <c r="G53"/>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C54" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>525</v>
+        <v>17</v>
       </c>
       <c r="E54"/>
       <c r="F54" s="5" t="s">
-        <v>60</v>
+        <v>391</v>
       </c>
       <c r="G54"/>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C55" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E55"/>
       <c r="F55" s="5" t="s">
-        <v>528</v>
+        <v>133</v>
       </c>
       <c r="G55"/>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E56"/>
       <c r="F56" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="G56" t="b">
-        <v>1</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G56"/>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C57" t="s">
-        <v>533</v>
+        <v>519</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>533</v>
+        <v>17</v>
       </c>
       <c r="E57"/>
       <c r="F57" s="5" t="s">
-        <v>534</v>
+        <v>133</v>
       </c>
       <c r="G57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E58"/>
       <c r="F58" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="G58" t="b">
-        <v>1</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="G58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C59" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>538</v>
+        <v>17</v>
       </c>
       <c r="E59"/>
       <c r="F59" s="5" t="s">
-        <v>55</v>
+        <v>391</v>
       </c>
       <c r="G59"/>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C60" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E60"/>
       <c r="F60" s="5" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="G60"/>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C61" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E61"/>
       <c r="F61" s="5" t="s">
-        <v>543</v>
+        <v>391</v>
       </c>
       <c r="G61"/>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C62" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E62"/>
       <c r="F62" s="5" t="s">
-        <v>452</v>
+        <v>391</v>
       </c>
       <c r="G62"/>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C63" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E63"/>
       <c r="F63" s="5" t="s">
-        <v>548</v>
+        <v>391</v>
       </c>
       <c r="G63"/>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>549</v>
+        <v>533</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C64" t="s">
-        <v>550</v>
+        <v>534</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E64"/>
       <c r="F64" s="5" t="s">
-        <v>548</v>
+        <v>462</v>
       </c>
       <c r="G64"/>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>551</v>
+        <v>535</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C65" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E65"/>
       <c r="F65" s="5" t="s">
-        <v>553</v>
+        <v>391</v>
       </c>
       <c r="G65"/>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C66" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E66"/>
       <c r="F66" s="5" t="s">
-        <v>553</v>
+        <v>391</v>
       </c>
       <c r="G66"/>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C67" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E67"/>
       <c r="F67" s="5" t="s">
-        <v>553</v>
+        <v>391</v>
       </c>
       <c r="G67"/>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C68" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E68"/>
       <c r="F68" s="5" t="s">
-        <v>553</v>
+        <v>462</v>
       </c>
       <c r="G68"/>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C69" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E69"/>
       <c r="F69" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G69"/>
+        <v>485</v>
+      </c>
+      <c r="G69" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>376</v>
+        <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E70"/>
       <c r="F70" s="5" t="s">
-        <v>553</v>
+        <v>11</v>
       </c>
       <c r="G70"/>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C71" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>17</v>
+        <v>549</v>
       </c>
       <c r="E71"/>
       <c r="F71" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G71"/>
+        <v>456</v>
+      </c>
+      <c r="G71" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>566</v>
+        <v>550</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C72" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E72"/>
       <c r="F72" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G72"/>
+        <v>552</v>
+      </c>
+      <c r="G72" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C73" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>17</v>
+        <v>555</v>
       </c>
       <c r="E73"/>
       <c r="F73" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G73"/>
+        <v>413</v>
+      </c>
+      <c r="G73" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C74" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E74"/>
       <c r="F74" s="5" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="G74"/>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>572</v>
+        <v>559</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C75" t="s">
-        <v>573</v>
+        <v>560</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E75"/>
       <c r="F75" s="5" t="s">
-        <v>553</v>
+        <v>462</v>
       </c>
       <c r="G75"/>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>376</v>
       </c>
       <c r="C76" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E76"/>
       <c r="F76" s="5" t="s">
-        <v>553</v>
+        <v>462</v>
       </c>
       <c r="G76"/>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>410</v>
+        <v>35</v>
       </c>
       <c r="C77" t="s">
-        <v>577</v>
+        <v>564</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>17</v>
+        <v>565</v>
       </c>
       <c r="E77"/>
       <c r="F77" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G77"/>
+        <v>11</v>
+      </c>
+      <c r="G77" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>578</v>
+        <v>566</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>410</v>
+        <v>8</v>
       </c>
       <c r="C78" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>17</v>
+        <v>568</v>
       </c>
       <c r="E78"/>
       <c r="F78" s="5" t="s">
-        <v>133</v>
+        <v>11</v>
       </c>
       <c r="G78"/>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C79" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E79"/>
       <c r="F79" s="5" t="s">
-        <v>133</v>
+        <v>391</v>
       </c>
       <c r="G79"/>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C80" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E80"/>
       <c r="F80" s="5" t="s">
-        <v>133</v>
+        <v>432</v>
       </c>
       <c r="G80"/>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C81" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>17</v>
+        <v>575</v>
       </c>
       <c r="E81"/>
       <c r="F81" s="5" t="s">
-        <v>133</v>
+        <v>432</v>
       </c>
       <c r="G81"/>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C82" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E82"/>
       <c r="F82" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G82"/>
+        <v>578</v>
+      </c>
+      <c r="G82" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>410</v>
+        <v>8</v>
       </c>
       <c r="C83" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="D83" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E83"/>
       <c r="F83" s="5" t="s">
-        <v>553</v>
-      </c>
-      <c r="G83"/>
+        <v>578</v>
+      </c>
+      <c r="G83" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C84" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E84"/>
       <c r="F84" s="5" t="s">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="G84"/>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C85" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E85"/>
       <c r="F85" s="5" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="G85" t="b">
         <v>1</v>
@@ -13645,151 +13655,149 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C86" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E86"/>
       <c r="F86" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="G86" t="b">
-        <v>1</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="G86"/>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C87" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E87"/>
       <c r="F87" s="5" t="s">
-        <v>553</v>
+        <v>462</v>
       </c>
       <c r="G87"/>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>410</v>
+        <v>8</v>
       </c>
       <c r="C88" t="s">
-        <v>597</v>
+        <v>17</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E88"/>
       <c r="F88" s="5" t="s">
-        <v>553</v>
+        <v>391</v>
       </c>
       <c r="G88"/>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C89" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E89"/>
       <c r="F89" s="5" t="s">
-        <v>553</v>
+        <v>462</v>
       </c>
       <c r="G89"/>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C90" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E90"/>
       <c r="F90" s="5" t="s">
-        <v>602</v>
+        <v>462</v>
       </c>
       <c r="G90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C91" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E91"/>
       <c r="F91" s="5" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="G91"/>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C92" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E92"/>
       <c r="F92" s="5" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="G92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C93" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>17</v>
+        <v>601</v>
       </c>
       <c r="E93"/>
       <c r="F93" s="5" t="s">
@@ -13799,294 +13807,294 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>410</v>
+        <v>25</v>
       </c>
       <c r="C94" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D94" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E94"/>
       <c r="F94" s="5" t="s">
-        <v>602</v>
+        <v>11</v>
       </c>
       <c r="G94"/>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C95" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>17</v>
+        <v>607</v>
       </c>
       <c r="E95"/>
       <c r="F95" s="5" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="G95"/>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C96" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E96"/>
       <c r="F96" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="G96"/>
+        <v>382</v>
+      </c>
+      <c r="G96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C97" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D97" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E97"/>
       <c r="F97" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="G97"/>
+        <v>382</v>
+      </c>
+      <c r="G97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C98" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E98"/>
       <c r="F98" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="G98"/>
+        <v>422</v>
+      </c>
+      <c r="G98" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C99" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="D99" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E99"/>
       <c r="F99" s="5" t="s">
-        <v>602</v>
+        <v>462</v>
       </c>
       <c r="G99"/>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C100" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E100"/>
       <c r="F100" s="5" t="s">
-        <v>602</v>
+        <v>60</v>
       </c>
       <c r="G100"/>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C101" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>17</v>
+        <v>620</v>
       </c>
       <c r="E101"/>
       <c r="F101" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="G101"/>
+        <v>495</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C102" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E102"/>
       <c r="F102" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="G102" t="b">
-        <v>1</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="G102"/>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>8</v>
+        <v>376</v>
       </c>
       <c r="C103" t="s">
-        <v>482</v>
+        <v>624</v>
       </c>
       <c r="D103" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E103"/>
       <c r="F103" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="G103" t="b">
-        <v>1</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="G103"/>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>8</v>
+        <v>376</v>
       </c>
       <c r="C104" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E104"/>
       <c r="F104" s="5" t="s">
-        <v>627</v>
+        <v>462</v>
       </c>
       <c r="G104"/>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>8</v>
+        <v>376</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>628</v>
       </c>
       <c r="D105" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E105"/>
       <c r="F105" s="5" t="s">
-        <v>553</v>
+        <v>596</v>
       </c>
       <c r="G105"/>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>410</v>
+        <v>502</v>
       </c>
       <c r="C106" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="E106"/>
       <c r="F106" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="G106" t="b">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G106"/>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>410</v>
+        <v>8</v>
       </c>
       <c r="C107" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>637</v>
+        <v>17</v>
       </c>
       <c r="E107"/>
       <c r="F107" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="G107" t="b">
-        <v>1</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="G107"/>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>410</v>
+        <v>25</v>
       </c>
       <c r="C108" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>17</v>
+        <v>636</v>
       </c>
       <c r="E108"/>
       <c r="F108" s="5" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="G108" t="b">
         <v>1</v>
@@ -14094,20 +14102,20 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>637</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="C109" t="s">
+        <v>639</v>
+      </c>
+      <c r="D109" s="5" t="s">
         <v>640</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C109" t="s">
-        <v>641</v>
-      </c>
-      <c r="D109" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="E109"/>
       <c r="F109" s="5" t="s">
-        <v>642</v>
+        <v>456</v>
       </c>
       <c r="G109" t="b">
         <v>1</v>
@@ -14115,73 +14123,67 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>641</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C110" t="s">
+        <v>642</v>
+      </c>
+      <c r="D110" s="5" t="s">
         <v>643</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C110" t="s">
-        <v>644</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="E110"/>
       <c r="F110" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="G110" t="b">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G110"/>
     </row>
     <row r="111">
       <c r="A111" t="s">
+        <v>644</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C111" t="s">
         <v>645</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C111" t="s">
-        <v>646</v>
       </c>
       <c r="D111" s="5" t="s">
         <v>17</v>
       </c>
       <c r="E111"/>
       <c r="F111" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="G111" t="b">
-        <v>1</v>
-      </c>
+        <v>462</v>
+      </c>
+      <c r="G111"/>
     </row>
     <row r="112">
       <c r="A112" t="s">
+        <v>646</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C112" t="s">
         <v>647</v>
       </c>
-      <c r="B112" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="D112" s="5" t="s">
         <v>648</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>17</v>
       </c>
       <c r="E112"/>
       <c r="F112" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="G112" t="b">
-        <v>1</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="G112"/>
     </row>
     <row r="113">
       <c r="A113" t="s">
         <v>649</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C113" t="s">
         <v>650</v>
@@ -14191,7 +14193,7 @@
       </c>
       <c r="E113"/>
       <c r="F113" s="5" t="s">
-        <v>635</v>
+        <v>456</v>
       </c>
       <c r="G113" t="b">
         <v>1</v>
@@ -14202,7 +14204,7 @@
         <v>651</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>410</v>
+        <v>25</v>
       </c>
       <c r="C114" t="s">
         <v>652</v>
@@ -14212,11 +14214,9 @@
       </c>
       <c r="E114"/>
       <c r="F114" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="G114" t="b">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G114"/>
     </row>
     <row r="116">
       <c r="A116" t="s">
@@ -14237,13 +14237,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="B117" t="s">
-        <v>653</v>
+        <v>338</v>
       </c>
       <c r="C117" t="s">
-        <v>654</v>
+        <v>339</v>
       </c>
       <c r="D117" t="s">
         <v>17</v>
@@ -14255,10 +14255,10 @@
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>655</v>
+        <v>340</v>
       </c>
       <c r="C118" t="s">
-        <v>656</v>
+        <v>341</v>
       </c>
       <c r="D118" t="s">
         <v>17</v>
@@ -14270,10 +14270,10 @@
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>657</v>
+        <v>336</v>
       </c>
       <c r="C119" t="s">
-        <v>658</v>
+        <v>337</v>
       </c>
       <c r="D119" t="s">
         <v>17</v>
@@ -14282,47 +14282,47 @@
         <v>17</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120"/>
-      <c r="B120" t="s">
-        <v>659</v>
-      </c>
-      <c r="C120" t="s">
-        <v>660</v>
-      </c>
-      <c r="D120" t="s">
-        <v>17</v>
-      </c>
-      <c r="E120" t="s">
-        <v>17</v>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>1</v>
+      </c>
+      <c r="B121" t="s">
+        <v>97</v>
+      </c>
+      <c r="C121" t="s">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>3</v>
+      </c>
+      <c r="E121" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>1</v>
+        <v>638</v>
       </c>
       <c r="B122" t="s">
-        <v>97</v>
+        <v>653</v>
       </c>
       <c r="C122" t="s">
-        <v>2</v>
+        <v>654</v>
       </c>
       <c r="D122" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E122" t="s">
-        <v>98</v>
+        <v>17</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="s">
-        <v>410</v>
-      </c>
+      <c r="A123"/>
       <c r="B123" t="s">
-        <v>338</v>
+        <v>655</v>
       </c>
       <c r="C123" t="s">
-        <v>339</v>
+        <v>656</v>
       </c>
       <c r="D123" t="s">
         <v>17</v>
@@ -14334,10 +14334,10 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>340</v>
+        <v>657</v>
       </c>
       <c r="C124" t="s">
-        <v>341</v>
+        <v>658</v>
       </c>
       <c r="D124" t="s">
         <v>17</v>
@@ -14349,10 +14349,10 @@
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>336</v>
+        <v>659</v>
       </c>
       <c r="C125" t="s">
-        <v>337</v>
+        <v>660</v>
       </c>
       <c r="D125" t="s">
         <v>17</v>
@@ -14461,7 +14461,7 @@
       </c>
       <c r="E4"/>
       <c r="F4" s="6" t="s">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="G4"/>
     </row>
@@ -14550,7 +14550,7 @@
       </c>
       <c r="E9"/>
       <c r="F9" s="6" t="s">
-        <v>602</v>
+        <v>462</v>
       </c>
       <c r="G9"/>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="E37"/>
       <c r="F37" s="6" t="s">
-        <v>421</v>
+        <v>394</v>
       </c>
       <c r="G37"/>
     </row>
@@ -15101,7 +15101,7 @@
       </c>
       <c r="E38"/>
       <c r="F38" s="6" t="s">
-        <v>553</v>
+        <v>391</v>
       </c>
       <c r="G38"/>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="E39"/>
       <c r="F39" s="6" t="s">
-        <v>553</v>
+        <v>391</v>
       </c>
       <c r="G39"/>
     </row>
@@ -15139,7 +15139,7 @@
       </c>
       <c r="E40"/>
       <c r="F40" s="6" t="s">
-        <v>553</v>
+        <v>391</v>
       </c>
       <c r="G40"/>
     </row>
@@ -17370,7 +17370,7 @@
         <v>924</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C23" t="s">
         <v>925</v>
@@ -17389,7 +17389,7 @@
         <v>926</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C24" t="s">
         <v>927</v>
@@ -17427,7 +17427,7 @@
         <v>931</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C26" t="s">
         <v>932</v>
@@ -17446,7 +17446,7 @@
         <v>933</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="C27" t="s">
         <v>934</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -4420,7 +4420,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.23.0-SNAPSHOT</t>
+    <t>1.24.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -4420,7 +4420,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.24.0-SNAPSHOT</t>
+    <t>1.25.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -4420,7 +4420,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.25.0-SNAPSHOT</t>
+    <t>1.26.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -4420,7 +4420,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.26.0-SNAPSHOT</t>
+    <t>1.27.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -4420,7 +4420,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.27.0-SNAPSHOT</t>
+    <t>1.28.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4504" uniqueCount="1462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4494" uniqueCount="1460">
   <si>
     <t>Field</t>
   </si>
@@ -4363,12 +4363,6 @@
     <t>Epid code</t>
   </si>
   <si>
-    <t>population</t>
-  </si>
-  <si>
-    <t>Population</t>
-  </si>
-  <si>
     <t>growthRate</t>
   </si>
   <si>
@@ -4420,7 +4414,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.28.0-SNAPSHOT</t>
+    <t>1.29.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -5691,7 +5685,7 @@
 </file>
 
 <file path=xl/tables/table82.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="82" name="Region" displayName="Region" ref="A1:G5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="82" name="Region" displayName="Region" ref="A1:G4">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -5707,7 +5701,7 @@
 </file>
 
 <file path=xl/tables/table83.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="83" name="District" displayName="District" ref="A1:G6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="83" name="District" displayName="District" ref="A1:G5">
   <autoFilter/>
   <tableColumns count="7">
     <tableColumn id="1" name="Field"/>
@@ -14471,6 +14465,108 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.0" customWidth="true"/>
+    <col min="2" max="2" width="30.0" customWidth="true"/>
+    <col min="3" max="3" width="30.0" customWidth="true"/>
+    <col min="4" max="4" width="60.0" customWidth="true"/>
+    <col min="5" max="5" width="10.0" customWidth="true"/>
+    <col min="6" max="6" width="45.0" customWidth="true"/>
+    <col min="7" max="7" width="10.0" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2"/>
+      <c r="F2" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1441</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -14510,17 +14606,17 @@
       <c r="A2" t="s">
         <v>1432</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
         <v>1433</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E2"/>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G2"/>
@@ -14529,17 +14625,17 @@
       <c r="A3" t="s">
         <v>1440</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
         <v>1441</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E3"/>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G3"/>
@@ -14548,151 +14644,30 @@
       <c r="A4" t="s">
         <v>1442</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>1443</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E4"/>
-      <c r="F4" s="20" t="s">
+      <c r="F4" s="21" t="s">
         <v>11</v>
       </c>
       <c r="G4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1444</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>29</v>
+        <v>214</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>1445</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5"/>
-      <c r="F5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5"/>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <tableParts>
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.0" customWidth="true"/>
-    <col min="2" max="2" width="30.0" customWidth="true"/>
-    <col min="3" max="3" width="30.0" customWidth="true"/>
-    <col min="4" max="4" width="60.0" customWidth="true"/>
-    <col min="5" max="5" width="10.0" customWidth="true"/>
-    <col min="6" max="6" width="45.0" customWidth="true"/>
-    <col min="7" max="7" width="10.0" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>1432</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1433</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2"/>
-      <c r="F2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>1440</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3"/>
-      <c r="F3" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>1442</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4"/>
-      <c r="F4" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>1444</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1445</v>
+        <v>215</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>17</v>
@@ -14702,25 +14677,6 @@
         <v>11</v>
       </c>
       <c r="G5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" t="s">
-        <v>215</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6"/>
-      <c r="F6" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -14871,13 +14827,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>584</v>
       </c>
       <c r="C2" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>17</v>
@@ -14890,13 +14846,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>17</v>
@@ -14947,7 +14903,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>8</v>
@@ -15004,11 +14960,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>17</v>
@@ -15097,7 +15053,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>52</v>
@@ -15122,7 +15078,7 @@
         <v>356</v>
       </c>
       <c r="C15" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>17</v>
@@ -15135,13 +15091,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>258</v>
       </c>
       <c r="C16" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>17</v>
@@ -15154,16 +15110,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="E17"/>
       <c r="F17" s="23" t="s">
@@ -15431,12 +15387,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -2821,7 +2821,7 @@
     <t>abnormalLungXrayFindings</t>
   </si>
   <si>
-    <t>Anormal lung X-Ray findings</t>
+    <t>Abnormal lung X-Ray findings</t>
   </si>
   <si>
     <t>conjunctivalInjection</t>
@@ -5218,7 +5218,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.32.0-SNAPSHOT</t>
+    <t>1.33.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -5218,7 +5218,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.33.0-SNAPSHOT</t>
+    <t>1.34.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6407" uniqueCount="1786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6412" uniqueCount="1784">
   <si>
     <t>Field</t>
   </si>
@@ -3763,12 +3763,6 @@
     <t>Source case</t>
   </si>
   <si>
-    <t>caseDisease</t>
-  </si>
-  <si>
-    <t>Disease of source case</t>
-  </si>
-  <si>
     <t>lastContactDate</t>
   </si>
   <si>
@@ -5392,7 +5386,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.36.0-SNAPSHOT</t>
+    <t>1.37.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -6179,7 +6173,7 @@
 </file>
 
 <file path=xl/tables/table51.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="Contact" displayName="Contact" ref="A1:H32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="51" name="Contact" displayName="Contact" ref="A1:H33">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6196,7 +6190,7 @@
 </file>
 
 <file path=xl/tables/table52.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="ContactDisease" displayName="ContactDisease" ref="A34:E90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="ContactDisease" displayName="ContactDisease" ref="A35:E91">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6210,7 +6204,7 @@
 </file>
 
 <file path=xl/tables/table53.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="ContactContactProximity" displayName="ContactContactProximity" ref="A92:E102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="ContactContactProximity" displayName="ContactContactProximity" ref="A93:E103">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6224,7 +6218,7 @@
 </file>
 
 <file path=xl/tables/table54.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="ContactContactClassification" displayName="ContactContactClassification" ref="A104:E107">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="ContactContactClassification" displayName="ContactContactClassification" ref="A105:E108">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6238,7 +6232,7 @@
 </file>
 
 <file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactStatus" displayName="ContactContactStatus" ref="A109:E112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactStatus" displayName="ContactContactStatus" ref="A110:E113">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6252,7 +6246,7 @@
 </file>
 
 <file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A114:E119">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A115:E120">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6266,7 +6260,7 @@
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactContactRelation" displayName="ContactContactRelation" ref="A121:E126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactContactRelation" displayName="ContactContactRelation" ref="A122:E127">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6280,7 +6274,7 @@
 </file>
 
 <file path=xl/tables/table58.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A128:E131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A129:E132">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6294,7 +6288,7 @@
 </file>
 
 <file path=xl/tables/table59.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A133:E137">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A134:E138">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -10336,7 +10330,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -10556,13 +10550,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1242</v>
+        <v>338</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>1243</v>
+        <v>71</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>18</v>
@@ -10575,13 +10569,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1244</v>
+        <v>340</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1245</v>
+        <v>18</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>18</v>
@@ -10594,16 +10588,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1247</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1249</v>
+        <v>18</v>
       </c>
       <c r="E13"/>
       <c r="G13" s="11" t="s">
@@ -10613,16 +10607,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="C14" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>18</v>
+        <v>1247</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="11" t="s">
@@ -10632,13 +10626,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="C15" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>18</v>
@@ -10651,16 +10645,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="C16" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>1259</v>
+        <v>18</v>
       </c>
       <c r="E16"/>
       <c r="G16" s="11" t="s">
@@ -10670,16 +10664,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>9</v>
+        <v>1255</v>
       </c>
       <c r="C17" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>18</v>
+        <v>1257</v>
       </c>
       <c r="E17"/>
       <c r="G17" s="11" t="s">
@@ -10689,13 +10683,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>18</v>
@@ -10708,13 +10702,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>359</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>18</v>
@@ -10727,13 +10721,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>9</v>
+        <v>359</v>
       </c>
       <c r="C20" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>18</v>
@@ -10746,16 +10740,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1269</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>1271</v>
+        <v>18</v>
       </c>
       <c r="E21"/>
       <c r="G21" s="11" t="s">
@@ -10765,16 +10759,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>9</v>
+        <v>1267</v>
       </c>
       <c r="C22" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>18</v>
+        <v>1269</v>
       </c>
       <c r="E22"/>
       <c r="G22" s="11" t="s">
@@ -10784,13 +10778,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>472</v>
+        <v>1270</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>473</v>
+        <v>1271</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>18</v>
@@ -10803,13 +10797,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1274</v>
+        <v>472</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1240</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>1275</v>
+        <v>473</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>18</v>
@@ -10822,13 +10816,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>359</v>
+        <v>1240</v>
       </c>
       <c r="C25" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>18</v>
@@ -10841,13 +10835,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>475</v>
+        <v>359</v>
       </c>
       <c r="C26" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>18</v>
@@ -10860,13 +10854,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>388</v>
+        <v>475</v>
       </c>
       <c r="C27" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>18</v>
@@ -10879,13 +10873,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>9</v>
+        <v>388</v>
       </c>
       <c r="C28" t="s">
-        <v>1061</v>
+        <v>1279</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>18</v>
@@ -10898,13 +10892,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>388</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>1284</v>
+        <v>1061</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>18</v>
@@ -10917,13 +10911,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1286</v>
+        <v>388</v>
       </c>
       <c r="C30" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>18</v>
@@ -10936,13 +10930,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1288</v>
+        <v>1283</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>39</v>
+        <v>1284</v>
       </c>
       <c r="C31" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>18</v>
@@ -10955,13 +10949,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>18</v>
@@ -10972,137 +10966,141 @@
       </c>
       <c r="H32"/>
     </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" t="s">
-        <v>117</v>
-      </c>
-      <c r="C34" t="s">
-        <v>2</v>
-      </c>
-      <c r="D34" t="s">
-        <v>3</v>
-      </c>
-      <c r="E34" t="s">
-        <v>118</v>
-      </c>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33"/>
+      <c r="G33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
         <v>71</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>139</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>140</v>
       </c>
-      <c r="D35" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="D36" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s">
         <v>139</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36"/>
-      <c r="B36" t="s">
-        <v>141</v>
-      </c>
-      <c r="C36" t="s">
-        <v>142</v>
-      </c>
-      <c r="D36" t="s">
-        <v>18</v>
-      </c>
-      <c r="E36" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C37" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>147</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C39" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
       </c>
       <c r="E39" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C40" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
       </c>
       <c r="E40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -11114,10 +11112,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -11129,10 +11127,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C44" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -11144,85 +11142,85 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C46" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
       </c>
       <c r="E48" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
       </c>
       <c r="E49" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
     </row>
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -11234,70 +11232,70 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>178</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C53" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>183</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C54" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C55" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -11309,10 +11307,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -11324,10 +11322,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C57" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -11339,10 +11337,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C58" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -11354,10 +11352,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C59" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -11369,10 +11367,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C60" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -11384,10 +11382,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C61" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -11399,10 +11397,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -11414,10 +11412,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C63" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -11429,10 +11427,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -11444,10 +11442,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C65" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -11459,10 +11457,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C66" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -11474,10 +11472,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C67" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -11489,10 +11487,10 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C68" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -11504,10 +11502,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C69" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -11519,10 +11517,10 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C70" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -11534,10 +11532,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C71" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -11549,10 +11547,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C72" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -11564,10 +11562,10 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C73" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -11579,10 +11577,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C74" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -11594,10 +11592,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C75" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -11609,10 +11607,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C76" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -11624,10 +11622,10 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C77" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -11639,10 +11637,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C78" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -11654,10 +11652,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -11669,10 +11667,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C80" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -11684,10 +11682,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C81" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -11699,55 +11697,55 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C82" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>241</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C83" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C84" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C85" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -11759,10 +11757,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C86" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -11774,10 +11772,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C87" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -11789,10 +11787,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C88" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -11804,74 +11802,74 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C89" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>257</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
+        <v>255</v>
+      </c>
+      <c r="C90" t="s">
+        <v>256</v>
+      </c>
+      <c r="D90" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91"/>
+      <c r="B91" t="s">
         <v>258</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" t="s">
         <v>259</v>
       </c>
-      <c r="D90" t="s">
-        <v>18</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="D91" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" t="s">
         <v>260</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>1</v>
-      </c>
-      <c r="B92" t="s">
-        <v>117</v>
-      </c>
-      <c r="C92" t="s">
-        <v>2</v>
-      </c>
-      <c r="D92" t="s">
-        <v>3</v>
-      </c>
-      <c r="E92" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>1247</v>
+        <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>1292</v>
+        <v>117</v>
       </c>
       <c r="C93" t="s">
-        <v>1293</v>
+        <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E93" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94"/>
+      <c r="A94" t="s">
+        <v>1245</v>
+      </c>
       <c r="B94" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="C94" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -11883,10 +11881,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="C95" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -11898,10 +11896,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="C96" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -11913,10 +11911,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="C97" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -11928,10 +11926,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="C98" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -11943,10 +11941,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="C99" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
@@ -11958,10 +11956,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C100" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -11973,10 +11971,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="C101" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -11988,10 +11986,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="C102" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -12000,111 +11998,111 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>1</v>
-      </c>
-      <c r="B104" t="s">
-        <v>117</v>
-      </c>
-      <c r="C104" t="s">
-        <v>2</v>
-      </c>
-      <c r="D104" t="s">
-        <v>3</v>
-      </c>
-      <c r="E104" t="s">
-        <v>118</v>
+    <row r="103">
+      <c r="A103"/>
+      <c r="B103" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D103" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>1251</v>
+        <v>1</v>
       </c>
       <c r="B105" t="s">
+        <v>117</v>
+      </c>
+      <c r="C105" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" t="s">
+        <v>3</v>
+      </c>
+      <c r="E105" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D106" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" t="s">
         <v>1312</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1313</v>
-      </c>
-      <c r="D105" t="s">
-        <v>18</v>
-      </c>
-      <c r="E105" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106"/>
-      <c r="B106" t="s">
-        <v>501</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1315</v>
-      </c>
-      <c r="D106" t="s">
-        <v>18</v>
-      </c>
-      <c r="E106" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
+        <v>501</v>
+      </c>
+      <c r="C107" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D107" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108"/>
+      <c r="B108" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D108" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" t="s">
         <v>1316</v>
-      </c>
-      <c r="C107" t="s">
-        <v>1317</v>
-      </c>
-      <c r="D107" t="s">
-        <v>18</v>
-      </c>
-      <c r="E107" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>1</v>
-      </c>
-      <c r="B109" t="s">
-        <v>117</v>
-      </c>
-      <c r="C109" t="s">
-        <v>2</v>
-      </c>
-      <c r="D109" t="s">
-        <v>3</v>
-      </c>
-      <c r="E109" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>1254</v>
+        <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>1319</v>
+        <v>117</v>
       </c>
       <c r="C110" t="s">
-        <v>1320</v>
+        <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E110" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111"/>
+      <c r="A111" t="s">
+        <v>1252</v>
+      </c>
       <c r="B111" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C111" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -12116,10 +12114,10 @@
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C112" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="D112" t="s">
         <v>18</v>
@@ -12128,141 +12126,141 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>1</v>
-      </c>
-      <c r="B114" t="s">
-        <v>117</v>
-      </c>
-      <c r="C114" t="s">
-        <v>2</v>
-      </c>
-      <c r="D114" t="s">
-        <v>3</v>
-      </c>
-      <c r="E114" t="s">
-        <v>118</v>
+    <row r="113">
+      <c r="A113"/>
+      <c r="B113" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D113" t="s">
+        <v>18</v>
+      </c>
+      <c r="E113" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>1257</v>
+        <v>1</v>
       </c>
       <c r="B115" t="s">
+        <v>117</v>
+      </c>
+      <c r="C115" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>3</v>
+      </c>
+      <c r="E115" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D116" t="s">
         <v>1325</v>
       </c>
-      <c r="C115" t="s">
+      <c r="E116" t="s">
         <v>1326</v>
-      </c>
-      <c r="D115" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E115" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116"/>
-      <c r="B116" t="s">
-        <v>1329</v>
-      </c>
-      <c r="C116" t="s">
-        <v>1330</v>
-      </c>
-      <c r="D116" t="s">
-        <v>1331</v>
-      </c>
-      <c r="E116" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="C117" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
       <c r="D117" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
       <c r="E117" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
       <c r="C118" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
       <c r="D118" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="E118" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C119" t="s">
+        <v>1336</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120"/>
+      <c r="B120" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D120" t="s">
         <v>1341</v>
       </c>
-      <c r="C119" t="s">
-        <v>1342</v>
-      </c>
-      <c r="D119" t="s">
-        <v>1343</v>
-      </c>
-      <c r="E119" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>1</v>
-      </c>
-      <c r="B121" t="s">
-        <v>117</v>
-      </c>
-      <c r="C121" t="s">
-        <v>2</v>
-      </c>
-      <c r="D121" t="s">
-        <v>3</v>
-      </c>
-      <c r="E121" t="s">
-        <v>118</v>
+      <c r="E120" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>1269</v>
+        <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>1344</v>
+        <v>117</v>
       </c>
       <c r="C122" t="s">
-        <v>1345</v>
+        <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E122" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123"/>
+      <c r="A123" t="s">
+        <v>1267</v>
+      </c>
       <c r="B123" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="C123" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="D123" t="s">
         <v>18</v>
@@ -12274,10 +12272,10 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="C124" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
@@ -12289,10 +12287,10 @@
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="C125" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="D125" t="s">
         <v>18</v>
@@ -12304,59 +12302,59 @@
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1349</v>
+      </c>
+      <c r="D126" t="s">
+        <v>18</v>
+      </c>
+      <c r="E126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127"/>
+      <c r="B127" t="s">
         <v>255</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C127" t="s">
         <v>257</v>
       </c>
-      <c r="D126" t="s">
-        <v>18</v>
-      </c>
-      <c r="E126" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>1</v>
-      </c>
-      <c r="B128" t="s">
-        <v>117</v>
-      </c>
-      <c r="C128" t="s">
-        <v>2</v>
-      </c>
-      <c r="D128" t="s">
-        <v>3</v>
-      </c>
-      <c r="E128" t="s">
-        <v>118</v>
+      <c r="D127" t="s">
+        <v>18</v>
+      </c>
+      <c r="E127" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>117</v>
+      </c>
+      <c r="C129" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E129" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
         <v>388</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B130" t="s">
         <v>522</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C130" t="s">
         <v>523</v>
-      </c>
-      <c r="D129" t="s">
-        <v>18</v>
-      </c>
-      <c r="E129" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130"/>
-      <c r="B130" t="s">
-        <v>524</v>
-      </c>
-      <c r="C130" t="s">
-        <v>525</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
@@ -12368,59 +12366,59 @@
     <row r="131">
       <c r="A131"/>
       <c r="B131" t="s">
+        <v>524</v>
+      </c>
+      <c r="C131" t="s">
+        <v>525</v>
+      </c>
+      <c r="D131" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132"/>
+      <c r="B132" t="s">
         <v>336</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C132" t="s">
         <v>337</v>
       </c>
-      <c r="D131" t="s">
-        <v>18</v>
-      </c>
-      <c r="E131" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>1</v>
-      </c>
-      <c r="B133" t="s">
-        <v>117</v>
-      </c>
-      <c r="C133" t="s">
-        <v>2</v>
-      </c>
-      <c r="D133" t="s">
-        <v>3</v>
-      </c>
-      <c r="E133" t="s">
-        <v>118</v>
+      <c r="D132" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>1286</v>
+        <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>1352</v>
+        <v>117</v>
       </c>
       <c r="C134" t="s">
-        <v>1353</v>
+        <v>2</v>
       </c>
       <c r="D134" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E134" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135"/>
+      <c r="A135" t="s">
+        <v>1284</v>
+      </c>
       <c r="B135" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="C135" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="D135" t="s">
         <v>18</v>
@@ -12432,10 +12430,10 @@
     <row r="136">
       <c r="A136"/>
       <c r="B136" t="s">
-        <v>269</v>
+        <v>1352</v>
       </c>
       <c r="C136" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="D136" t="s">
         <v>18</v>
@@ -12447,15 +12445,30 @@
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
+        <v>269</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D137" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138"/>
+      <c r="B138" t="s">
         <v>336</v>
       </c>
-      <c r="C137" t="s">
+      <c r="C138" t="s">
         <v>337</v>
       </c>
-      <c r="D137" t="s">
-        <v>18</v>
-      </c>
-      <c r="E137" t="s">
+      <c r="D138" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" t="s">
         <v>18</v>
       </c>
     </row>
@@ -12524,7 +12537,7 @@
         <v>352</v>
       </c>
       <c r="C2" t="s">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>18</v>
@@ -12567,7 +12580,7 @@
         <v>1228</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -12579,13 +12592,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>359</v>
       </c>
       <c r="C5" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>18</v>
@@ -12600,16 +12613,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C6" t="s">
         <v>1361</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>1362</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>1364</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -12627,10 +12640,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1366</v>
+        <v>1364</v>
       </c>
       <c r="E7"/>
       <c r="G7" s="12" t="s">
@@ -13592,13 +13605,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="B72" t="s">
-        <v>1367</v>
+        <v>1365</v>
       </c>
       <c r="C72" t="s">
-        <v>1368</v>
+        <v>1366</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -13610,31 +13623,31 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D73" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" t="s">
         <v>1369</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D73" t="s">
-        <v>18</v>
-      </c>
-      <c r="E73" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1371</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
         <v>1372</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1373</v>
-      </c>
-      <c r="D74" t="s">
-        <v>18</v>
-      </c>
-      <c r="E74" t="s">
-        <v>1374</v>
       </c>
     </row>
   </sheetData>
@@ -13690,13 +13703,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>1240</v>
       </c>
       <c r="C2" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>18</v>
@@ -13711,13 +13724,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1378</v>
+        <v>1376</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>18</v>
@@ -13730,16 +13743,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1379</v>
+        <v>1377</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -13850,13 +13863,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C10" t="s">
         <v>1382</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>1383</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1384</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>18</v>
@@ -13871,13 +13884,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1385</v>
+        <v>1383</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1386</v>
+        <v>1384</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>18</v>
@@ -13890,13 +13903,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C12" t="s">
         <v>1387</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>1388</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1389</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>18</v>
@@ -13911,13 +13924,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>18</v>
@@ -13932,13 +13945,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>18</v>
@@ -13951,13 +13964,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1394</v>
+        <v>1392</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>18</v>
@@ -13970,13 +13983,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1396</v>
+        <v>1394</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>18</v>
@@ -13989,13 +14002,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>1399</v>
+        <v>1397</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>18</v>
@@ -14008,13 +14021,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C18" t="s">
         <v>1400</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>1401</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1402</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>18</v>
@@ -14027,13 +14040,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1403</v>
+        <v>1401</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>1404</v>
+        <v>1402</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>18</v>
@@ -14046,13 +14059,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1405</v>
+        <v>1403</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>1406</v>
+        <v>1404</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>18</v>
@@ -14065,13 +14078,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>1406</v>
+      </c>
+      <c r="C21" t="s">
         <v>1407</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>1408</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1409</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>18</v>
@@ -14084,10 +14097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1410</v>
+        <v>1408</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
@@ -14103,13 +14116,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>475</v>
       </c>
       <c r="C23" t="s">
-        <v>1413</v>
+        <v>1411</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>18</v>
@@ -14122,13 +14135,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1414</v>
+        <v>1412</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>475</v>
       </c>
       <c r="C24" t="s">
-        <v>1415</v>
+        <v>1413</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>18</v>
@@ -14141,13 +14154,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C25" t="s">
         <v>1416</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1418</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>18</v>
@@ -14160,13 +14173,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1419</v>
+        <v>1417</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>475</v>
       </c>
       <c r="C26" t="s">
-        <v>1420</v>
+        <v>1418</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>18</v>
@@ -14179,13 +14192,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1421</v>
+        <v>1419</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>475</v>
       </c>
       <c r="C27" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>18</v>
@@ -14198,11 +14211,11 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1423</v>
+        <v>1421</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" t="s">
-        <v>1424</v>
+        <v>1422</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>18</v>
@@ -14215,11 +14228,11 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1425</v>
+        <v>1423</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>18</v>
@@ -14232,13 +14245,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>18</v>
@@ -14251,13 +14264,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>18</v>
@@ -14287,13 +14300,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="B34" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="C34" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -14305,10 +14318,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="C35" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -14320,10 +14333,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="C36" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -14335,10 +14348,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="C37" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -14350,10 +14363,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="C38" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -14365,10 +14378,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="C39" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -14380,10 +14393,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="C40" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -14395,10 +14408,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="C41" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -14410,10 +14423,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="C42" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -14425,10 +14438,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="C43" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -14440,10 +14453,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="C44" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -14455,10 +14468,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="C45" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -14470,10 +14483,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="C46" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -14485,10 +14498,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="C47" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -14500,10 +14513,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="C48" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -14515,10 +14528,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="C49" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -14530,10 +14543,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="C50" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -14545,10 +14558,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="C51" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -14560,10 +14573,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="C52" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -14606,13 +14619,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="B56" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="C56" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -14624,10 +14637,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="C57" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -14655,13 +14668,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1401</v>
+        <v>1399</v>
       </c>
       <c r="B60" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="C60" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -14673,10 +14686,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="C61" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -14704,13 +14717,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1408</v>
+        <v>1406</v>
       </c>
       <c r="B64" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="C64" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -14722,10 +14735,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="C65" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -14737,10 +14750,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="C66" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -14768,13 +14781,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B69" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C69" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -14801,10 +14814,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C71" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -14816,10 +14829,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C72" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -14884,10 +14897,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -14905,16 +14918,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -14926,16 +14939,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="E4"/>
       <c r="G4" s="14" t="s">
@@ -14945,16 +14958,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C5" t="s">
         <v>1496</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="D5" s="14" t="s">
         <v>1497</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1498</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>1499</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -14966,16 +14979,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="E6"/>
       <c r="G6" s="14" t="s">
@@ -14985,16 +14998,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -15006,16 +15019,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -15027,16 +15040,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="14" t="s">
@@ -15046,7 +15059,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>359</v>
@@ -15067,16 +15080,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>1509</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>1511</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -15088,16 +15101,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -15109,16 +15122,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>475</v>
       </c>
       <c r="C13" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="E13"/>
       <c r="G13" s="14" t="s">
@@ -15128,16 +15141,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>475</v>
       </c>
       <c r="C14" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="14" t="s">
@@ -15147,16 +15160,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="E15"/>
       <c r="G15" s="14" t="s">
@@ -15166,13 +15179,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>18</v>
@@ -16061,13 +16074,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="B77" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="C77" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -16079,10 +16092,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="C78" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -16094,10 +16107,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="C79" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -16109,10 +16122,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="C80" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -16124,10 +16137,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="C81" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -16139,7 +16152,7 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="C82" t="s">
         <v>559</v>
@@ -16154,10 +16167,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="C83" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -16169,10 +16182,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="C84" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -16184,10 +16197,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="C85" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -16199,10 +16212,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="C86" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -16214,10 +16227,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="C87" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -16229,10 +16242,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="C88" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -16244,10 +16257,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="C89" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -16259,10 +16272,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="C90" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -16274,10 +16287,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="C91" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -16289,10 +16302,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="C92" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -16304,10 +16317,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="C93" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -16319,10 +16332,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="C94" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -16365,13 +16378,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>1417</v>
+        <v>1415</v>
       </c>
       <c r="B98" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C98" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -16398,10 +16411,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C100" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -16413,10 +16426,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C101" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -16479,10 +16492,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1411</v>
+        <v>1409</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -16498,13 +16511,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>18</v>
@@ -16517,13 +16530,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C4" t="s">
         <v>1561</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>1562</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1563</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>18</v>
@@ -16536,13 +16549,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="C5" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>18</v>
@@ -16555,13 +16568,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="C6" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>18</v>
@@ -16574,13 +16587,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>18</v>
@@ -16593,13 +16606,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>18</v>
@@ -16612,13 +16625,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>18</v>
@@ -16631,13 +16644,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>18</v>
@@ -16650,13 +16663,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>18</v>
@@ -16669,13 +16682,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>18</v>
@@ -16688,13 +16701,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>18</v>
@@ -16707,13 +16720,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>18</v>
@@ -16726,13 +16739,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>18</v>
@@ -16745,13 +16758,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>18</v>
@@ -16764,13 +16777,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>18</v>
@@ -16783,13 +16796,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>18</v>
@@ -16802,13 +16815,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>18</v>
@@ -16821,13 +16834,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>18</v>
@@ -16840,13 +16853,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>18</v>
@@ -16859,13 +16872,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>18</v>
@@ -16878,13 +16891,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>18</v>
@@ -16914,13 +16927,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="B26" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="C26" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -16932,10 +16945,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="C27" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -16947,10 +16960,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="C28" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -17011,13 +17024,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C2" t="s">
         <v>1602</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>1603</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1604</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>18</v>
@@ -17038,7 +17051,7 @@
         <v>1240</v>
       </c>
       <c r="C3" t="s">
-        <v>1376</v>
+        <v>1374</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>18</v>
@@ -17051,13 +17064,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C4" t="s">
         <v>1605</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>1606</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1607</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>18</v>
@@ -17070,13 +17083,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C5" t="s">
         <v>1608</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>1609</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1610</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>18</v>
@@ -17089,16 +17102,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C6" t="s">
         <v>1611</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>1612</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1613</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>1614</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -17110,13 +17123,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C7" t="s">
         <v>1615</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>1616</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1617</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>18</v>
@@ -17129,13 +17142,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>18</v>
@@ -17150,13 +17163,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>18</v>
@@ -17169,13 +17182,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C10" t="s">
         <v>1622</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>1623</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1624</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>18</v>
@@ -17188,13 +17201,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>18</v>
@@ -17207,13 +17220,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>18</v>
@@ -17226,13 +17239,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>359</v>
       </c>
       <c r="C13" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>18</v>
@@ -17245,13 +17258,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>18</v>
@@ -17264,13 +17277,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>359</v>
       </c>
       <c r="C15" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>18</v>
@@ -17285,13 +17298,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>18</v>
@@ -17304,7 +17317,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>29</v>
@@ -17323,7 +17336,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>29</v>
@@ -17342,7 +17355,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>29</v>
@@ -17378,13 +17391,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="B22" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="C22" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -17396,10 +17409,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="C23" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -17411,10 +17424,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="C24" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -17426,10 +17439,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="C25" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -17457,13 +17470,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="B28" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="C28" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -17475,10 +17488,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="C29" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -17490,10 +17503,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="C30" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -17505,10 +17518,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="C31" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -17520,10 +17533,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="C32" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -17535,10 +17548,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="C33" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -17550,10 +17563,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="C34" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -17565,10 +17578,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="C35" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -17580,10 +17593,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="C36" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -17595,10 +17608,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="C37" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -17610,10 +17623,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="C38" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -17625,10 +17638,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="C39" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -17640,10 +17653,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="C40" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -17655,10 +17668,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="C41" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -17670,10 +17683,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="C42" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -17685,10 +17698,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="C43" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -17700,10 +17713,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="C44" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -17718,7 +17731,7 @@
         <v>255</v>
       </c>
       <c r="C45" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -17730,10 +17743,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="C46" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -17745,10 +17758,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="C47" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -17760,10 +17773,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="C48" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -17791,13 +17804,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="B51" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="C51" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -17809,10 +17822,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="C52" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -17824,10 +17837,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="C53" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -17855,13 +17868,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="B56" t="s">
         <v>507</v>
       </c>
       <c r="C56" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -17876,7 +17889,7 @@
         <v>510</v>
       </c>
       <c r="C57" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -17888,10 +17901,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="C58" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -17903,10 +17916,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="C59" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -17970,16 +17983,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>1700</v>
+      </c>
+      <c r="C2" t="s">
         <v>1701</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="D2" s="17" t="s">
         <v>1702</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1703</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>1704</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -17991,16 +18004,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -18012,16 +18025,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="E4"/>
       <c r="G4" s="17" t="s">
@@ -18073,13 +18086,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>18</v>
@@ -18092,16 +18105,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C8" t="s">
         <v>1713</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="D8" s="17" t="s">
         <v>1714</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1715</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>1716</v>
       </c>
       <c r="E8"/>
       <c r="G8" s="17" t="s">
@@ -18111,16 +18124,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="17" t="s">
@@ -18130,16 +18143,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="E10"/>
       <c r="G10" s="17" t="s">
@@ -18149,16 +18162,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="E11"/>
       <c r="G11" s="17" t="s">
@@ -18168,16 +18181,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="E12"/>
       <c r="G12" s="17" t="s">
@@ -18244,13 +18257,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>18</v>
@@ -18337,13 +18350,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="B22" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="C22" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -18358,7 +18371,7 @@
         <v>501</v>
       </c>
       <c r="C23" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -18370,16 +18383,16 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
+        <v>1731</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1732</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s">
         <v>1733</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1734</v>
-      </c>
-      <c r="D24" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="26">
@@ -18401,13 +18414,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="B27" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="C27" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -18419,10 +18432,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="C28" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -18449,10 +18462,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="C30" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -18464,10 +18477,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="C31" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -19419,13 +19432,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="C2" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>18</v>
@@ -19443,10 +19456,10 @@
         <v>351</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="C3" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>18</v>
@@ -19461,13 +19474,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>18</v>
@@ -19480,7 +19493,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>1240</v>
@@ -19548,13 +19561,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>18</v>
@@ -19649,7 +19662,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>18</v>
@@ -19668,7 +19681,7 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>18</v>
@@ -19681,10 +19694,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -19700,7 +19713,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>475</v>
@@ -19719,7 +19732,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>475</v>
@@ -19774,7 +19787,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="B15" t="s">
         <v>273</v>
@@ -19822,10 +19835,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="C18" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -20209,13 +20222,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>18</v>
@@ -20228,13 +20241,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>18</v>
@@ -20247,13 +20260,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>18</v>
@@ -20266,7 +20279,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>475</v>
@@ -20353,13 +20366,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>18</v>
@@ -20372,13 +20385,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>18</v>
@@ -20391,13 +20404,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
@@ -20429,7 +20442,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>475</v>
@@ -20516,13 +20529,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>18</v>
@@ -20573,7 +20586,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>475</v>
@@ -20660,13 +20673,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>475</v>
       </c>
       <c r="C2" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>18</v>
@@ -20679,13 +20692,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>18</v>
@@ -20736,13 +20749,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>18</v>
@@ -20793,11 +20806,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>18</v>
@@ -20886,13 +20899,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>18</v>
@@ -20911,7 +20924,7 @@
         <v>466</v>
       </c>
       <c r="C15" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>18</v>
@@ -20924,13 +20937,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>359</v>
       </c>
       <c r="C16" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>18</v>
@@ -20943,16 +20956,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="E17"/>
       <c r="G17" s="23" t="s">
@@ -20962,10 +20975,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -21857,13 +21870,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C79" t="s">
         <v>1773</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1774</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1775</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -21875,10 +21888,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="C80" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -21890,10 +21903,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="C81" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -21905,10 +21918,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="C82" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -21920,10 +21933,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="C83" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -21949,12 +21962,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -3787,6 +3787,30 @@
     <t>Attending clinician</t>
   </si>
   <si>
+    <t>caze</t>
+  </si>
+  <si>
+    <t>CaseReference</t>
+  </si>
+  <si>
+    <t>Source case</t>
+  </si>
+  <si>
+    <t>caseIdExternalSystem</t>
+  </si>
+  <si>
+    <t>Case ID in external system</t>
+  </si>
+  <si>
+    <t>caseOrEventInformation</t>
+  </si>
+  <si>
+    <t>Case or event information</t>
+  </si>
+  <si>
+    <t>Disease of source case</t>
+  </si>
+  <si>
     <t>reportDateTime</t>
   </si>
   <si>
@@ -3802,117 +3826,141 @@
     <t>Responsible district</t>
   </si>
   <si>
+    <t>lastContactDate</t>
+  </si>
+  <si>
+    <t>Date of last contact</t>
+  </si>
+  <si>
+    <t>contactProximity</t>
+  </si>
+  <si>
+    <t>ContactProximity</t>
+  </si>
+  <si>
+    <t>Type of contact - if multiple pick the closest contact proximity</t>
+  </si>
+  <si>
+    <t>Select the type of contact with the case</t>
+  </si>
+  <si>
+    <t>contactProximityDetails</t>
+  </si>
+  <si>
+    <t>Additional information on the type of contact</t>
+  </si>
+  <si>
+    <t>contactCategory</t>
+  </si>
+  <si>
+    <t>ContactCategory</t>
+  </si>
+  <si>
+    <t>Contact Category</t>
+  </si>
+  <si>
+    <t>contactClassification</t>
+  </si>
+  <si>
+    <t>ContactClassification</t>
+  </si>
+  <si>
+    <t>Contact classification</t>
+  </si>
+  <si>
+    <t>contactStatus</t>
+  </si>
+  <si>
+    <t>ContactStatus</t>
+  </si>
+  <si>
+    <t>Contact status</t>
+  </si>
+  <si>
+    <t>followUpStatus</t>
+  </si>
+  <si>
+    <t>FollowUpStatus</t>
+  </si>
+  <si>
+    <t>Follow-up status</t>
+  </si>
+  <si>
+    <t>&lt;ul&gt;&lt;li&gt;Under follow-up: The follow-up process is running.&lt;/li&gt;&lt;li&gt;Follow-up completed: The follow-up has been completed.&lt;/li&gt;&lt;li&gt;Follow-up canceled: The follow-up process has been canceled, e.g. because the person died or the contact became irrelevant.&lt;/li&gt;&lt;li&gt;Lost to follow-up: The follow-up process could not be continued, e.g. because the person could not be found.&lt;/li&gt;&lt;li&gt;No follow-up: No contact follow-up is being done.&lt;/li&gt;&lt;/ul&gt;</t>
+  </si>
+  <si>
+    <t>followUpComment</t>
+  </si>
+  <si>
+    <t>Follow-up status comment</t>
+  </si>
+  <si>
+    <t>followUpUntil</t>
+  </si>
+  <si>
+    <t>Follow-up until</t>
+  </si>
+  <si>
+    <t>overwriteFollowUpUntil</t>
+  </si>
+  <si>
+    <t>Overwrite follow-up until date</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Description of how contact took place</t>
+  </si>
+  <si>
+    <t>relationToCase</t>
+  </si>
+  <si>
+    <t>ContactRelation</t>
+  </si>
+  <si>
+    <t>Relationship with case</t>
+  </si>
+  <si>
+    <t>Select the person's relation to the case</t>
+  </si>
+  <si>
+    <t>relationDescription</t>
+  </si>
+  <si>
+    <t>Relationship description</t>
+  </si>
+  <si>
+    <t>highPriority</t>
+  </si>
+  <si>
+    <t>High priority contact</t>
+  </si>
+  <si>
+    <t>immunosuppressiveTherapyBasicDisease</t>
+  </si>
+  <si>
+    <t>Immunosuppressive therapy or basic disease is present</t>
+  </si>
+  <si>
+    <t>immunosuppressiveTherapyBasicDiseaseDetails</t>
+  </si>
+  <si>
+    <t>careForPeopleOver60</t>
+  </si>
+  <si>
+    <t>Is the person medically/nursingly active in the care of patients or people over 60 years of age?</t>
+  </si>
+  <si>
     <t>Contact person</t>
   </si>
   <si>
-    <t>caze</t>
-  </si>
-  <si>
-    <t>CaseReference</t>
-  </si>
-  <si>
-    <t>Source case</t>
-  </si>
-  <si>
-    <t>Disease of source case</t>
-  </si>
-  <si>
-    <t>lastContactDate</t>
-  </si>
-  <si>
-    <t>Date of last contact</t>
-  </si>
-  <si>
-    <t>contactProximity</t>
-  </si>
-  <si>
-    <t>ContactProximity</t>
-  </si>
-  <si>
-    <t>Type of contact - if multiple pick the closest contact proximity</t>
-  </si>
-  <si>
-    <t>Select the type of contact with the case</t>
-  </si>
-  <si>
-    <t>contactClassification</t>
-  </si>
-  <si>
-    <t>ContactClassification</t>
-  </si>
-  <si>
-    <t>Contact classification</t>
-  </si>
-  <si>
-    <t>contactStatus</t>
-  </si>
-  <si>
-    <t>ContactStatus</t>
-  </si>
-  <si>
-    <t>Contact status</t>
-  </si>
-  <si>
-    <t>followUpStatus</t>
-  </si>
-  <si>
-    <t>FollowUpStatus</t>
-  </si>
-  <si>
-    <t>Follow-up status</t>
-  </si>
-  <si>
-    <t>&lt;ul&gt;&lt;li&gt;Under follow-up: The follow-up process is running.&lt;/li&gt;&lt;li&gt;Follow-up completed: The follow-up has been completed.&lt;/li&gt;&lt;li&gt;Follow-up canceled: The follow-up process has been canceled, e.g. because the person died or the contact became irrelevant.&lt;/li&gt;&lt;li&gt;Lost to follow-up: The follow-up process could not be continued, e.g. because the person could not be found.&lt;/li&gt;&lt;li&gt;No follow-up: No contact follow-up is being done.&lt;/li&gt;&lt;/ul&gt;</t>
-  </si>
-  <si>
-    <t>followUpComment</t>
-  </si>
-  <si>
-    <t>Follow-up status comment</t>
-  </si>
-  <si>
-    <t>followUpUntil</t>
-  </si>
-  <si>
-    <t>Follow-up until</t>
-  </si>
-  <si>
-    <t>overwriteFollowUpUntil</t>
-  </si>
-  <si>
-    <t>Overwrite follow-up until date</t>
-  </si>
-  <si>
     <t>contactOfficer</t>
   </si>
   <si>
     <t>Responsible contact officer</t>
   </si>
   <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Description of how contact took place</t>
-  </si>
-  <si>
-    <t>relationToCase</t>
-  </si>
-  <si>
-    <t>ContactRelation</t>
-  </si>
-  <si>
-    <t>Relationship with case</t>
-  </si>
-  <si>
-    <t>Select the person's relation to the case</t>
-  </si>
-  <si>
-    <t>relationDescription</t>
-  </si>
-  <si>
-    <t>Relationship description</t>
-  </si>
-  <si>
     <t>resultingCase</t>
   </si>
   <si>
@@ -3925,54 +3973,6 @@
     <t>Resulting case assigned by</t>
   </si>
   <si>
-    <t>highPriority</t>
-  </si>
-  <si>
-    <t>High priority contact</t>
-  </si>
-  <si>
-    <t>immunosuppressiveTherapyBasicDisease</t>
-  </si>
-  <si>
-    <t>Immunosuppressive therapy or basic disease is present</t>
-  </si>
-  <si>
-    <t>immunosuppressiveTherapyBasicDiseaseDetails</t>
-  </si>
-  <si>
-    <t>careForPeopleOver60</t>
-  </si>
-  <si>
-    <t>Is the person medically/nursingly active in the care of patients or people over 60 years of age?</t>
-  </si>
-  <si>
-    <t>caseIdExternalSystem</t>
-  </si>
-  <si>
-    <t>Case ID in external system</t>
-  </si>
-  <si>
-    <t>caseOrEventInformation</t>
-  </si>
-  <si>
-    <t>Case or event information</t>
-  </si>
-  <si>
-    <t>contactProximityDetails</t>
-  </si>
-  <si>
-    <t>Additional information on the type of contact</t>
-  </si>
-  <si>
-    <t>contactCategory</t>
-  </si>
-  <si>
-    <t>ContactCategory</t>
-  </si>
-  <si>
-    <t>Contact Category</t>
-  </si>
-  <si>
     <t>TOUCHED_FLUID</t>
   </si>
   <si>
@@ -4051,6 +4051,24 @@
     <t>Medical personnel at save proximity (&gt; 2 meter), without direct contact with secretions or excretions of the patient and without aerosol exposure</t>
   </si>
   <si>
+    <t>HIGH_RISK</t>
+  </si>
+  <si>
+    <t>High risk contact</t>
+  </si>
+  <si>
+    <t>LOW_RISK</t>
+  </si>
+  <si>
+    <t>Low risk contact</t>
+  </si>
+  <si>
+    <t>NO_RISK</t>
+  </si>
+  <si>
+    <t>No risk contact</t>
+  </si>
+  <si>
     <t>UNCONFIRMED</t>
   </si>
   <si>
@@ -4171,24 +4189,6 @@
     <t>Provided medical care for the case</t>
   </si>
   <si>
-    <t>HIGH_RISK</t>
-  </si>
-  <si>
-    <t>High risk contact</t>
-  </si>
-  <si>
-    <t>LOW_RISK</t>
-  </si>
-  <si>
-    <t>Low risk contact</t>
-  </si>
-  <si>
-    <t>NO_RISK</t>
-  </si>
-  <si>
-    <t>No risk contact</t>
-  </si>
-  <si>
     <t>Visited person</t>
   </si>
   <si>
@@ -5473,7 +5473,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.37.0-SNAPSHOT</t>
+    <t>1.38.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -6319,7 +6319,7 @@
 </file>
 
 <file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactClassification" displayName="ContactContactClassification" ref="A113:E116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactCategory" displayName="ContactContactCategory" ref="A113:E116">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6333,7 +6333,7 @@
 </file>
 
 <file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactContactStatus" displayName="ContactContactStatus" ref="A118:E121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactContactClassification" displayName="ContactContactClassification" ref="A118:E121">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6347,7 +6347,7 @@
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A123:E128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactContactStatus" displayName="ContactContactStatus" ref="A123:E126">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6361,7 +6361,7 @@
 </file>
 
 <file path=xl/tables/table58.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactContactRelation" displayName="ContactContactRelation" ref="A130:E135">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A128:E133">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6375,7 +6375,7 @@
 </file>
 
 <file path=xl/tables/table59.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A137:E140">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactContactRelation" displayName="ContactContactRelation" ref="A135:E140">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6403,7 +6403,7 @@
 </file>
 
 <file path=xl/tables/table60.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A142:E146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A142:E145">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6417,7 +6417,7 @@
 </file>
 
 <file path=xl/tables/table61.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ContactContactCategory" displayName="ContactContactCategory" ref="A148:E151">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A147:E151">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -10546,17 +10546,15 @@
         <v>1250</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>39</v>
+        <v>1251</v>
       </c>
       <c r="C2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
+      <c r="E2"/>
       <c r="G2" s="11" t="s">
         <v>12</v>
       </c>
@@ -10564,20 +10562,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>363</v>
+        <v>1253</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>364</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>365</v>
+        <v>1254</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
+      <c r="E3"/>
       <c r="G3" s="11" t="s">
         <v>12</v>
       </c>
@@ -10585,13 +10581,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>439</v>
+        <v>1255</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>1256</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>18</v>
@@ -10604,13 +10600,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>442</v>
+        <v>343</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>1257</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>18</v>
@@ -10623,13 +10619,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>445</v>
+        <v>345</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>346</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>18</v>
@@ -10642,18 +10638,20 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>312</v>
+        <v>1258</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>1252</v>
+        <v>1259</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E7"/>
+        <v>18</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
       <c r="G7" s="11" t="s">
         <v>12</v>
       </c>
@@ -10661,18 +10659,20 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>314</v>
+        <v>363</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>46</v>
+        <v>364</v>
       </c>
       <c r="C8" t="s">
-        <v>1254</v>
+        <v>365</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E8"/>
+        <v>18</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
       <c r="G8" s="11" t="s">
         <v>12</v>
       </c>
@@ -10680,20 +10680,18 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>356</v>
+        <v>439</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>357</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1255</v>
+        <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
+      <c r="E9"/>
       <c r="G9" s="11" t="s">
         <v>12</v>
       </c>
@@ -10701,20 +10699,18 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1256</v>
+        <v>442</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1257</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1258</v>
+        <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E10" t="b">
-        <v>1</v>
-      </c>
+      <c r="E10"/>
       <c r="G10" s="11" t="s">
         <v>12</v>
       </c>
@@ -10722,13 +10718,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>343</v>
+        <v>445</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>1259</v>
+        <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>18</v>
@@ -10741,16 +10737,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>345</v>
+        <v>312</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>346</v>
+        <v>1260</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>18</v>
+        <v>1261</v>
       </c>
       <c r="E12"/>
       <c r="G12" s="11" t="s">
@@ -10760,16 +10756,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1260</v>
+        <v>314</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>1261</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>18</v>
       </c>
       <c r="E13"/>
       <c r="G13" s="11" t="s">
@@ -10779,18 +10775,20 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1263</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
         <v>1264</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1265</v>
-      </c>
-      <c r="E14"/>
+        <v>18</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
       <c r="G14" s="11" t="s">
         <v>12</v>
       </c>
@@ -10798,16 +10796,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>1266</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="C15" t="s">
         <v>1267</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="11" t="s">
         <v>1268</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>18</v>
       </c>
       <c r="E15"/>
       <c r="G15" s="11" t="s">
@@ -10820,10 +10818,10 @@
         <v>1269</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
         <v>1270</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1271</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>18</v>
@@ -10836,16 +10834,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>1272</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" t="s">
         <v>1273</v>
       </c>
-      <c r="C17" t="s">
-        <v>1274</v>
-      </c>
       <c r="D17" s="11" t="s">
-        <v>1275</v>
+        <v>18</v>
       </c>
       <c r="E17"/>
       <c r="G17" s="11" t="s">
@@ -10855,13 +10853,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C18" t="s">
         <v>1276</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1277</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>18</v>
@@ -10874,10 +10872,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>1278</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>1279</v>
@@ -10896,13 +10894,13 @@
         <v>1280</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>480</v>
+        <v>1281</v>
       </c>
       <c r="C20" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>18</v>
+        <v>1283</v>
       </c>
       <c r="E20"/>
       <c r="G20" s="11" t="s">
@@ -10912,13 +10910,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>364</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>18</v>
@@ -10931,13 +10929,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>18</v>
@@ -10950,16 +10948,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1287</v>
+        <v>480</v>
       </c>
       <c r="C23" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>1289</v>
+        <v>18</v>
       </c>
       <c r="E23"/>
       <c r="G23" s="11" t="s">
@@ -10988,16 +10986,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>477</v>
+        <v>1292</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>9</v>
+        <v>1293</v>
       </c>
       <c r="C25" t="s">
-        <v>478</v>
+        <v>1294</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>18</v>
+        <v>1295</v>
       </c>
       <c r="E25"/>
       <c r="G25" s="11" t="s">
@@ -11007,13 +11005,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1292</v>
+        <v>1296</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>1257</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>18</v>
@@ -11026,13 +11024,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1294</v>
+        <v>477</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>364</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>1295</v>
+        <v>478</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>18</v>
@@ -11045,13 +11043,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>480</v>
       </c>
       <c r="C28" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>18</v>
@@ -11064,13 +11062,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>393</v>
       </c>
       <c r="C29" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>18</v>
@@ -11083,7 +11081,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>9</v>
@@ -11102,13 +11100,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>393</v>
       </c>
       <c r="C31" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>18</v>
@@ -11178,18 +11176,20 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1303</v>
+        <v>356</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="C35" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E35"/>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
       <c r="G35" s="11" t="s">
         <v>12</v>
       </c>
@@ -11197,13 +11197,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>9</v>
+        <v>364</v>
       </c>
       <c r="C36" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>18</v>
@@ -11216,13 +11216,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>9</v>
+        <v>1251</v>
       </c>
       <c r="C37" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>18</v>
@@ -11235,10 +11235,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>1310</v>
+        <v>364</v>
       </c>
       <c r="C38" t="s">
         <v>1311</v>
@@ -12130,7 +12130,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="B99" t="s">
         <v>1312</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="B114" t="s">
         <v>1338</v>
@@ -12356,13 +12356,13 @@
         <v>18</v>
       </c>
       <c r="E114" t="s">
-        <v>1340</v>
+        <v>18</v>
       </c>
     </row>
     <row r="115">
       <c r="A115"/>
       <c r="B115" t="s">
-        <v>513</v>
+        <v>1340</v>
       </c>
       <c r="C115" t="s">
         <v>1341</v>
@@ -12371,7 +12371,7 @@
         <v>18</v>
       </c>
       <c r="E115" t="s">
-        <v>515</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
@@ -12386,7 +12386,7 @@
         <v>18</v>
       </c>
       <c r="E116" t="s">
-        <v>1344</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118">
@@ -12408,49 +12408,49 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>1270</v>
+        <v>1275</v>
       </c>
       <c r="B119" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C119" t="s">
         <v>1345</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
+        <v>18</v>
+      </c>
+      <c r="E119" t="s">
         <v>1346</v>
-      </c>
-      <c r="D119" t="s">
-        <v>18</v>
-      </c>
-      <c r="E119" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
+        <v>513</v>
+      </c>
+      <c r="C120" t="s">
         <v>1347</v>
       </c>
-      <c r="C120" t="s">
-        <v>1348</v>
-      </c>
       <c r="D120" t="s">
         <v>18</v>
       </c>
       <c r="E120" t="s">
-        <v>18</v>
+        <v>515</v>
       </c>
     </row>
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C121" t="s">
         <v>1349</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
+        <v>18</v>
+      </c>
+      <c r="E121" t="s">
         <v>1350</v>
-      </c>
-      <c r="D121" t="s">
-        <v>18</v>
-      </c>
-      <c r="E121" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="123">
@@ -12472,7 +12472,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="B124" t="s">
         <v>1351</v>
@@ -12481,192 +12481,192 @@
         <v>1352</v>
       </c>
       <c r="D124" t="s">
-        <v>1353</v>
+        <v>18</v>
       </c>
       <c r="E124" t="s">
-        <v>1354</v>
+        <v>18</v>
       </c>
     </row>
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C125" t="s">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="D125" t="s">
-        <v>1357</v>
+        <v>18</v>
       </c>
       <c r="E125" t="s">
-        <v>1358</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C126" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D126" t="s">
+        <v>18</v>
+      </c>
+      <c r="E126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>1</v>
+      </c>
+      <c r="B128" t="s">
+        <v>123</v>
+      </c>
+      <c r="C128" t="s">
+        <v>2</v>
+      </c>
+      <c r="D128" t="s">
+        <v>3</v>
+      </c>
+      <c r="E128" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B129" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D129" t="s">
         <v>1359</v>
       </c>
-      <c r="C126" t="s">
+      <c r="E129" t="s">
         <v>1360</v>
       </c>
-      <c r="D126" t="s">
+    </row>
+    <row r="130">
+      <c r="A130"/>
+      <c r="B130" t="s">
         <v>1361</v>
       </c>
-      <c r="E126" t="s">
+      <c r="C130" t="s">
         <v>1362</v>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127"/>
-      <c r="B127" t="s">
+      <c r="D130" t="s">
         <v>1363</v>
       </c>
-      <c r="C127" t="s">
+      <c r="E130" t="s">
         <v>1364</v>
       </c>
-      <c r="D127" t="s">
+    </row>
+    <row r="131">
+      <c r="A131"/>
+      <c r="B131" t="s">
         <v>1365</v>
       </c>
-      <c r="E127" t="s">
+      <c r="C131" t="s">
         <v>1366</v>
       </c>
-    </row>
-    <row r="128">
-      <c r="A128"/>
-      <c r="B128" t="s">
+      <c r="D131" t="s">
         <v>1367</v>
       </c>
-      <c r="C128" t="s">
+      <c r="E131" t="s">
         <v>1368</v>
-      </c>
-      <c r="D128" t="s">
-        <v>1369</v>
-      </c>
-      <c r="E128" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>1</v>
-      </c>
-      <c r="B130" t="s">
-        <v>123</v>
-      </c>
-      <c r="C130" t="s">
-        <v>2</v>
-      </c>
-      <c r="D130" t="s">
-        <v>3</v>
-      </c>
-      <c r="E130" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B131" t="s">
-        <v>1370</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D131" t="s">
-        <v>18</v>
-      </c>
-      <c r="E131" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="132">
       <c r="A132"/>
       <c r="B132" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E132" t="s">
         <v>1372</v>
-      </c>
-      <c r="C132" t="s">
-        <v>1373</v>
-      </c>
-      <c r="D132" t="s">
-        <v>18</v>
-      </c>
-      <c r="E132" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="133">
       <c r="A133"/>
       <c r="B133" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C133" t="s">
         <v>1374</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
         <v>1375</v>
       </c>
-      <c r="D133" t="s">
-        <v>18</v>
-      </c>
       <c r="E133" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134"/>
-      <c r="B134" t="s">
+    <row r="135">
+      <c r="A135" t="s">
+        <v>1</v>
+      </c>
+      <c r="B135" t="s">
+        <v>123</v>
+      </c>
+      <c r="C135" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135" t="s">
+        <v>3</v>
+      </c>
+      <c r="E135" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B136" t="s">
         <v>1376</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C136" t="s">
         <v>1377</v>
       </c>
-      <c r="D134" t="s">
-        <v>18</v>
-      </c>
-      <c r="E134" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135"/>
-      <c r="B135" t="s">
-        <v>260</v>
-      </c>
-      <c r="C135" t="s">
-        <v>262</v>
-      </c>
-      <c r="D135" t="s">
-        <v>18</v>
-      </c>
-      <c r="E135" t="s">
+      <c r="D136" t="s">
+        <v>18</v>
+      </c>
+      <c r="E136" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
-        <v>1</v>
-      </c>
+      <c r="A137"/>
       <c r="B137" t="s">
-        <v>123</v>
+        <v>1378</v>
       </c>
       <c r="C137" t="s">
-        <v>2</v>
+        <v>1379</v>
       </c>
       <c r="D137" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E137" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
-        <v>393</v>
-      </c>
+      <c r="A138"/>
       <c r="B138" t="s">
-        <v>534</v>
+        <v>1380</v>
       </c>
       <c r="C138" t="s">
-        <v>535</v>
+        <v>1381</v>
       </c>
       <c r="D138" t="s">
         <v>18</v>
@@ -12678,10 +12678,10 @@
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
-        <v>536</v>
+        <v>1382</v>
       </c>
       <c r="C139" t="s">
-        <v>537</v>
+        <v>1383</v>
       </c>
       <c r="D139" t="s">
         <v>18</v>
@@ -12693,10 +12693,10 @@
     <row r="140">
       <c r="A140"/>
       <c r="B140" t="s">
-        <v>341</v>
+        <v>260</v>
       </c>
       <c r="C140" t="s">
-        <v>342</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
         <v>18</v>
@@ -12724,13 +12724,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>483</v>
+        <v>393</v>
       </c>
       <c r="B143" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="C143" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="D143" t="s">
         <v>18</v>
@@ -12742,10 +12742,10 @@
     <row r="144">
       <c r="A144"/>
       <c r="B144" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="C144" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="D144" t="s">
         <v>18</v>
@@ -12757,10 +12757,10 @@
     <row r="145">
       <c r="A145"/>
       <c r="B145" t="s">
-        <v>274</v>
+        <v>341</v>
       </c>
       <c r="C145" t="s">
-        <v>564</v>
+        <v>342</v>
       </c>
       <c r="D145" t="s">
         <v>18</v>
@@ -12769,47 +12769,47 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146"/>
-      <c r="B146" t="s">
-        <v>341</v>
-      </c>
-      <c r="C146" t="s">
-        <v>342</v>
-      </c>
-      <c r="D146" t="s">
-        <v>18</v>
-      </c>
-      <c r="E146" t="s">
-        <v>18</v>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>1</v>
+      </c>
+      <c r="B147" t="s">
+        <v>123</v>
+      </c>
+      <c r="C147" t="s">
+        <v>2</v>
+      </c>
+      <c r="D147" t="s">
+        <v>3</v>
+      </c>
+      <c r="E147" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>1</v>
+        <v>483</v>
       </c>
       <c r="B148" t="s">
-        <v>123</v>
+        <v>560</v>
       </c>
       <c r="C148" t="s">
-        <v>2</v>
+        <v>561</v>
       </c>
       <c r="D148" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E148" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
-        <v>1310</v>
-      </c>
+      <c r="A149"/>
       <c r="B149" t="s">
-        <v>1378</v>
+        <v>562</v>
       </c>
       <c r="C149" t="s">
-        <v>1379</v>
+        <v>563</v>
       </c>
       <c r="D149" t="s">
         <v>18</v>
@@ -12821,10 +12821,10 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>1380</v>
+        <v>274</v>
       </c>
       <c r="C150" t="s">
-        <v>1381</v>
+        <v>564</v>
       </c>
       <c r="D150" t="s">
         <v>18</v>
@@ -12836,10 +12836,10 @@
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
-        <v>1382</v>
+        <v>341</v>
       </c>
       <c r="C151" t="s">
-        <v>1383</v>
+        <v>342</v>
       </c>
       <c r="D151" t="s">
         <v>18</v>
@@ -14083,7 +14083,7 @@
         <v>1402</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="C2" t="s">
         <v>1403</v>
@@ -14141,7 +14141,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>39</v>
@@ -17422,10 +17422,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="C3" t="s">
         <v>1403</v>
@@ -18421,7 +18421,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1250</v>
+        <v>1258</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>39</v>
@@ -19870,10 +19870,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1292</v>
+        <v>1308</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6519" uniqueCount="1813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6542" uniqueCount="1824">
   <si>
     <t>Field</t>
   </si>
@@ -1021,7 +1021,7 @@
     <t>GPS latitude</t>
   </si>
   <si>
-    <t>GPS latitude is the the north/south angular location in degrees</t>
+    <t>GPS latitude is the north/south angular location in degrees</t>
   </si>
   <si>
     <t>longitude</t>
@@ -3973,6 +3973,21 @@
     <t>Resulting case assigned by</t>
   </si>
   <si>
+    <t>quarantineOrderMeans</t>
+  </si>
+  <si>
+    <t>OrderMeans</t>
+  </si>
+  <si>
+    <t>Means of quarantine order</t>
+  </si>
+  <si>
+    <t>quarantineHelpNeeded</t>
+  </si>
+  <si>
+    <t>Help needed in quarantine?</t>
+  </si>
+  <si>
     <t>TOUCHED_FLUID</t>
   </si>
   <si>
@@ -4189,6 +4204,18 @@
     <t>Provided medical care for the case</t>
   </si>
   <si>
+    <t>VERBALLY</t>
+  </si>
+  <si>
+    <t>Verbally</t>
+  </si>
+  <si>
+    <t>OFFICIAL_DOCUMENT</t>
+  </si>
+  <si>
+    <t>Official document</t>
+  </si>
+  <si>
     <t>Visited person</t>
   </si>
   <si>
@@ -5468,6 +5495,12 @@
   </si>
   <si>
     <t>Deutsch</t>
+  </si>
+  <si>
+    <t>ES_EC</t>
+  </si>
+  <si>
+    <t>Español (Ecuador)</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -6274,7 +6307,7 @@
 </file>
 
 <file path=xl/tables/table52.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="Contact" displayName="Contact" ref="A1:H38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="52" name="Contact" displayName="Contact" ref="A1:H39">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6291,7 +6324,7 @@
 </file>
 
 <file path=xl/tables/table53.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="ContactDisease" displayName="ContactDisease" ref="A40:E96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="53" name="ContactDisease" displayName="ContactDisease" ref="A41:E97">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6305,7 +6338,7 @@
 </file>
 
 <file path=xl/tables/table54.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="ContactContactProximity" displayName="ContactContactProximity" ref="A98:E111">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="54" name="ContactContactProximity" displayName="ContactContactProximity" ref="A99:E112">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6319,7 +6352,7 @@
 </file>
 
 <file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactCategory" displayName="ContactContactCategory" ref="A113:E116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactCategory" displayName="ContactContactCategory" ref="A114:E117">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6333,7 +6366,7 @@
 </file>
 
 <file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactContactClassification" displayName="ContactContactClassification" ref="A118:E121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactContactClassification" displayName="ContactContactClassification" ref="A119:E122">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6347,7 +6380,7 @@
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactContactStatus" displayName="ContactContactStatus" ref="A123:E126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactContactStatus" displayName="ContactContactStatus" ref="A124:E127">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6361,7 +6394,7 @@
 </file>
 
 <file path=xl/tables/table58.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A128:E133">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A129:E134">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6375,7 +6408,7 @@
 </file>
 
 <file path=xl/tables/table59.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactContactRelation" displayName="ContactContactRelation" ref="A135:E140">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactContactRelation" displayName="ContactContactRelation" ref="A136:E141">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6403,7 +6436,7 @@
 </file>
 
 <file path=xl/tables/table60.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A142:E145">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A143:E146">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6417,7 +6450,7 @@
 </file>
 
 <file path=xl/tables/table61.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A147:E151">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A148:E152">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6431,7 +6464,21 @@
 </file>
 
 <file path=xl/tables/table62.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="Visit" displayName="Visit" ref="A1:H11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="ContactOrderMeans" displayName="ContactOrderMeans" ref="A154:E156">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table63.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="63" name="Visit" displayName="Visit" ref="A1:H11">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6447,22 +6494,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table63.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="63" name="VisitDisease" displayName="VisitDisease" ref="A13:E69">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
 <file path=xl/tables/table64.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="VisitVisitStatus" displayName="VisitVisitStatus" ref="A71:E74">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="VisitDisease" displayName="VisitDisease" ref="A13:E69">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6476,7 +6509,21 @@
 </file>
 
 <file path=xl/tables/table65.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="Sample" displayName="Sample" ref="A1:H31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="VisitVisitStatus" displayName="VisitVisitStatus" ref="A71:E74">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table66.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="66" name="Sample" displayName="Sample" ref="A1:H31">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6492,22 +6539,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table66.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="66" name="SampleSampleMaterial" displayName="SampleSampleMaterial" ref="A33:E53">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
 <file path=xl/tables/table67.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="67" name="SampleSamplePurpose" displayName="SampleSamplePurpose" ref="A55:E57">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="67" name="SampleSampleMaterial" displayName="SampleSampleMaterial" ref="A33:E53">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6521,7 +6554,7 @@
 </file>
 
 <file path=xl/tables/table68.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="68" name="SampleSpecimenCondition" displayName="SampleSpecimenCondition" ref="A59:E61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="68" name="SampleSamplePurpose" displayName="SampleSamplePurpose" ref="A55:E57">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6535,7 +6568,7 @@
 </file>
 
 <file path=xl/tables/table69.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="69" name="SampleSampleSource" displayName="SampleSampleSource" ref="A63:E66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="69" name="SampleSpecimenCondition" displayName="SampleSpecimenCondition" ref="A59:E61">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6563,7 +6596,7 @@
 </file>
 
 <file path=xl/tables/table70.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="70" name="SamplePathogenTestResultType" displayName="SamplePathogenTestResultType" ref="A68:E72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="70" name="SampleSampleSource" displayName="SampleSampleSource" ref="A63:E66">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6577,7 +6610,21 @@
 </file>
 
 <file path=xl/tables/table71.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="71" name="Pathogen_test" displayName="Pathogen_test" ref="A1:H16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="71" name="SamplePathogenTestResultType" displayName="SamplePathogenTestResultType" ref="A68:E72">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table72.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="72" name="Pathogen_test" displayName="Pathogen_test" ref="A1:H16">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6593,22 +6640,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table72.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="72" name="Pathogen_testDisease" displayName="Pathogen_testDisease" ref="A18:E74">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
 <file path=xl/tables/table73.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="73" name="Pathogen_testPathogenTestType" displayName="Pathogen_testPathogenTestType" ref="A76:E95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="73" name="Pathogen_testDisease" displayName="Pathogen_testDisease" ref="A18:E74">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6622,7 +6655,7 @@
 </file>
 
 <file path=xl/tables/table74.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="74" name="Pathogen_testPathogenTestResultType" displayName="Pathogen_testPathogenTestResultType" ref="A97:E101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="74" name="Pathogen_testPathogenTestType" displayName="Pathogen_testPathogenTestType" ref="A76:E95">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6636,7 +6669,21 @@
 </file>
 
 <file path=xl/tables/table75.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="75" name="Additional_test" displayName="Additional_test" ref="A1:H23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="75" name="Pathogen_testPathogenTestResultType" displayName="Pathogen_testPathogenTestResultType" ref="A97:E101">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table76.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="76" name="Additional_test" displayName="Additional_test" ref="A1:H23">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6652,8 +6699,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table76.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="76" name="Additional_testSimpleTestResultType" displayName="Additional_testSimpleTestResultType" ref="A25:E28">
+<file path=xl/tables/table77.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="77" name="Additional_testSimpleTestResultType" displayName="Additional_testSimpleTestResultType" ref="A25:E28">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6666,8 +6713,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table77.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="77" name="Task" displayName="Task" ref="A1:H19">
+<file path=xl/tables/table78.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="78" name="Task" displayName="Task" ref="A1:H19">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6683,22 +6730,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table78.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="78" name="TaskTaskContext" displayName="TaskTaskContext" ref="A21:E25">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
 <file path=xl/tables/table79.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="79" name="TaskTaskType" displayName="TaskTaskType" ref="A27:E48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="79" name="TaskTaskContext" displayName="TaskTaskContext" ref="A21:E25">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6726,7 +6759,7 @@
 </file>
 
 <file path=xl/tables/table80.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="80" name="TaskTaskPriority" displayName="TaskTaskPriority" ref="A50:E53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="80" name="TaskTaskType" displayName="TaskTaskType" ref="A27:E48">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6740,7 +6773,7 @@
 </file>
 
 <file path=xl/tables/table81.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="81" name="TaskTaskStatus" displayName="TaskTaskStatus" ref="A55:E59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="81" name="TaskTaskPriority" displayName="TaskTaskPriority" ref="A50:E53">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6754,7 +6787,21 @@
 </file>
 
 <file path=xl/tables/table82.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="82" name="Event" displayName="Event" ref="A1:H19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="82" name="TaskTaskStatus" displayName="TaskTaskStatus" ref="A55:E59">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table83.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="83" name="Event" displayName="Event" ref="A1:H19">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6770,22 +6817,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table83.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="83" name="EventEventStatus" displayName="EventEventStatus" ref="A21:E24">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
 <file path=xl/tables/table84.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="84" name="EventTypeOfPlace" displayName="EventTypeOfPlace" ref="A26:E33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="84" name="EventEventStatus" displayName="EventEventStatus" ref="A21:E24">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6799,7 +6832,7 @@
 </file>
 
 <file path=xl/tables/table85.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="85" name="EventDisease" displayName="EventDisease" ref="A35:E91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="85" name="EventTypeOfPlace" displayName="EventTypeOfPlace" ref="A26:E33">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6813,24 +6846,21 @@
 </file>
 
 <file path=xl/tables/table86.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="86" name="Person_involved" displayName="Person_involved" ref="A1:H5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="86" name="EventDisease" displayName="EventDisease" ref="A35:E91">
   <autoFilter/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Type"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
     <tableColumn id="3" name="Caption"/>
     <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Required"/>
-    <tableColumn id="6" name="New disease"/>
-    <tableColumn id="7" name="Diseases"/>
-    <tableColumn id="8" name="Outbreaks"/>
+    <tableColumn id="5" name="Short"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
 <file path=xl/tables/table87.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="87" name="Facility" displayName="Facility" ref="A1:H12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="87" name="Person_involved" displayName="Person_involved" ref="A1:H5">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6847,21 +6877,7 @@
 </file>
 
 <file path=xl/tables/table88.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="88" name="FacilityFacilityType" displayName="FacilityFacilityType" ref="A14:E18">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table89.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="89" name="Region" displayName="Region" ref="A1:H6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="88" name="Facility" displayName="Facility" ref="A1:H12">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6874,6 +6890,20 @@
     <tableColumn id="8" name="Outbreaks"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table89.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="89" name="FacilityFacilityType" displayName="FacilityFacilityType" ref="A14:E18">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
@@ -6892,7 +6922,7 @@
 </file>
 
 <file path=xl/tables/table90.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="90" name="District" displayName="District" ref="A1:H7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="90" name="Region" displayName="Region" ref="A1:H6">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6909,7 +6939,7 @@
 </file>
 
 <file path=xl/tables/table91.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="91" name="Community" displayName="Community" ref="A1:H6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="91" name="District" displayName="District" ref="A1:H7">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6926,7 +6956,7 @@
 </file>
 
 <file path=xl/tables/table92.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="92" name="User" displayName="User" ref="A1:H18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="92" name="Community" displayName="Community" ref="A1:H6">
   <autoFilter/>
   <tableColumns count="8">
     <tableColumn id="1" name="Field"/>
@@ -6943,7 +6973,24 @@
 </file>
 
 <file path=xl/tables/table93.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="93" name="UserDisease" displayName="UserDisease" ref="A20:E76">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="93" name="User" displayName="User" ref="A1:H18">
+  <autoFilter/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Type"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Required"/>
+    <tableColumn id="6" name="New disease"/>
+    <tableColumn id="7" name="Diseases"/>
+    <tableColumn id="8" name="Outbreaks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table94.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="94" name="UserDisease" displayName="UserDisease" ref="A20:E76">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6956,8 +7003,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table94.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="94" name="UserLanguage" displayName="UserLanguage" ref="A78:E83">
+<file path=xl/tables/table95.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="95" name="UserLanguage" displayName="UserLanguage" ref="A78:E84">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -10502,7 +10549,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I151"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -11157,18 +11204,20 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>487</v>
+        <v>356</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>39</v>
+        <v>357</v>
       </c>
       <c r="C34" t="s">
-        <v>488</v>
+        <v>1305</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E34"/>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
       <c r="G34" s="11" t="s">
         <v>12</v>
       </c>
@@ -11176,20 +11225,18 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>356</v>
+        <v>1306</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="C35" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
+      <c r="E35"/>
       <c r="G35" s="11" t="s">
         <v>12</v>
       </c>
@@ -11197,13 +11244,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>364</v>
+        <v>1251</v>
       </c>
       <c r="C36" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>18</v>
@@ -11216,13 +11263,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>1251</v>
+        <v>364</v>
       </c>
       <c r="C37" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>18</v>
@@ -11235,13 +11282,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>364</v>
+        <v>1313</v>
       </c>
       <c r="C38" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>18</v>
@@ -11252,137 +11299,141 @@
       </c>
       <c r="H38"/>
     </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D40" t="s">
-        <v>3</v>
-      </c>
-      <c r="E40" t="s">
-        <v>124</v>
-      </c>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39"/>
+      <c r="G39" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H39"/>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
         <v>71</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>145</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>146</v>
       </c>
-      <c r="D41" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" t="s">
+      <c r="D42" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s">
         <v>145</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42"/>
-      <c r="B42" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" t="s">
-        <v>18</v>
-      </c>
-      <c r="E42" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C43" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
       </c>
       <c r="E43" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C44" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
       </c>
       <c r="E44" t="s">
-        <v>153</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C45" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
       </c>
       <c r="E45" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C46" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
       </c>
       <c r="E46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C47" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
       </c>
       <c r="E47" t="s">
-        <v>18</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -11394,10 +11445,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C49" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -11409,10 +11460,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C50" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -11424,85 +11475,85 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
       </c>
       <c r="E51" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C52" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
       </c>
       <c r="E52" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C53" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
       </c>
       <c r="E53" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
       </c>
       <c r="E54" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C55" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C56" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -11514,40 +11565,40 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C57" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>184</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C58" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C59" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -11559,10 +11610,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C60" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -11574,10 +11625,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C61" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -11589,10 +11640,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C62" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -11604,10 +11655,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -11619,10 +11670,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C64" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -11634,10 +11685,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C65" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -11649,10 +11700,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C66" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -11664,10 +11715,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C67" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -11679,10 +11730,10 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C68" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -11694,10 +11745,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C69" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -11709,10 +11760,10 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C70" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -11724,10 +11775,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C71" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -11739,10 +11790,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C72" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -11754,10 +11805,10 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C73" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -11769,10 +11820,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C74" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -11784,10 +11835,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C75" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -11799,10 +11850,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C76" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -11814,10 +11865,10 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C77" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -11829,10 +11880,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C78" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -11844,10 +11895,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C79" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -11859,10 +11910,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C80" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -11874,10 +11925,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C81" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -11889,10 +11940,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C82" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -11904,10 +11955,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C83" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -11919,10 +11970,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C84" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -11934,10 +11985,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C85" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -11949,10 +12000,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C86" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -11964,10 +12015,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C87" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -11979,55 +12030,55 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C88" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
       </c>
       <c r="E88" t="s">
-        <v>246</v>
+        <v>18</v>
       </c>
     </row>
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C89" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
       </c>
       <c r="E89" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C90" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
       </c>
       <c r="E90" t="s">
-        <v>18</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C91" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -12039,10 +12090,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C92" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -12054,10 +12105,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C93" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -12069,10 +12120,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C94" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -12084,74 +12135,74 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C95" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>262</v>
+        <v>18</v>
       </c>
     </row>
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
+        <v>260</v>
+      </c>
+      <c r="C96" t="s">
+        <v>261</v>
+      </c>
+      <c r="D96" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97"/>
+      <c r="B97" t="s">
         <v>263</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C97" t="s">
         <v>264</v>
       </c>
-      <c r="D96" t="s">
-        <v>18</v>
-      </c>
-      <c r="E96" t="s">
+      <c r="D97" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
         <v>265</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>1</v>
-      </c>
-      <c r="B98" t="s">
-        <v>123</v>
-      </c>
-      <c r="C98" t="s">
-        <v>2</v>
-      </c>
-      <c r="D98" t="s">
-        <v>3</v>
-      </c>
-      <c r="E98" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
+        <v>1</v>
+      </c>
+      <c r="B99" t="s">
+        <v>123</v>
+      </c>
+      <c r="C99" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>3</v>
+      </c>
+      <c r="E99" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
         <v>1266</v>
       </c>
-      <c r="B99" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1313</v>
-      </c>
-      <c r="D99" t="s">
-        <v>18</v>
-      </c>
-      <c r="E99" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100"/>
       <c r="B100" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
       <c r="C100" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -12163,10 +12214,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="C101" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -12178,10 +12229,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="C102" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -12193,10 +12244,10 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="C103" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="D103" t="s">
         <v>18</v>
@@ -12208,10 +12259,10 @@
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="C104" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
@@ -12223,10 +12274,10 @@
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="C105" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
@@ -12238,10 +12289,10 @@
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="C106" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
@@ -12253,10 +12304,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="C107" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -12268,10 +12319,10 @@
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="C108" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -12283,10 +12334,10 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="C109" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -12298,10 +12349,10 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="C110" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
@@ -12313,10 +12364,10 @@
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="C111" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -12325,47 +12376,47 @@
         <v>18</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>1</v>
-      </c>
-      <c r="B113" t="s">
-        <v>123</v>
-      </c>
-      <c r="C113" t="s">
-        <v>2</v>
-      </c>
-      <c r="D113" t="s">
-        <v>3</v>
-      </c>
-      <c r="E113" t="s">
-        <v>124</v>
+    <row r="112">
+      <c r="A112"/>
+      <c r="B112" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D112" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>123</v>
+      </c>
+      <c r="C114" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114" t="s">
+        <v>3</v>
+      </c>
+      <c r="E114" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
         <v>1272</v>
       </c>
-      <c r="B114" t="s">
-        <v>1338</v>
-      </c>
-      <c r="C114" t="s">
-        <v>1339</v>
-      </c>
-      <c r="D114" t="s">
-        <v>18</v>
-      </c>
-      <c r="E114" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115"/>
       <c r="B115" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="C115" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="D115" t="s">
         <v>18</v>
@@ -12377,10 +12428,10 @@
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="C116" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
@@ -12389,111 +12440,111 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>1</v>
-      </c>
-      <c r="B118" t="s">
-        <v>123</v>
-      </c>
-      <c r="C118" t="s">
-        <v>2</v>
-      </c>
-      <c r="D118" t="s">
-        <v>3</v>
-      </c>
-      <c r="E118" t="s">
-        <v>124</v>
+    <row r="117">
+      <c r="A117"/>
+      <c r="B117" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C117" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D117" t="s">
+        <v>18</v>
+      </c>
+      <c r="E117" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>1</v>
+      </c>
+      <c r="B119" t="s">
+        <v>123</v>
+      </c>
+      <c r="C119" t="s">
+        <v>2</v>
+      </c>
+      <c r="D119" t="s">
+        <v>3</v>
+      </c>
+      <c r="E119" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
         <v>1275</v>
       </c>
-      <c r="B119" t="s">
-        <v>1344</v>
-      </c>
-      <c r="C119" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D119" t="s">
-        <v>18</v>
-      </c>
-      <c r="E119" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120"/>
       <c r="B120" t="s">
-        <v>513</v>
+        <v>1349</v>
       </c>
       <c r="C120" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
       <c r="D120" t="s">
         <v>18</v>
       </c>
       <c r="E120" t="s">
-        <v>515</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
-        <v>1348</v>
+        <v>513</v>
       </c>
       <c r="C121" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="D121" t="s">
         <v>18</v>
       </c>
       <c r="E121" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>1</v>
-      </c>
-      <c r="B123" t="s">
-        <v>123</v>
-      </c>
-      <c r="C123" t="s">
-        <v>2</v>
-      </c>
-      <c r="D123" t="s">
-        <v>3</v>
-      </c>
-      <c r="E123" t="s">
-        <v>124</v>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122"/>
+      <c r="B122" t="s">
+        <v>1353</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D122" t="s">
+        <v>18</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1355</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" t="s">
+        <v>123</v>
+      </c>
+      <c r="C124" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>3</v>
+      </c>
+      <c r="E124" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
         <v>1278</v>
       </c>
-      <c r="B124" t="s">
-        <v>1351</v>
-      </c>
-      <c r="C124" t="s">
-        <v>1352</v>
-      </c>
-      <c r="D124" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125"/>
       <c r="B125" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="C125" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="D125" t="s">
         <v>18</v>
@@ -12505,10 +12556,10 @@
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="C126" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="D126" t="s">
         <v>18</v>
@@ -12517,141 +12568,141 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>1</v>
-      </c>
-      <c r="B128" t="s">
-        <v>123</v>
-      </c>
-      <c r="C128" t="s">
-        <v>2</v>
-      </c>
-      <c r="D128" t="s">
-        <v>3</v>
-      </c>
-      <c r="E128" t="s">
-        <v>124</v>
+    <row r="127">
+      <c r="A127"/>
+      <c r="B127" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D127" t="s">
+        <v>18</v>
+      </c>
+      <c r="E127" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
+        <v>1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>123</v>
+      </c>
+      <c r="C129" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129" t="s">
+        <v>3</v>
+      </c>
+      <c r="E129" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
         <v>1281</v>
       </c>
-      <c r="B129" t="s">
-        <v>1357</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1358</v>
-      </c>
-      <c r="D129" t="s">
-        <v>1359</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130"/>
       <c r="B130" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="C130" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D130" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="E130" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="131">
       <c r="A131"/>
       <c r="B131" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C131" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D131" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="E131" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="132">
       <c r="A132"/>
       <c r="B132" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="C132" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="D132" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E132" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="133">
       <c r="A133"/>
       <c r="B133" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C133" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="D133" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E133" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>1</v>
-      </c>
-      <c r="B135" t="s">
-        <v>123</v>
-      </c>
-      <c r="C135" t="s">
-        <v>2</v>
-      </c>
-      <c r="D135" t="s">
-        <v>3</v>
-      </c>
-      <c r="E135" t="s">
-        <v>124</v>
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134"/>
+      <c r="B134" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1380</v>
+      </c>
+      <c r="E134" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
+        <v>1</v>
+      </c>
+      <c r="B136" t="s">
+        <v>123</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136" t="s">
+        <v>3</v>
+      </c>
+      <c r="E136" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
         <v>1293</v>
       </c>
-      <c r="B136" t="s">
-        <v>1376</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D136" t="s">
-        <v>18</v>
-      </c>
-      <c r="E136" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137"/>
       <c r="B137" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="C137" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="D137" t="s">
         <v>18</v>
@@ -12663,10 +12714,10 @@
     <row r="138">
       <c r="A138"/>
       <c r="B138" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="C138" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="D138" t="s">
         <v>18</v>
@@ -12678,10 +12729,10 @@
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
       <c r="C139" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="D139" t="s">
         <v>18</v>
@@ -12693,59 +12744,59 @@
     <row r="140">
       <c r="A140"/>
       <c r="B140" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C140" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D140" t="s">
+        <v>18</v>
+      </c>
+      <c r="E140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141"/>
+      <c r="B141" t="s">
         <v>260</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C141" t="s">
         <v>262</v>
       </c>
-      <c r="D140" t="s">
-        <v>18</v>
-      </c>
-      <c r="E140" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>1</v>
-      </c>
-      <c r="B142" t="s">
-        <v>123</v>
-      </c>
-      <c r="C142" t="s">
-        <v>2</v>
-      </c>
-      <c r="D142" t="s">
-        <v>3</v>
-      </c>
-      <c r="E142" t="s">
-        <v>124</v>
+      <c r="D141" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>123</v>
+      </c>
+      <c r="C143" t="s">
+        <v>2</v>
+      </c>
+      <c r="D143" t="s">
+        <v>3</v>
+      </c>
+      <c r="E143" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
         <v>393</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B144" t="s">
         <v>534</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C144" t="s">
         <v>535</v>
-      </c>
-      <c r="D143" t="s">
-        <v>18</v>
-      </c>
-      <c r="E143" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144"/>
-      <c r="B144" t="s">
-        <v>536</v>
-      </c>
-      <c r="C144" t="s">
-        <v>537</v>
       </c>
       <c r="D144" t="s">
         <v>18</v>
@@ -12757,59 +12808,59 @@
     <row r="145">
       <c r="A145"/>
       <c r="B145" t="s">
+        <v>536</v>
+      </c>
+      <c r="C145" t="s">
+        <v>537</v>
+      </c>
+      <c r="D145" t="s">
+        <v>18</v>
+      </c>
+      <c r="E145" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146"/>
+      <c r="B146" t="s">
         <v>341</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C146" t="s">
         <v>342</v>
       </c>
-      <c r="D145" t="s">
-        <v>18</v>
-      </c>
-      <c r="E145" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>1</v>
-      </c>
-      <c r="B147" t="s">
-        <v>123</v>
-      </c>
-      <c r="C147" t="s">
-        <v>2</v>
-      </c>
-      <c r="D147" t="s">
-        <v>3</v>
-      </c>
-      <c r="E147" t="s">
-        <v>124</v>
+      <c r="D146" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>123</v>
+      </c>
+      <c r="C148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E148" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
         <v>483</v>
       </c>
-      <c r="B148" t="s">
+      <c r="B149" t="s">
         <v>560</v>
       </c>
-      <c r="C148" t="s">
+      <c r="C149" t="s">
         <v>561</v>
-      </c>
-      <c r="D148" t="s">
-        <v>18</v>
-      </c>
-      <c r="E148" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149"/>
-      <c r="B149" t="s">
-        <v>562</v>
-      </c>
-      <c r="C149" t="s">
-        <v>563</v>
       </c>
       <c r="D149" t="s">
         <v>18</v>
@@ -12821,10 +12872,10 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>274</v>
+        <v>562</v>
       </c>
       <c r="C150" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D150" t="s">
         <v>18</v>
@@ -12836,15 +12887,79 @@
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
+        <v>274</v>
+      </c>
+      <c r="C151" t="s">
+        <v>564</v>
+      </c>
+      <c r="D151" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152"/>
+      <c r="B152" t="s">
         <v>341</v>
       </c>
-      <c r="C151" t="s">
+      <c r="C152" t="s">
         <v>342</v>
       </c>
-      <c r="D151" t="s">
-        <v>18</v>
-      </c>
-      <c r="E151" t="s">
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>123</v>
+      </c>
+      <c r="C154" t="s">
+        <v>2</v>
+      </c>
+      <c r="D154" t="s">
+        <v>3</v>
+      </c>
+      <c r="E154" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B155" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C155" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D155" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156"/>
+      <c r="B156" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C156" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D156" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" t="s">
         <v>18</v>
       </c>
     </row>
@@ -12861,6 +12976,7 @@
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
     <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12914,7 +13030,7 @@
         <v>357</v>
       </c>
       <c r="C2" t="s">
-        <v>1384</v>
+        <v>1393</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>18</v>
@@ -12957,7 +13073,7 @@
         <v>1245</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1385</v>
+        <v>1394</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -12969,13 +13085,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1386</v>
+        <v>1395</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>364</v>
       </c>
       <c r="C5" t="s">
-        <v>1387</v>
+        <v>1396</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>18</v>
@@ -12990,16 +13106,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1388</v>
+        <v>1397</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="C6" t="s">
-        <v>1390</v>
+        <v>1399</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1391</v>
+        <v>1400</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -13017,10 +13133,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>1392</v>
+        <v>1401</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1393</v>
+        <v>1402</v>
       </c>
       <c r="E7"/>
       <c r="G7" s="12" t="s">
@@ -13982,13 +14098,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1389</v>
+        <v>1398</v>
       </c>
       <c r="B72" t="s">
-        <v>1394</v>
+        <v>1403</v>
       </c>
       <c r="C72" t="s">
-        <v>1395</v>
+        <v>1404</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -14000,31 +14116,31 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>1396</v>
+        <v>1405</v>
       </c>
       <c r="C73" t="s">
-        <v>1397</v>
+        <v>1406</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>1398</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>1399</v>
+        <v>1408</v>
       </c>
       <c r="C74" t="s">
-        <v>1400</v>
+        <v>1409</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>1401</v>
+        <v>1410</v>
       </c>
     </row>
   </sheetData>
@@ -14080,13 +14196,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1402</v>
+        <v>1411</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>1251</v>
       </c>
       <c r="C2" t="s">
-        <v>1403</v>
+        <v>1412</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>18</v>
@@ -14101,13 +14217,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1404</v>
+        <v>1413</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1405</v>
+        <v>1414</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>18</v>
@@ -14120,16 +14236,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1406</v>
+        <v>1415</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>1407</v>
+        <v>1416</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>1408</v>
+        <v>1417</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -14240,13 +14356,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1409</v>
+        <v>1418</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>1410</v>
+        <v>1419</v>
       </c>
       <c r="C10" t="s">
-        <v>1411</v>
+        <v>1420</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>18</v>
@@ -14261,13 +14377,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1412</v>
+        <v>1421</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1413</v>
+        <v>1422</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>18</v>
@@ -14280,13 +14396,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1414</v>
+        <v>1423</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1415</v>
+        <v>1424</v>
       </c>
       <c r="C12" t="s">
-        <v>1416</v>
+        <v>1425</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>18</v>
@@ -14301,13 +14417,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1417</v>
+        <v>1426</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>1418</v>
+        <v>1427</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>18</v>
@@ -14322,13 +14438,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1419</v>
+        <v>1428</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>18</v>
@@ -14341,13 +14457,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1421</v>
+        <v>1430</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>1422</v>
+        <v>1431</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>18</v>
@@ -14360,13 +14476,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1423</v>
+        <v>1432</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1424</v>
+        <v>1433</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>18</v>
@@ -14379,13 +14495,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1425</v>
+        <v>1434</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>1426</v>
+        <v>1435</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>18</v>
@@ -14398,13 +14514,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1427</v>
+        <v>1436</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>1428</v>
+        <v>1437</v>
       </c>
       <c r="C18" t="s">
-        <v>1429</v>
+        <v>1438</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>18</v>
@@ -14417,13 +14533,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1430</v>
+        <v>1439</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>1431</v>
+        <v>1440</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>18</v>
@@ -14436,13 +14552,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1432</v>
+        <v>1441</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>1433</v>
+        <v>1442</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>18</v>
@@ -14455,13 +14571,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="C21" t="s">
-        <v>1436</v>
+        <v>1445</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>18</v>
@@ -14474,10 +14590,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1437</v>
+        <v>1446</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1438</v>
+        <v>1447</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
@@ -14493,13 +14609,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1439</v>
+        <v>1448</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C23" t="s">
-        <v>1440</v>
+        <v>1449</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>18</v>
@@ -14512,13 +14628,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1441</v>
+        <v>1450</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C24" t="s">
-        <v>1442</v>
+        <v>1451</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>18</v>
@@ -14531,13 +14647,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1443</v>
+        <v>1452</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1444</v>
+        <v>1453</v>
       </c>
       <c r="C25" t="s">
-        <v>1445</v>
+        <v>1454</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>18</v>
@@ -14550,13 +14666,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1446</v>
+        <v>1455</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C26" t="s">
-        <v>1447</v>
+        <v>1456</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>18</v>
@@ -14569,13 +14685,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1448</v>
+        <v>1457</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C27" t="s">
-        <v>1449</v>
+        <v>1458</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>18</v>
@@ -14588,11 +14704,11 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1450</v>
+        <v>1459</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" t="s">
-        <v>1451</v>
+        <v>1460</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>18</v>
@@ -14605,11 +14721,11 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1452</v>
+        <v>1461</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" t="s">
-        <v>1453</v>
+        <v>1462</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>18</v>
@@ -14622,13 +14738,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1454</v>
+        <v>1463</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>1455</v>
+        <v>1464</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>18</v>
@@ -14641,13 +14757,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1456</v>
+        <v>1465</v>
       </c>
       <c r="B31" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>1457</v>
+        <v>1466</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>18</v>
@@ -14677,13 +14793,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1410</v>
+        <v>1419</v>
       </c>
       <c r="B34" t="s">
-        <v>1458</v>
+        <v>1467</v>
       </c>
       <c r="C34" t="s">
-        <v>1459</v>
+        <v>1468</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -14695,10 +14811,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1460</v>
+        <v>1469</v>
       </c>
       <c r="C35" t="s">
-        <v>1461</v>
+        <v>1470</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -14710,10 +14826,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1462</v>
+        <v>1471</v>
       </c>
       <c r="C36" t="s">
-        <v>1463</v>
+        <v>1472</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -14725,10 +14841,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1464</v>
+        <v>1473</v>
       </c>
       <c r="C37" t="s">
-        <v>1465</v>
+        <v>1474</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -14740,10 +14856,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1466</v>
+        <v>1475</v>
       </c>
       <c r="C38" t="s">
-        <v>1467</v>
+        <v>1476</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -14755,10 +14871,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1468</v>
+        <v>1477</v>
       </c>
       <c r="C39" t="s">
-        <v>1469</v>
+        <v>1478</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -14770,10 +14886,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1470</v>
+        <v>1479</v>
       </c>
       <c r="C40" t="s">
-        <v>1471</v>
+        <v>1480</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -14785,10 +14901,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1472</v>
+        <v>1481</v>
       </c>
       <c r="C41" t="s">
-        <v>1473</v>
+        <v>1482</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -14800,10 +14916,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1474</v>
+        <v>1483</v>
       </c>
       <c r="C42" t="s">
-        <v>1475</v>
+        <v>1484</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -14815,10 +14931,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1476</v>
+        <v>1485</v>
       </c>
       <c r="C43" t="s">
-        <v>1477</v>
+        <v>1486</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -14830,10 +14946,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1478</v>
+        <v>1487</v>
       </c>
       <c r="C44" t="s">
-        <v>1479</v>
+        <v>1488</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -14845,10 +14961,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>1480</v>
+        <v>1489</v>
       </c>
       <c r="C45" t="s">
-        <v>1481</v>
+        <v>1490</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -14860,10 +14976,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1482</v>
+        <v>1491</v>
       </c>
       <c r="C46" t="s">
-        <v>1483</v>
+        <v>1492</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -14875,10 +14991,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1484</v>
+        <v>1493</v>
       </c>
       <c r="C47" t="s">
-        <v>1485</v>
+        <v>1494</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -14890,10 +15006,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1486</v>
+        <v>1495</v>
       </c>
       <c r="C48" t="s">
-        <v>1487</v>
+        <v>1496</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -14905,10 +15021,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>1488</v>
+        <v>1497</v>
       </c>
       <c r="C49" t="s">
-        <v>1489</v>
+        <v>1498</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -14920,10 +15036,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>1490</v>
+        <v>1499</v>
       </c>
       <c r="C50" t="s">
-        <v>1491</v>
+        <v>1500</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -14935,10 +15051,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>1492</v>
+        <v>1501</v>
       </c>
       <c r="C51" t="s">
-        <v>1493</v>
+        <v>1502</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -14950,10 +15066,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1494</v>
+        <v>1503</v>
       </c>
       <c r="C52" t="s">
-        <v>1495</v>
+        <v>1504</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -14996,13 +15112,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1415</v>
+        <v>1424</v>
       </c>
       <c r="B56" t="s">
-        <v>1496</v>
+        <v>1505</v>
       </c>
       <c r="C56" t="s">
-        <v>1497</v>
+        <v>1506</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -15014,10 +15130,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>1498</v>
+        <v>1507</v>
       </c>
       <c r="C57" t="s">
-        <v>1499</v>
+        <v>1508</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -15045,13 +15161,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1428</v>
+        <v>1437</v>
       </c>
       <c r="B60" t="s">
-        <v>1500</v>
+        <v>1509</v>
       </c>
       <c r="C60" t="s">
-        <v>1501</v>
+        <v>1510</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -15063,10 +15179,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>1502</v>
+        <v>1511</v>
       </c>
       <c r="C61" t="s">
-        <v>1503</v>
+        <v>1512</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -15094,13 +15210,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="B64" t="s">
-        <v>1504</v>
+        <v>1513</v>
       </c>
       <c r="C64" t="s">
-        <v>1505</v>
+        <v>1514</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -15112,10 +15228,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>1506</v>
+        <v>1515</v>
       </c>
       <c r="C65" t="s">
-        <v>1507</v>
+        <v>1516</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -15127,10 +15243,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>1508</v>
+        <v>1517</v>
       </c>
       <c r="C66" t="s">
-        <v>1509</v>
+        <v>1518</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -15158,13 +15274,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>1444</v>
+        <v>1453</v>
       </c>
       <c r="B69" t="s">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="C69" t="s">
-        <v>1511</v>
+        <v>1520</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -15191,10 +15307,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>1512</v>
+        <v>1521</v>
       </c>
       <c r="C71" t="s">
-        <v>1513</v>
+        <v>1522</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -15206,10 +15322,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>1514</v>
+        <v>1523</v>
       </c>
       <c r="C72" t="s">
-        <v>1515</v>
+        <v>1524</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -15274,10 +15390,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1516</v>
+        <v>1525</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1438</v>
+        <v>1447</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -15295,16 +15411,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1517</v>
+        <v>1526</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>1518</v>
+        <v>1527</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1519</v>
+        <v>1528</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -15316,16 +15432,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1520</v>
+        <v>1529</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1521</v>
+        <v>1530</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1522</v>
+        <v>1531</v>
       </c>
       <c r="E4"/>
       <c r="G4" s="14" t="s">
@@ -15335,16 +15451,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1523</v>
+        <v>1532</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="C5" t="s">
-        <v>1525</v>
+        <v>1534</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1526</v>
+        <v>1535</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -15356,16 +15472,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1527</v>
+        <v>1536</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1528</v>
+        <v>1537</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1529</v>
+        <v>1538</v>
       </c>
       <c r="E6"/>
       <c r="G6" s="14" t="s">
@@ -15375,16 +15491,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1530</v>
+        <v>1539</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1532</v>
+        <v>1541</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -15396,16 +15512,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1417</v>
+        <v>1426</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>1418</v>
+        <v>1427</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1533</v>
+        <v>1542</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -15417,16 +15533,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1419</v>
+        <v>1428</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>1420</v>
+        <v>1429</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1534</v>
+        <v>1543</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="14" t="s">
@@ -15436,7 +15552,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1535</v>
+        <v>1544</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>364</v>
@@ -15457,16 +15573,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1536</v>
+        <v>1545</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1444</v>
+        <v>1453</v>
       </c>
       <c r="C11" t="s">
-        <v>1537</v>
+        <v>1546</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1538</v>
+        <v>1547</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -15478,16 +15594,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1539</v>
+        <v>1548</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1540</v>
+        <v>1549</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1541</v>
+        <v>1550</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -15499,16 +15615,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1542</v>
+        <v>1551</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>480</v>
       </c>
       <c r="C13" t="s">
-        <v>1543</v>
+        <v>1552</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1544</v>
+        <v>1553</v>
       </c>
       <c r="E13"/>
       <c r="G13" s="14" t="s">
@@ -15518,16 +15634,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1545</v>
+        <v>1554</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>480</v>
       </c>
       <c r="C14" t="s">
-        <v>1546</v>
+        <v>1555</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1547</v>
+        <v>1556</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="14" t="s">
@@ -15537,16 +15653,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1548</v>
+        <v>1557</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>1549</v>
+        <v>1558</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1550</v>
+        <v>1559</v>
       </c>
       <c r="E15"/>
       <c r="G15" s="14" t="s">
@@ -15556,13 +15672,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1551</v>
+        <v>1560</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1552</v>
+        <v>1561</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>18</v>
@@ -16451,13 +16567,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1524</v>
+        <v>1533</v>
       </c>
       <c r="B77" t="s">
-        <v>1553</v>
+        <v>1562</v>
       </c>
       <c r="C77" t="s">
-        <v>1554</v>
+        <v>1563</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -16469,10 +16585,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>1555</v>
+        <v>1564</v>
       </c>
       <c r="C78" t="s">
-        <v>1556</v>
+        <v>1565</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -16484,10 +16600,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>1557</v>
+        <v>1566</v>
       </c>
       <c r="C79" t="s">
-        <v>1558</v>
+        <v>1567</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -16499,10 +16615,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>1559</v>
+        <v>1568</v>
       </c>
       <c r="C80" t="s">
-        <v>1560</v>
+        <v>1569</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -16514,10 +16630,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>1561</v>
+        <v>1570</v>
       </c>
       <c r="C81" t="s">
-        <v>1562</v>
+        <v>1571</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -16529,7 +16645,7 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>1563</v>
+        <v>1572</v>
       </c>
       <c r="C82" t="s">
         <v>576</v>
@@ -16544,10 +16660,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>1564</v>
+        <v>1573</v>
       </c>
       <c r="C83" t="s">
-        <v>1565</v>
+        <v>1574</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -16559,10 +16675,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>1566</v>
+        <v>1575</v>
       </c>
       <c r="C84" t="s">
-        <v>1567</v>
+        <v>1576</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -16574,10 +16690,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>1568</v>
+        <v>1577</v>
       </c>
       <c r="C85" t="s">
-        <v>1569</v>
+        <v>1578</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -16589,10 +16705,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>1570</v>
+        <v>1579</v>
       </c>
       <c r="C86" t="s">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -16604,10 +16720,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>1572</v>
+        <v>1581</v>
       </c>
       <c r="C87" t="s">
-        <v>1573</v>
+        <v>1582</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -16619,10 +16735,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>1574</v>
+        <v>1583</v>
       </c>
       <c r="C88" t="s">
-        <v>1575</v>
+        <v>1584</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -16634,10 +16750,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>1576</v>
+        <v>1585</v>
       </c>
       <c r="C89" t="s">
-        <v>1577</v>
+        <v>1586</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -16649,10 +16765,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>1578</v>
+        <v>1587</v>
       </c>
       <c r="C90" t="s">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -16664,10 +16780,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>1580</v>
+        <v>1589</v>
       </c>
       <c r="C91" t="s">
-        <v>1581</v>
+        <v>1590</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -16679,10 +16795,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>1582</v>
+        <v>1591</v>
       </c>
       <c r="C92" t="s">
-        <v>1583</v>
+        <v>1592</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -16694,10 +16810,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>1584</v>
+        <v>1593</v>
       </c>
       <c r="C93" t="s">
-        <v>1585</v>
+        <v>1594</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -16709,10 +16825,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>1586</v>
+        <v>1595</v>
       </c>
       <c r="C94" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -16755,13 +16871,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>1444</v>
+        <v>1453</v>
       </c>
       <c r="B98" t="s">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="C98" t="s">
-        <v>1511</v>
+        <v>1520</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -16788,10 +16904,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>1512</v>
+        <v>1521</v>
       </c>
       <c r="C100" t="s">
-        <v>1513</v>
+        <v>1522</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -16803,10 +16919,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>1514</v>
+        <v>1523</v>
       </c>
       <c r="C101" t="s">
-        <v>1515</v>
+        <v>1524</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -16869,10 +16985,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1516</v>
+        <v>1525</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1438</v>
+        <v>1447</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -16888,13 +17004,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1530</v>
+        <v>1539</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>18</v>
@@ -16907,13 +17023,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1588</v>
+        <v>1597</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="C4" t="s">
-        <v>1590</v>
+        <v>1599</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>18</v>
@@ -16926,13 +17042,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1591</v>
+        <v>1600</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="C5" t="s">
-        <v>1592</v>
+        <v>1601</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>18</v>
@@ -16945,13 +17061,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1593</v>
+        <v>1602</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="C6" t="s">
-        <v>1594</v>
+        <v>1603</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>18</v>
@@ -16964,13 +17080,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1595</v>
+        <v>1604</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>1596</v>
+        <v>1605</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>18</v>
@@ -16983,13 +17099,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1597</v>
+        <v>1606</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1598</v>
+        <v>1607</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>18</v>
@@ -17002,13 +17118,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1599</v>
+        <v>1608</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1600</v>
+        <v>1609</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>18</v>
@@ -17021,13 +17137,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1601</v>
+        <v>1610</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1602</v>
+        <v>1611</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>18</v>
@@ -17040,13 +17156,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1603</v>
+        <v>1612</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>1604</v>
+        <v>1613</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>18</v>
@@ -17059,13 +17175,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1605</v>
+        <v>1614</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>1606</v>
+        <v>1615</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>18</v>
@@ -17078,13 +17194,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1607</v>
+        <v>1616</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>1608</v>
+        <v>1617</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>18</v>
@@ -17097,13 +17213,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1609</v>
+        <v>1618</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>1610</v>
+        <v>1619</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>18</v>
@@ -17116,13 +17232,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1611</v>
+        <v>1620</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1612</v>
+        <v>1621</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>18</v>
@@ -17135,13 +17251,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1613</v>
+        <v>1622</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1614</v>
+        <v>1623</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>18</v>
@@ -17154,13 +17270,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1615</v>
+        <v>1624</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1616</v>
+        <v>1625</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>18</v>
@@ -17173,13 +17289,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1617</v>
+        <v>1626</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>1618</v>
+        <v>1627</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>18</v>
@@ -17192,13 +17308,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1619</v>
+        <v>1628</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>1620</v>
+        <v>1629</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>18</v>
@@ -17211,13 +17327,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1621</v>
+        <v>1630</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>1622</v>
+        <v>1631</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>18</v>
@@ -17230,13 +17346,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1623</v>
+        <v>1632</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>1624</v>
+        <v>1633</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>18</v>
@@ -17249,13 +17365,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1625</v>
+        <v>1634</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>1626</v>
+        <v>1635</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>18</v>
@@ -17268,13 +17384,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1627</v>
+        <v>1636</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>1628</v>
+        <v>1637</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>18</v>
@@ -17304,13 +17420,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="B26" t="s">
-        <v>1514</v>
+        <v>1523</v>
       </c>
       <c r="C26" t="s">
-        <v>1515</v>
+        <v>1524</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -17322,10 +17438,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1512</v>
+        <v>1521</v>
       </c>
       <c r="C27" t="s">
-        <v>1513</v>
+        <v>1522</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -17337,10 +17453,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>1510</v>
+        <v>1519</v>
       </c>
       <c r="C28" t="s">
-        <v>1511</v>
+        <v>1520</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -17401,13 +17517,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1629</v>
+        <v>1638</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="C2" t="s">
-        <v>1631</v>
+        <v>1640</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>18</v>
@@ -17428,7 +17544,7 @@
         <v>1251</v>
       </c>
       <c r="C3" t="s">
-        <v>1403</v>
+        <v>1412</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>18</v>
@@ -17441,13 +17557,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1632</v>
+        <v>1641</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1633</v>
+        <v>1642</v>
       </c>
       <c r="C4" t="s">
-        <v>1634</v>
+        <v>1643</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>18</v>
@@ -17460,13 +17576,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1635</v>
+        <v>1644</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1636</v>
+        <v>1645</v>
       </c>
       <c r="C5" t="s">
-        <v>1637</v>
+        <v>1646</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>18</v>
@@ -17479,16 +17595,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1638</v>
+        <v>1647</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1639</v>
+        <v>1648</v>
       </c>
       <c r="C6" t="s">
-        <v>1640</v>
+        <v>1649</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1641</v>
+        <v>1650</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -17500,13 +17616,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1642</v>
+        <v>1651</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1643</v>
+        <v>1652</v>
       </c>
       <c r="C7" t="s">
-        <v>1644</v>
+        <v>1653</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>18</v>
@@ -17519,13 +17635,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1645</v>
+        <v>1654</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1646</v>
+        <v>1655</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>18</v>
@@ -17540,13 +17656,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1647</v>
+        <v>1656</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>1648</v>
+        <v>1657</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>18</v>
@@ -17559,13 +17675,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1649</v>
+        <v>1658</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1650</v>
+        <v>1659</v>
       </c>
       <c r="C10" t="s">
-        <v>1651</v>
+        <v>1660</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>18</v>
@@ -17578,13 +17694,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1652</v>
+        <v>1661</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>1653</v>
+        <v>1662</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>18</v>
@@ -17597,13 +17713,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1654</v>
+        <v>1663</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>1655</v>
+        <v>1664</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>18</v>
@@ -17616,13 +17732,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1656</v>
+        <v>1665</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>364</v>
       </c>
       <c r="C13" t="s">
-        <v>1657</v>
+        <v>1666</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>18</v>
@@ -17635,13 +17751,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>18</v>
@@ -17654,13 +17770,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1660</v>
+        <v>1669</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>364</v>
       </c>
       <c r="C15" t="s">
-        <v>1661</v>
+        <v>1670</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>18</v>
@@ -17675,13 +17791,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1662</v>
+        <v>1671</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1663</v>
+        <v>1672</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>18</v>
@@ -17694,7 +17810,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1664</v>
+        <v>1673</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>29</v>
@@ -17713,7 +17829,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1665</v>
+        <v>1674</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>29</v>
@@ -17732,7 +17848,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1666</v>
+        <v>1675</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>29</v>
@@ -17768,13 +17884,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1630</v>
+        <v>1639</v>
       </c>
       <c r="B22" t="s">
-        <v>1667</v>
+        <v>1676</v>
       </c>
       <c r="C22" t="s">
-        <v>1668</v>
+        <v>1677</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -17786,10 +17902,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1669</v>
+        <v>1678</v>
       </c>
       <c r="C23" t="s">
-        <v>1670</v>
+        <v>1679</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -17801,10 +17917,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1671</v>
+        <v>1680</v>
       </c>
       <c r="C24" t="s">
-        <v>1672</v>
+        <v>1681</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -17816,10 +17932,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1673</v>
+        <v>1682</v>
       </c>
       <c r="C25" t="s">
-        <v>1674</v>
+        <v>1683</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -17847,13 +17963,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1639</v>
+        <v>1648</v>
       </c>
       <c r="B28" t="s">
-        <v>1675</v>
+        <v>1684</v>
       </c>
       <c r="C28" t="s">
-        <v>1676</v>
+        <v>1685</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -17865,10 +17981,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1677</v>
+        <v>1686</v>
       </c>
       <c r="C29" t="s">
-        <v>1678</v>
+        <v>1687</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -17880,10 +17996,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1679</v>
+        <v>1688</v>
       </c>
       <c r="C30" t="s">
-        <v>1680</v>
+        <v>1689</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -17895,10 +18011,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1681</v>
+        <v>1690</v>
       </c>
       <c r="C31" t="s">
-        <v>1682</v>
+        <v>1691</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -17910,10 +18026,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1683</v>
+        <v>1692</v>
       </c>
       <c r="C32" t="s">
-        <v>1684</v>
+        <v>1693</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -17925,10 +18041,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1685</v>
+        <v>1694</v>
       </c>
       <c r="C33" t="s">
-        <v>1686</v>
+        <v>1695</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -17940,10 +18056,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1687</v>
+        <v>1696</v>
       </c>
       <c r="C34" t="s">
-        <v>1688</v>
+        <v>1697</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -17955,10 +18071,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1689</v>
+        <v>1698</v>
       </c>
       <c r="C35" t="s">
-        <v>1690</v>
+        <v>1699</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -17970,10 +18086,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1691</v>
+        <v>1700</v>
       </c>
       <c r="C36" t="s">
-        <v>1692</v>
+        <v>1701</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -17985,10 +18101,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1693</v>
+        <v>1702</v>
       </c>
       <c r="C37" t="s">
-        <v>1694</v>
+        <v>1703</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -18000,10 +18116,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1695</v>
+        <v>1704</v>
       </c>
       <c r="C38" t="s">
-        <v>1696</v>
+        <v>1705</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -18015,10 +18131,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1697</v>
+        <v>1706</v>
       </c>
       <c r="C39" t="s">
-        <v>1698</v>
+        <v>1707</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -18030,10 +18146,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1699</v>
+        <v>1708</v>
       </c>
       <c r="C40" t="s">
-        <v>1700</v>
+        <v>1709</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -18045,10 +18161,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1701</v>
+        <v>1710</v>
       </c>
       <c r="C41" t="s">
-        <v>1702</v>
+        <v>1711</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -18060,10 +18176,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1703</v>
+        <v>1712</v>
       </c>
       <c r="C42" t="s">
-        <v>1704</v>
+        <v>1713</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -18075,10 +18191,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1705</v>
+        <v>1714</v>
       </c>
       <c r="C43" t="s">
-        <v>1706</v>
+        <v>1715</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -18090,10 +18206,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1707</v>
+        <v>1716</v>
       </c>
       <c r="C44" t="s">
-        <v>1708</v>
+        <v>1717</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -18108,7 +18224,7 @@
         <v>260</v>
       </c>
       <c r="C45" t="s">
-        <v>1709</v>
+        <v>1718</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -18120,10 +18236,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1710</v>
+        <v>1719</v>
       </c>
       <c r="C46" t="s">
-        <v>1711</v>
+        <v>1720</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -18135,10 +18251,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1712</v>
+        <v>1721</v>
       </c>
       <c r="C47" t="s">
-        <v>1713</v>
+        <v>1722</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -18150,10 +18266,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1714</v>
+        <v>1723</v>
       </c>
       <c r="C48" t="s">
-        <v>1715</v>
+        <v>1724</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -18181,13 +18297,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1643</v>
+        <v>1652</v>
       </c>
       <c r="B51" t="s">
-        <v>1716</v>
+        <v>1725</v>
       </c>
       <c r="C51" t="s">
-        <v>1717</v>
+        <v>1726</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -18199,10 +18315,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1718</v>
+        <v>1727</v>
       </c>
       <c r="C52" t="s">
-        <v>1719</v>
+        <v>1728</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -18214,10 +18330,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1720</v>
+        <v>1729</v>
       </c>
       <c r="C53" t="s">
-        <v>1721</v>
+        <v>1730</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -18245,13 +18361,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1650</v>
+        <v>1659</v>
       </c>
       <c r="B56" t="s">
         <v>519</v>
       </c>
       <c r="C56" t="s">
-        <v>1722</v>
+        <v>1731</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -18266,7 +18382,7 @@
         <v>522</v>
       </c>
       <c r="C57" t="s">
-        <v>1723</v>
+        <v>1732</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -18278,10 +18394,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1724</v>
+        <v>1733</v>
       </c>
       <c r="C58" t="s">
-        <v>1725</v>
+        <v>1734</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -18293,10 +18409,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1726</v>
+        <v>1735</v>
       </c>
       <c r="C59" t="s">
-        <v>1727</v>
+        <v>1736</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -18360,16 +18476,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="C2" t="s">
-        <v>1730</v>
+        <v>1739</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1731</v>
+        <v>1740</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -18381,16 +18497,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1732</v>
+        <v>1741</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1733</v>
+        <v>1742</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1734</v>
+        <v>1743</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -18402,16 +18518,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1735</v>
+        <v>1744</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>1736</v>
+        <v>1745</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1737</v>
+        <v>1746</v>
       </c>
       <c r="E4"/>
       <c r="G4" s="17" t="s">
@@ -18463,13 +18579,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1738</v>
+        <v>1747</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>1739</v>
+        <v>1748</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>18</v>
@@ -18482,16 +18598,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1740</v>
+        <v>1749</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1741</v>
+        <v>1750</v>
       </c>
       <c r="C8" t="s">
-        <v>1742</v>
+        <v>1751</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1743</v>
+        <v>1752</v>
       </c>
       <c r="E8"/>
       <c r="G8" s="17" t="s">
@@ -18501,16 +18617,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1744</v>
+        <v>1753</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>1745</v>
+        <v>1754</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1746</v>
+        <v>1755</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="17" t="s">
@@ -18520,16 +18636,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1747</v>
+        <v>1756</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>1748</v>
+        <v>1757</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1749</v>
+        <v>1758</v>
       </c>
       <c r="E10"/>
       <c r="G10" s="17" t="s">
@@ -18539,16 +18655,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1750</v>
+        <v>1759</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1751</v>
+        <v>1760</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1752</v>
+        <v>1761</v>
       </c>
       <c r="E11"/>
       <c r="G11" s="17" t="s">
@@ -18558,16 +18674,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1753</v>
+        <v>1762</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1755</v>
+        <v>1764</v>
       </c>
       <c r="E12"/>
       <c r="G12" s="17" t="s">
@@ -18634,13 +18750,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1756</v>
+        <v>1765</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1757</v>
+        <v>1766</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>18</v>
@@ -18727,13 +18843,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1729</v>
+        <v>1738</v>
       </c>
       <c r="B22" t="s">
-        <v>1758</v>
+        <v>1767</v>
       </c>
       <c r="C22" t="s">
-        <v>1759</v>
+        <v>1768</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -18748,7 +18864,7 @@
         <v>513</v>
       </c>
       <c r="C23" t="s">
-        <v>1672</v>
+        <v>1681</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -18760,16 +18876,16 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1760</v>
+        <v>1769</v>
       </c>
       <c r="C24" t="s">
-        <v>1761</v>
+        <v>1770</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>1762</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="26">
@@ -18791,13 +18907,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1741</v>
+        <v>1750</v>
       </c>
       <c r="B27" t="s">
-        <v>1763</v>
+        <v>1772</v>
       </c>
       <c r="C27" t="s">
-        <v>1764</v>
+        <v>1773</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -18839,10 +18955,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1765</v>
+        <v>1774</v>
       </c>
       <c r="C30" t="s">
-        <v>1766</v>
+        <v>1775</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -18854,10 +18970,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1767</v>
+        <v>1776</v>
       </c>
       <c r="C31" t="s">
-        <v>1768</v>
+        <v>1777</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -19809,13 +19925,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1632</v>
+        <v>1641</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>1633</v>
+        <v>1642</v>
       </c>
       <c r="C2" t="s">
-        <v>1672</v>
+        <v>1681</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>18</v>
@@ -19833,10 +19949,10 @@
         <v>356</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>1769</v>
+        <v>1778</v>
       </c>
       <c r="C3" t="s">
-        <v>1769</v>
+        <v>1778</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>18</v>
@@ -19851,13 +19967,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1770</v>
+        <v>1779</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1771</v>
+        <v>1780</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>18</v>
@@ -19938,13 +20054,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1772</v>
+        <v>1781</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>18</v>
@@ -20039,7 +20155,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>1774</v>
+        <v>1783</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>18</v>
@@ -20058,7 +20174,7 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1775</v>
+        <v>1784</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>18</v>
@@ -20071,10 +20187,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1776</v>
+        <v>1785</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1777</v>
+        <v>1786</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -20090,7 +20206,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1778</v>
+        <v>1787</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>480</v>
@@ -20109,7 +20225,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1779</v>
+        <v>1788</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>480</v>
@@ -20164,7 +20280,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1777</v>
+        <v>1786</v>
       </c>
       <c r="B15" t="s">
         <v>278</v>
@@ -20212,10 +20328,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>1780</v>
+        <v>1789</v>
       </c>
       <c r="C18" t="s">
-        <v>1780</v>
+        <v>1789</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -20599,13 +20715,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1772</v>
+        <v>1781</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>18</v>
@@ -20618,13 +20734,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1781</v>
+        <v>1790</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1782</v>
+        <v>1791</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>18</v>
@@ -20637,13 +20753,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1783</v>
+        <v>1792</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>1784</v>
+        <v>1793</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>18</v>
@@ -20656,7 +20772,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1779</v>
+        <v>1788</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>480</v>
@@ -20743,13 +20859,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1772</v>
+        <v>1781</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>18</v>
@@ -20762,13 +20878,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1781</v>
+        <v>1790</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1782</v>
+        <v>1791</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>18</v>
@@ -20781,13 +20897,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1783</v>
+        <v>1792</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>1784</v>
+        <v>1793</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
@@ -20819,7 +20935,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1779</v>
+        <v>1788</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>480</v>
@@ -20906,13 +21022,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1772</v>
+        <v>1781</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1773</v>
+        <v>1782</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>18</v>
@@ -20963,7 +21079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1779</v>
+        <v>1788</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>480</v>
@@ -21009,7 +21125,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -21050,13 +21166,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1785</v>
+        <v>1794</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>480</v>
       </c>
       <c r="C2" t="s">
-        <v>1786</v>
+        <v>1795</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>18</v>
@@ -21069,13 +21185,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1787</v>
+        <v>1796</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1788</v>
+        <v>1797</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>18</v>
@@ -21126,13 +21242,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1789</v>
+        <v>1798</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1754</v>
+        <v>1763</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>18</v>
@@ -21183,11 +21299,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1790</v>
+        <v>1799</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" t="s">
-        <v>1791</v>
+        <v>1800</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>18</v>
@@ -21276,13 +21392,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1792</v>
+        <v>1801</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>1418</v>
+        <v>1427</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>18</v>
@@ -21301,7 +21417,7 @@
         <v>471</v>
       </c>
       <c r="C15" t="s">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>18</v>
@@ -21314,13 +21430,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1794</v>
+        <v>1803</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>364</v>
       </c>
       <c r="C16" t="s">
-        <v>1795</v>
+        <v>1804</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>18</v>
@@ -21333,16 +21449,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1796</v>
+        <v>1805</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>1797</v>
+        <v>1806</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>1798</v>
+        <v>1807</v>
       </c>
       <c r="E17"/>
       <c r="G17" s="23" t="s">
@@ -21352,10 +21468,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1799</v>
+        <v>1808</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1800</v>
+        <v>1809</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -22247,13 +22363,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1800</v>
+        <v>1809</v>
       </c>
       <c r="B79" t="s">
-        <v>1801</v>
+        <v>1810</v>
       </c>
       <c r="C79" t="s">
-        <v>1802</v>
+        <v>1811</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -22265,10 +22381,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>1803</v>
+        <v>1812</v>
       </c>
       <c r="C80" t="s">
-        <v>1804</v>
+        <v>1813</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -22280,10 +22396,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>1805</v>
+        <v>1814</v>
       </c>
       <c r="C81" t="s">
-        <v>1806</v>
+        <v>1815</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -22295,10 +22411,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>1807</v>
+        <v>1816</v>
       </c>
       <c r="C82" t="s">
-        <v>1808</v>
+        <v>1817</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -22310,15 +22426,30 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>1809</v>
+        <v>1818</v>
       </c>
       <c r="C83" t="s">
-        <v>1810</v>
+        <v>1819</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
       </c>
       <c r="E83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84"/>
+      <c r="B84" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D84" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
         <v>18</v>
       </c>
     </row>
@@ -22339,12 +22470,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1811</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1812</v>
+        <v>1823</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6812" uniqueCount="1906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6824" uniqueCount="1912">
   <si>
     <t>Field</t>
   </si>
@@ -4264,10 +4264,10 @@
     <t>Face-to-face contact of at least 15 minutes</t>
   </si>
   <si>
-    <t>MEDICAL_UNSAVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical personal at close proximity (2 meter) without protective equipment		</t>
+    <t>MEDICAL_UNSAFE</t>
+  </si>
+  <si>
+    <t>Medical personnel with a high risk of exposure, e.g. unprotected relevant exposure to secretions, exposure to aerosols from COVID-19 cases</t>
   </si>
   <si>
     <t>SAME_ROOM</t>
@@ -4288,16 +4288,16 @@
     <t>Face-to-face contact of less than 15 minutes</t>
   </si>
   <si>
-    <t>MEDICAL_SAVE</t>
-  </si>
-  <si>
-    <t>Medical personal at save proximity (&gt; 2 meter) or with protective equipment</t>
+    <t>MEDICAL_SAFE</t>
+  </si>
+  <si>
+    <t>Medical personnel at save proximity (&gt; 2 meter) or with protective equipment</t>
   </si>
   <si>
     <t>MEDICAL_SAME_ROOM</t>
   </si>
   <si>
-    <t>Medical personal that was in same room or house with source case</t>
+    <t>Medical personnel that was in same room or house with source case</t>
   </si>
   <si>
     <t>AEROSOL</t>
@@ -4312,12 +4312,30 @@
     <t>Medical personnel at save proximity (&gt; 2 meter), without direct contact with secretions or excretions of the patient and without aerosol exposure</t>
   </si>
   <si>
+    <t>MEDICAL_LIMITED</t>
+  </si>
+  <si>
+    <t>Medical personnel with limited exposure, e.g. with contact &lt; 2m to COVID-19 cases without protective equipment, ≥ 15min face-to-face contact (without exposure as described under Ia)</t>
+  </si>
+  <si>
     <t>HIGH_RISK</t>
   </si>
   <si>
     <t>High risk contact</t>
   </si>
   <si>
+    <t>HIGH_RISK_MED</t>
+  </si>
+  <si>
+    <t>High risk medical contact</t>
+  </si>
+  <si>
+    <t>MEDIUM_RISK_MED</t>
+  </si>
+  <si>
+    <t>Medium risk medical contact</t>
+  </si>
+  <si>
     <t>LOW_RISK</t>
   </si>
   <si>
@@ -5752,7 +5770,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.41.0-SNAPSHOT</t>
+    <t>1.42.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -6598,7 +6616,7 @@
 </file>
 
 <file path=xl/tables/table55.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactProximity" displayName="ContactContactProximity" ref="A108:E121">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="55" name="ContactContactProximity" displayName="ContactContactProximity" ref="A108:E122">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6612,7 +6630,7 @@
 </file>
 
 <file path=xl/tables/table56.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactContactCategory" displayName="ContactContactCategory" ref="A123:E126">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="56" name="ContactContactCategory" displayName="ContactContactCategory" ref="A124:E129">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6626,7 +6644,7 @@
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactContactClassification" displayName="ContactContactClassification" ref="A128:E131">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ContactContactClassification" displayName="ContactContactClassification" ref="A131:E134">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6640,7 +6658,7 @@
 </file>
 
 <file path=xl/tables/table58.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactContactStatus" displayName="ContactContactStatus" ref="A133:E136">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ContactContactStatus" displayName="ContactContactStatus" ref="A136:E139">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6654,7 +6672,7 @@
 </file>
 
 <file path=xl/tables/table59.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A138:E143">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ContactFollowUpStatus" displayName="ContactFollowUpStatus" ref="A141:E146">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6682,7 +6700,7 @@
 </file>
 
 <file path=xl/tables/table60.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ContactContactRelation" displayName="ContactContactRelation" ref="A145:E150">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ContactContactRelation" displayName="ContactContactRelation" ref="A148:E153">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6696,7 +6714,7 @@
 </file>
 
 <file path=xl/tables/table61.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A152:E155">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ContactYesNoUnknown" displayName="ContactYesNoUnknown" ref="A155:E158">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6710,7 +6728,7 @@
 </file>
 
 <file path=xl/tables/table62.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A157:E161">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="ContactQuarantineType" displayName="ContactQuarantineType" ref="A160:E164">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -10795,7 +10813,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I161"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -12808,42 +12826,42 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>1</v>
-      </c>
-      <c r="B123" t="s">
-        <v>123</v>
-      </c>
-      <c r="C123" t="s">
-        <v>2</v>
-      </c>
-      <c r="D123" t="s">
-        <v>3</v>
-      </c>
-      <c r="E123" t="s">
-        <v>124</v>
+    <row r="122">
+      <c r="A122"/>
+      <c r="B122" t="s">
+        <v>1425</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D122" t="s">
+        <v>18</v>
+      </c>
+      <c r="E122" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" t="s">
+        <v>123</v>
+      </c>
+      <c r="C124" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>3</v>
+      </c>
+      <c r="E124" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
         <v>1359</v>
       </c>
-      <c r="B124" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C124" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D124" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125"/>
       <c r="B125" t="s">
         <v>1427</v>
       </c>
@@ -12872,294 +12890,294 @@
         <v>18</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127"/>
+      <c r="B127" t="s">
+        <v>1431</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D127" t="s">
+        <v>18</v>
+      </c>
+      <c r="E127" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="128">
-      <c r="A128" t="s">
+      <c r="A128"/>
+      <c r="B128" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C128" t="s">
+        <v>1434</v>
+      </c>
+      <c r="D128" t="s">
+        <v>18</v>
+      </c>
+      <c r="E128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129"/>
+      <c r="B129" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C129" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D129" t="s">
+        <v>18</v>
+      </c>
+      <c r="E129" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
         <v>1</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B131" t="s">
         <v>123</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C131" t="s">
         <v>2</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D131" t="s">
         <v>3</v>
       </c>
-      <c r="E128" t="s">
+      <c r="E131" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" t="s">
+    <row r="132">
+      <c r="A132" t="s">
         <v>1362</v>
       </c>
-      <c r="B129" t="s">
-        <v>1431</v>
-      </c>
-      <c r="C129" t="s">
-        <v>1432</v>
-      </c>
-      <c r="D129" t="s">
-        <v>18</v>
-      </c>
-      <c r="E129" t="s">
-        <v>1433</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130"/>
-      <c r="B130" t="s">
+      <c r="B132" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C132" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D132" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133"/>
+      <c r="B133" t="s">
         <v>536</v>
       </c>
-      <c r="C130" t="s">
-        <v>1434</v>
-      </c>
-      <c r="D130" t="s">
-        <v>18</v>
-      </c>
-      <c r="E130" t="s">
+      <c r="C133" t="s">
+        <v>1440</v>
+      </c>
+      <c r="D133" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131"/>
-      <c r="B131" t="s">
-        <v>1435</v>
-      </c>
-      <c r="C131" t="s">
-        <v>1436</v>
-      </c>
-      <c r="D131" t="s">
-        <v>18</v>
-      </c>
-      <c r="E131" t="s">
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
+    <row r="134">
+      <c r="A134"/>
+      <c r="B134" t="s">
+        <v>1441</v>
+      </c>
+      <c r="C134" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D134" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
         <v>1</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B136" t="s">
         <v>123</v>
       </c>
-      <c r="C133" t="s">
+      <c r="C136" t="s">
         <v>2</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D136" t="s">
         <v>3</v>
       </c>
-      <c r="E133" t="s">
+      <c r="E136" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" t="s">
+    <row r="137">
+      <c r="A137" t="s">
         <v>1365</v>
       </c>
-      <c r="B134" t="s">
-        <v>1438</v>
-      </c>
-      <c r="C134" t="s">
-        <v>1439</v>
-      </c>
-      <c r="D134" t="s">
-        <v>18</v>
-      </c>
-      <c r="E134" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135"/>
-      <c r="B135" t="s">
-        <v>1440</v>
-      </c>
-      <c r="C135" t="s">
-        <v>1441</v>
-      </c>
-      <c r="D135" t="s">
-        <v>18</v>
-      </c>
-      <c r="E135" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136"/>
-      <c r="B136" t="s">
-        <v>1442</v>
-      </c>
-      <c r="C136" t="s">
-        <v>1443</v>
-      </c>
-      <c r="D136" t="s">
-        <v>18</v>
-      </c>
-      <c r="E136" t="s">
+      <c r="B137" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C137" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D137" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="s">
+      <c r="A138"/>
+      <c r="B138" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C138" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D138" t="s">
+        <v>18</v>
+      </c>
+      <c r="E138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139"/>
+      <c r="B139" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D139" t="s">
+        <v>18</v>
+      </c>
+      <c r="E139" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
         <v>1</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B141" t="s">
         <v>123</v>
       </c>
-      <c r="C138" t="s">
+      <c r="C141" t="s">
         <v>2</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D141" t="s">
         <v>3</v>
       </c>
-      <c r="E138" t="s">
+      <c r="E141" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" t="s">
+    <row r="142">
+      <c r="A142" t="s">
         <v>1368</v>
       </c>
-      <c r="B139" t="s">
-        <v>1444</v>
-      </c>
-      <c r="C139" t="s">
-        <v>1445</v>
-      </c>
-      <c r="D139" t="s">
-        <v>1446</v>
-      </c>
-      <c r="E139" t="s">
-        <v>1447</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140"/>
-      <c r="B140" t="s">
-        <v>1448</v>
-      </c>
-      <c r="C140" t="s">
-        <v>1449</v>
-      </c>
-      <c r="D140" t="s">
+      <c r="B142" t="s">
         <v>1450</v>
       </c>
-      <c r="E140" t="s">
+      <c r="C142" t="s">
         <v>1451</v>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141"/>
-      <c r="B141" t="s">
+      <c r="D142" t="s">
         <v>1452</v>
       </c>
-      <c r="C141" t="s">
+      <c r="E142" t="s">
         <v>1453</v>
-      </c>
-      <c r="D141" t="s">
-        <v>1454</v>
-      </c>
-      <c r="E141" t="s">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142"/>
-      <c r="B142" t="s">
-        <v>1456</v>
-      </c>
-      <c r="C142" t="s">
-        <v>1457</v>
-      </c>
-      <c r="D142" t="s">
-        <v>1458</v>
-      </c>
-      <c r="E142" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="143">
       <c r="A143"/>
       <c r="B143" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C143" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D143" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E143" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144"/>
+      <c r="B144" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C144" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D144" t="s">
         <v>1460</v>
       </c>
-      <c r="C143" t="s">
+      <c r="E144" t="s">
         <v>1461</v>
       </c>
-      <c r="D143" t="s">
+    </row>
+    <row r="145">
+      <c r="A145"/>
+      <c r="B145" t="s">
         <v>1462</v>
       </c>
-      <c r="E143" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
+      <c r="C145" t="s">
+        <v>1463</v>
+      </c>
+      <c r="D145" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E145" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146"/>
+      <c r="B146" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C146" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D146" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
         <v>1</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B148" t="s">
         <v>123</v>
       </c>
-      <c r="C145" t="s">
+      <c r="C148" t="s">
         <v>2</v>
       </c>
-      <c r="D145" t="s">
+      <c r="D148" t="s">
         <v>3</v>
       </c>
-      <c r="E145" t="s">
+      <c r="E148" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" t="s">
+    <row r="149">
+      <c r="A149" t="s">
         <v>1380</v>
       </c>
-      <c r="B146" t="s">
-        <v>1463</v>
-      </c>
-      <c r="C146" t="s">
-        <v>1464</v>
-      </c>
-      <c r="D146" t="s">
-        <v>18</v>
-      </c>
-      <c r="E146" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147"/>
-      <c r="B147" t="s">
-        <v>1465</v>
-      </c>
-      <c r="C147" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D147" t="s">
-        <v>18</v>
-      </c>
-      <c r="E147" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148"/>
-      <c r="B148" t="s">
-        <v>1467</v>
-      </c>
-      <c r="C148" t="s">
-        <v>1468</v>
-      </c>
-      <c r="D148" t="s">
-        <v>18</v>
-      </c>
-      <c r="E148" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149"/>
       <c r="B149" t="s">
         <v>1469</v>
       </c>
@@ -13176,158 +13194,203 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C150" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D150" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151"/>
+      <c r="B151" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C151" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D151" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152"/>
+      <c r="B152" t="s">
+        <v>1475</v>
+      </c>
+      <c r="C152" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153"/>
+      <c r="B153" t="s">
         <v>260</v>
       </c>
-      <c r="C150" t="s">
+      <c r="C153" t="s">
         <v>262</v>
       </c>
-      <c r="D150" t="s">
-        <v>18</v>
-      </c>
-      <c r="E150" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
+      <c r="D153" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
         <v>1</v>
       </c>
-      <c r="B152" t="s">
+      <c r="B155" t="s">
         <v>123</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C155" t="s">
         <v>2</v>
       </c>
-      <c r="D152" t="s">
+      <c r="D155" t="s">
         <v>3</v>
       </c>
-      <c r="E152" t="s">
+      <c r="E155" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" t="s">
+    <row r="156">
+      <c r="A156" t="s">
         <v>393</v>
       </c>
-      <c r="B153" t="s">
+      <c r="B156" t="s">
         <v>557</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C156" t="s">
         <v>558</v>
       </c>
-      <c r="D153" t="s">
-        <v>18</v>
-      </c>
-      <c r="E153" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154"/>
-      <c r="B154" t="s">
+      <c r="D156" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157"/>
+      <c r="B157" t="s">
         <v>559</v>
       </c>
-      <c r="C154" t="s">
+      <c r="C157" t="s">
         <v>560</v>
       </c>
-      <c r="D154" t="s">
-        <v>18</v>
-      </c>
-      <c r="E154" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155"/>
-      <c r="B155" t="s">
+      <c r="D157" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158"/>
+      <c r="B158" t="s">
         <v>341</v>
       </c>
-      <c r="C155" t="s">
+      <c r="C158" t="s">
         <v>342</v>
       </c>
-      <c r="D155" t="s">
-        <v>18</v>
-      </c>
-      <c r="E155" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
+      <c r="D158" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
         <v>1</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B160" t="s">
         <v>123</v>
       </c>
-      <c r="C157" t="s">
+      <c r="C160" t="s">
         <v>2</v>
       </c>
-      <c r="D157" t="s">
+      <c r="D160" t="s">
         <v>3</v>
       </c>
-      <c r="E157" t="s">
+      <c r="E160" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" t="s">
+    <row r="161">
+      <c r="A161" t="s">
         <v>483</v>
       </c>
-      <c r="B158" t="s">
+      <c r="B161" t="s">
         <v>583</v>
       </c>
-      <c r="C158" t="s">
+      <c r="C161" t="s">
         <v>584</v>
       </c>
-      <c r="D158" t="s">
-        <v>18</v>
-      </c>
-      <c r="E158" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159"/>
-      <c r="B159" t="s">
+      <c r="D161" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162"/>
+      <c r="B162" t="s">
         <v>585</v>
       </c>
-      <c r="C159" t="s">
+      <c r="C162" t="s">
         <v>586</v>
       </c>
-      <c r="D159" t="s">
-        <v>18</v>
-      </c>
-      <c r="E159" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160"/>
-      <c r="B160" t="s">
+      <c r="D162" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163"/>
+      <c r="B163" t="s">
         <v>274</v>
       </c>
-      <c r="C160" t="s">
+      <c r="C163" t="s">
         <v>587</v>
       </c>
-      <c r="D160" t="s">
-        <v>18</v>
-      </c>
-      <c r="E160" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161"/>
-      <c r="B161" t="s">
+      <c r="D163" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164"/>
+      <c r="B164" t="s">
         <v>341</v>
       </c>
-      <c r="C161" t="s">
+      <c r="C164" t="s">
         <v>342</v>
       </c>
-      <c r="D161" t="s">
-        <v>18</v>
-      </c>
-      <c r="E161" t="s">
+      <c r="D164" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164" t="s">
         <v>18</v>
       </c>
     </row>
@@ -13397,7 +13460,7 @@
         <v>357</v>
       </c>
       <c r="C2" t="s">
-        <v>1471</v>
+        <v>1477</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>18</v>
@@ -13440,7 +13503,7 @@
         <v>1332</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1472</v>
+        <v>1478</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -13452,13 +13515,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1473</v>
+        <v>1479</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>364</v>
       </c>
       <c r="C5" t="s">
-        <v>1474</v>
+        <v>1480</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>18</v>
@@ -13473,16 +13536,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1475</v>
+        <v>1481</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="C6" t="s">
-        <v>1477</v>
+        <v>1483</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1478</v>
+        <v>1484</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -13500,10 +13563,10 @@
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>1479</v>
+        <v>1485</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1480</v>
+        <v>1486</v>
       </c>
       <c r="E7"/>
       <c r="G7" s="12" t="s">
@@ -13538,7 +13601,7 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1481</v>
+        <v>1487</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>18</v>
@@ -13557,7 +13620,7 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1482</v>
+        <v>1488</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>18</v>
@@ -14465,13 +14528,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1476</v>
+        <v>1482</v>
       </c>
       <c r="B72" t="s">
-        <v>1483</v>
+        <v>1489</v>
       </c>
       <c r="C72" t="s">
-        <v>1484</v>
+        <v>1490</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -14483,31 +14546,31 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>1485</v>
+        <v>1491</v>
       </c>
       <c r="C73" t="s">
-        <v>1486</v>
+        <v>1492</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>1487</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>1488</v>
+        <v>1494</v>
       </c>
       <c r="C74" t="s">
-        <v>1489</v>
+        <v>1495</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>1490</v>
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -14563,13 +14626,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1491</v>
+        <v>1497</v>
       </c>
       <c r="B2" s="13" t="s">
         <v>1338</v>
       </c>
       <c r="C2" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>18</v>
@@ -14582,10 +14645,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -14601,13 +14664,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1496</v>
+        <v>1502</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>18</v>
@@ -14620,13 +14683,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1497</v>
+        <v>1503</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>1498</v>
+        <v>1504</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>18</v>
@@ -14639,16 +14702,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1499</v>
+        <v>1505</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>1500</v>
+        <v>1506</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>1501</v>
+        <v>1507</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -14759,13 +14822,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1502</v>
+        <v>1508</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="C12" t="s">
-        <v>1504</v>
+        <v>1510</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>18</v>
@@ -14780,13 +14843,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1505</v>
+        <v>1511</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>1506</v>
+        <v>1512</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>18</v>
@@ -14799,13 +14862,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1507</v>
+        <v>1513</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="C14" t="s">
-        <v>1509</v>
+        <v>1515</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>18</v>
@@ -14820,7 +14883,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>52</v>
@@ -14841,13 +14904,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>18</v>
@@ -14860,13 +14923,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>18</v>
@@ -14879,13 +14942,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1515</v>
+        <v>1521</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>1516</v>
+        <v>1522</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>18</v>
@@ -14898,13 +14961,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1517</v>
+        <v>1523</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>1518</v>
+        <v>1524</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>18</v>
@@ -14917,13 +14980,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1519</v>
+        <v>1525</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="C20" t="s">
-        <v>1521</v>
+        <v>1527</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>18</v>
@@ -14936,13 +14999,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1522</v>
+        <v>1528</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>1523</v>
+        <v>1529</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>18</v>
@@ -14955,7 +15018,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1524</v>
+        <v>1530</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>9</v>
@@ -14974,13 +15037,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1525</v>
+        <v>1531</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="C23" t="s">
-        <v>1527</v>
+        <v>1533</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>18</v>
@@ -14993,10 +15056,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1528</v>
+        <v>1534</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
@@ -15012,13 +15075,13 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1530</v>
+        <v>1536</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C25" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>18</v>
@@ -15031,13 +15094,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1532</v>
+        <v>1538</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C26" t="s">
-        <v>1533</v>
+        <v>1539</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>18</v>
@@ -15050,13 +15113,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1534</v>
+        <v>1540</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="C27" t="s">
-        <v>1536</v>
+        <v>1542</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>18</v>
@@ -15069,13 +15132,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1537</v>
+        <v>1543</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C28" t="s">
-        <v>1538</v>
+        <v>1544</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>18</v>
@@ -15088,13 +15151,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1539</v>
+        <v>1545</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>480</v>
       </c>
       <c r="C29" t="s">
-        <v>1540</v>
+        <v>1546</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>18</v>
@@ -15107,11 +15170,11 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1541</v>
+        <v>1547</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" t="s">
-        <v>1542</v>
+        <v>1548</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>18</v>
@@ -15124,11 +15187,11 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1543</v>
+        <v>1549</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" t="s">
-        <v>1544</v>
+        <v>1550</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>18</v>
@@ -15141,13 +15204,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1545</v>
+        <v>1551</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>1546</v>
+        <v>1552</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>18</v>
@@ -15160,13 +15223,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1547</v>
+        <v>1553</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>1548</v>
+        <v>1554</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>18</v>
@@ -15196,13 +15259,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1503</v>
+        <v>1509</v>
       </c>
       <c r="B36" t="s">
-        <v>1549</v>
+        <v>1555</v>
       </c>
       <c r="C36" t="s">
-        <v>1550</v>
+        <v>1556</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -15214,10 +15277,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1551</v>
+        <v>1557</v>
       </c>
       <c r="C37" t="s">
-        <v>1552</v>
+        <v>1558</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -15229,10 +15292,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1553</v>
+        <v>1559</v>
       </c>
       <c r="C38" t="s">
-        <v>1554</v>
+        <v>1560</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -15244,10 +15307,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1555</v>
+        <v>1561</v>
       </c>
       <c r="C39" t="s">
-        <v>1556</v>
+        <v>1562</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -15259,10 +15322,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1557</v>
+        <v>1563</v>
       </c>
       <c r="C40" t="s">
-        <v>1558</v>
+        <v>1564</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -15274,10 +15337,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1559</v>
+        <v>1565</v>
       </c>
       <c r="C41" t="s">
-        <v>1560</v>
+        <v>1566</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -15289,10 +15352,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1561</v>
+        <v>1567</v>
       </c>
       <c r="C42" t="s">
-        <v>1562</v>
+        <v>1568</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -15304,10 +15367,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1563</v>
+        <v>1569</v>
       </c>
       <c r="C43" t="s">
-        <v>1564</v>
+        <v>1570</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -15319,10 +15382,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1565</v>
+        <v>1571</v>
       </c>
       <c r="C44" t="s">
-        <v>1566</v>
+        <v>1572</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -15334,10 +15397,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>1567</v>
+        <v>1573</v>
       </c>
       <c r="C45" t="s">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -15349,10 +15412,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1569</v>
+        <v>1575</v>
       </c>
       <c r="C46" t="s">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -15364,10 +15427,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1571</v>
+        <v>1577</v>
       </c>
       <c r="C47" t="s">
-        <v>1572</v>
+        <v>1578</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -15379,10 +15442,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1573</v>
+        <v>1579</v>
       </c>
       <c r="C48" t="s">
-        <v>1574</v>
+        <v>1580</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -15394,10 +15457,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>1575</v>
+        <v>1581</v>
       </c>
       <c r="C49" t="s">
-        <v>1576</v>
+        <v>1582</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -15409,10 +15472,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>1577</v>
+        <v>1583</v>
       </c>
       <c r="C50" t="s">
-        <v>1578</v>
+        <v>1584</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -15424,10 +15487,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="C51" t="s">
-        <v>1580</v>
+        <v>1586</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -15439,10 +15502,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="C52" t="s">
-        <v>1582</v>
+        <v>1588</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -15454,10 +15517,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1583</v>
+        <v>1589</v>
       </c>
       <c r="C53" t="s">
-        <v>1584</v>
+        <v>1590</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -15469,10 +15532,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>1585</v>
+        <v>1591</v>
       </c>
       <c r="C54" t="s">
-        <v>1586</v>
+        <v>1592</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -15515,13 +15578,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1508</v>
+        <v>1514</v>
       </c>
       <c r="B58" t="s">
-        <v>1587</v>
+        <v>1593</v>
       </c>
       <c r="C58" t="s">
-        <v>1588</v>
+        <v>1594</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -15533,10 +15596,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1589</v>
+        <v>1595</v>
       </c>
       <c r="C59" t="s">
-        <v>1590</v>
+        <v>1596</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -15564,13 +15627,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>1520</v>
+        <v>1526</v>
       </c>
       <c r="B62" t="s">
-        <v>1591</v>
+        <v>1597</v>
       </c>
       <c r="C62" t="s">
-        <v>1592</v>
+        <v>1598</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -15582,10 +15645,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>1593</v>
+        <v>1599</v>
       </c>
       <c r="C63" t="s">
-        <v>1594</v>
+        <v>1600</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -15613,13 +15676,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1526</v>
+        <v>1532</v>
       </c>
       <c r="B66" t="s">
-        <v>1595</v>
+        <v>1601</v>
       </c>
       <c r="C66" t="s">
-        <v>1596</v>
+        <v>1602</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -15631,10 +15694,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="C67" t="s">
-        <v>1598</v>
+        <v>1604</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -15646,10 +15709,10 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>1599</v>
+        <v>1605</v>
       </c>
       <c r="C68" t="s">
-        <v>1600</v>
+        <v>1606</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -15677,13 +15740,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="B71" t="s">
-        <v>1601</v>
+        <v>1607</v>
       </c>
       <c r="C71" t="s">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -15710,10 +15773,10 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
       <c r="C73" t="s">
-        <v>1604</v>
+        <v>1610</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -15725,10 +15788,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>1605</v>
+        <v>1611</v>
       </c>
       <c r="C74" t="s">
-        <v>1606</v>
+        <v>1612</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -15793,10 +15856,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -15814,16 +15877,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1608</v>
+        <v>1614</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>1609</v>
+        <v>1615</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1610</v>
+        <v>1616</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -15835,16 +15898,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1611</v>
+        <v>1617</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1612</v>
+        <v>1618</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1613</v>
+        <v>1619</v>
       </c>
       <c r="E4"/>
       <c r="G4" s="14" t="s">
@@ -15854,16 +15917,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1614</v>
+        <v>1620</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1615</v>
+        <v>1621</v>
       </c>
       <c r="C5" t="s">
-        <v>1616</v>
+        <v>1622</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1617</v>
+        <v>1623</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -15875,16 +15938,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1618</v>
+        <v>1624</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1619</v>
+        <v>1625</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1620</v>
+        <v>1626</v>
       </c>
       <c r="E6"/>
       <c r="G6" s="14" t="s">
@@ -15894,16 +15957,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1621</v>
+        <v>1627</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>1622</v>
+        <v>1628</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1623</v>
+        <v>1629</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -15915,7 +15978,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1510</v>
+        <v>1516</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>52</v>
@@ -15924,7 +15987,7 @@
         <v>597</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1624</v>
+        <v>1630</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -15936,16 +15999,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1511</v>
+        <v>1517</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1625</v>
+        <v>1631</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="14" t="s">
@@ -15955,7 +16018,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1626</v>
+        <v>1632</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>364</v>
@@ -15976,16 +16039,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1627</v>
+        <v>1633</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="C11" t="s">
-        <v>1628</v>
+        <v>1634</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1629</v>
+        <v>1635</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -15997,16 +16060,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1630</v>
+        <v>1636</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1631</v>
+        <v>1637</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1632</v>
+        <v>1638</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -16018,16 +16081,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1633</v>
+        <v>1639</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>480</v>
       </c>
       <c r="C13" t="s">
-        <v>1634</v>
+        <v>1640</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1635</v>
+        <v>1641</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -16039,16 +16102,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1636</v>
+        <v>1642</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>480</v>
       </c>
       <c r="C14" t="s">
-        <v>1637</v>
+        <v>1643</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1638</v>
+        <v>1644</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="14" t="s">
@@ -16058,16 +16121,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1639</v>
+        <v>1645</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>1640</v>
+        <v>1646</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1641</v>
+        <v>1647</v>
       </c>
       <c r="E15"/>
       <c r="G15" s="14" t="s">
@@ -16077,13 +16140,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1642</v>
+        <v>1648</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1643</v>
+        <v>1649</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>18</v>
@@ -16972,13 +17035,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1615</v>
+        <v>1621</v>
       </c>
       <c r="B77" t="s">
-        <v>1644</v>
+        <v>1650</v>
       </c>
       <c r="C77" t="s">
-        <v>1645</v>
+        <v>1651</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -16990,10 +17053,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>1646</v>
+        <v>1652</v>
       </c>
       <c r="C78" t="s">
-        <v>1647</v>
+        <v>1653</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -17005,10 +17068,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>1648</v>
+        <v>1654</v>
       </c>
       <c r="C79" t="s">
-        <v>1649</v>
+        <v>1655</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -17020,10 +17083,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>1650</v>
+        <v>1656</v>
       </c>
       <c r="C80" t="s">
-        <v>1651</v>
+        <v>1657</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -17035,10 +17098,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>1652</v>
+        <v>1658</v>
       </c>
       <c r="C81" t="s">
-        <v>1653</v>
+        <v>1659</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -17050,7 +17113,7 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>1654</v>
+        <v>1660</v>
       </c>
       <c r="C82" t="s">
         <v>618</v>
@@ -17065,10 +17128,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>1655</v>
+        <v>1661</v>
       </c>
       <c r="C83" t="s">
-        <v>1656</v>
+        <v>1662</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -17080,10 +17143,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>1657</v>
+        <v>1663</v>
       </c>
       <c r="C84" t="s">
-        <v>1658</v>
+        <v>1664</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -17095,10 +17158,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>1659</v>
+        <v>1665</v>
       </c>
       <c r="C85" t="s">
-        <v>1660</v>
+        <v>1666</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -17110,10 +17173,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>1661</v>
+        <v>1667</v>
       </c>
       <c r="C86" t="s">
-        <v>1662</v>
+        <v>1668</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -17125,10 +17188,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>1663</v>
+        <v>1669</v>
       </c>
       <c r="C87" t="s">
-        <v>1664</v>
+        <v>1670</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -17140,10 +17203,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>1665</v>
+        <v>1671</v>
       </c>
       <c r="C88" t="s">
-        <v>1666</v>
+        <v>1672</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -17155,10 +17218,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>1667</v>
+        <v>1673</v>
       </c>
       <c r="C89" t="s">
-        <v>1668</v>
+        <v>1674</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -17170,10 +17233,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>1669</v>
+        <v>1675</v>
       </c>
       <c r="C90" t="s">
-        <v>1670</v>
+        <v>1676</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -17185,10 +17248,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>1671</v>
+        <v>1677</v>
       </c>
       <c r="C91" t="s">
-        <v>1672</v>
+        <v>1678</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -17200,10 +17263,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>1673</v>
+        <v>1679</v>
       </c>
       <c r="C92" t="s">
-        <v>1674</v>
+        <v>1680</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -17215,10 +17278,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>1675</v>
+        <v>1681</v>
       </c>
       <c r="C93" t="s">
-        <v>1676</v>
+        <v>1682</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -17230,10 +17293,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>1677</v>
+        <v>1683</v>
       </c>
       <c r="C94" t="s">
-        <v>1678</v>
+        <v>1684</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -17276,13 +17339,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>1535</v>
+        <v>1541</v>
       </c>
       <c r="B98" t="s">
-        <v>1601</v>
+        <v>1607</v>
       </c>
       <c r="C98" t="s">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -17309,10 +17372,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
       <c r="C100" t="s">
-        <v>1604</v>
+        <v>1610</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -17324,10 +17387,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>1605</v>
+        <v>1611</v>
       </c>
       <c r="C101" t="s">
-        <v>1606</v>
+        <v>1612</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -17390,10 +17453,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1607</v>
+        <v>1613</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1529</v>
+        <v>1535</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -17409,13 +17472,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1621</v>
+        <v>1627</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>1622</v>
+        <v>1628</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>18</v>
@@ -17428,13 +17491,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1679</v>
+        <v>1685</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="C4" t="s">
-        <v>1681</v>
+        <v>1687</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>18</v>
@@ -17447,13 +17510,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1682</v>
+        <v>1688</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="C5" t="s">
-        <v>1683</v>
+        <v>1689</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>18</v>
@@ -17466,13 +17529,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1684</v>
+        <v>1690</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="C6" t="s">
-        <v>1685</v>
+        <v>1691</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>18</v>
@@ -17485,13 +17548,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1686</v>
+        <v>1692</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>1687</v>
+        <v>1693</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>18</v>
@@ -17504,13 +17567,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1688</v>
+        <v>1694</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1689</v>
+        <v>1695</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>18</v>
@@ -17523,13 +17586,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1690</v>
+        <v>1696</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1691</v>
+        <v>1697</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>18</v>
@@ -17542,13 +17605,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1692</v>
+        <v>1698</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1693</v>
+        <v>1699</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>18</v>
@@ -17561,13 +17624,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1694</v>
+        <v>1700</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>1695</v>
+        <v>1701</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>18</v>
@@ -17580,13 +17643,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1696</v>
+        <v>1702</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>1697</v>
+        <v>1703</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>18</v>
@@ -17599,13 +17662,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1698</v>
+        <v>1704</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>1699</v>
+        <v>1705</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>18</v>
@@ -17618,13 +17681,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1700</v>
+        <v>1706</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>1701</v>
+        <v>1707</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>18</v>
@@ -17637,13 +17700,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1702</v>
+        <v>1708</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1703</v>
+        <v>1709</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>18</v>
@@ -17656,13 +17719,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1704</v>
+        <v>1710</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1705</v>
+        <v>1711</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>18</v>
@@ -17675,13 +17738,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1706</v>
+        <v>1712</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1707</v>
+        <v>1713</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>18</v>
@@ -17694,13 +17757,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1708</v>
+        <v>1714</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>1709</v>
+        <v>1715</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>18</v>
@@ -17713,13 +17776,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1710</v>
+        <v>1716</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>1711</v>
+        <v>1717</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>18</v>
@@ -17732,13 +17795,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>1713</v>
+        <v>1719</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>18</v>
@@ -17751,13 +17814,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1714</v>
+        <v>1720</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>1715</v>
+        <v>1721</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>18</v>
@@ -17770,13 +17833,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1716</v>
+        <v>1722</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>1717</v>
+        <v>1723</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>18</v>
@@ -17789,13 +17852,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1718</v>
+        <v>1724</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>1719</v>
+        <v>1725</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>18</v>
@@ -17825,13 +17888,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="B26" t="s">
-        <v>1605</v>
+        <v>1611</v>
       </c>
       <c r="C26" t="s">
-        <v>1606</v>
+        <v>1612</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -17843,10 +17906,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1603</v>
+        <v>1609</v>
       </c>
       <c r="C27" t="s">
-        <v>1604</v>
+        <v>1610</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -17858,10 +17921,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>1601</v>
+        <v>1607</v>
       </c>
       <c r="C28" t="s">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -17922,13 +17985,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1720</v>
+        <v>1726</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="C2" t="s">
-        <v>1722</v>
+        <v>1728</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>18</v>
@@ -17949,7 +18012,7 @@
         <v>1338</v>
       </c>
       <c r="C3" t="s">
-        <v>1492</v>
+        <v>1498</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>18</v>
@@ -17962,13 +18025,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1723</v>
+        <v>1729</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1724</v>
+        <v>1730</v>
       </c>
       <c r="C4" t="s">
-        <v>1725</v>
+        <v>1731</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>18</v>
@@ -17981,13 +18044,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1726</v>
+        <v>1732</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1494</v>
+        <v>1500</v>
       </c>
       <c r="C5" t="s">
-        <v>1727</v>
+        <v>1733</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>18</v>
@@ -18000,16 +18063,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1728</v>
+        <v>1734</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1729</v>
+        <v>1735</v>
       </c>
       <c r="C6" t="s">
-        <v>1730</v>
+        <v>1736</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1731</v>
+        <v>1737</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -18021,13 +18084,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1732</v>
+        <v>1738</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1733</v>
+        <v>1739</v>
       </c>
       <c r="C7" t="s">
-        <v>1734</v>
+        <v>1740</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>18</v>
@@ -18040,13 +18103,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1735</v>
+        <v>1741</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>1736</v>
+        <v>1742</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>18</v>
@@ -18061,13 +18124,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1737</v>
+        <v>1743</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
-        <v>1738</v>
+        <v>1744</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>18</v>
@@ -18080,13 +18143,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1739</v>
+        <v>1745</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1740</v>
+        <v>1746</v>
       </c>
       <c r="C10" t="s">
-        <v>1741</v>
+        <v>1747</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>18</v>
@@ -18099,13 +18162,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1742</v>
+        <v>1748</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>1743</v>
+        <v>1749</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>18</v>
@@ -18118,13 +18181,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1744</v>
+        <v>1750</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>1745</v>
+        <v>1751</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>18</v>
@@ -18137,13 +18200,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1746</v>
+        <v>1752</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>364</v>
       </c>
       <c r="C13" t="s">
-        <v>1747</v>
+        <v>1753</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>18</v>
@@ -18156,13 +18219,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1748</v>
+        <v>1754</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1749</v>
+        <v>1755</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>18</v>
@@ -18175,13 +18238,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1750</v>
+        <v>1756</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>364</v>
       </c>
       <c r="C15" t="s">
-        <v>1751</v>
+        <v>1757</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>18</v>
@@ -18196,13 +18259,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1752</v>
+        <v>1758</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1753</v>
+        <v>1759</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>18</v>
@@ -18215,7 +18278,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1754</v>
+        <v>1760</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>29</v>
@@ -18234,7 +18297,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1755</v>
+        <v>1761</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>29</v>
@@ -18253,7 +18316,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1756</v>
+        <v>1762</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>29</v>
@@ -18289,13 +18352,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="B22" t="s">
-        <v>1757</v>
+        <v>1763</v>
       </c>
       <c r="C22" t="s">
-        <v>1758</v>
+        <v>1764</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -18307,10 +18370,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1759</v>
+        <v>1765</v>
       </c>
       <c r="C23" t="s">
-        <v>1760</v>
+        <v>1766</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -18322,10 +18385,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1761</v>
+        <v>1767</v>
       </c>
       <c r="C24" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -18337,10 +18400,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1763</v>
+        <v>1769</v>
       </c>
       <c r="C25" t="s">
-        <v>1764</v>
+        <v>1770</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -18368,13 +18431,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1729</v>
+        <v>1735</v>
       </c>
       <c r="B28" t="s">
-        <v>1765</v>
+        <v>1771</v>
       </c>
       <c r="C28" t="s">
-        <v>1766</v>
+        <v>1772</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -18386,10 +18449,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1767</v>
+        <v>1773</v>
       </c>
       <c r="C29" t="s">
-        <v>1768</v>
+        <v>1774</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -18401,10 +18464,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1769</v>
+        <v>1775</v>
       </c>
       <c r="C30" t="s">
-        <v>1770</v>
+        <v>1776</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -18416,10 +18479,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1771</v>
+        <v>1777</v>
       </c>
       <c r="C31" t="s">
-        <v>1772</v>
+        <v>1778</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -18431,10 +18494,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1773</v>
+        <v>1779</v>
       </c>
       <c r="C32" t="s">
-        <v>1774</v>
+        <v>1780</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -18446,10 +18509,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1775</v>
+        <v>1781</v>
       </c>
       <c r="C33" t="s">
-        <v>1776</v>
+        <v>1782</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -18461,10 +18524,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1777</v>
+        <v>1783</v>
       </c>
       <c r="C34" t="s">
-        <v>1778</v>
+        <v>1784</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -18476,10 +18539,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1779</v>
+        <v>1785</v>
       </c>
       <c r="C35" t="s">
-        <v>1780</v>
+        <v>1786</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -18491,10 +18554,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1781</v>
+        <v>1787</v>
       </c>
       <c r="C36" t="s">
-        <v>1782</v>
+        <v>1788</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -18506,10 +18569,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1783</v>
+        <v>1789</v>
       </c>
       <c r="C37" t="s">
-        <v>1784</v>
+        <v>1790</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -18521,10 +18584,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1785</v>
+        <v>1791</v>
       </c>
       <c r="C38" t="s">
-        <v>1786</v>
+        <v>1792</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -18536,10 +18599,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1787</v>
+        <v>1793</v>
       </c>
       <c r="C39" t="s">
-        <v>1788</v>
+        <v>1794</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -18551,10 +18614,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
       <c r="C40" t="s">
-        <v>1790</v>
+        <v>1796</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -18566,10 +18629,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1791</v>
+        <v>1797</v>
       </c>
       <c r="C41" t="s">
-        <v>1792</v>
+        <v>1798</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -18581,10 +18644,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1793</v>
+        <v>1799</v>
       </c>
       <c r="C42" t="s">
-        <v>1794</v>
+        <v>1800</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -18596,10 +18659,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1795</v>
+        <v>1801</v>
       </c>
       <c r="C43" t="s">
-        <v>1796</v>
+        <v>1802</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -18611,10 +18674,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1797</v>
+        <v>1803</v>
       </c>
       <c r="C44" t="s">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -18629,7 +18692,7 @@
         <v>260</v>
       </c>
       <c r="C45" t="s">
-        <v>1799</v>
+        <v>1805</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -18641,10 +18704,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1800</v>
+        <v>1806</v>
       </c>
       <c r="C46" t="s">
-        <v>1801</v>
+        <v>1807</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -18656,10 +18719,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1802</v>
+        <v>1808</v>
       </c>
       <c r="C47" t="s">
-        <v>1803</v>
+        <v>1809</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -18671,10 +18734,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1804</v>
+        <v>1810</v>
       </c>
       <c r="C48" t="s">
-        <v>1805</v>
+        <v>1811</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -18702,13 +18765,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1733</v>
+        <v>1739</v>
       </c>
       <c r="B51" t="s">
-        <v>1806</v>
+        <v>1812</v>
       </c>
       <c r="C51" t="s">
-        <v>1807</v>
+        <v>1813</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -18720,10 +18783,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1808</v>
+        <v>1814</v>
       </c>
       <c r="C52" t="s">
-        <v>1809</v>
+        <v>1815</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -18735,10 +18798,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1810</v>
+        <v>1816</v>
       </c>
       <c r="C53" t="s">
-        <v>1811</v>
+        <v>1817</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -18766,13 +18829,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1740</v>
+        <v>1746</v>
       </c>
       <c r="B56" t="s">
         <v>542</v>
       </c>
       <c r="C56" t="s">
-        <v>1812</v>
+        <v>1818</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -18787,7 +18850,7 @@
         <v>545</v>
       </c>
       <c r="C57" t="s">
-        <v>1813</v>
+        <v>1819</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -18799,10 +18862,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>1814</v>
+        <v>1820</v>
       </c>
       <c r="C58" t="s">
-        <v>1815</v>
+        <v>1821</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -18814,10 +18877,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>1816</v>
+        <v>1822</v>
       </c>
       <c r="C59" t="s">
-        <v>1817</v>
+        <v>1823</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -18881,16 +18944,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1818</v>
+        <v>1824</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1819</v>
+        <v>1825</v>
       </c>
       <c r="C2" t="s">
-        <v>1820</v>
+        <v>1826</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1821</v>
+        <v>1827</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -18902,16 +18965,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1822</v>
+        <v>1828</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1823</v>
+        <v>1829</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1824</v>
+        <v>1830</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -18923,16 +18986,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1825</v>
+        <v>1831</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>1826</v>
+        <v>1832</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1827</v>
+        <v>1833</v>
       </c>
       <c r="E4"/>
       <c r="G4" s="17" t="s">
@@ -18984,13 +19047,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1828</v>
+        <v>1834</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>1829</v>
+        <v>1835</v>
       </c>
       <c r="D7" s="17" t="s">
         <v>18</v>
@@ -19003,16 +19066,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1830</v>
+        <v>1836</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1831</v>
+        <v>1837</v>
       </c>
       <c r="C8" t="s">
-        <v>1832</v>
+        <v>1838</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1833</v>
+        <v>1839</v>
       </c>
       <c r="E8"/>
       <c r="G8" s="17" t="s">
@@ -19022,16 +19085,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1834</v>
+        <v>1840</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>1835</v>
+        <v>1841</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1836</v>
+        <v>1842</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="17" t="s">
@@ -19041,16 +19104,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1837</v>
+        <v>1843</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>1838</v>
+        <v>1844</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="E10"/>
       <c r="G10" s="17" t="s">
@@ -19060,16 +19123,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1840</v>
+        <v>1846</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1841</v>
+        <v>1847</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1842</v>
+        <v>1848</v>
       </c>
       <c r="E11"/>
       <c r="G11" s="17" t="s">
@@ -19079,16 +19142,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1843</v>
+        <v>1849</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1844</v>
+        <v>1850</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1845</v>
+        <v>1851</v>
       </c>
       <c r="E12"/>
       <c r="G12" s="17" t="s">
@@ -19155,13 +19218,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1846</v>
+        <v>1852</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1847</v>
+        <v>1853</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>18</v>
@@ -19248,13 +19311,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1819</v>
+        <v>1825</v>
       </c>
       <c r="B22" t="s">
-        <v>1848</v>
+        <v>1854</v>
       </c>
       <c r="C22" t="s">
-        <v>1849</v>
+        <v>1855</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -19269,7 +19332,7 @@
         <v>536</v>
       </c>
       <c r="C23" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -19281,16 +19344,16 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1850</v>
+        <v>1856</v>
       </c>
       <c r="C24" t="s">
-        <v>1851</v>
+        <v>1857</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>1852</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="26">
@@ -19312,13 +19375,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1831</v>
+        <v>1837</v>
       </c>
       <c r="B27" t="s">
-        <v>1853</v>
+        <v>1859</v>
       </c>
       <c r="C27" t="s">
-        <v>1854</v>
+        <v>1860</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -19360,10 +19423,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1855</v>
+        <v>1861</v>
       </c>
       <c r="C30" t="s">
-        <v>1856</v>
+        <v>1862</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -19375,10 +19438,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1857</v>
+        <v>1863</v>
       </c>
       <c r="C31" t="s">
-        <v>1858</v>
+        <v>1864</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -20330,13 +20393,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1723</v>
+        <v>1729</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>1724</v>
+        <v>1730</v>
       </c>
       <c r="C2" t="s">
-        <v>1762</v>
+        <v>1768</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>18</v>
@@ -20354,10 +20417,10 @@
         <v>356</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="C3" t="s">
-        <v>1859</v>
+        <v>1865</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>18</v>
@@ -20372,13 +20435,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1860</v>
+        <v>1866</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1861</v>
+        <v>1867</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>18</v>
@@ -20459,13 +20522,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1862</v>
+        <v>1868</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1863</v>
+        <v>1869</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>18</v>
@@ -20560,7 +20623,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>1864</v>
+        <v>1870</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>18</v>
@@ -20579,7 +20642,7 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1865</v>
+        <v>1871</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>18</v>
@@ -20592,10 +20655,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1866</v>
+        <v>1872</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>1867</v>
+        <v>1873</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -20611,7 +20674,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1868</v>
+        <v>1874</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>480</v>
@@ -20630,7 +20693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1869</v>
+        <v>1875</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>480</v>
@@ -20685,7 +20748,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1867</v>
+        <v>1873</v>
       </c>
       <c r="B15" t="s">
         <v>278</v>
@@ -21120,13 +21183,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1862</v>
+        <v>1868</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1863</v>
+        <v>1869</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>18</v>
@@ -21139,13 +21202,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1870</v>
+        <v>1876</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1871</v>
+        <v>1877</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>18</v>
@@ -21158,13 +21221,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1872</v>
+        <v>1878</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>1873</v>
+        <v>1879</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>18</v>
@@ -21177,7 +21240,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1869</v>
+        <v>1875</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>480</v>
@@ -21264,13 +21327,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1862</v>
+        <v>1868</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1863</v>
+        <v>1869</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>18</v>
@@ -21283,13 +21346,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1870</v>
+        <v>1876</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1871</v>
+        <v>1877</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>18</v>
@@ -21302,13 +21365,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1872</v>
+        <v>1878</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>1873</v>
+        <v>1879</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
@@ -21340,7 +21403,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1869</v>
+        <v>1875</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>480</v>
@@ -21427,13 +21490,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1862</v>
+        <v>1868</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>1863</v>
+        <v>1869</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>18</v>
@@ -21484,7 +21547,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1869</v>
+        <v>1875</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>480</v>
@@ -21571,13 +21634,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1874</v>
+        <v>1880</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>480</v>
       </c>
       <c r="C2" t="s">
-        <v>1875</v>
+        <v>1881</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>18</v>
@@ -21590,13 +21653,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1876</v>
+        <v>1882</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1877</v>
+        <v>1883</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>18</v>
@@ -21647,13 +21710,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1878</v>
+        <v>1884</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1844</v>
+        <v>1850</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>18</v>
@@ -21704,11 +21767,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1879</v>
+        <v>1885</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" t="s">
-        <v>1880</v>
+        <v>1886</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>18</v>
@@ -21797,7 +21860,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1881</v>
+        <v>1887</v>
       </c>
       <c r="B14" s="23" t="s">
         <v>52</v>
@@ -21822,7 +21885,7 @@
         <v>471</v>
       </c>
       <c r="C15" t="s">
-        <v>1882</v>
+        <v>1888</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>18</v>
@@ -21835,13 +21898,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1883</v>
+        <v>1889</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>364</v>
       </c>
       <c r="C16" t="s">
-        <v>1884</v>
+        <v>1890</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>18</v>
@@ -21854,16 +21917,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1885</v>
+        <v>1891</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>1886</v>
+        <v>1892</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>1887</v>
+        <v>1893</v>
       </c>
       <c r="E17"/>
       <c r="G17" s="23" t="s">
@@ -21873,10 +21936,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1888</v>
+        <v>1894</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1889</v>
+        <v>1895</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
@@ -22768,13 +22831,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>1889</v>
+        <v>1895</v>
       </c>
       <c r="B79" t="s">
-        <v>1890</v>
+        <v>1896</v>
       </c>
       <c r="C79" t="s">
-        <v>1891</v>
+        <v>1897</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -22786,10 +22849,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>1892</v>
+        <v>1898</v>
       </c>
       <c r="C80" t="s">
-        <v>1893</v>
+        <v>1899</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -22801,10 +22864,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>1894</v>
+        <v>1900</v>
       </c>
       <c r="C81" t="s">
-        <v>1895</v>
+        <v>1901</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -22816,10 +22879,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>1896</v>
+        <v>1902</v>
       </c>
       <c r="C82" t="s">
-        <v>1897</v>
+        <v>1903</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -22831,10 +22894,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>1898</v>
+        <v>1904</v>
       </c>
       <c r="C83" t="s">
-        <v>1899</v>
+        <v>1905</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -22846,10 +22909,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>1900</v>
+        <v>1906</v>
       </c>
       <c r="C84" t="s">
-        <v>1901</v>
+        <v>1907</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -22861,10 +22924,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>1902</v>
+        <v>1908</v>
       </c>
       <c r="C85" t="s">
-        <v>1903</v>
+        <v>1909</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -22890,12 +22953,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1904</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1905</v>
+        <v>1911</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6824" uniqueCount="1912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6832" uniqueCount="1916">
   <si>
     <t>Field</t>
   </si>
@@ -5761,10 +5761,22 @@
     <t>Español (Ecuador)</t>
   </si>
   <si>
+    <t>ES_CU</t>
+  </si>
+  <si>
+    <t>Español (Cuba)</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Italiano</t>
+  </si>
+  <si>
     <t>FI</t>
   </si>
   <si>
-    <t>Suomi</t>
+    <t>Suom</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -7268,7 +7280,7 @@
 </file>
 
 <file path=xl/tables/table95.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="95" name="UserLanguage" displayName="UserLanguage" ref="A78:E85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="95" name="UserLanguage" displayName="UserLanguage" ref="A78:E87">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -21593,7 +21605,7 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -22933,6 +22945,36 @@
         <v>18</v>
       </c>
       <c r="E85" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86"/>
+      <c r="B86" t="s">
+        <v>1910</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87" t="s">
+        <v>1912</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1913</v>
+      </c>
+      <c r="D87" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" t="s">
         <v>18</v>
       </c>
     </row>
@@ -22953,12 +22995,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1910</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1911</v>
+        <v>1915</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -1228,6 +1228,12 @@
     <t>Describe sequelae</t>
   </si>
   <si>
+    <t>facilityType</t>
+  </si>
+  <si>
+    <t>FacilityType</t>
+  </si>
+  <si>
     <t>healthFacility</t>
   </si>
   <si>
@@ -1582,12 +1588,6 @@
     <t>Trimester</t>
   </si>
   <si>
-    <t>facilityType</t>
-  </si>
-  <si>
-    <t>FacilityType</t>
-  </si>
-  <si>
     <t>BUBONIC</t>
   </si>
   <si>
@@ -1735,6 +1735,246 @@
     <t>No</t>
   </si>
   <si>
+    <t>ASSOCIATION</t>
+  </si>
+  <si>
+    <t>Association, club</t>
+  </si>
+  <si>
+    <t>BUSINESS</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>CAMPSITE</t>
+  </si>
+  <si>
+    <t>Campsite</t>
+  </si>
+  <si>
+    <t>CANTINE</t>
+  </si>
+  <si>
+    <t>Cantine</t>
+  </si>
+  <si>
+    <t>CHILDRENS_DAY_CARE</t>
+  </si>
+  <si>
+    <t>Children's day care</t>
+  </si>
+  <si>
+    <t>CHILDRENS_HOME</t>
+  </si>
+  <si>
+    <t>Children's home</t>
+  </si>
+  <si>
+    <t>CORRECTIONAL_FACILITY</t>
+  </si>
+  <si>
+    <t>Correctional facility</t>
+  </si>
+  <si>
+    <t>CRUISE_SHIP</t>
+  </si>
+  <si>
+    <t>Cruise ship</t>
+  </si>
+  <si>
+    <t>ELDERLY_CARE</t>
+  </si>
+  <si>
+    <t>Elderly care</t>
+  </si>
+  <si>
+    <t>EVENT_VENUE</t>
+  </si>
+  <si>
+    <t>Event venue</t>
+  </si>
+  <si>
+    <t>FOOD_STALL</t>
+  </si>
+  <si>
+    <t>Food stall</t>
+  </si>
+  <si>
+    <t>HOLIDAY_CAMP</t>
+  </si>
+  <si>
+    <t>Holiday camp</t>
+  </si>
+  <si>
+    <t>HOMELESS_SHELTER</t>
+  </si>
+  <si>
+    <t>Homeless shelter</t>
+  </si>
+  <si>
+    <t>HOSTEL</t>
+  </si>
+  <si>
+    <t>Hostel, dormitory</t>
+  </si>
+  <si>
+    <t>HOTEL</t>
+  </si>
+  <si>
+    <t>Hotel, B&amp;B, inn, lodge</t>
+  </si>
+  <si>
+    <t>KINDERGARTEN</t>
+  </si>
+  <si>
+    <t>Kindergarten/After school care</t>
+  </si>
+  <si>
+    <t>LABORATORY</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
+  </si>
+  <si>
+    <t>MASS_ACCOMMODATION</t>
+  </si>
+  <si>
+    <t>Mass accomodation (e.g. guest and harvest workers)</t>
+  </si>
+  <si>
+    <t>MILITARY_BARRACKS</t>
+  </si>
+  <si>
+    <t>Military barracks</t>
+  </si>
+  <si>
+    <t>MOBILE_NURSING_SERVICE</t>
+  </si>
+  <si>
+    <t>Mobile nursing service</t>
+  </si>
+  <si>
+    <t>OTHER_ACCOMMODATION</t>
+  </si>
+  <si>
+    <t>Other Accomodation</t>
+  </si>
+  <si>
+    <t>OTHER_CARE_FACILITY</t>
+  </si>
+  <si>
+    <t>Other Care facility</t>
+  </si>
+  <si>
+    <t>OTHER_CATERING_OUTLET</t>
+  </si>
+  <si>
+    <t>Other Catering outlet</t>
+  </si>
+  <si>
+    <t>OTHER_EDUCATIONAL_FACILITY</t>
+  </si>
+  <si>
+    <t>Other Educational facility</t>
+  </si>
+  <si>
+    <t>OTHER_LEISURE_FACILITY</t>
+  </si>
+  <si>
+    <t>Other Leisure facility</t>
+  </si>
+  <si>
+    <t>OTHER_MEDICAL_FACILITY</t>
+  </si>
+  <si>
+    <t>Other Medical facility</t>
+  </si>
+  <si>
+    <t>OTHER_RESIDENCE</t>
+  </si>
+  <si>
+    <t>Other Residence</t>
+  </si>
+  <si>
+    <t>OTHER_WORKING_PLACE</t>
+  </si>
+  <si>
+    <t>Other Working place/company</t>
+  </si>
+  <si>
+    <t>OUTPATIENT_TREATMENT_FACILITY</t>
+  </si>
+  <si>
+    <t>Outpatient treatment facility</t>
+  </si>
+  <si>
+    <t>PLACE_OF_WORSHIP</t>
+  </si>
+  <si>
+    <t>Place of worship</t>
+  </si>
+  <si>
+    <t>PUBLIC_PLACE</t>
+  </si>
+  <si>
+    <t>Public place/playground</t>
+  </si>
+  <si>
+    <t>REFUGEE_ACCOMMODATION</t>
+  </si>
+  <si>
+    <t>Refrugee accomodation/initial reception facility</t>
+  </si>
+  <si>
+    <t>REHAB_FACILITY</t>
+  </si>
+  <si>
+    <t>Rehab facility</t>
+  </si>
+  <si>
+    <t>RESTAURANT</t>
+  </si>
+  <si>
+    <t>Restaurant/tavern</t>
+  </si>
+  <si>
+    <t>RETIREMENT_HOME</t>
+  </si>
+  <si>
+    <t>Retirement home</t>
+  </si>
+  <si>
+    <t>SCHOOL</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>SWIMMING_POOL</t>
+  </si>
+  <si>
+    <t>Swimming pool</t>
+  </si>
+  <si>
+    <t>THEATER</t>
+  </si>
+  <si>
+    <t>Theater/cinema</t>
+  </si>
+  <si>
+    <t>UNIVERSITY</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>ZOO</t>
+  </si>
+  <si>
+    <t>Zoological garden, animal park</t>
+  </si>
+  <si>
     <t>VACCINATED</t>
   </si>
   <si>
@@ -1840,12 +2080,6 @@
     <t>Community facility</t>
   </si>
   <si>
-    <t>LABORATORY</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
-  </si>
-  <si>
     <t>OWN_DETERMINATION</t>
   </si>
   <si>
@@ -1880,240 +2114,6 @@
   </si>
   <si>
     <t>Third</t>
-  </si>
-  <si>
-    <t>ASSOCIATION</t>
-  </si>
-  <si>
-    <t>Association, club</t>
-  </si>
-  <si>
-    <t>BUSINESS</t>
-  </si>
-  <si>
-    <t>Business</t>
-  </si>
-  <si>
-    <t>CAMPSITE</t>
-  </si>
-  <si>
-    <t>Campsite</t>
-  </si>
-  <si>
-    <t>CANTINE</t>
-  </si>
-  <si>
-    <t>Cantine</t>
-  </si>
-  <si>
-    <t>CHILDRENS_DAY_CARE</t>
-  </si>
-  <si>
-    <t>Children's day care</t>
-  </si>
-  <si>
-    <t>CHILDRENS_HOME</t>
-  </si>
-  <si>
-    <t>Children's home</t>
-  </si>
-  <si>
-    <t>CORRECTIONAL_FACILITY</t>
-  </si>
-  <si>
-    <t>Correctional facility</t>
-  </si>
-  <si>
-    <t>CRUISE_SHIP</t>
-  </si>
-  <si>
-    <t>Cruise ship</t>
-  </si>
-  <si>
-    <t>ELDERLY_CARE</t>
-  </si>
-  <si>
-    <t>Elderly care</t>
-  </si>
-  <si>
-    <t>EVENT_VENUE</t>
-  </si>
-  <si>
-    <t>Event venue</t>
-  </si>
-  <si>
-    <t>FOOD_STALL</t>
-  </si>
-  <si>
-    <t>Food stall</t>
-  </si>
-  <si>
-    <t>HOLIDAY_CAMP</t>
-  </si>
-  <si>
-    <t>Holiday camp</t>
-  </si>
-  <si>
-    <t>HOMELESS_SHELTER</t>
-  </si>
-  <si>
-    <t>Homeless shelter</t>
-  </si>
-  <si>
-    <t>HOSTEL</t>
-  </si>
-  <si>
-    <t>Hostel, dormitory</t>
-  </si>
-  <si>
-    <t>HOTEL</t>
-  </si>
-  <si>
-    <t>Hotel, B&amp;B, inn, lodge</t>
-  </si>
-  <si>
-    <t>KINDERGARTEN</t>
-  </si>
-  <si>
-    <t>Kindergarten/After school care</t>
-  </si>
-  <si>
-    <t>MASS_ACCOMMODATION</t>
-  </si>
-  <si>
-    <t>Mass accomodation (e.g. guest and harvest workers)</t>
-  </si>
-  <si>
-    <t>MILITARY_BARRACKS</t>
-  </si>
-  <si>
-    <t>Military barracks</t>
-  </si>
-  <si>
-    <t>MOBILE_NURSING_SERVICE</t>
-  </si>
-  <si>
-    <t>Mobile nursing service</t>
-  </si>
-  <si>
-    <t>OTHER_ACCOMMODATION</t>
-  </si>
-  <si>
-    <t>Other Accomodation</t>
-  </si>
-  <si>
-    <t>OTHER_CARE_FACILITY</t>
-  </si>
-  <si>
-    <t>Other Care facility</t>
-  </si>
-  <si>
-    <t>OTHER_CATERING_OUTLET</t>
-  </si>
-  <si>
-    <t>Other Catering outlet</t>
-  </si>
-  <si>
-    <t>OTHER_EDUCATIONAL_FACILITY</t>
-  </si>
-  <si>
-    <t>Other Educational facility</t>
-  </si>
-  <si>
-    <t>OTHER_LEISURE_FACILITY</t>
-  </si>
-  <si>
-    <t>Other Leisure facility</t>
-  </si>
-  <si>
-    <t>OTHER_MEDICAL_FACILITY</t>
-  </si>
-  <si>
-    <t>Other Medical facility</t>
-  </si>
-  <si>
-    <t>OTHER_RESIDENCE</t>
-  </si>
-  <si>
-    <t>Other Residence</t>
-  </si>
-  <si>
-    <t>OTHER_WORKING_PLACE</t>
-  </si>
-  <si>
-    <t>Other Working place/company</t>
-  </si>
-  <si>
-    <t>OUTPATIENT_TREATMENT_FACILITY</t>
-  </si>
-  <si>
-    <t>Outpatient treatment facility</t>
-  </si>
-  <si>
-    <t>PLACE_OF_WORSHIP</t>
-  </si>
-  <si>
-    <t>Place of worship</t>
-  </si>
-  <si>
-    <t>PUBLIC_PLACE</t>
-  </si>
-  <si>
-    <t>Public place/playground</t>
-  </si>
-  <si>
-    <t>REFUGEE_ACCOMMODATION</t>
-  </si>
-  <si>
-    <t>Refrugee accomodation/initial reception facility</t>
-  </si>
-  <si>
-    <t>REHAB_FACILITY</t>
-  </si>
-  <si>
-    <t>Rehab facility</t>
-  </si>
-  <si>
-    <t>RESTAURANT</t>
-  </si>
-  <si>
-    <t>Restaurant/tavern</t>
-  </si>
-  <si>
-    <t>RETIREMENT_HOME</t>
-  </si>
-  <si>
-    <t>Retirement home</t>
-  </si>
-  <si>
-    <t>SCHOOL</t>
-  </si>
-  <si>
-    <t>School</t>
-  </si>
-  <si>
-    <t>SWIMMING_POOL</t>
-  </si>
-  <si>
-    <t>Swimming pool</t>
-  </si>
-  <si>
-    <t>THEATER</t>
-  </si>
-  <si>
-    <t>Theater/cinema</t>
-  </si>
-  <si>
-    <t>UNIVERSITY</t>
-  </si>
-  <si>
-    <t>University</t>
-  </si>
-  <si>
-    <t>ZOO</t>
-  </si>
-  <si>
-    <t>Zoological garden, animal park</t>
   </si>
   <si>
     <t>admittedToHealthFacility</t>
@@ -6457,7 +6457,7 @@
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="CaseVaccination" displayName="CaseVaccination" ref="A174:E177">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="CaseFacilityType" displayName="CaseFacilityType" ref="A174:E215">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6471,7 +6471,7 @@
 </file>
 
 <file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="CaseVaccinationInfoSource" displayName="CaseVaccinationInfoSource" ref="A179:E181">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="CaseVaccination" displayName="CaseVaccination" ref="A217:E220">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6485,7 +6485,7 @@
 </file>
 
 <file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="CaseHospitalWardType" displayName="CaseHospitalWardType" ref="A183:E192">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="CaseVaccinationInfoSource" displayName="CaseVaccinationInfoSource" ref="A222:E224">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6499,7 +6499,7 @@
 </file>
 
 <file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="CaseCaseOrigin" displayName="CaseCaseOrigin" ref="A194:E196">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="CaseHospitalWardType" displayName="CaseHospitalWardType" ref="A226:E235">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6513,7 +6513,7 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="CaseQuarantineType" displayName="CaseQuarantineType" ref="A198:E203">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="CaseCaseOrigin" displayName="CaseCaseOrigin" ref="A237:E239">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6527,7 +6527,7 @@
 </file>
 
 <file path=xl/tables/table27.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="CaseReportingType" displayName="CaseReportingType" ref="A205:E214">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="CaseQuarantineType" displayName="CaseQuarantineType" ref="A241:E246">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6541,7 +6541,7 @@
 </file>
 
 <file path=xl/tables/table28.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="CaseTrimester" displayName="CaseTrimester" ref="A216:E220">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="28" name="CaseReportingType" displayName="CaseReportingType" ref="A248:E257">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6555,7 +6555,7 @@
 </file>
 
 <file path=xl/tables/table29.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="CaseFacilityType" displayName="CaseFacilityType" ref="A222:E263">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="29" name="CaseTrimester" displayName="CaseTrimester" ref="A259:E263">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -10242,7 +10242,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>1413</v>
@@ -10261,10 +10261,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -11402,7 +11402,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>29</v>
@@ -11421,7 +11421,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>29</v>
@@ -11440,7 +11440,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>29</v>
@@ -11673,7 +11673,7 @@
         <v>1458</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C23" t="s">
         <v>1459</v>
@@ -11746,13 +11746,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>18</v>
@@ -11768,7 +11768,7 @@
         <v>1468</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C28" t="s">
         <v>1469</v>
@@ -11841,13 +11841,13 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C32" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>18</v>
@@ -11860,13 +11860,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>18</v>
@@ -11879,13 +11879,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>18</v>
@@ -11898,13 +11898,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C35" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>18</v>
@@ -11995,13 +11995,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>18</v>
@@ -12014,13 +12014,13 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C41" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>18</v>
@@ -12033,13 +12033,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C42" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>18</v>
@@ -12052,13 +12052,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C43" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>18</v>
@@ -12071,13 +12071,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>18</v>
@@ -12090,13 +12090,13 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>393</v>
       </c>
       <c r="C45" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>18</v>
@@ -12109,13 +12109,13 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>18</v>
@@ -12128,13 +12128,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>393</v>
       </c>
       <c r="C47" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>18</v>
@@ -12147,13 +12147,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>18</v>
@@ -12166,13 +12166,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>18</v>
@@ -12185,13 +12185,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C50" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>18</v>
@@ -13783,13 +13783,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B163" t="s">
-        <v>588</v>
+        <v>668</v>
       </c>
       <c r="C163" t="s">
-        <v>589</v>
+        <v>669</v>
       </c>
       <c r="D163" t="s">
         <v>18</v>
@@ -13801,10 +13801,10 @@
     <row r="164">
       <c r="A164"/>
       <c r="B164" t="s">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="C164" t="s">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="D164" t="s">
         <v>18</v>
@@ -13819,7 +13819,7 @@
         <v>274</v>
       </c>
       <c r="C165" t="s">
-        <v>592</v>
+        <v>672</v>
       </c>
       <c r="D165" t="s">
         <v>18</v>
@@ -14040,13 +14040,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>18</v>
@@ -14059,7 +14059,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>29</v>
@@ -14078,7 +14078,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>29</v>
@@ -14097,7 +14097,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>29</v>
@@ -15248,7 +15248,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>29</v>
@@ -15267,7 +15267,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>29</v>
@@ -15286,7 +15286,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>29</v>
@@ -15372,7 +15372,7 @@
         <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>18</v>
@@ -15507,7 +15507,7 @@
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>18</v>
@@ -15561,7 +15561,7 @@
         <v>1621</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C26" t="s">
         <v>1622</v>
@@ -15580,7 +15580,7 @@
         <v>1623</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C27" t="s">
         <v>1624</v>
@@ -15618,7 +15618,7 @@
         <v>1628</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C29" t="s">
         <v>1629</v>
@@ -15637,7 +15637,7 @@
         <v>1630</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C30" t="s">
         <v>1631</v>
@@ -16467,7 +16467,7 @@
         <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D8" s="14" t="s">
         <v>1715</v>
@@ -16567,7 +16567,7 @@
         <v>1724</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C13" t="s">
         <v>1725</v>
@@ -16588,7 +16588,7 @@
         <v>1727</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C14" t="s">
         <v>1728</v>
@@ -19454,7 +19454,7 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D3" s="17" t="s">
         <v>18</v>
@@ -19815,13 +19815,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>364</v>
       </c>
       <c r="C22" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D22" s="17" t="s">
         <v>18</v>
@@ -19853,7 +19853,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B24" s="17" t="s">
         <v>29</v>
@@ -19872,7 +19872,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B25" s="17" t="s">
         <v>29</v>
@@ -19891,7 +19891,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B26" s="17" t="s">
         <v>29</v>
@@ -20103,10 +20103,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="C42" t="s">
-        <v>591</v>
+        <v>671</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -20148,7 +20148,7 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>673</v>
+        <v>626</v>
       </c>
       <c r="C45" t="s">
         <v>1966</v>
@@ -21449,7 +21449,7 @@
         <v>1982</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>516</v>
+        <v>398</v>
       </c>
       <c r="C9" t="s">
         <v>1983</v>
@@ -21468,7 +21468,7 @@
         <v>1984</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -21487,7 +21487,7 @@
         <v>1985</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
@@ -21503,13 +21503,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>18</v>
@@ -21539,13 +21539,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>516</v>
+        <v>398</v>
       </c>
       <c r="B15" t="s">
-        <v>615</v>
+        <v>566</v>
       </c>
       <c r="C15" t="s">
-        <v>616</v>
+        <v>567</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -21557,10 +21557,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>617</v>
+        <v>568</v>
       </c>
       <c r="C16" t="s">
-        <v>618</v>
+        <v>569</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -21572,10 +21572,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>619</v>
+        <v>570</v>
       </c>
       <c r="C17" t="s">
-        <v>620</v>
+        <v>571</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -21587,10 +21587,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>621</v>
+        <v>572</v>
       </c>
       <c r="C18" t="s">
-        <v>622</v>
+        <v>573</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -21602,10 +21602,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>623</v>
+        <v>574</v>
       </c>
       <c r="C19" t="s">
-        <v>624</v>
+        <v>575</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -21617,10 +21617,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>625</v>
+        <v>576</v>
       </c>
       <c r="C20" t="s">
-        <v>626</v>
+        <v>577</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -21632,10 +21632,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>627</v>
+        <v>578</v>
       </c>
       <c r="C21" t="s">
-        <v>628</v>
+        <v>579</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -21647,10 +21647,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>629</v>
+        <v>580</v>
       </c>
       <c r="C22" t="s">
-        <v>630</v>
+        <v>581</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -21662,10 +21662,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>631</v>
+        <v>582</v>
       </c>
       <c r="C23" t="s">
-        <v>632</v>
+        <v>583</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -21677,10 +21677,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>633</v>
+        <v>584</v>
       </c>
       <c r="C24" t="s">
-        <v>634</v>
+        <v>585</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -21692,10 +21692,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>635</v>
+        <v>586</v>
       </c>
       <c r="C25" t="s">
-        <v>636</v>
+        <v>587</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -21707,10 +21707,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>637</v>
+        <v>588</v>
       </c>
       <c r="C26" t="s">
-        <v>638</v>
+        <v>589</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -21722,10 +21722,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>639</v>
+        <v>590</v>
       </c>
       <c r="C27" t="s">
-        <v>640</v>
+        <v>591</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -21752,10 +21752,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>641</v>
+        <v>592</v>
       </c>
       <c r="C29" t="s">
-        <v>642</v>
+        <v>593</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -21767,10 +21767,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>643</v>
+        <v>594</v>
       </c>
       <c r="C30" t="s">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -21782,10 +21782,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>645</v>
+        <v>596</v>
       </c>
       <c r="C31" t="s">
-        <v>646</v>
+        <v>597</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -21797,10 +21797,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C32" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -21812,10 +21812,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>647</v>
+        <v>600</v>
       </c>
       <c r="C33" t="s">
-        <v>648</v>
+        <v>601</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -21827,10 +21827,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>649</v>
+        <v>602</v>
       </c>
       <c r="C34" t="s">
-        <v>650</v>
+        <v>603</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -21842,10 +21842,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>651</v>
+        <v>604</v>
       </c>
       <c r="C35" t="s">
-        <v>652</v>
+        <v>605</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -21857,10 +21857,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>653</v>
+        <v>606</v>
       </c>
       <c r="C36" t="s">
-        <v>654</v>
+        <v>607</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -21872,10 +21872,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>655</v>
+        <v>608</v>
       </c>
       <c r="C37" t="s">
-        <v>656</v>
+        <v>609</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -21887,10 +21887,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>657</v>
+        <v>610</v>
       </c>
       <c r="C38" t="s">
-        <v>658</v>
+        <v>611</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -21902,10 +21902,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>659</v>
+        <v>612</v>
       </c>
       <c r="C39" t="s">
-        <v>660</v>
+        <v>613</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -21917,10 +21917,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>661</v>
+        <v>614</v>
       </c>
       <c r="C40" t="s">
-        <v>662</v>
+        <v>615</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -21932,10 +21932,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>663</v>
+        <v>616</v>
       </c>
       <c r="C41" t="s">
-        <v>664</v>
+        <v>617</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -21947,10 +21947,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>665</v>
+        <v>618</v>
       </c>
       <c r="C42" t="s">
-        <v>666</v>
+        <v>619</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -21962,10 +21962,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>667</v>
+        <v>620</v>
       </c>
       <c r="C43" t="s">
-        <v>668</v>
+        <v>621</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -21977,10 +21977,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>669</v>
+        <v>622</v>
       </c>
       <c r="C44" t="s">
-        <v>670</v>
+        <v>623</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -21992,10 +21992,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>671</v>
+        <v>624</v>
       </c>
       <c r="C45" t="s">
-        <v>672</v>
+        <v>625</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -22007,10 +22007,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>673</v>
+        <v>626</v>
       </c>
       <c r="C46" t="s">
-        <v>674</v>
+        <v>627</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -22022,10 +22022,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>675</v>
+        <v>628</v>
       </c>
       <c r="C47" t="s">
-        <v>676</v>
+        <v>629</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -22037,10 +22037,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>677</v>
+        <v>630</v>
       </c>
       <c r="C48" t="s">
-        <v>678</v>
+        <v>631</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -22052,10 +22052,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>679</v>
+        <v>632</v>
       </c>
       <c r="C49" t="s">
-        <v>680</v>
+        <v>633</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -22067,10 +22067,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>681</v>
+        <v>634</v>
       </c>
       <c r="C50" t="s">
-        <v>682</v>
+        <v>635</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -22082,10 +22082,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>683</v>
+        <v>636</v>
       </c>
       <c r="C51" t="s">
-        <v>684</v>
+        <v>637</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -22097,10 +22097,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>685</v>
+        <v>638</v>
       </c>
       <c r="C52" t="s">
-        <v>686</v>
+        <v>639</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -22112,10 +22112,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>687</v>
+        <v>640</v>
       </c>
       <c r="C53" t="s">
-        <v>688</v>
+        <v>641</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -22127,10 +22127,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>689</v>
+        <v>642</v>
       </c>
       <c r="C54" t="s">
-        <v>690</v>
+        <v>643</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -22142,10 +22142,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>691</v>
+        <v>644</v>
       </c>
       <c r="C55" t="s">
-        <v>692</v>
+        <v>645</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -22589,7 +22589,7 @@
         <v>1985</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -22605,13 +22605,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B6" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>18</v>
@@ -22771,7 +22771,7 @@
         <v>1985</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -22787,13 +22787,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B7" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>18</v>
@@ -22915,7 +22915,7 @@
         <v>1985</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
@@ -22931,13 +22931,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D6" s="22" t="s">
         <v>18</v>
@@ -23002,7 +23002,7 @@
         <v>1992</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C2" t="s">
         <v>1993</v>
@@ -23206,13 +23206,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B13" s="23" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D13" s="23" t="s">
         <v>18</v>
@@ -23231,7 +23231,7 @@
         <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>18</v>
@@ -23244,10 +23244,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C15" t="s">
         <v>2001</v>
@@ -24983,38 +24983,36 @@
         <v>397</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>52</v>
+        <v>398</v>
       </c>
       <c r="C27" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E27"/>
       <c r="G27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H27" t="b">
-        <v>1</v>
-      </c>
+      <c r="H27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>399</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s">
         <v>400</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>55</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E28"/>
+        <v>401</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
       <c r="G28" s="3" t="s">
         <v>12</v>
       </c>
@@ -25024,60 +25022,60 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>393</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>402</v>
+        <v>55</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>403</v>
+        <v>18</v>
       </c>
       <c r="E29"/>
       <c r="G29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H29"/>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>403</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C30" t="s">
         <v>404</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="C30" t="s">
-        <v>406</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="E30"/>
       <c r="G30" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="H30" t="b">
-        <v>1</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>406</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C31" t="s">
         <v>408</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" t="s">
-        <v>409</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E31"/>
       <c r="G31" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -25085,20 +25083,20 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
+        <v>410</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
         <v>411</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" t="s">
-        <v>412</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E32"/>
       <c r="G32" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -25106,29 +25104,31 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>413</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
         <v>414</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="C33" t="s">
-        <v>416</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E33"/>
       <c r="G33" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="H33"/>
+        <v>415</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>416</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C34" t="s">
         <v>418</v>
@@ -25138,30 +25138,30 @@
       </c>
       <c r="E34"/>
       <c r="G34" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="H34" t="b">
-        <v>1</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="H34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>419</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
         <v>420</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C35" t="s">
-        <v>421</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E35"/>
       <c r="G35" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H35"/>
+        <v>421</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
@@ -25187,7 +25187,7 @@
         <v>424</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>364</v>
+        <v>393</v>
       </c>
       <c r="C37" t="s">
         <v>425</v>
@@ -25197,18 +25197,16 @@
       </c>
       <c r="E37"/>
       <c r="G37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H37" t="b">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="H37"/>
     </row>
     <row r="38">
       <c r="A38" t="s">
         <v>426</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>9</v>
+        <v>364</v>
       </c>
       <c r="C38" t="s">
         <v>427</v>
@@ -25220,7 +25218,9 @@
       <c r="G38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H38"/>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
@@ -25265,26 +25265,26 @@
         <v>432</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" t="s">
         <v>433</v>
-      </c>
-      <c r="C41" t="s">
-        <v>434</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E41"/>
       <c r="G41" s="3" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="H41"/>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>434</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>435</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C42" t="s">
         <v>436</v>
@@ -25303,7 +25303,7 @@
         <v>437</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>364</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
         <v>438</v>
@@ -25313,7 +25313,7 @@
       </c>
       <c r="E43"/>
       <c r="G43" s="3" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H43"/>
     </row>
@@ -25322,13 +25322,13 @@
         <v>439</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>29</v>
+        <v>364</v>
       </c>
       <c r="C44" t="s">
         <v>440</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>441</v>
+        <v>18</v>
       </c>
       <c r="E44"/>
       <c r="G44" s="3" t="s">
@@ -25338,16 +25338,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C45" t="s">
+        <v>442</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>443</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>444</v>
       </c>
       <c r="E45"/>
       <c r="G45" s="3" t="s">
@@ -25357,16 +25357,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C46" t="s">
+        <v>445</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="E46"/>
       <c r="G46" s="3" t="s">
@@ -25376,16 +25376,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>447</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" t="s">
         <v>448</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="C47" t="s">
-        <v>449</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="E47"/>
       <c r="G47" s="3" t="s">
@@ -25420,7 +25420,7 @@
         <v>453</v>
       </c>
       <c r="C49" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>18</v>
@@ -25433,10 +25433,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>454</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="C50" t="s">
         <v>456</v>
@@ -25458,7 +25458,7 @@
         <v>458</v>
       </c>
       <c r="C51" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>18</v>
@@ -25471,13 +25471,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>459</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" t="s">
         <v>461</v>
-      </c>
-      <c r="C52" t="s">
-        <v>462</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>18</v>
@@ -25490,13 +25490,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>462</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>464</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>18</v>
@@ -25509,13 +25509,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>465</v>
+        <v>9</v>
       </c>
       <c r="C54" t="s">
-        <v>466</v>
+        <v>18</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>18</v>
@@ -25528,13 +25528,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>466</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" t="s">
         <v>468</v>
-      </c>
-      <c r="C55" t="s">
-        <v>469</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>18</v>
@@ -25547,13 +25547,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>469</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" t="s">
         <v>471</v>
-      </c>
-      <c r="C56" t="s">
-        <v>472</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>18</v>
@@ -25566,10 +25566,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>472</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C57" t="s">
         <v>474</v>
@@ -25626,10 +25626,10 @@
         <v>479</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" t="s">
         <v>480</v>
-      </c>
-      <c r="C60" t="s">
-        <v>481</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>18</v>
@@ -25642,13 +25642,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>481</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" t="s">
         <v>483</v>
-      </c>
-      <c r="C61" t="s">
-        <v>484</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>18</v>
@@ -25661,10 +25661,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>484</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>485</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C62" t="s">
         <v>486</v>
@@ -25683,7 +25683,7 @@
         <v>487</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="C63" t="s">
         <v>488</v>
@@ -25721,7 +25721,7 @@
         <v>491</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C65" t="s">
         <v>492</v>
@@ -25740,7 +25740,7 @@
         <v>493</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>480</v>
+        <v>9</v>
       </c>
       <c r="C66" t="s">
         <v>494</v>
@@ -25759,7 +25759,7 @@
         <v>495</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C67" t="s">
         <v>496</v>
@@ -25778,7 +25778,7 @@
         <v>497</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>39</v>
+        <v>482</v>
       </c>
       <c r="C68" t="s">
         <v>498</v>
@@ -25816,7 +25816,7 @@
         <v>501</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>393</v>
+        <v>39</v>
       </c>
       <c r="C70" t="s">
         <v>502</v>
@@ -25835,7 +25835,7 @@
         <v>503</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>9</v>
+        <v>393</v>
       </c>
       <c r="C71" t="s">
         <v>504</v>
@@ -25854,7 +25854,7 @@
         <v>505</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>393</v>
+        <v>9</v>
       </c>
       <c r="C72" t="s">
         <v>506</v>
@@ -25873,10 +25873,10 @@
         <v>507</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>9</v>
+        <v>393</v>
       </c>
       <c r="C73" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>18</v>
@@ -25889,13 +25889,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>509</v>
+        <v>9</v>
       </c>
       <c r="C74" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>18</v>
@@ -25908,10 +25908,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>510</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="C75" t="s">
         <v>512</v>
@@ -25930,7 +25930,7 @@
         <v>513</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>514</v>
+        <v>393</v>
       </c>
       <c r="C76" t="s">
         <v>514</v>
@@ -25952,7 +25952,7 @@
         <v>516</v>
       </c>
       <c r="C77" t="s">
-        <v>18</v>
+        <v>516</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>18</v>
@@ -27319,7 +27319,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B175" t="s">
         <v>566</v>
@@ -27352,10 +27352,10 @@
     <row r="177">
       <c r="A177"/>
       <c r="B177" t="s">
-        <v>341</v>
+        <v>570</v>
       </c>
       <c r="C177" t="s">
-        <v>342</v>
+        <v>571</v>
       </c>
       <c r="D177" t="s">
         <v>18</v>
@@ -27364,32 +27364,43 @@
         <v>18</v>
       </c>
     </row>
+    <row r="178">
+      <c r="A178"/>
+      <c r="B178" t="s">
+        <v>572</v>
+      </c>
+      <c r="C178" t="s">
+        <v>573</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="179">
-      <c r="A179" t="s">
-        <v>1</v>
-      </c>
+      <c r="A179"/>
       <c r="B179" t="s">
-        <v>123</v>
+        <v>574</v>
       </c>
       <c r="C179" t="s">
-        <v>2</v>
+        <v>575</v>
       </c>
       <c r="D179" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E179" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="s">
-        <v>415</v>
-      </c>
+      <c r="A180"/>
       <c r="B180" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C180" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="D180" t="s">
         <v>18</v>
@@ -27401,10 +27412,10 @@
     <row r="181">
       <c r="A181"/>
       <c r="B181" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C181" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="D181" t="s">
         <v>18</v>
@@ -27413,32 +27424,43 @@
         <v>18</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182"/>
+      <c r="B182" t="s">
+        <v>580</v>
+      </c>
+      <c r="C182" t="s">
+        <v>581</v>
+      </c>
+      <c r="D182" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="183">
-      <c r="A183" t="s">
-        <v>1</v>
-      </c>
+      <c r="A183"/>
       <c r="B183" t="s">
-        <v>123</v>
+        <v>582</v>
       </c>
       <c r="C183" t="s">
-        <v>2</v>
+        <v>583</v>
       </c>
       <c r="D183" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E183" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="s">
-        <v>433</v>
-      </c>
+      <c r="A184"/>
       <c r="B184" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="C184" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="D184" t="s">
         <v>18</v>
@@ -27450,10 +27472,10 @@
     <row r="185">
       <c r="A185"/>
       <c r="B185" t="s">
-        <v>276</v>
+        <v>586</v>
       </c>
       <c r="C185" t="s">
-        <v>277</v>
+        <v>587</v>
       </c>
       <c r="D185" t="s">
         <v>18</v>
@@ -27465,10 +27487,10 @@
     <row r="186">
       <c r="A186"/>
       <c r="B186" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C186" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="D186" t="s">
         <v>18</v>
@@ -27480,10 +27502,10 @@
     <row r="187">
       <c r="A187"/>
       <c r="B187" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="C187" t="s">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="D187" t="s">
         <v>18</v>
@@ -27495,10 +27517,10 @@
     <row r="188">
       <c r="A188"/>
       <c r="B188" t="s">
-        <v>578</v>
+        <v>268</v>
       </c>
       <c r="C188" t="s">
-        <v>578</v>
+        <v>269</v>
       </c>
       <c r="D188" t="s">
         <v>18</v>
@@ -27510,10 +27532,10 @@
     <row r="189">
       <c r="A189"/>
       <c r="B189" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="C189" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
       <c r="D189" t="s">
         <v>18</v>
@@ -27525,10 +27547,10 @@
     <row r="190">
       <c r="A190"/>
       <c r="B190" t="s">
-        <v>581</v>
+        <v>594</v>
       </c>
       <c r="C190" t="s">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="D190" t="s">
         <v>18</v>
@@ -27540,10 +27562,10 @@
     <row r="191">
       <c r="A191"/>
       <c r="B191" t="s">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="C191" t="s">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="D191" t="s">
         <v>18</v>
@@ -27555,10 +27577,10 @@
     <row r="192">
       <c r="A192"/>
       <c r="B192" t="s">
-        <v>260</v>
+        <v>598</v>
       </c>
       <c r="C192" t="s">
-        <v>262</v>
+        <v>599</v>
       </c>
       <c r="D192" t="s">
         <v>18</v>
@@ -27567,32 +27589,43 @@
         <v>18</v>
       </c>
     </row>
+    <row r="193">
+      <c r="A193"/>
+      <c r="B193" t="s">
+        <v>600</v>
+      </c>
+      <c r="C193" t="s">
+        <v>601</v>
+      </c>
+      <c r="D193" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="194">
-      <c r="A194" t="s">
-        <v>1</v>
-      </c>
+      <c r="A194"/>
       <c r="B194" t="s">
-        <v>123</v>
+        <v>602</v>
       </c>
       <c r="C194" t="s">
-        <v>2</v>
+        <v>603</v>
       </c>
       <c r="D194" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E194" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="s">
-        <v>468</v>
-      </c>
+      <c r="A195"/>
       <c r="B195" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="C195" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="D195" t="s">
         <v>18</v>
@@ -27604,10 +27637,10 @@
     <row r="196">
       <c r="A196"/>
       <c r="B196" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="C196" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="D196" t="s">
         <v>18</v>
@@ -27616,32 +27649,43 @@
         <v>18</v>
       </c>
     </row>
+    <row r="197">
+      <c r="A197"/>
+      <c r="B197" t="s">
+        <v>608</v>
+      </c>
+      <c r="C197" t="s">
+        <v>609</v>
+      </c>
+      <c r="D197" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="198">
-      <c r="A198" t="s">
-        <v>1</v>
-      </c>
+      <c r="A198"/>
       <c r="B198" t="s">
-        <v>123</v>
+        <v>610</v>
       </c>
       <c r="C198" t="s">
-        <v>2</v>
+        <v>611</v>
       </c>
       <c r="D198" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E198" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="s">
-        <v>483</v>
-      </c>
+      <c r="A199"/>
       <c r="B199" t="s">
-        <v>588</v>
+        <v>612</v>
       </c>
       <c r="C199" t="s">
-        <v>589</v>
+        <v>613</v>
       </c>
       <c r="D199" t="s">
         <v>18</v>
@@ -27653,10 +27697,10 @@
     <row r="200">
       <c r="A200"/>
       <c r="B200" t="s">
-        <v>590</v>
+        <v>614</v>
       </c>
       <c r="C200" t="s">
-        <v>591</v>
+        <v>615</v>
       </c>
       <c r="D200" t="s">
         <v>18</v>
@@ -27668,10 +27712,10 @@
     <row r="201">
       <c r="A201"/>
       <c r="B201" t="s">
-        <v>274</v>
+        <v>616</v>
       </c>
       <c r="C201" t="s">
-        <v>592</v>
+        <v>617</v>
       </c>
       <c r="D201" t="s">
         <v>18</v>
@@ -27683,10 +27727,10 @@
     <row r="202">
       <c r="A202"/>
       <c r="B202" t="s">
-        <v>341</v>
+        <v>618</v>
       </c>
       <c r="C202" t="s">
-        <v>342</v>
+        <v>619</v>
       </c>
       <c r="D202" t="s">
         <v>18</v>
@@ -27698,10 +27742,10 @@
     <row r="203">
       <c r="A203"/>
       <c r="B203" t="s">
-        <v>260</v>
+        <v>620</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>621</v>
       </c>
       <c r="D203" t="s">
         <v>18</v>
@@ -27710,32 +27754,43 @@
         <v>18</v>
       </c>
     </row>
+    <row r="204">
+      <c r="A204"/>
+      <c r="B204" t="s">
+        <v>622</v>
+      </c>
+      <c r="C204" t="s">
+        <v>623</v>
+      </c>
+      <c r="D204" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="205">
-      <c r="A205" t="s">
-        <v>1</v>
-      </c>
+      <c r="A205"/>
       <c r="B205" t="s">
-        <v>123</v>
+        <v>624</v>
       </c>
       <c r="C205" t="s">
-        <v>2</v>
+        <v>625</v>
       </c>
       <c r="D205" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E205" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="s">
-        <v>509</v>
-      </c>
+      <c r="A206"/>
       <c r="B206" t="s">
-        <v>593</v>
+        <v>626</v>
       </c>
       <c r="C206" t="s">
-        <v>594</v>
+        <v>627</v>
       </c>
       <c r="D206" t="s">
         <v>18</v>
@@ -27747,10 +27802,10 @@
     <row r="207">
       <c r="A207"/>
       <c r="B207" t="s">
-        <v>595</v>
+        <v>628</v>
       </c>
       <c r="C207" t="s">
-        <v>596</v>
+        <v>629</v>
       </c>
       <c r="D207" t="s">
         <v>18</v>
@@ -27762,10 +27817,10 @@
     <row r="208">
       <c r="A208"/>
       <c r="B208" t="s">
-        <v>597</v>
+        <v>630</v>
       </c>
       <c r="C208" t="s">
-        <v>598</v>
+        <v>631</v>
       </c>
       <c r="D208" t="s">
         <v>18</v>
@@ -27777,10 +27832,10 @@
     <row r="209">
       <c r="A209"/>
       <c r="B209" t="s">
-        <v>599</v>
+        <v>632</v>
       </c>
       <c r="C209" t="s">
-        <v>600</v>
+        <v>633</v>
       </c>
       <c r="D209" t="s">
         <v>18</v>
@@ -27792,10 +27847,10 @@
     <row r="210">
       <c r="A210"/>
       <c r="B210" t="s">
-        <v>601</v>
+        <v>634</v>
       </c>
       <c r="C210" t="s">
-        <v>602</v>
+        <v>635</v>
       </c>
       <c r="D210" t="s">
         <v>18</v>
@@ -27807,10 +27862,10 @@
     <row r="211">
       <c r="A211"/>
       <c r="B211" t="s">
-        <v>603</v>
+        <v>636</v>
       </c>
       <c r="C211" t="s">
-        <v>604</v>
+        <v>637</v>
       </c>
       <c r="D211" t="s">
         <v>18</v>
@@ -27822,10 +27877,10 @@
     <row r="212">
       <c r="A212"/>
       <c r="B212" t="s">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="C212" t="s">
-        <v>606</v>
+        <v>639</v>
       </c>
       <c r="D212" t="s">
         <v>18</v>
@@ -27837,10 +27892,10 @@
     <row r="213">
       <c r="A213"/>
       <c r="B213" t="s">
-        <v>607</v>
+        <v>640</v>
       </c>
       <c r="C213" t="s">
-        <v>608</v>
+        <v>641</v>
       </c>
       <c r="D213" t="s">
         <v>18</v>
@@ -27852,10 +27907,10 @@
     <row r="214">
       <c r="A214"/>
       <c r="B214" t="s">
-        <v>260</v>
+        <v>642</v>
       </c>
       <c r="C214" t="s">
-        <v>262</v>
+        <v>643</v>
       </c>
       <c r="D214" t="s">
         <v>18</v>
@@ -27864,47 +27919,47 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" t="s">
-        <v>1</v>
-      </c>
-      <c r="B216" t="s">
-        <v>123</v>
-      </c>
-      <c r="C216" t="s">
-        <v>2</v>
-      </c>
-      <c r="D216" t="s">
-        <v>3</v>
-      </c>
-      <c r="E216" t="s">
-        <v>124</v>
+    <row r="215">
+      <c r="A215"/>
+      <c r="B215" t="s">
+        <v>644</v>
+      </c>
+      <c r="C215" t="s">
+        <v>645</v>
+      </c>
+      <c r="D215" t="s">
+        <v>18</v>
+      </c>
+      <c r="E215" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>514</v>
+        <v>1</v>
       </c>
       <c r="B217" t="s">
-        <v>609</v>
+        <v>123</v>
       </c>
       <c r="C217" t="s">
-        <v>610</v>
+        <v>2</v>
       </c>
       <c r="D217" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E217" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="218">
-      <c r="A218"/>
+      <c r="A218" t="s">
+        <v>407</v>
+      </c>
       <c r="B218" t="s">
-        <v>611</v>
+        <v>646</v>
       </c>
       <c r="C218" t="s">
-        <v>612</v>
+        <v>647</v>
       </c>
       <c r="D218" t="s">
         <v>18</v>
@@ -27916,10 +27971,10 @@
     <row r="219">
       <c r="A219"/>
       <c r="B219" t="s">
-        <v>613</v>
+        <v>648</v>
       </c>
       <c r="C219" t="s">
-        <v>614</v>
+        <v>649</v>
       </c>
       <c r="D219" t="s">
         <v>18</v>
@@ -27962,13 +28017,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>516</v>
+        <v>417</v>
       </c>
       <c r="B223" t="s">
-        <v>615</v>
+        <v>650</v>
       </c>
       <c r="C223" t="s">
-        <v>616</v>
+        <v>651</v>
       </c>
       <c r="D223" t="s">
         <v>18</v>
@@ -27980,10 +28035,10 @@
     <row r="224">
       <c r="A224"/>
       <c r="B224" t="s">
-        <v>617</v>
+        <v>652</v>
       </c>
       <c r="C224" t="s">
-        <v>618</v>
+        <v>653</v>
       </c>
       <c r="D224" t="s">
         <v>18</v>
@@ -27992,43 +28047,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225"/>
-      <c r="B225" t="s">
-        <v>619</v>
-      </c>
-      <c r="C225" t="s">
-        <v>620</v>
-      </c>
-      <c r="D225" t="s">
-        <v>18</v>
-      </c>
-      <c r="E225" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="226">
-      <c r="A226"/>
+      <c r="A226" t="s">
+        <v>1</v>
+      </c>
       <c r="B226" t="s">
-        <v>621</v>
+        <v>123</v>
       </c>
       <c r="C226" t="s">
-        <v>622</v>
+        <v>2</v>
       </c>
       <c r="D226" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E226" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227"/>
+      <c r="A227" t="s">
+        <v>435</v>
+      </c>
       <c r="B227" t="s">
-        <v>623</v>
+        <v>654</v>
       </c>
       <c r="C227" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="D227" t="s">
         <v>18</v>
@@ -28040,10 +28084,10 @@
     <row r="228">
       <c r="A228"/>
       <c r="B228" t="s">
-        <v>625</v>
+        <v>276</v>
       </c>
       <c r="C228" t="s">
-        <v>626</v>
+        <v>277</v>
       </c>
       <c r="D228" t="s">
         <v>18</v>
@@ -28055,10 +28099,10 @@
     <row r="229">
       <c r="A229"/>
       <c r="B229" t="s">
-        <v>627</v>
+        <v>656</v>
       </c>
       <c r="C229" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="D229" t="s">
         <v>18</v>
@@ -28070,10 +28114,10 @@
     <row r="230">
       <c r="A230"/>
       <c r="B230" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="C230" t="s">
-        <v>630</v>
+        <v>657</v>
       </c>
       <c r="D230" t="s">
         <v>18</v>
@@ -28085,10 +28129,10 @@
     <row r="231">
       <c r="A231"/>
       <c r="B231" t="s">
-        <v>631</v>
+        <v>658</v>
       </c>
       <c r="C231" t="s">
-        <v>632</v>
+        <v>658</v>
       </c>
       <c r="D231" t="s">
         <v>18</v>
@@ -28100,10 +28144,10 @@
     <row r="232">
       <c r="A232"/>
       <c r="B232" t="s">
-        <v>633</v>
+        <v>659</v>
       </c>
       <c r="C232" t="s">
-        <v>634</v>
+        <v>660</v>
       </c>
       <c r="D232" t="s">
         <v>18</v>
@@ -28115,10 +28159,10 @@
     <row r="233">
       <c r="A233"/>
       <c r="B233" t="s">
-        <v>635</v>
+        <v>661</v>
       </c>
       <c r="C233" t="s">
-        <v>636</v>
+        <v>661</v>
       </c>
       <c r="D233" t="s">
         <v>18</v>
@@ -28130,10 +28174,10 @@
     <row r="234">
       <c r="A234"/>
       <c r="B234" t="s">
-        <v>637</v>
+        <v>662</v>
       </c>
       <c r="C234" t="s">
-        <v>638</v>
+        <v>663</v>
       </c>
       <c r="D234" t="s">
         <v>18</v>
@@ -28145,10 +28189,10 @@
     <row r="235">
       <c r="A235"/>
       <c r="B235" t="s">
-        <v>639</v>
+        <v>260</v>
       </c>
       <c r="C235" t="s">
-        <v>640</v>
+        <v>262</v>
       </c>
       <c r="D235" t="s">
         <v>18</v>
@@ -28157,43 +28201,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="236">
-      <c r="A236"/>
-      <c r="B236" t="s">
-        <v>268</v>
-      </c>
-      <c r="C236" t="s">
-        <v>269</v>
-      </c>
-      <c r="D236" t="s">
-        <v>18</v>
-      </c>
-      <c r="E236" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="237">
-      <c r="A237"/>
+      <c r="A237" t="s">
+        <v>1</v>
+      </c>
       <c r="B237" t="s">
-        <v>641</v>
+        <v>123</v>
       </c>
       <c r="C237" t="s">
-        <v>642</v>
+        <v>2</v>
       </c>
       <c r="D237" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E237" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="238">
-      <c r="A238"/>
+      <c r="A238" t="s">
+        <v>470</v>
+      </c>
       <c r="B238" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="C238" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="D238" t="s">
         <v>18</v>
@@ -28205,10 +28238,10 @@
     <row r="239">
       <c r="A239"/>
       <c r="B239" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="C239" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
       <c r="D239" t="s">
         <v>18</v>
@@ -28217,43 +28250,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240">
-      <c r="A240"/>
-      <c r="B240" t="s">
-        <v>601</v>
-      </c>
-      <c r="C240" t="s">
-        <v>602</v>
-      </c>
-      <c r="D240" t="s">
-        <v>18</v>
-      </c>
-      <c r="E240" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="241">
-      <c r="A241"/>
+      <c r="A241" t="s">
+        <v>1</v>
+      </c>
       <c r="B241" t="s">
-        <v>647</v>
+        <v>123</v>
       </c>
       <c r="C241" t="s">
-        <v>648</v>
+        <v>2</v>
       </c>
       <c r="D241" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E241" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="242">
-      <c r="A242"/>
+      <c r="A242" t="s">
+        <v>485</v>
+      </c>
       <c r="B242" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="C242" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="D242" t="s">
         <v>18</v>
@@ -28265,10 +28287,10 @@
     <row r="243">
       <c r="A243"/>
       <c r="B243" t="s">
-        <v>651</v>
+        <v>670</v>
       </c>
       <c r="C243" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="D243" t="s">
         <v>18</v>
@@ -28280,10 +28302,10 @@
     <row r="244">
       <c r="A244"/>
       <c r="B244" t="s">
-        <v>653</v>
+        <v>274</v>
       </c>
       <c r="C244" t="s">
-        <v>654</v>
+        <v>672</v>
       </c>
       <c r="D244" t="s">
         <v>18</v>
@@ -28295,10 +28317,10 @@
     <row r="245">
       <c r="A245"/>
       <c r="B245" t="s">
-        <v>655</v>
+        <v>341</v>
       </c>
       <c r="C245" t="s">
-        <v>656</v>
+        <v>342</v>
       </c>
       <c r="D245" t="s">
         <v>18</v>
@@ -28310,10 +28332,10 @@
     <row r="246">
       <c r="A246"/>
       <c r="B246" t="s">
-        <v>657</v>
+        <v>260</v>
       </c>
       <c r="C246" t="s">
-        <v>658</v>
+        <v>262</v>
       </c>
       <c r="D246" t="s">
         <v>18</v>
@@ -28322,43 +28344,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="247">
-      <c r="A247"/>
-      <c r="B247" t="s">
-        <v>659</v>
-      </c>
-      <c r="C247" t="s">
-        <v>660</v>
-      </c>
-      <c r="D247" t="s">
-        <v>18</v>
-      </c>
-      <c r="E247" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="248">
-      <c r="A248"/>
+      <c r="A248" t="s">
+        <v>1</v>
+      </c>
       <c r="B248" t="s">
-        <v>661</v>
+        <v>123</v>
       </c>
       <c r="C248" t="s">
-        <v>662</v>
+        <v>2</v>
       </c>
       <c r="D248" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E248" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="249">
-      <c r="A249"/>
+      <c r="A249" t="s">
+        <v>511</v>
+      </c>
       <c r="B249" t="s">
-        <v>663</v>
+        <v>673</v>
       </c>
       <c r="C249" t="s">
-        <v>664</v>
+        <v>674</v>
       </c>
       <c r="D249" t="s">
         <v>18</v>
@@ -28370,10 +28381,10 @@
     <row r="250">
       <c r="A250"/>
       <c r="B250" t="s">
-        <v>665</v>
+        <v>675</v>
       </c>
       <c r="C250" t="s">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="D250" t="s">
         <v>18</v>
@@ -28385,10 +28396,10 @@
     <row r="251">
       <c r="A251"/>
       <c r="B251" t="s">
-        <v>667</v>
+        <v>677</v>
       </c>
       <c r="C251" t="s">
-        <v>668</v>
+        <v>678</v>
       </c>
       <c r="D251" t="s">
         <v>18</v>
@@ -28400,10 +28411,10 @@
     <row r="252">
       <c r="A252"/>
       <c r="B252" t="s">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="C252" t="s">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="D252" t="s">
         <v>18</v>
@@ -28415,10 +28426,10 @@
     <row r="253">
       <c r="A253"/>
       <c r="B253" t="s">
-        <v>671</v>
+        <v>598</v>
       </c>
       <c r="C253" t="s">
-        <v>672</v>
+        <v>599</v>
       </c>
       <c r="D253" t="s">
         <v>18</v>
@@ -28430,10 +28441,10 @@
     <row r="254">
       <c r="A254"/>
       <c r="B254" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="C254" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="D254" t="s">
         <v>18</v>
@@ -28445,10 +28456,10 @@
     <row r="255">
       <c r="A255"/>
       <c r="B255" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="C255" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="D255" t="s">
         <v>18</v>
@@ -28460,10 +28471,10 @@
     <row r="256">
       <c r="A256"/>
       <c r="B256" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="C256" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="D256" t="s">
         <v>18</v>
@@ -28475,10 +28486,10 @@
     <row r="257">
       <c r="A257"/>
       <c r="B257" t="s">
-        <v>679</v>
+        <v>260</v>
       </c>
       <c r="C257" t="s">
-        <v>680</v>
+        <v>262</v>
       </c>
       <c r="D257" t="s">
         <v>18</v>
@@ -28487,43 +28498,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258">
-      <c r="A258"/>
-      <c r="B258" t="s">
-        <v>681</v>
-      </c>
-      <c r="C258" t="s">
-        <v>682</v>
-      </c>
-      <c r="D258" t="s">
-        <v>18</v>
-      </c>
-      <c r="E258" t="s">
-        <v>18</v>
-      </c>
-    </row>
     <row r="259">
-      <c r="A259"/>
+      <c r="A259" t="s">
+        <v>1</v>
+      </c>
       <c r="B259" t="s">
-        <v>683</v>
+        <v>123</v>
       </c>
       <c r="C259" t="s">
-        <v>684</v>
+        <v>2</v>
       </c>
       <c r="D259" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E259" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
     </row>
     <row r="260">
-      <c r="A260"/>
+      <c r="A260" t="s">
+        <v>516</v>
+      </c>
       <c r="B260" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C260" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="D260" t="s">
         <v>18</v>
@@ -28535,10 +28535,10 @@
     <row r="261">
       <c r="A261"/>
       <c r="B261" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C261" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D261" t="s">
         <v>18</v>
@@ -28550,10 +28550,10 @@
     <row r="262">
       <c r="A262"/>
       <c r="B262" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C262" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="D262" t="s">
         <v>18</v>
@@ -28565,10 +28565,10 @@
     <row r="263">
       <c r="A263"/>
       <c r="B263" t="s">
-        <v>691</v>
+        <v>341</v>
       </c>
       <c r="C263" t="s">
-        <v>692</v>
+        <v>342</v>
       </c>
       <c r="D263" t="s">
         <v>18</v>
@@ -29811,7 +29811,7 @@
         <v>839</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C45" t="s">
         <v>840</v>
@@ -29830,7 +29830,7 @@
         <v>841</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C46" t="s">
         <v>842</v>
@@ -29868,7 +29868,7 @@
         <v>845</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C48" t="s">
         <v>846</v>
@@ -29887,7 +29887,7 @@
         <v>847</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C49" t="s">
         <v>848</v>
@@ -29906,7 +29906,7 @@
         <v>849</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C50" t="s">
         <v>850</v>
@@ -29944,7 +29944,7 @@
         <v>854</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C52" t="s">
         <v>855</v>
@@ -30077,7 +30077,7 @@
         <v>865</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C59" t="s">
         <v>866</v>
@@ -30115,7 +30115,7 @@
         <v>869</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C61" t="s">
         <v>870</v>
@@ -30891,7 +30891,7 @@
         <v>969</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C101" t="s">
         <v>970</v>
@@ -33471,7 +33471,7 @@
         <v>1276</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C51" t="s">
         <v>1277</v>
@@ -33874,13 +33874,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B79" t="s">
-        <v>566</v>
+        <v>646</v>
       </c>
       <c r="C79" t="s">
-        <v>567</v>
+        <v>647</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -33892,10 +33892,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>568</v>
+        <v>648</v>
       </c>
       <c r="C80" t="s">
-        <v>569</v>
+        <v>649</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -34525,7 +34525,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>1350</v>
@@ -35136,7 +35136,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1350</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7047" uniqueCount="1984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7055" uniqueCount="1984">
   <si>
     <t>Field</t>
   </si>
@@ -424,6 +424,18 @@
     <t>Female</t>
   </si>
   <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
     <t>YEARS</t>
   </si>
   <si>
@@ -817,15 +829,9 @@
     <t>C.pneumoniae</t>
   </si>
   <si>
-    <t>OTHER</t>
-  </si>
-  <si>
     <t>Other Epidemic Disease</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>UNDEFINED</t>
   </si>
   <si>
@@ -1058,12 +1064,6 @@
   </si>
   <si>
     <t>Rural</t>
-  </si>
-  <si>
-    <t>UNKNOWN</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>disease</t>
@@ -6116,7 +6116,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="PersonOccupationType" displayName="PersonOccupationType" ref="A142:E157">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="PersonOccupationType" displayName="PersonOccupationType" ref="A144:E159">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6262,7 +6262,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PersonSex" displayName="PersonSex" ref="A49:E51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PersonSex" displayName="PersonSex" ref="A49:E53">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6419,7 +6419,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PersonApproximateAgeType" displayName="PersonApproximateAgeType" ref="A53:E56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PersonApproximateAgeType" displayName="PersonApproximateAgeType" ref="A55:E58">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6579,7 +6579,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PersonPresentCondition" displayName="PersonPresentCondition" ref="A58:E61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PersonPresentCondition" displayName="PersonPresentCondition" ref="A60:E63">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6742,7 +6742,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PersonCauseOfDeath" displayName="PersonCauseOfDeath" ref="A63:E65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PersonCauseOfDeath" displayName="PersonCauseOfDeath" ref="A65:E67">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6902,7 +6902,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="PersonDisease" displayName="PersonDisease" ref="A67:E123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="PersonDisease" displayName="PersonDisease" ref="A69:E125">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7062,7 +7062,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PersonDeathPlaceType" displayName="PersonDeathPlaceType" ref="A125:E128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PersonDeathPlaceType" displayName="PersonDeathPlaceType" ref="A127:E130">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7222,7 +7222,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PersonBurialConductor" displayName="PersonBurialConductor" ref="A130:E132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PersonBurialConductor" displayName="PersonBurialConductor" ref="A132:E134">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7382,7 +7382,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="PersonEducationType" displayName="PersonEducationType" ref="A134:E140">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="PersonEducationType" displayName="PersonEducationType" ref="A136:E142">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7555,7 +7555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I157"/>
+  <dimension ref="A1:I159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -8541,57 +8541,57 @@
         <v>18</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52"/>
+      <c r="B52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="53">
-      <c r="A53" t="s">
+      <c r="A53"/>
+      <c r="B53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
         <v>1</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B55" t="s">
         <v>123</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C55" t="s">
         <v>2</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D55" t="s">
         <v>3</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E55" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="s">
+    <row r="56">
+      <c r="A56" t="s">
         <v>36</v>
       </c>
-      <c r="B54" t="s">
-        <v>129</v>
-      </c>
-      <c r="C54" t="s">
-        <v>130</v>
-      </c>
-      <c r="D54" t="s">
-        <v>18</v>
-      </c>
-      <c r="E54" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55"/>
-      <c r="B55" t="s">
-        <v>131</v>
-      </c>
-      <c r="C55" t="s">
-        <v>132</v>
-      </c>
-      <c r="D55" t="s">
-        <v>18</v>
-      </c>
-      <c r="E55" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56"/>
       <c r="B56" t="s">
         <v>133</v>
       </c>
@@ -8605,57 +8605,57 @@
         <v>18</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57"/>
+      <c r="B57" t="s">
+        <v>135</v>
+      </c>
+      <c r="C57" t="s">
+        <v>136</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="58">
-      <c r="A58" t="s">
+      <c r="A58"/>
+      <c r="B58" t="s">
+        <v>137</v>
+      </c>
+      <c r="C58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>1</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B60" t="s">
         <v>123</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" t="s">
         <v>2</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D60" t="s">
         <v>3</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E60" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="s">
+    <row r="61">
+      <c r="A61" t="s">
         <v>61</v>
       </c>
-      <c r="B59" t="s">
-        <v>135</v>
-      </c>
-      <c r="C59" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" t="s">
-        <v>18</v>
-      </c>
-      <c r="E59" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60"/>
-      <c r="B60" t="s">
-        <v>137</v>
-      </c>
-      <c r="C60" t="s">
-        <v>138</v>
-      </c>
-      <c r="D60" t="s">
-        <v>18</v>
-      </c>
-      <c r="E60" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61"/>
       <c r="B61" t="s">
         <v>139</v>
       </c>
@@ -8669,106 +8669,106 @@
         <v>18</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62"/>
+      <c r="B62" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" t="s">
+        <v>142</v>
+      </c>
+      <c r="D62" t="s">
+        <v>18</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" t="s">
+      <c r="A63"/>
+      <c r="B63" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" t="s">
+        <v>144</v>
+      </c>
+      <c r="D63" t="s">
+        <v>18</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
         <v>1</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B65" t="s">
         <v>123</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C65" t="s">
         <v>2</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D65" t="s">
         <v>3</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E65" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="s">
+    <row r="66">
+      <c r="A66" t="s">
         <v>68</v>
       </c>
-      <c r="B64" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" t="s">
-        <v>142</v>
-      </c>
-      <c r="D64" t="s">
-        <v>18</v>
-      </c>
-      <c r="E64" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65"/>
-      <c r="B65" t="s">
-        <v>143</v>
-      </c>
-      <c r="C65" t="s">
-        <v>144</v>
-      </c>
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="B66" t="s">
+        <v>145</v>
+      </c>
+      <c r="C66" t="s">
+        <v>146</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="s">
+      <c r="A67"/>
+      <c r="B67" t="s">
+        <v>147</v>
+      </c>
+      <c r="C67" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" t="s">
+        <v>18</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
         <v>1</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B69" t="s">
         <v>123</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C69" t="s">
         <v>2</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D69" t="s">
         <v>3</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E69" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="s">
+    <row r="70">
+      <c r="A70" t="s">
         <v>71</v>
       </c>
-      <c r="B68" t="s">
-        <v>145</v>
-      </c>
-      <c r="C68" t="s">
-        <v>146</v>
-      </c>
-      <c r="D68" t="s">
-        <v>18</v>
-      </c>
-      <c r="E68" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69"/>
-      <c r="B69" t="s">
-        <v>147</v>
-      </c>
-      <c r="C69" t="s">
-        <v>148</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70"/>
       <c r="B70" t="s">
         <v>149</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71">
@@ -8794,31 +8794,31 @@
         <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>153</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" t="s">
         <v>154</v>
       </c>
-      <c r="C72" t="s">
-        <v>155</v>
-      </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>156</v>
+        <v>44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C73" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -8830,16 +8830,16 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" t="s">
         <v>159</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
         <v>160</v>
-      </c>
-      <c r="D74" t="s">
-        <v>18</v>
-      </c>
-      <c r="E74" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="75">
@@ -8854,7 +8854,7 @@
         <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>18</v>
+        <v>161</v>
       </c>
     </row>
     <row r="76">
@@ -8899,16 +8899,16 @@
         <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>169</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" t="s">
         <v>170</v>
-      </c>
-      <c r="C79" t="s">
-        <v>171</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -8920,61 +8920,61 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
+        <v>171</v>
+      </c>
+      <c r="C80" t="s">
         <v>172</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" t="s">
         <v>173</v>
-      </c>
-      <c r="D80" t="s">
-        <v>18</v>
-      </c>
-      <c r="E80" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
+        <v>174</v>
+      </c>
+      <c r="C81" t="s">
         <v>175</v>
       </c>
-      <c r="C81" t="s">
-        <v>176</v>
-      </c>
       <c r="D81" t="s">
         <v>18</v>
       </c>
       <c r="E81" t="s">
-        <v>177</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
+        <v>176</v>
+      </c>
+      <c r="C82" t="s">
+        <v>177</v>
+      </c>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" t="s">
         <v>178</v>
-      </c>
-      <c r="C82" t="s">
-        <v>179</v>
-      </c>
-      <c r="D82" t="s">
-        <v>18</v>
-      </c>
-      <c r="E82" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
+        <v>179</v>
+      </c>
+      <c r="C83" t="s">
         <v>180</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" t="s">
         <v>181</v>
-      </c>
-      <c r="D83" t="s">
-        <v>18</v>
-      </c>
-      <c r="E83" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -8989,16 +8989,16 @@
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>184</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
+        <v>184</v>
+      </c>
+      <c r="C85" t="s">
         <v>185</v>
-      </c>
-      <c r="C85" t="s">
-        <v>186</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -9010,16 +9010,16 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86" t="s">
         <v>187</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" t="s">
         <v>188</v>
-      </c>
-      <c r="D86" t="s">
-        <v>18</v>
-      </c>
-      <c r="E86" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="87">
@@ -9103,7 +9103,7 @@
         <v>199</v>
       </c>
       <c r="C92" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -9115,10 +9115,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C93" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -9130,7 +9130,7 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C94" t="s">
         <v>203</v>
@@ -9454,52 +9454,52 @@
         <v>18</v>
       </c>
       <c r="E115" t="s">
-        <v>246</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
+        <v>246</v>
+      </c>
+      <c r="C116" t="s">
         <v>247</v>
       </c>
-      <c r="C116" t="s">
-        <v>248</v>
-      </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="E116" t="s">
-        <v>249</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
+        <v>248</v>
+      </c>
+      <c r="C117" t="s">
+        <v>249</v>
+      </c>
+      <c r="D117" t="s">
+        <v>18</v>
+      </c>
+      <c r="E117" t="s">
         <v>250</v>
-      </c>
-      <c r="C117" t="s">
-        <v>251</v>
-      </c>
-      <c r="D117" t="s">
-        <v>18</v>
-      </c>
-      <c r="E117" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
+        <v>251</v>
+      </c>
+      <c r="C118" t="s">
         <v>252</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>18</v>
+      </c>
+      <c r="E118" t="s">
         <v>253</v>
-      </c>
-      <c r="D118" t="s">
-        <v>18</v>
-      </c>
-      <c r="E118" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="119">
@@ -9559,81 +9559,81 @@
         <v>18</v>
       </c>
       <c r="E122" t="s">
-        <v>262</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
+        <v>262</v>
+      </c>
+      <c r="C123" t="s">
         <v>263</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124"/>
+      <c r="B124" t="s">
+        <v>129</v>
+      </c>
+      <c r="C124" t="s">
         <v>264</v>
       </c>
-      <c r="D123" t="s">
-        <v>18</v>
-      </c>
-      <c r="E123" t="s">
+      <c r="D124" t="s">
+        <v>18</v>
+      </c>
+      <c r="E124" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125"/>
+      <c r="B125" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
+      <c r="C125" t="s">
+        <v>266</v>
+      </c>
+      <c r="D125" t="s">
+        <v>18</v>
+      </c>
+      <c r="E125" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
         <v>1</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B127" t="s">
         <v>123</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C127" t="s">
         <v>2</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D127" t="s">
         <v>3</v>
       </c>
-      <c r="E125" t="s">
+      <c r="E127" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" t="s">
+    <row r="128">
+      <c r="A128" t="s">
         <v>76</v>
       </c>
-      <c r="B126" t="s">
-        <v>266</v>
-      </c>
-      <c r="C126" t="s">
-        <v>267</v>
-      </c>
-      <c r="D126" t="s">
-        <v>18</v>
-      </c>
-      <c r="E126" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127"/>
-      <c r="B127" t="s">
+      <c r="B128" t="s">
         <v>268</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C128" t="s">
         <v>269</v>
       </c>
-      <c r="D127" t="s">
-        <v>18</v>
-      </c>
-      <c r="E127" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128"/>
-      <c r="B128" t="s">
-        <v>260</v>
-      </c>
-      <c r="C128" t="s">
-        <v>262</v>
-      </c>
       <c r="D128" t="s">
         <v>18</v>
       </c>
@@ -9641,111 +9641,111 @@
         <v>18</v>
       </c>
     </row>
+    <row r="129">
+      <c r="A129"/>
+      <c r="B129" t="s">
+        <v>270</v>
+      </c>
+      <c r="C129" t="s">
+        <v>271</v>
+      </c>
+      <c r="D129" t="s">
+        <v>18</v>
+      </c>
+      <c r="E129" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="130">
-      <c r="A130" t="s">
+      <c r="A130"/>
+      <c r="B130" t="s">
+        <v>129</v>
+      </c>
+      <c r="C130" t="s">
+        <v>130</v>
+      </c>
+      <c r="D130" t="s">
+        <v>18</v>
+      </c>
+      <c r="E130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
         <v>1</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B132" t="s">
         <v>123</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C132" t="s">
         <v>2</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D132" t="s">
         <v>3</v>
       </c>
-      <c r="E130" t="s">
+      <c r="E132" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="s">
+    <row r="133">
+      <c r="A133" t="s">
         <v>87</v>
       </c>
-      <c r="B131" t="s">
-        <v>270</v>
-      </c>
-      <c r="C131" t="s">
-        <v>271</v>
-      </c>
-      <c r="D131" t="s">
-        <v>18</v>
-      </c>
-      <c r="E131" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132"/>
-      <c r="B132" t="s">
+      <c r="B133" t="s">
         <v>272</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C133" t="s">
         <v>273</v>
       </c>
-      <c r="D132" t="s">
-        <v>18</v>
-      </c>
-      <c r="E132" t="s">
+      <c r="D133" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
+      <c r="A134"/>
+      <c r="B134" t="s">
+        <v>274</v>
+      </c>
+      <c r="C134" t="s">
+        <v>275</v>
+      </c>
+      <c r="D134" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
         <v>1</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B136" t="s">
         <v>123</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C136" t="s">
         <v>2</v>
       </c>
-      <c r="D134" t="s">
+      <c r="D136" t="s">
         <v>3</v>
       </c>
-      <c r="E134" t="s">
+      <c r="E136" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="s">
+    <row r="137">
+      <c r="A137" t="s">
         <v>100</v>
       </c>
-      <c r="B135" t="s">
-        <v>274</v>
-      </c>
-      <c r="C135" t="s">
-        <v>275</v>
-      </c>
-      <c r="D135" t="s">
-        <v>18</v>
-      </c>
-      <c r="E135" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136"/>
-      <c r="B136" t="s">
+      <c r="B137" t="s">
         <v>276</v>
       </c>
-      <c r="C136" t="s">
+      <c r="C137" t="s">
         <v>277</v>
-      </c>
-      <c r="D136" t="s">
-        <v>18</v>
-      </c>
-      <c r="E136" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137"/>
-      <c r="B137" t="s">
-        <v>278</v>
-      </c>
-      <c r="C137" t="s">
-        <v>279</v>
       </c>
       <c r="D137" t="s">
         <v>18</v>
@@ -9757,10 +9757,10 @@
     <row r="138">
       <c r="A138"/>
       <c r="B138" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C138" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D138" t="s">
         <v>18</v>
@@ -9772,10 +9772,10 @@
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C139" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D139" t="s">
         <v>18</v>
@@ -9787,10 +9787,10 @@
     <row r="140">
       <c r="A140"/>
       <c r="B140" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C140" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="D140" t="s">
         <v>18</v>
@@ -9799,62 +9799,62 @@
         <v>18</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141"/>
+      <c r="B141" t="s">
+        <v>284</v>
+      </c>
+      <c r="C141" t="s">
+        <v>285</v>
+      </c>
+      <c r="D141" t="s">
+        <v>18</v>
+      </c>
+      <c r="E141" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="142">
-      <c r="A142" t="s">
+      <c r="A142"/>
+      <c r="B142" t="s">
+        <v>129</v>
+      </c>
+      <c r="C142" t="s">
+        <v>130</v>
+      </c>
+      <c r="D142" t="s">
+        <v>18</v>
+      </c>
+      <c r="E142" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
         <v>1</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B144" t="s">
         <v>123</v>
       </c>
-      <c r="C142" t="s">
+      <c r="C144" t="s">
         <v>2</v>
       </c>
-      <c r="D142" t="s">
+      <c r="D144" t="s">
         <v>3</v>
       </c>
-      <c r="E142" t="s">
+      <c r="E144" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" t="s">
+    <row r="145">
+      <c r="A145" t="s">
         <v>105</v>
       </c>
-      <c r="B143" t="s">
-        <v>284</v>
-      </c>
-      <c r="C143" t="s">
-        <v>285</v>
-      </c>
-      <c r="D143" t="s">
-        <v>18</v>
-      </c>
-      <c r="E143" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144"/>
-      <c r="B144" t="s">
+      <c r="B145" t="s">
         <v>286</v>
       </c>
-      <c r="C144" t="s">
+      <c r="C145" t="s">
         <v>287</v>
-      </c>
-      <c r="D144" t="s">
-        <v>18</v>
-      </c>
-      <c r="E144" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145"/>
-      <c r="B145" t="s">
-        <v>288</v>
-      </c>
-      <c r="C145" t="s">
-        <v>289</v>
       </c>
       <c r="D145" t="s">
         <v>18</v>
@@ -9866,10 +9866,10 @@
     <row r="146">
       <c r="A146"/>
       <c r="B146" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C146" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D146" t="s">
         <v>18</v>
@@ -9881,10 +9881,10 @@
     <row r="147">
       <c r="A147"/>
       <c r="B147" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C147" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D147" t="s">
         <v>18</v>
@@ -9896,10 +9896,10 @@
     <row r="148">
       <c r="A148"/>
       <c r="B148" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C148" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D148" t="s">
         <v>18</v>
@@ -9911,10 +9911,10 @@
     <row r="149">
       <c r="A149"/>
       <c r="B149" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C149" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D149" t="s">
         <v>18</v>
@@ -9926,10 +9926,10 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C150" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D150" t="s">
         <v>18</v>
@@ -9941,10 +9941,10 @@
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C151" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D151" t="s">
         <v>18</v>
@@ -9956,10 +9956,10 @@
     <row r="152">
       <c r="A152"/>
       <c r="B152" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C152" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D152" t="s">
         <v>18</v>
@@ -9971,10 +9971,10 @@
     <row r="153">
       <c r="A153"/>
       <c r="B153" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C153" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D153" t="s">
         <v>18</v>
@@ -9986,10 +9986,10 @@
     <row r="154">
       <c r="A154"/>
       <c r="B154" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C154" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D154" t="s">
         <v>18</v>
@@ -10001,10 +10001,10 @@
     <row r="155">
       <c r="A155"/>
       <c r="B155" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C155" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D155" t="s">
         <v>18</v>
@@ -10016,10 +10016,10 @@
     <row r="156">
       <c r="A156"/>
       <c r="B156" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C156" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D156" t="s">
         <v>18</v>
@@ -10031,15 +10031,45 @@
     <row r="157">
       <c r="A157"/>
       <c r="B157" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="C157" t="s">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="D157" t="s">
         <v>18</v>
       </c>
       <c r="E157" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158"/>
+      <c r="B158" t="s">
+        <v>312</v>
+      </c>
+      <c r="C158" t="s">
+        <v>313</v>
+      </c>
+      <c r="D158" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159"/>
+      <c r="B159" t="s">
+        <v>129</v>
+      </c>
+      <c r="C159" t="s">
+        <v>130</v>
+      </c>
+      <c r="D159" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" t="s">
         <v>18</v>
       </c>
     </row>
@@ -10237,25 +10267,25 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -10267,10 +10297,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -10282,55 +10312,55 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C13" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C14" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C16" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -10342,10 +10372,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -10357,10 +10387,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C18" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -10372,10 +10402,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -10387,25 +10417,25 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -10417,40 +10447,40 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C22" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -10462,10 +10492,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -10477,25 +10507,25 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C27" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -10507,10 +10537,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C28" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -10522,10 +10552,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C29" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -10537,10 +10567,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C30" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -10552,10 +10582,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C31" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -10567,10 +10597,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C32" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -10582,10 +10612,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C33" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -10597,10 +10627,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C34" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -10612,10 +10642,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C35" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -10627,10 +10657,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C36" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -10642,10 +10672,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C37" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -10657,10 +10687,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C38" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -10672,10 +10702,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C39" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -10687,10 +10717,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C40" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -10702,10 +10732,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C41" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -10717,10 +10747,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C42" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -10732,10 +10762,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -10747,10 +10777,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C44" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -10762,10 +10792,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -10777,10 +10807,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C46" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -10792,10 +10822,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -10807,10 +10837,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C48" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -10822,10 +10852,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C49" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -10837,10 +10867,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C50" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -10852,10 +10882,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C51" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -10867,10 +10897,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C52" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -10882,10 +10912,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -10897,10 +10927,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C54" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -10912,10 +10942,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -10927,10 +10957,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C56" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -10942,40 +10972,40 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C57" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C58" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C59" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -10987,10 +11017,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C60" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -11002,10 +11032,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C61" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -11017,10 +11047,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C62" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -11032,10 +11062,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -11047,31 +11077,31 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C64" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C65" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -11320,7 +11350,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>42</v>
@@ -11339,7 +11369,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>46</v>
@@ -12161,25 +12191,25 @@
         <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -12191,10 +12221,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C59" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -12206,55 +12236,55 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C61" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C63" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -12266,10 +12296,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C64" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -12281,10 +12311,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C65" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -12296,10 +12326,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -12311,25 +12341,25 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C67" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C68" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -12341,40 +12371,40 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C70" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -12386,10 +12416,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C72" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -12401,25 +12431,25 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C73" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -12431,10 +12461,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C75" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -12446,10 +12476,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C76" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -12461,10 +12491,10 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C77" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -12476,10 +12506,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C78" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -12491,10 +12521,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C79" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -12506,10 +12536,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C80" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -12521,10 +12551,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C81" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -12536,10 +12566,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C82" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -12551,10 +12581,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C83" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -12566,10 +12596,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C84" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -12581,10 +12611,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C85" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -12596,10 +12626,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C86" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -12611,10 +12641,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C87" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -12626,10 +12656,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C88" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -12641,10 +12671,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C89" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -12656,10 +12686,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C90" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -12671,10 +12701,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C91" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -12686,10 +12716,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C92" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -12701,10 +12731,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C93" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -12716,10 +12746,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C94" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -12731,10 +12761,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C95" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -12746,10 +12776,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C96" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -12761,10 +12791,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C97" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -12776,10 +12806,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C98" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -12791,10 +12821,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C99" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
@@ -12806,10 +12836,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C100" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -12821,10 +12851,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C101" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -12836,10 +12866,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C102" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -12851,10 +12881,10 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C103" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D103" t="s">
         <v>18</v>
@@ -12866,40 +12896,40 @@
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C104" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
       </c>
       <c r="E104" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C105" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
       </c>
       <c r="E105" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C106" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
@@ -12911,10 +12941,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C107" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -12926,10 +12956,10 @@
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C108" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -12941,10 +12971,10 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C109" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -12956,10 +12986,10 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
@@ -12971,31 +13001,31 @@
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C111" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C112" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
         <v>18</v>
       </c>
       <c r="E112" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="114">
@@ -13065,10 +13095,10 @@
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D118" t="s">
         <v>18</v>
@@ -13080,10 +13110,10 @@
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C119" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D119" t="s">
         <v>18</v>
@@ -13129,10 +13159,10 @@
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D123" t="s">
         <v>18</v>
@@ -13144,10 +13174,10 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C124" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
@@ -13783,10 +13813,10 @@
     <row r="171">
       <c r="A171"/>
       <c r="B171" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C171" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D171" t="s">
         <v>18</v>
@@ -13847,10 +13877,10 @@
     <row r="176">
       <c r="A176"/>
       <c r="B176" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C176" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D176" t="s">
         <v>18</v>
@@ -13911,7 +13941,7 @@
     <row r="181">
       <c r="A181"/>
       <c r="B181" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C181" t="s">
         <v>602</v>
@@ -13926,10 +13956,10 @@
     <row r="182">
       <c r="A182"/>
       <c r="B182" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C182" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D182" t="s">
         <v>18</v>
@@ -13941,10 +13971,10 @@
     <row r="183">
       <c r="A183"/>
       <c r="B183" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C183" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D183" t="s">
         <v>18</v>
@@ -14233,25 +14263,25 @@
         <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -14263,10 +14293,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -14278,55 +14308,55 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C18" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C20" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -14338,10 +14368,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -14353,10 +14383,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -14368,10 +14398,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C23" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -14383,25 +14413,25 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C25" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -14413,40 +14443,40 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="E27" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C28" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -14458,10 +14488,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -14473,25 +14503,25 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C30" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C31" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -14503,10 +14533,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C32" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -14518,10 +14548,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C33" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -14533,10 +14563,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C34" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -14548,10 +14578,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -14563,10 +14593,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C36" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -14578,10 +14608,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C37" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -14593,10 +14623,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C38" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -14608,10 +14638,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C39" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -14623,10 +14653,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -14638,10 +14668,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -14653,10 +14683,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C42" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -14668,10 +14698,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -14683,10 +14713,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C44" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -14698,10 +14728,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C45" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -14713,10 +14743,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -14728,10 +14758,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C47" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -14743,10 +14773,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C48" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -14758,10 +14788,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -14773,10 +14803,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -14788,10 +14818,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -14803,10 +14833,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C52" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -14818,10 +14848,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C53" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -14833,10 +14863,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C54" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -14848,10 +14878,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C55" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -14863,10 +14893,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C56" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -14878,10 +14908,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C57" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -14893,10 +14923,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C58" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -14908,10 +14938,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C59" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -14923,10 +14953,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -14938,40 +14968,40 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C61" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C63" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -14983,10 +15013,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C64" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -14998,10 +15028,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -15013,10 +15043,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C66" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -15028,10 +15058,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -15043,31 +15073,31 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C68" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C69" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71">
@@ -16127,10 +16157,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -16759,25 +16789,25 @@
         <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -16789,10 +16819,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -16804,55 +16834,55 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C23" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C25" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -16864,10 +16894,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -16879,10 +16909,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -16894,10 +16924,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C28" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -16909,25 +16939,25 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C30" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -16939,40 +16969,40 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C31" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C32" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -16984,10 +17014,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C34" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -16999,25 +17029,25 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -17029,10 +17059,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C37" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -17044,10 +17074,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C38" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -17059,10 +17089,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -17074,10 +17104,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C40" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -17089,10 +17119,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -17104,10 +17134,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -17119,10 +17149,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -17134,10 +17164,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C44" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -17149,10 +17179,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C45" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -17164,10 +17194,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -17179,10 +17209,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C47" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -17194,10 +17224,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C48" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -17209,10 +17239,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C49" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -17224,10 +17254,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C50" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -17239,10 +17269,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -17254,10 +17284,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C52" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -17269,10 +17299,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -17284,10 +17314,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C54" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -17299,10 +17329,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C55" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -17314,10 +17344,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C56" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -17329,10 +17359,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C57" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -17344,10 +17374,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -17359,10 +17389,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C59" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -17374,10 +17404,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C60" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -17389,10 +17419,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C61" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -17404,10 +17434,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C62" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -17419,10 +17449,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C63" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -17434,10 +17464,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -17449,10 +17479,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C65" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -17464,40 +17494,40 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C66" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C68" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -17509,10 +17539,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -17524,10 +17554,10 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C70" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -17539,10 +17569,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C71" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -17554,10 +17584,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -17569,31 +17599,31 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C74" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="76">
@@ -17888,10 +17918,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -19269,7 +19299,7 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C45" t="s">
         <v>1838</v>
@@ -20151,10 +20181,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -20215,10 +20245,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C43" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -20260,10 +20290,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C46" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -20275,10 +20305,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -20388,25 +20418,25 @@
         <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -20418,10 +20448,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C58" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -20433,55 +20463,55 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -20493,10 +20523,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C63" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -20508,10 +20538,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C64" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -20523,10 +20553,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C65" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -20538,25 +20568,25 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C66" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C67" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -20568,40 +20598,40 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C69" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C70" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -20613,10 +20643,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C71" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -20628,25 +20658,25 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C73" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -20658,10 +20688,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C74" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -20673,10 +20703,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C75" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -20688,10 +20718,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C76" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -20703,10 +20733,10 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C77" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -20718,10 +20748,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C78" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -20733,10 +20763,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C79" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -20748,10 +20778,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C80" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -20763,10 +20793,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C81" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -20778,10 +20808,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C82" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -20793,10 +20823,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C83" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -20808,10 +20838,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C84" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -20823,10 +20853,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C85" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -20838,10 +20868,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C86" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -20853,10 +20883,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C87" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -20868,10 +20898,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C88" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -20883,10 +20913,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C89" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -20898,10 +20928,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C90" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -20913,10 +20943,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C91" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -20928,10 +20958,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C92" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -20943,10 +20973,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C93" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -20958,10 +20988,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C94" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -20973,10 +21003,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C95" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -20988,10 +21018,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C96" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -21003,10 +21033,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C97" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -21018,10 +21048,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C98" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -21033,10 +21063,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C99" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
@@ -21048,10 +21078,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C100" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -21063,10 +21093,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C101" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -21078,10 +21108,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C102" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -21093,40 +21123,40 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C103" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D103" t="s">
         <v>18</v>
       </c>
       <c r="E103" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C104" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
       </c>
       <c r="E104" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C105" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
@@ -21138,10 +21168,10 @@
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C106" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
@@ -21153,10 +21183,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C107" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -21168,10 +21198,10 @@
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C108" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -21183,10 +21213,10 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -21198,31 +21228,31 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C110" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
       </c>
       <c r="E110" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C111" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -21429,13 +21459,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>18</v>
@@ -21448,13 +21478,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>18</v>
@@ -21467,13 +21497,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>18</v>
@@ -21486,13 +21516,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>18</v>
@@ -21505,7 +21535,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>29</v>
@@ -21524,7 +21554,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>29</v>
@@ -21639,10 +21669,10 @@
         <v>1932</v>
       </c>
       <c r="B15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -21654,10 +21684,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -21669,10 +21699,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C17" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -21748,13 +21778,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
@@ -21767,13 +21797,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>18</v>
@@ -21786,13 +21816,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
@@ -21811,7 +21841,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
@@ -21824,13 +21854,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
@@ -21843,13 +21873,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -21862,16 +21892,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E8"/>
       <c r="G8" s="2" t="s">
@@ -21881,16 +21911,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="2" t="s">
@@ -21900,16 +21930,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E10"/>
       <c r="G10" s="2" t="s">
@@ -21919,16 +21949,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E11"/>
       <c r="G11" s="2" t="s">
@@ -21938,13 +21968,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -21974,13 +22004,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -21992,10 +22022,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C16" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -22007,10 +22037,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -22291,13 +22321,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>18</v>
@@ -22416,13 +22446,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>18</v>
@@ -22435,13 +22465,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>18</v>
@@ -22691,13 +22721,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>18</v>
@@ -22710,13 +22740,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>18</v>
@@ -22729,13 +22759,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>18</v>
@@ -22882,25 +22912,25 @@
         <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -22912,10 +22942,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -22927,55 +22957,55 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C27" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -22987,10 +23017,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -23002,10 +23032,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -23017,10 +23047,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C30" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -23032,25 +23062,25 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C31" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C32" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -23062,40 +23092,40 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -23107,10 +23137,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -23122,25 +23152,25 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C37" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -23152,10 +23182,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -23167,10 +23197,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -23182,10 +23212,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -23197,10 +23227,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C42" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -23212,10 +23242,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -23227,10 +23257,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C44" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -23242,10 +23272,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C45" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -23257,10 +23287,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C46" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -23272,10 +23302,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C47" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -23287,10 +23317,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C48" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -23302,10 +23332,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -23317,10 +23347,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -23332,10 +23362,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C51" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -23347,10 +23377,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C52" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -23362,10 +23392,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C53" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -23377,10 +23407,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C54" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -23392,10 +23422,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -23407,10 +23437,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C56" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -23422,10 +23452,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C57" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -23437,10 +23467,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -23452,10 +23482,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C59" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -23467,10 +23497,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C60" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -23482,10 +23512,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C61" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -23497,10 +23527,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C62" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -23512,10 +23542,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C63" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -23527,10 +23557,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C64" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -23542,10 +23572,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C65" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -23557,10 +23587,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C66" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -23572,10 +23602,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C67" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -23587,40 +23617,40 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C68" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C69" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C70" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -23632,10 +23662,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C71" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -23647,10 +23677,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -23662,10 +23692,10 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C73" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -23677,10 +23707,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -23692,31 +23722,31 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C75" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C76" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
       </c>
       <c r="E76" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="78">
@@ -24048,7 +24078,7 @@
       </c>
       <c r="E4"/>
       <c r="G4" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -24069,7 +24099,7 @@
       </c>
       <c r="E5"/>
       <c r="G5" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -24090,7 +24120,7 @@
       </c>
       <c r="E6"/>
       <c r="G6" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -24512,13 +24542,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>18</v>
@@ -24535,13 +24565,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>18</v>
@@ -24558,13 +24588,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>18</v>
@@ -24758,7 +24788,7 @@
       </c>
       <c r="E38"/>
       <c r="G38" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H38"/>
     </row>
@@ -24777,7 +24807,7 @@
       </c>
       <c r="E39"/>
       <c r="G39" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H39"/>
     </row>
@@ -25565,25 +25595,25 @@
         <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C82" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C83" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -25595,10 +25625,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C84" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -25610,55 +25640,55 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C85" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
       </c>
       <c r="E85" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C86" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C87" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C88" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -25670,10 +25700,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C89" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -25685,10 +25715,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C90" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -25700,10 +25730,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C91" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -25715,25 +25745,25 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C92" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
       </c>
       <c r="E92" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C93" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -25745,40 +25775,40 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C95" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C96" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -25790,10 +25820,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C97" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -25805,25 +25835,25 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C98" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C99" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
@@ -25835,10 +25865,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C100" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -25850,10 +25880,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C101" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -25865,10 +25895,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C102" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -25880,10 +25910,10 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C103" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D103" t="s">
         <v>18</v>
@@ -25895,10 +25925,10 @@
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C104" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
@@ -25910,10 +25940,10 @@
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C105" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
@@ -25925,10 +25955,10 @@
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C106" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
@@ -25940,10 +25970,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C107" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -25955,10 +25985,10 @@
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C108" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -25970,10 +26000,10 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C109" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -25985,10 +26015,10 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C110" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
@@ -26000,10 +26030,10 @@
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C111" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -26015,10 +26045,10 @@
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C112" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D112" t="s">
         <v>18</v>
@@ -26030,10 +26060,10 @@
     <row r="113">
       <c r="A113"/>
       <c r="B113" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C113" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D113" t="s">
         <v>18</v>
@@ -26045,10 +26075,10 @@
     <row r="114">
       <c r="A114"/>
       <c r="B114" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C114" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D114" t="s">
         <v>18</v>
@@ -26060,10 +26090,10 @@
     <row r="115">
       <c r="A115"/>
       <c r="B115" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C115" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D115" t="s">
         <v>18</v>
@@ -26075,10 +26105,10 @@
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C116" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
@@ -26090,10 +26120,10 @@
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C117" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D117" t="s">
         <v>18</v>
@@ -26105,10 +26135,10 @@
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C118" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D118" t="s">
         <v>18</v>
@@ -26120,10 +26150,10 @@
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C119" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D119" t="s">
         <v>18</v>
@@ -26135,10 +26165,10 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C120" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D120" t="s">
         <v>18</v>
@@ -26150,10 +26180,10 @@
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C121" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D121" t="s">
         <v>18</v>
@@ -26165,10 +26195,10 @@
     <row r="122">
       <c r="A122"/>
       <c r="B122" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C122" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D122" t="s">
         <v>18</v>
@@ -26180,10 +26210,10 @@
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C123" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D123" t="s">
         <v>18</v>
@@ -26195,10 +26225,10 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C124" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
@@ -26210,10 +26240,10 @@
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C125" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D125" t="s">
         <v>18</v>
@@ -26225,10 +26255,10 @@
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C126" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D126" t="s">
         <v>18</v>
@@ -26240,10 +26270,10 @@
     <row r="127">
       <c r="A127"/>
       <c r="B127" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C127" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D127" t="s">
         <v>18</v>
@@ -26255,10 +26285,10 @@
     <row r="128">
       <c r="A128"/>
       <c r="B128" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C128" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="D128" t="s">
         <v>18</v>
@@ -26270,40 +26300,40 @@
     <row r="129">
       <c r="A129"/>
       <c r="B129" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C129" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D129" t="s">
         <v>18</v>
       </c>
       <c r="E129" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="130">
       <c r="A130"/>
       <c r="B130" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C130" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
       </c>
       <c r="E130" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="131">
       <c r="A131"/>
       <c r="B131" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C131" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="D131" t="s">
         <v>18</v>
@@ -26315,10 +26345,10 @@
     <row r="132">
       <c r="A132"/>
       <c r="B132" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C132" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
@@ -26330,10 +26360,10 @@
     <row r="133">
       <c r="A133"/>
       <c r="B133" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="C133" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D133" t="s">
         <v>18</v>
@@ -26345,10 +26375,10 @@
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C134" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
@@ -26360,10 +26390,10 @@
     <row r="135">
       <c r="A135"/>
       <c r="B135" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C135" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D135" t="s">
         <v>18</v>
@@ -26375,31 +26405,31 @@
     <row r="136">
       <c r="A136"/>
       <c r="B136" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D136" t="s">
         <v>18</v>
       </c>
       <c r="E136" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
     </row>
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C137" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D137" t="s">
         <v>18</v>
       </c>
       <c r="E137" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="139">
@@ -26491,7 +26521,7 @@
         <v>527</v>
       </c>
       <c r="C145" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D145" t="s">
         <v>18</v>
@@ -26755,10 +26785,10 @@
     <row r="165">
       <c r="A165"/>
       <c r="B165" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C165" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D165" t="s">
         <v>18</v>
@@ -26898,10 +26928,10 @@
     <row r="176">
       <c r="A176"/>
       <c r="B176" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C176" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D176" t="s">
         <v>18</v>
@@ -26962,10 +26992,10 @@
     <row r="181">
       <c r="A181"/>
       <c r="B181" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C181" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D181" t="s">
         <v>18</v>
@@ -27060,10 +27090,10 @@
     <row r="189">
       <c r="A189"/>
       <c r="B189" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C189" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D189" t="s">
         <v>18</v>
@@ -27165,10 +27195,10 @@
     <row r="196">
       <c r="A196"/>
       <c r="B196" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C196" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D196" t="s">
         <v>18</v>
@@ -27278,7 +27308,7 @@
     <row r="205">
       <c r="A205"/>
       <c r="B205" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C205" t="s">
         <v>602</v>
@@ -27293,10 +27323,10 @@
     <row r="206">
       <c r="A206"/>
       <c r="B206" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C206" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D206" t="s">
         <v>18</v>
@@ -27308,10 +27338,10 @@
     <row r="207">
       <c r="A207"/>
       <c r="B207" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C207" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D207" t="s">
         <v>18</v>
@@ -27462,10 +27492,10 @@
     <row r="218">
       <c r="A218"/>
       <c r="B218" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C218" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D218" t="s">
         <v>18</v>
@@ -27541,10 +27571,10 @@
     <row r="224">
       <c r="A224"/>
       <c r="B224" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C224" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D224" t="s">
         <v>18</v>
@@ -27878,10 +27908,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C17" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -28288,7 +28318,7 @@
       </c>
       <c r="E19"/>
       <c r="G19" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H19"/>
     </row>
@@ -28307,7 +28337,7 @@
       </c>
       <c r="E20"/>
       <c r="G20" s="5" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="H20"/>
     </row>
@@ -28948,7 +28978,7 @@
       </c>
       <c r="E53"/>
       <c r="G53" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H53"/>
     </row>
@@ -28967,7 +28997,7 @@
       </c>
       <c r="E54"/>
       <c r="G54" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H54"/>
     </row>
@@ -28986,7 +29016,7 @@
       </c>
       <c r="E55"/>
       <c r="G55" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H55"/>
     </row>
@@ -29005,7 +29035,7 @@
       </c>
       <c r="E56"/>
       <c r="G56" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H56"/>
     </row>
@@ -30281,7 +30311,7 @@
       </c>
       <c r="E122"/>
       <c r="G122" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H122"/>
     </row>
@@ -30300,7 +30330,7 @@
       </c>
       <c r="E123"/>
       <c r="G123" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H123"/>
     </row>
@@ -30319,7 +30349,7 @@
       </c>
       <c r="E124"/>
       <c r="G124" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H124"/>
     </row>
@@ -30338,7 +30368,7 @@
       </c>
       <c r="E125"/>
       <c r="G125" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H125"/>
     </row>
@@ -30357,7 +30387,7 @@
       </c>
       <c r="E126"/>
       <c r="G126" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H126"/>
     </row>
@@ -30376,7 +30406,7 @@
       </c>
       <c r="E127"/>
       <c r="G127" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H127"/>
     </row>
@@ -30395,7 +30425,7 @@
       </c>
       <c r="E128"/>
       <c r="G128" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H128"/>
     </row>
@@ -30414,7 +30444,7 @@
       </c>
       <c r="E129"/>
       <c r="G129" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H129"/>
     </row>
@@ -30433,7 +30463,7 @@
       </c>
       <c r="E130"/>
       <c r="G130" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H130"/>
     </row>
@@ -30452,7 +30482,7 @@
       </c>
       <c r="E131"/>
       <c r="G131" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H131"/>
     </row>
@@ -30471,7 +30501,7 @@
       </c>
       <c r="E132"/>
       <c r="G132" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H132"/>
     </row>
@@ -30490,7 +30520,7 @@
       </c>
       <c r="E133"/>
       <c r="G133" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H133"/>
     </row>
@@ -30509,7 +30539,7 @@
       </c>
       <c r="E134"/>
       <c r="G134" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H134"/>
     </row>
@@ -30528,7 +30558,7 @@
       </c>
       <c r="E135"/>
       <c r="G135" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H135"/>
     </row>
@@ -30547,7 +30577,7 @@
       </c>
       <c r="E136"/>
       <c r="G136" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H136"/>
     </row>
@@ -30566,7 +30596,7 @@
       </c>
       <c r="E137"/>
       <c r="G137" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H137"/>
     </row>
@@ -30585,7 +30615,7 @@
       </c>
       <c r="E138"/>
       <c r="G138" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="H138"/>
     </row>
@@ -30623,7 +30653,7 @@
       </c>
       <c r="E140"/>
       <c r="G140" s="5" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="H140"/>
     </row>
@@ -31229,10 +31259,10 @@
     <row r="173">
       <c r="A173"/>
       <c r="B173" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C173" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D173" t="s">
         <v>18</v>
@@ -31293,10 +31323,10 @@
     <row r="178">
       <c r="A178"/>
       <c r="B178" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C178" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D178" t="s">
         <v>18</v>
@@ -31451,7 +31481,7 @@
     <row r="190">
       <c r="A190"/>
       <c r="B190" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C190" t="s">
         <v>1073</v>
@@ -32354,7 +32384,7 @@
         <v>383</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>18</v>
@@ -32645,10 +32675,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -32739,10 +32769,10 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C70" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -32773,10 +32803,10 @@
         <v>1206</v>
       </c>
       <c r="B73" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C73" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -32788,10 +32818,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C74" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -32818,10 +32848,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C76" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -32882,10 +32912,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C81" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -32955,7 +32985,7 @@
         <v>383</v>
       </c>
       <c r="C2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -33031,7 +33061,7 @@
         <v>383</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>18</v>
@@ -33436,10 +33466,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>341</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>342</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -33887,10 +33917,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -33951,10 +33981,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -34045,10 +34075,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -34460,10 +34490,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -34524,10 +34554,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -34618,10 +34648,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>260</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7055" uniqueCount="1984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7047" uniqueCount="1984">
   <si>
     <t>Field</t>
   </si>
@@ -424,646 +424,646 @@
     <t>Female</t>
   </si>
   <si>
+    <t>YEARS</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>MONTHS</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>DAYS</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t>ALIVE</t>
+  </si>
+  <si>
+    <t>Alive</t>
+  </si>
+  <si>
+    <t>DEAD</t>
+  </si>
+  <si>
+    <t>Dead</t>
+  </si>
+  <si>
+    <t>BURIED</t>
+  </si>
+  <si>
+    <t>Buried</t>
+  </si>
+  <si>
+    <t>EPIDEMIC_DISEASE</t>
+  </si>
+  <si>
+    <t>Epidemic disease</t>
+  </si>
+  <si>
+    <t>OTHER_CAUSE</t>
+  </si>
+  <si>
+    <t>Other cause</t>
+  </si>
+  <si>
+    <t>AFP</t>
+  </si>
+  <si>
+    <t>Acute Flaccid Paralysis</t>
+  </si>
+  <si>
+    <t>CHOLERA</t>
+  </si>
+  <si>
+    <t>Cholera</t>
+  </si>
+  <si>
+    <t>CONGENITAL_RUBELLA</t>
+  </si>
+  <si>
+    <t>Congenital Rubella</t>
+  </si>
+  <si>
+    <t>CSM</t>
+  </si>
+  <si>
+    <t>Meningitis (CSM)</t>
+  </si>
+  <si>
+    <t>Meningitis</t>
+  </si>
+  <si>
+    <t>DENGUE</t>
+  </si>
+  <si>
+    <t>Dengue Fever</t>
+  </si>
+  <si>
+    <t>Dengue</t>
+  </si>
+  <si>
+    <t>EVD</t>
+  </si>
+  <si>
+    <t>Ebola Virus Disease</t>
+  </si>
+  <si>
+    <t>GUINEA_WORM</t>
+  </si>
+  <si>
+    <t>Guinea Worm</t>
+  </si>
+  <si>
+    <t>LASSA</t>
+  </si>
+  <si>
+    <t>Lassa</t>
+  </si>
+  <si>
+    <t>MEASLES</t>
+  </si>
+  <si>
+    <t>Measles</t>
+  </si>
+  <si>
+    <t>MONKEYPOX</t>
+  </si>
+  <si>
+    <t>Monkeypox</t>
+  </si>
+  <si>
+    <t>NEW_INFLUENZA</t>
+  </si>
+  <si>
+    <t>Influenza (New subtype)</t>
+  </si>
+  <si>
+    <t>New Flu</t>
+  </si>
+  <si>
+    <t>PLAGUE</t>
+  </si>
+  <si>
+    <t>Plague</t>
+  </si>
+  <si>
+    <t>POLIO</t>
+  </si>
+  <si>
+    <t>Poliomyelitis</t>
+  </si>
+  <si>
+    <t>Polio</t>
+  </si>
+  <si>
+    <t>UNSPECIFIED_VHF</t>
+  </si>
+  <si>
+    <t>Unspecified VHF</t>
+  </si>
+  <si>
+    <t>VHF</t>
+  </si>
+  <si>
+    <t>WEST_NILE_FEVER</t>
+  </si>
+  <si>
+    <t>West Nile Fever</t>
+  </si>
+  <si>
+    <t>YELLOW_FEVER</t>
+  </si>
+  <si>
+    <t>Yellow Fever</t>
+  </si>
+  <si>
+    <t>RABIES</t>
+  </si>
+  <si>
+    <t>Human Rabies</t>
+  </si>
+  <si>
+    <t>Rabies</t>
+  </si>
+  <si>
+    <t>ANTHRAX</t>
+  </si>
+  <si>
+    <t>Anthrax</t>
+  </si>
+  <si>
+    <t>CORONAVIRUS</t>
+  </si>
+  <si>
+    <t>COVID-19</t>
+  </si>
+  <si>
+    <t>PNEUMONIA</t>
+  </si>
+  <si>
+    <t>Pneumonia</t>
+  </si>
+  <si>
+    <t>MALARIA</t>
+  </si>
+  <si>
+    <t>Malaria</t>
+  </si>
+  <si>
+    <t>TYPHOID_FEVER</t>
+  </si>
+  <si>
+    <t>Typhoid Fever</t>
+  </si>
+  <si>
+    <t>ACUTE_VIRAL_HEPATITIS</t>
+  </si>
+  <si>
+    <t>Acute Viral Hepatitis</t>
+  </si>
+  <si>
+    <t>NON_NEONATAL_TETANUS</t>
+  </si>
+  <si>
+    <t>Non-Neonatal Tetanus</t>
+  </si>
+  <si>
+    <t>HIV</t>
+  </si>
+  <si>
+    <t>SCHISTOSOMIASIS</t>
+  </si>
+  <si>
+    <t>Schistosomiasis</t>
+  </si>
+  <si>
+    <t>SOIL_TRANSMITTED_HELMINTHS</t>
+  </si>
+  <si>
+    <t>Soil-Transmitted Helminths</t>
+  </si>
+  <si>
+    <t>TRYPANOSOMIASIS</t>
+  </si>
+  <si>
+    <t>Trypanosomiasis</t>
+  </si>
+  <si>
+    <t>DIARRHEA_DEHYDRATION</t>
+  </si>
+  <si>
+    <t>Diarrhea w/ Dehydration (&lt; 5)</t>
+  </si>
+  <si>
+    <t>DIARRHEA_BLOOD</t>
+  </si>
+  <si>
+    <t>Diarrhea w/ Blood (Shigella)</t>
+  </si>
+  <si>
+    <t>SNAKE_BITE</t>
+  </si>
+  <si>
+    <t>Snake Bite</t>
+  </si>
+  <si>
+    <t>RUBELLA</t>
+  </si>
+  <si>
+    <t>Rubella</t>
+  </si>
+  <si>
+    <t>TUBERCULOSIS</t>
+  </si>
+  <si>
+    <t>Tuberculosis</t>
+  </si>
+  <si>
+    <t>LEPROSY</t>
+  </si>
+  <si>
+    <t>Leprosy</t>
+  </si>
+  <si>
+    <t>LYMPHATIC_FILARIASIS</t>
+  </si>
+  <si>
+    <t>Lymphatic Filariasis</t>
+  </si>
+  <si>
+    <t>BURULI_ULCER</t>
+  </si>
+  <si>
+    <t>Buruli Ulcer</t>
+  </si>
+  <si>
+    <t>PERTUSSIS</t>
+  </si>
+  <si>
+    <t>Pertussis</t>
+  </si>
+  <si>
+    <t>NEONATAL_TETANUS</t>
+  </si>
+  <si>
+    <t>Neonatal Tetanus</t>
+  </si>
+  <si>
+    <t>ONCHOCERCIASIS</t>
+  </si>
+  <si>
+    <t>Onchocerciasis</t>
+  </si>
+  <si>
+    <t>DIPHTERIA</t>
+  </si>
+  <si>
+    <t>Diphteria</t>
+  </si>
+  <si>
+    <t>TRACHOMA</t>
+  </si>
+  <si>
+    <t>Trachoma</t>
+  </si>
+  <si>
+    <t>YAWS_ENDEMIC_SYPHILIS</t>
+  </si>
+  <si>
+    <t>Yaws and Endemic Syphilis</t>
+  </si>
+  <si>
+    <t>MATERNAL_DEATHS</t>
+  </si>
+  <si>
+    <t>Maternal Deaths</t>
+  </si>
+  <si>
+    <t>PERINATAL_DEATHS</t>
+  </si>
+  <si>
+    <t>Perinatal Deaths</t>
+  </si>
+  <si>
+    <t>INFLUENZA_A</t>
+  </si>
+  <si>
+    <t>Influenza A</t>
+  </si>
+  <si>
+    <t>INFLUENZA_B</t>
+  </si>
+  <si>
+    <t>Influenza B</t>
+  </si>
+  <si>
+    <t>H_METAPNEUMOVIRUS</t>
+  </si>
+  <si>
+    <t>H.metapneumovirus</t>
+  </si>
+  <si>
+    <t>RESPIRATORY_SYNCYTIAL_VIRUS</t>
+  </si>
+  <si>
+    <t>Respiratory syncytial virus (RSV)</t>
+  </si>
+  <si>
+    <t>RSV</t>
+  </si>
+  <si>
+    <t>PARAINFLUENZA_1_4</t>
+  </si>
+  <si>
+    <t>Parainfluenza (1-4)</t>
+  </si>
+  <si>
+    <t>Parainfluenza</t>
+  </si>
+  <si>
+    <t>ADENOVIRUS</t>
+  </si>
+  <si>
+    <t>Adenovirus</t>
+  </si>
+  <si>
+    <t>RHINOVIRUS</t>
+  </si>
+  <si>
+    <t>Rhinovirus</t>
+  </si>
+  <si>
+    <t>ENTEROVIRUS</t>
+  </si>
+  <si>
+    <t>Enterovirus</t>
+  </si>
+  <si>
+    <t>M_PNEUMONIAE</t>
+  </si>
+  <si>
+    <t>M.pneumoniae</t>
+  </si>
+  <si>
+    <t>C_PNEUMONIAE</t>
+  </si>
+  <si>
+    <t>C.pneumoniae</t>
+  </si>
+  <si>
     <t>OTHER</t>
   </si>
   <si>
+    <t>Other Epidemic Disease</t>
+  </si>
+  <si>
     <t>Other</t>
   </si>
   <si>
+    <t>UNDEFINED</t>
+  </si>
+  <si>
+    <t>Not Yet Defined</t>
+  </si>
+  <si>
+    <t>Undefined</t>
+  </si>
+  <si>
+    <t>COMMUNITY</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>HOSPITAL</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>FAMILY_COMMUNITY</t>
+  </si>
+  <si>
+    <t>Family/Community</t>
+  </si>
+  <si>
+    <t>OUTBREAK_TEAM</t>
+  </si>
+  <si>
+    <t>Outbreak burial team</t>
+  </si>
+  <si>
+    <t>NONE</t>
+  </si>
+  <si>
+    <t>No education</t>
+  </si>
+  <si>
+    <t>NURSERY</t>
+  </si>
+  <si>
+    <t>Nursery</t>
+  </si>
+  <si>
+    <t>PRIMARY</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>SECONDARY</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>TERTIARY</t>
+  </si>
+  <si>
+    <t>Tertiary</t>
+  </si>
+  <si>
+    <t>FARMER</t>
+  </si>
+  <si>
+    <t>Farmer</t>
+  </si>
+  <si>
+    <t>BUTCHER</t>
+  </si>
+  <si>
+    <t>Butcher</t>
+  </si>
+  <si>
+    <t>HUNTER_MEAT_TRADER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hunter / trader of  game meat </t>
+  </si>
+  <si>
+    <t>MINER</t>
+  </si>
+  <si>
+    <t>Miner</t>
+  </si>
+  <si>
+    <t>RELIGIOUS_LEADER</t>
+  </si>
+  <si>
+    <t>Religious leader</t>
+  </si>
+  <si>
+    <t>HOUSEWIFE</t>
+  </si>
+  <si>
+    <t>Housewife</t>
+  </si>
+  <si>
+    <t>PUPIL_STUDENT</t>
+  </si>
+  <si>
+    <t>Pupil / student</t>
+  </si>
+  <si>
+    <t>CHILD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child </t>
+  </si>
+  <si>
+    <t>BUSINESSMAN_WOMAN</t>
+  </si>
+  <si>
+    <t>Businessman / woman</t>
+  </si>
+  <si>
+    <t>TRANSPORTER</t>
+  </si>
+  <si>
+    <t>Transporter</t>
+  </si>
+  <si>
+    <t>HEALTHCARE_WORKER</t>
+  </si>
+  <si>
+    <t>Healthcare worker</t>
+  </si>
+  <si>
+    <t>TRADITIONAL_SPIRITUAL_HEALER</t>
+  </si>
+  <si>
+    <t>Traditional / spiritual healer</t>
+  </si>
+  <si>
+    <t>WORKING_WITH_ANIMALS</t>
+  </si>
+  <si>
+    <t>Working with animals</t>
+  </si>
+  <si>
+    <t>LABORATORY_STAFF</t>
+  </si>
+  <si>
+    <t>Laboratory staff</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>community</t>
+  </si>
+  <si>
+    <t>Address or landmark</t>
+  </si>
+  <si>
+    <t>details</t>
+  </si>
+  <si>
+    <t>Community contact person</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>areaType</t>
+  </si>
+  <si>
+    <t>AreaType</t>
+  </si>
+  <si>
+    <t>Area type (urban/rural)</t>
+  </si>
+  <si>
+    <t>The type of area of the community.</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>GPS latitude</t>
+  </si>
+  <si>
+    <t>GPS latitude is the north/south angular location in degrees</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>GPS longitude</t>
+  </si>
+  <si>
+    <t>GPS longitude is the the east/west angular location in degrees</t>
+  </si>
+  <si>
+    <t>latLonAccuracy</t>
+  </si>
+  <si>
+    <t>GPS accuracy in m</t>
+  </si>
+  <si>
+    <t>If you draw a circle centered at this location's latitude and longitude, and with a radius equal to the accuracy, then there is a 68% probability that the true location is inside the circle</t>
+  </si>
+  <si>
+    <t>postalCode</t>
+  </si>
+  <si>
+    <t>Postal code</t>
+  </si>
+  <si>
+    <t>URBAN</t>
+  </si>
+  <si>
+    <t>Urban</t>
+  </si>
+  <si>
+    <t>RURAL</t>
+  </si>
+  <si>
+    <t>Rural</t>
+  </si>
+  <si>
     <t>UNKNOWN</t>
   </si>
   <si>
     <t>Unknown</t>
-  </si>
-  <si>
-    <t>YEARS</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>MONTHS</t>
-  </si>
-  <si>
-    <t>Months</t>
-  </si>
-  <si>
-    <t>DAYS</t>
-  </si>
-  <si>
-    <t>Days</t>
-  </si>
-  <si>
-    <t>ALIVE</t>
-  </si>
-  <si>
-    <t>Alive</t>
-  </si>
-  <si>
-    <t>DEAD</t>
-  </si>
-  <si>
-    <t>Dead</t>
-  </si>
-  <si>
-    <t>BURIED</t>
-  </si>
-  <si>
-    <t>Buried</t>
-  </si>
-  <si>
-    <t>EPIDEMIC_DISEASE</t>
-  </si>
-  <si>
-    <t>Epidemic disease</t>
-  </si>
-  <si>
-    <t>OTHER_CAUSE</t>
-  </si>
-  <si>
-    <t>Other cause</t>
-  </si>
-  <si>
-    <t>AFP</t>
-  </si>
-  <si>
-    <t>Acute Flaccid Paralysis</t>
-  </si>
-  <si>
-    <t>CHOLERA</t>
-  </si>
-  <si>
-    <t>Cholera</t>
-  </si>
-  <si>
-    <t>CONGENITAL_RUBELLA</t>
-  </si>
-  <si>
-    <t>Congenital Rubella</t>
-  </si>
-  <si>
-    <t>CSM</t>
-  </si>
-  <si>
-    <t>Meningitis (CSM)</t>
-  </si>
-  <si>
-    <t>Meningitis</t>
-  </si>
-  <si>
-    <t>DENGUE</t>
-  </si>
-  <si>
-    <t>Dengue Fever</t>
-  </si>
-  <si>
-    <t>Dengue</t>
-  </si>
-  <si>
-    <t>EVD</t>
-  </si>
-  <si>
-    <t>Ebola Virus Disease</t>
-  </si>
-  <si>
-    <t>GUINEA_WORM</t>
-  </si>
-  <si>
-    <t>Guinea Worm</t>
-  </si>
-  <si>
-    <t>LASSA</t>
-  </si>
-  <si>
-    <t>Lassa</t>
-  </si>
-  <si>
-    <t>MEASLES</t>
-  </si>
-  <si>
-    <t>Measles</t>
-  </si>
-  <si>
-    <t>MONKEYPOX</t>
-  </si>
-  <si>
-    <t>Monkeypox</t>
-  </si>
-  <si>
-    <t>NEW_INFLUENZA</t>
-  </si>
-  <si>
-    <t>Influenza (New subtype)</t>
-  </si>
-  <si>
-    <t>New Flu</t>
-  </si>
-  <si>
-    <t>PLAGUE</t>
-  </si>
-  <si>
-    <t>Plague</t>
-  </si>
-  <si>
-    <t>POLIO</t>
-  </si>
-  <si>
-    <t>Poliomyelitis</t>
-  </si>
-  <si>
-    <t>Polio</t>
-  </si>
-  <si>
-    <t>UNSPECIFIED_VHF</t>
-  </si>
-  <si>
-    <t>Unspecified VHF</t>
-  </si>
-  <si>
-    <t>VHF</t>
-  </si>
-  <si>
-    <t>WEST_NILE_FEVER</t>
-  </si>
-  <si>
-    <t>West Nile Fever</t>
-  </si>
-  <si>
-    <t>YELLOW_FEVER</t>
-  </si>
-  <si>
-    <t>Yellow Fever</t>
-  </si>
-  <si>
-    <t>RABIES</t>
-  </si>
-  <si>
-    <t>Human Rabies</t>
-  </si>
-  <si>
-    <t>Rabies</t>
-  </si>
-  <si>
-    <t>ANTHRAX</t>
-  </si>
-  <si>
-    <t>Anthrax</t>
-  </si>
-  <si>
-    <t>CORONAVIRUS</t>
-  </si>
-  <si>
-    <t>COVID-19</t>
-  </si>
-  <si>
-    <t>PNEUMONIA</t>
-  </si>
-  <si>
-    <t>Pneumonia</t>
-  </si>
-  <si>
-    <t>MALARIA</t>
-  </si>
-  <si>
-    <t>Malaria</t>
-  </si>
-  <si>
-    <t>TYPHOID_FEVER</t>
-  </si>
-  <si>
-    <t>Typhoid Fever</t>
-  </si>
-  <si>
-    <t>ACUTE_VIRAL_HEPATITIS</t>
-  </si>
-  <si>
-    <t>Acute Viral Hepatitis</t>
-  </si>
-  <si>
-    <t>NON_NEONATAL_TETANUS</t>
-  </si>
-  <si>
-    <t>Non-Neonatal Tetanus</t>
-  </si>
-  <si>
-    <t>HIV</t>
-  </si>
-  <si>
-    <t>SCHISTOSOMIASIS</t>
-  </si>
-  <si>
-    <t>Schistosomiasis</t>
-  </si>
-  <si>
-    <t>SOIL_TRANSMITTED_HELMINTHS</t>
-  </si>
-  <si>
-    <t>Soil-Transmitted Helminths</t>
-  </si>
-  <si>
-    <t>TRYPANOSOMIASIS</t>
-  </si>
-  <si>
-    <t>Trypanosomiasis</t>
-  </si>
-  <si>
-    <t>DIARRHEA_DEHYDRATION</t>
-  </si>
-  <si>
-    <t>Diarrhea w/ Dehydration (&lt; 5)</t>
-  </si>
-  <si>
-    <t>DIARRHEA_BLOOD</t>
-  </si>
-  <si>
-    <t>Diarrhea w/ Blood (Shigella)</t>
-  </si>
-  <si>
-    <t>SNAKE_BITE</t>
-  </si>
-  <si>
-    <t>Snake Bite</t>
-  </si>
-  <si>
-    <t>RUBELLA</t>
-  </si>
-  <si>
-    <t>Rubella</t>
-  </si>
-  <si>
-    <t>TUBERCULOSIS</t>
-  </si>
-  <si>
-    <t>Tuberculosis</t>
-  </si>
-  <si>
-    <t>LEPROSY</t>
-  </si>
-  <si>
-    <t>Leprosy</t>
-  </si>
-  <si>
-    <t>LYMPHATIC_FILARIASIS</t>
-  </si>
-  <si>
-    <t>Lymphatic Filariasis</t>
-  </si>
-  <si>
-    <t>BURULI_ULCER</t>
-  </si>
-  <si>
-    <t>Buruli Ulcer</t>
-  </si>
-  <si>
-    <t>PERTUSSIS</t>
-  </si>
-  <si>
-    <t>Pertussis</t>
-  </si>
-  <si>
-    <t>NEONATAL_TETANUS</t>
-  </si>
-  <si>
-    <t>Neonatal Tetanus</t>
-  </si>
-  <si>
-    <t>ONCHOCERCIASIS</t>
-  </si>
-  <si>
-    <t>Onchocerciasis</t>
-  </si>
-  <si>
-    <t>DIPHTERIA</t>
-  </si>
-  <si>
-    <t>Diphteria</t>
-  </si>
-  <si>
-    <t>TRACHOMA</t>
-  </si>
-  <si>
-    <t>Trachoma</t>
-  </si>
-  <si>
-    <t>YAWS_ENDEMIC_SYPHILIS</t>
-  </si>
-  <si>
-    <t>Yaws and Endemic Syphilis</t>
-  </si>
-  <si>
-    <t>MATERNAL_DEATHS</t>
-  </si>
-  <si>
-    <t>Maternal Deaths</t>
-  </si>
-  <si>
-    <t>PERINATAL_DEATHS</t>
-  </si>
-  <si>
-    <t>Perinatal Deaths</t>
-  </si>
-  <si>
-    <t>INFLUENZA_A</t>
-  </si>
-  <si>
-    <t>Influenza A</t>
-  </si>
-  <si>
-    <t>INFLUENZA_B</t>
-  </si>
-  <si>
-    <t>Influenza B</t>
-  </si>
-  <si>
-    <t>H_METAPNEUMOVIRUS</t>
-  </si>
-  <si>
-    <t>H.metapneumovirus</t>
-  </si>
-  <si>
-    <t>RESPIRATORY_SYNCYTIAL_VIRUS</t>
-  </si>
-  <si>
-    <t>Respiratory syncytial virus (RSV)</t>
-  </si>
-  <si>
-    <t>RSV</t>
-  </si>
-  <si>
-    <t>PARAINFLUENZA_1_4</t>
-  </si>
-  <si>
-    <t>Parainfluenza (1-4)</t>
-  </si>
-  <si>
-    <t>Parainfluenza</t>
-  </si>
-  <si>
-    <t>ADENOVIRUS</t>
-  </si>
-  <si>
-    <t>Adenovirus</t>
-  </si>
-  <si>
-    <t>RHINOVIRUS</t>
-  </si>
-  <si>
-    <t>Rhinovirus</t>
-  </si>
-  <si>
-    <t>ENTEROVIRUS</t>
-  </si>
-  <si>
-    <t>Enterovirus</t>
-  </si>
-  <si>
-    <t>M_PNEUMONIAE</t>
-  </si>
-  <si>
-    <t>M.pneumoniae</t>
-  </si>
-  <si>
-    <t>C_PNEUMONIAE</t>
-  </si>
-  <si>
-    <t>C.pneumoniae</t>
-  </si>
-  <si>
-    <t>Other Epidemic Disease</t>
-  </si>
-  <si>
-    <t>UNDEFINED</t>
-  </si>
-  <si>
-    <t>Not Yet Defined</t>
-  </si>
-  <si>
-    <t>Undefined</t>
-  </si>
-  <si>
-    <t>COMMUNITY</t>
-  </si>
-  <si>
-    <t>Community</t>
-  </si>
-  <si>
-    <t>HOSPITAL</t>
-  </si>
-  <si>
-    <t>Hospital</t>
-  </si>
-  <si>
-    <t>FAMILY_COMMUNITY</t>
-  </si>
-  <si>
-    <t>Family/Community</t>
-  </si>
-  <si>
-    <t>OUTBREAK_TEAM</t>
-  </si>
-  <si>
-    <t>Outbreak burial team</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>No education</t>
-  </si>
-  <si>
-    <t>NURSERY</t>
-  </si>
-  <si>
-    <t>Nursery</t>
-  </si>
-  <si>
-    <t>PRIMARY</t>
-  </si>
-  <si>
-    <t>Primary</t>
-  </si>
-  <si>
-    <t>SECONDARY</t>
-  </si>
-  <si>
-    <t>Secondary</t>
-  </si>
-  <si>
-    <t>TERTIARY</t>
-  </si>
-  <si>
-    <t>Tertiary</t>
-  </si>
-  <si>
-    <t>FARMER</t>
-  </si>
-  <si>
-    <t>Farmer</t>
-  </si>
-  <si>
-    <t>BUTCHER</t>
-  </si>
-  <si>
-    <t>Butcher</t>
-  </si>
-  <si>
-    <t>HUNTER_MEAT_TRADER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hunter / trader of  game meat </t>
-  </si>
-  <si>
-    <t>MINER</t>
-  </si>
-  <si>
-    <t>Miner</t>
-  </si>
-  <si>
-    <t>RELIGIOUS_LEADER</t>
-  </si>
-  <si>
-    <t>Religious leader</t>
-  </si>
-  <si>
-    <t>HOUSEWIFE</t>
-  </si>
-  <si>
-    <t>Housewife</t>
-  </si>
-  <si>
-    <t>PUPIL_STUDENT</t>
-  </si>
-  <si>
-    <t>Pupil / student</t>
-  </si>
-  <si>
-    <t>CHILD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Child </t>
-  </si>
-  <si>
-    <t>BUSINESSMAN_WOMAN</t>
-  </si>
-  <si>
-    <t>Businessman / woman</t>
-  </si>
-  <si>
-    <t>TRANSPORTER</t>
-  </si>
-  <si>
-    <t>Transporter</t>
-  </si>
-  <si>
-    <t>HEALTHCARE_WORKER</t>
-  </si>
-  <si>
-    <t>Healthcare worker</t>
-  </si>
-  <si>
-    <t>TRADITIONAL_SPIRITUAL_HEALER</t>
-  </si>
-  <si>
-    <t>Traditional / spiritual healer</t>
-  </si>
-  <si>
-    <t>WORKING_WITH_ANIMALS</t>
-  </si>
-  <si>
-    <t>Working with animals</t>
-  </si>
-  <si>
-    <t>LABORATORY_STAFF</t>
-  </si>
-  <si>
-    <t>Laboratory staff</t>
-  </si>
-  <si>
-    <t>region</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t>district</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>community</t>
-  </si>
-  <si>
-    <t>Address or landmark</t>
-  </si>
-  <si>
-    <t>details</t>
-  </si>
-  <si>
-    <t>Community contact person</t>
-  </si>
-  <si>
-    <t>city</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>areaType</t>
-  </si>
-  <si>
-    <t>AreaType</t>
-  </si>
-  <si>
-    <t>Area type (urban/rural)</t>
-  </si>
-  <si>
-    <t>The type of area of the community.</t>
-  </si>
-  <si>
-    <t>latitude</t>
-  </si>
-  <si>
-    <t>GPS latitude</t>
-  </si>
-  <si>
-    <t>GPS latitude is the north/south angular location in degrees</t>
-  </si>
-  <si>
-    <t>longitude</t>
-  </si>
-  <si>
-    <t>GPS longitude</t>
-  </si>
-  <si>
-    <t>GPS longitude is the the east/west angular location in degrees</t>
-  </si>
-  <si>
-    <t>latLonAccuracy</t>
-  </si>
-  <si>
-    <t>GPS accuracy in m</t>
-  </si>
-  <si>
-    <t>If you draw a circle centered at this location's latitude and longitude, and with a radius equal to the accuracy, then there is a 68% probability that the true location is inside the circle</t>
-  </si>
-  <si>
-    <t>postalCode</t>
-  </si>
-  <si>
-    <t>Postal code</t>
-  </si>
-  <si>
-    <t>URBAN</t>
-  </si>
-  <si>
-    <t>Urban</t>
-  </si>
-  <si>
-    <t>RURAL</t>
-  </si>
-  <si>
-    <t>Rural</t>
   </si>
   <si>
     <t>disease</t>
@@ -6116,7 +6116,7 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="PersonOccupationType" displayName="PersonOccupationType" ref="A144:E159">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="PersonOccupationType" displayName="PersonOccupationType" ref="A142:E157">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6262,7 +6262,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PersonSex" displayName="PersonSex" ref="A49:E53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PersonSex" displayName="PersonSex" ref="A49:E51">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6419,7 +6419,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PersonApproximateAgeType" displayName="PersonApproximateAgeType" ref="A55:E58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PersonApproximateAgeType" displayName="PersonApproximateAgeType" ref="A53:E56">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6579,7 +6579,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PersonPresentCondition" displayName="PersonPresentCondition" ref="A60:E63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PersonPresentCondition" displayName="PersonPresentCondition" ref="A58:E61">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6742,7 +6742,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PersonCauseOfDeath" displayName="PersonCauseOfDeath" ref="A65:E67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="PersonCauseOfDeath" displayName="PersonCauseOfDeath" ref="A63:E65">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -6902,7 +6902,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="PersonDisease" displayName="PersonDisease" ref="A69:E125">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="PersonDisease" displayName="PersonDisease" ref="A67:E123">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7062,7 +7062,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PersonDeathPlaceType" displayName="PersonDeathPlaceType" ref="A127:E130">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="PersonDeathPlaceType" displayName="PersonDeathPlaceType" ref="A125:E128">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7222,7 +7222,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PersonBurialConductor" displayName="PersonBurialConductor" ref="A132:E134">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="PersonBurialConductor" displayName="PersonBurialConductor" ref="A130:E132">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7382,7 +7382,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="PersonEducationType" displayName="PersonEducationType" ref="A136:E142">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="PersonEducationType" displayName="PersonEducationType" ref="A134:E140">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7555,7 +7555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I159"/>
+  <dimension ref="A1:I157"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -8541,57 +8541,57 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52"/>
-      <c r="B52" t="s">
+    <row r="53">
+      <c r="A53" t="s">
+        <v>1</v>
+      </c>
+      <c r="B53" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>3</v>
+      </c>
+      <c r="E53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" t="s">
         <v>129</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C54" t="s">
         <v>130</v>
       </c>
-      <c r="D52" t="s">
-        <v>18</v>
-      </c>
-      <c r="E52" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53"/>
-      <c r="B53" t="s">
+      <c r="D54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55"/>
+      <c r="B55" t="s">
         <v>131</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C55" t="s">
         <v>132</v>
       </c>
-      <c r="D53" t="s">
-        <v>18</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" t="s">
-        <v>2</v>
-      </c>
       <c r="D55" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E55" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="s">
-        <v>36</v>
-      </c>
+      <c r="A56"/>
       <c r="B56" t="s">
         <v>133</v>
       </c>
@@ -8605,57 +8605,57 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57"/>
-      <c r="B57" t="s">
+    <row r="58">
+      <c r="A58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B59" t="s">
         <v>135</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C59" t="s">
         <v>136</v>
       </c>
-      <c r="D57" t="s">
-        <v>18</v>
-      </c>
-      <c r="E57" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58"/>
-      <c r="B58" t="s">
+      <c r="D59" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60"/>
+      <c r="B60" t="s">
         <v>137</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" t="s">
         <v>138</v>
       </c>
-      <c r="D58" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>1</v>
-      </c>
-      <c r="B60" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" t="s">
-        <v>2</v>
-      </c>
       <c r="D60" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="s">
-        <v>61</v>
-      </c>
+      <c r="A61"/>
       <c r="B61" t="s">
         <v>139</v>
       </c>
@@ -8669,106 +8669,106 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62"/>
-      <c r="B62" t="s">
+    <row r="63">
+      <c r="A63" t="s">
+        <v>1</v>
+      </c>
+      <c r="B63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" t="s">
+        <v>3</v>
+      </c>
+      <c r="E63" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64" t="s">
         <v>141</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C64" t="s">
         <v>142</v>
       </c>
-      <c r="D62" t="s">
-        <v>18</v>
-      </c>
-      <c r="E62" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63"/>
-      <c r="B63" t="s">
+      <c r="D64" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65"/>
+      <c r="B65" t="s">
         <v>143</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C65" t="s">
         <v>144</v>
       </c>
-      <c r="D63" t="s">
-        <v>18</v>
-      </c>
-      <c r="E63" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
         <v>1</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B67" t="s">
         <v>123</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C67" t="s">
         <v>2</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D67" t="s">
         <v>3</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E67" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>68</v>
-      </c>
-      <c r="B66" t="s">
+    <row r="68">
+      <c r="A68" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" t="s">
         <v>145</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C68" t="s">
         <v>146</v>
       </c>
-      <c r="D66" t="s">
-        <v>18</v>
-      </c>
-      <c r="E66" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67"/>
-      <c r="B67" t="s">
+      <c r="D68" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69"/>
+      <c r="B69" t="s">
         <v>147</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C69" t="s">
         <v>148</v>
       </c>
-      <c r="D67" t="s">
-        <v>18</v>
-      </c>
-      <c r="E67" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>1</v>
-      </c>
-      <c r="B69" t="s">
-        <v>123</v>
-      </c>
-      <c r="C69" t="s">
-        <v>2</v>
-      </c>
       <c r="D69" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="s">
-        <v>71</v>
-      </c>
+      <c r="A70"/>
       <c r="B70" t="s">
         <v>149</v>
       </c>
@@ -8779,7 +8779,7 @@
         <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71">
@@ -8794,31 +8794,31 @@
         <v>18</v>
       </c>
       <c r="E71" t="s">
-        <v>18</v>
+        <v>153</v>
       </c>
     </row>
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C72" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>44</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -8830,16 +8830,16 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C74" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>160</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75">
@@ -8854,7 +8854,7 @@
         <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>161</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -8899,16 +8899,16 @@
         <v>18</v>
       </c>
       <c r="E78" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C79" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -8920,61 +8920,61 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
       </c>
       <c r="E81" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
     </row>
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C82" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>178</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
       </c>
       <c r="E83" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -8989,16 +8989,16 @@
         <v>18</v>
       </c>
       <c r="E84" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
     </row>
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C85" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -9010,16 +9010,16 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C86" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>188</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87">
@@ -9103,7 +9103,7 @@
         <v>199</v>
       </c>
       <c r="C92" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -9115,10 +9115,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
+        <v>200</v>
+      </c>
+      <c r="C93" t="s">
         <v>201</v>
-      </c>
-      <c r="C93" t="s">
-        <v>202</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -9130,7 +9130,7 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C94" t="s">
         <v>203</v>
@@ -9454,52 +9454,52 @@
         <v>18</v>
       </c>
       <c r="E115" t="s">
-        <v>18</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C116" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
       </c>
       <c r="E116" t="s">
-        <v>18</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C117" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D117" t="s">
         <v>18</v>
       </c>
       <c r="E117" t="s">
-        <v>250</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C118" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D118" t="s">
         <v>18</v>
       </c>
       <c r="E118" t="s">
-        <v>253</v>
+        <v>18</v>
       </c>
     </row>
     <row r="119">
@@ -9559,193 +9559,193 @@
         <v>18</v>
       </c>
       <c r="E122" t="s">
-        <v>18</v>
+        <v>262</v>
       </c>
     </row>
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
+        <v>263</v>
+      </c>
+      <c r="C123" t="s">
+        <v>264</v>
+      </c>
+      <c r="D123" t="s">
+        <v>18</v>
+      </c>
+      <c r="E123" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>123</v>
+      </c>
+      <c r="C125" t="s">
+        <v>2</v>
+      </c>
+      <c r="D125" t="s">
+        <v>3</v>
+      </c>
+      <c r="E125" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>76</v>
+      </c>
+      <c r="B126" t="s">
+        <v>266</v>
+      </c>
+      <c r="C126" t="s">
+        <v>267</v>
+      </c>
+      <c r="D126" t="s">
+        <v>18</v>
+      </c>
+      <c r="E126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127"/>
+      <c r="B127" t="s">
+        <v>268</v>
+      </c>
+      <c r="C127" t="s">
+        <v>269</v>
+      </c>
+      <c r="D127" t="s">
+        <v>18</v>
+      </c>
+      <c r="E127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128"/>
+      <c r="B128" t="s">
+        <v>260</v>
+      </c>
+      <c r="C128" t="s">
         <v>262</v>
       </c>
-      <c r="C123" t="s">
-        <v>263</v>
-      </c>
-      <c r="D123" t="s">
-        <v>18</v>
-      </c>
-      <c r="E123" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124"/>
-      <c r="B124" t="s">
-        <v>129</v>
-      </c>
-      <c r="C124" t="s">
-        <v>264</v>
-      </c>
-      <c r="D124" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125"/>
-      <c r="B125" t="s">
-        <v>265</v>
-      </c>
-      <c r="C125" t="s">
-        <v>266</v>
-      </c>
-      <c r="D125" t="s">
-        <v>18</v>
-      </c>
-      <c r="E125" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
+      <c r="D128" t="s">
+        <v>18</v>
+      </c>
+      <c r="E128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
         <v>1</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B130" t="s">
         <v>123</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C130" t="s">
         <v>2</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D130" t="s">
         <v>3</v>
       </c>
-      <c r="E127" t="s">
+      <c r="E130" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>76</v>
-      </c>
-      <c r="B128" t="s">
-        <v>268</v>
-      </c>
-      <c r="C128" t="s">
-        <v>269</v>
-      </c>
-      <c r="D128" t="s">
-        <v>18</v>
-      </c>
-      <c r="E128" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129"/>
-      <c r="B129" t="s">
+    <row r="131">
+      <c r="A131" t="s">
+        <v>87</v>
+      </c>
+      <c r="B131" t="s">
         <v>270</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C131" t="s">
         <v>271</v>
       </c>
-      <c r="D129" t="s">
-        <v>18</v>
-      </c>
-      <c r="E129" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130"/>
-      <c r="B130" t="s">
-        <v>129</v>
-      </c>
-      <c r="C130" t="s">
-        <v>130</v>
-      </c>
-      <c r="D130" t="s">
-        <v>18</v>
-      </c>
-      <c r="E130" t="s">
+      <c r="D131" t="s">
+        <v>18</v>
+      </c>
+      <c r="E131" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
+      <c r="A132"/>
+      <c r="B132" t="s">
+        <v>272</v>
+      </c>
+      <c r="C132" t="s">
+        <v>273</v>
+      </c>
+      <c r="D132" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
         <v>1</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B134" t="s">
         <v>123</v>
       </c>
-      <c r="C132" t="s">
+      <c r="C134" t="s">
         <v>2</v>
       </c>
-      <c r="D132" t="s">
+      <c r="D134" t="s">
         <v>3</v>
       </c>
-      <c r="E132" t="s">
+      <c r="E134" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>87</v>
-      </c>
-      <c r="B133" t="s">
-        <v>272</v>
-      </c>
-      <c r="C133" t="s">
-        <v>273</v>
-      </c>
-      <c r="D133" t="s">
-        <v>18</v>
-      </c>
-      <c r="E133" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134"/>
-      <c r="B134" t="s">
+    <row r="135">
+      <c r="A135" t="s">
+        <v>100</v>
+      </c>
+      <c r="B135" t="s">
         <v>274</v>
       </c>
-      <c r="C134" t="s">
+      <c r="C135" t="s">
         <v>275</v>
       </c>
-      <c r="D134" t="s">
-        <v>18</v>
-      </c>
-      <c r="E134" t="s">
+      <c r="D135" t="s">
+        <v>18</v>
+      </c>
+      <c r="E135" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="s">
-        <v>1</v>
-      </c>
+      <c r="A136"/>
       <c r="B136" t="s">
-        <v>123</v>
+        <v>276</v>
       </c>
       <c r="C136" t="s">
-        <v>2</v>
+        <v>277</v>
       </c>
       <c r="D136" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E136" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
-        <v>100</v>
-      </c>
+      <c r="A137"/>
       <c r="B137" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C137" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D137" t="s">
         <v>18</v>
@@ -9757,10 +9757,10 @@
     <row r="138">
       <c r="A138"/>
       <c r="B138" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C138" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D138" t="s">
         <v>18</v>
@@ -9772,10 +9772,10 @@
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C139" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D139" t="s">
         <v>18</v>
@@ -9787,10 +9787,10 @@
     <row r="140">
       <c r="A140"/>
       <c r="B140" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="C140" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
         <v>18</v>
@@ -9799,62 +9799,62 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141"/>
-      <c r="B141" t="s">
+    <row r="142">
+      <c r="A142" t="s">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>123</v>
+      </c>
+      <c r="C142" t="s">
+        <v>2</v>
+      </c>
+      <c r="D142" t="s">
+        <v>3</v>
+      </c>
+      <c r="E142" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>105</v>
+      </c>
+      <c r="B143" t="s">
         <v>284</v>
       </c>
-      <c r="C141" t="s">
+      <c r="C143" t="s">
         <v>285</v>
       </c>
-      <c r="D141" t="s">
-        <v>18</v>
-      </c>
-      <c r="E141" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142"/>
-      <c r="B142" t="s">
-        <v>129</v>
-      </c>
-      <c r="C142" t="s">
-        <v>130</v>
-      </c>
-      <c r="D142" t="s">
-        <v>18</v>
-      </c>
-      <c r="E142" t="s">
+      <c r="D143" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="s">
-        <v>1</v>
-      </c>
+      <c r="A144"/>
       <c r="B144" t="s">
-        <v>123</v>
+        <v>286</v>
       </c>
       <c r="C144" t="s">
-        <v>2</v>
+        <v>287</v>
       </c>
       <c r="D144" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E144" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="s">
-        <v>105</v>
-      </c>
+      <c r="A145"/>
       <c r="B145" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C145" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D145" t="s">
         <v>18</v>
@@ -9866,10 +9866,10 @@
     <row r="146">
       <c r="A146"/>
       <c r="B146" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C146" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D146" t="s">
         <v>18</v>
@@ -9881,10 +9881,10 @@
     <row r="147">
       <c r="A147"/>
       <c r="B147" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C147" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D147" t="s">
         <v>18</v>
@@ -9896,10 +9896,10 @@
     <row r="148">
       <c r="A148"/>
       <c r="B148" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C148" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D148" t="s">
         <v>18</v>
@@ -9911,10 +9911,10 @@
     <row r="149">
       <c r="A149"/>
       <c r="B149" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C149" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D149" t="s">
         <v>18</v>
@@ -9926,10 +9926,10 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C150" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D150" t="s">
         <v>18</v>
@@ -9941,10 +9941,10 @@
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C151" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D151" t="s">
         <v>18</v>
@@ -9956,10 +9956,10 @@
     <row r="152">
       <c r="A152"/>
       <c r="B152" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C152" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D152" t="s">
         <v>18</v>
@@ -9971,10 +9971,10 @@
     <row r="153">
       <c r="A153"/>
       <c r="B153" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C153" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D153" t="s">
         <v>18</v>
@@ -9986,10 +9986,10 @@
     <row r="154">
       <c r="A154"/>
       <c r="B154" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C154" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D154" t="s">
         <v>18</v>
@@ -10001,10 +10001,10 @@
     <row r="155">
       <c r="A155"/>
       <c r="B155" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C155" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D155" t="s">
         <v>18</v>
@@ -10016,10 +10016,10 @@
     <row r="156">
       <c r="A156"/>
       <c r="B156" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C156" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D156" t="s">
         <v>18</v>
@@ -10031,45 +10031,15 @@
     <row r="157">
       <c r="A157"/>
       <c r="B157" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="C157" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="D157" t="s">
         <v>18</v>
       </c>
       <c r="E157" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158"/>
-      <c r="B158" t="s">
-        <v>312</v>
-      </c>
-      <c r="C158" t="s">
-        <v>313</v>
-      </c>
-      <c r="D158" t="s">
-        <v>18</v>
-      </c>
-      <c r="E158" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159"/>
-      <c r="B159" t="s">
-        <v>129</v>
-      </c>
-      <c r="C159" t="s">
-        <v>130</v>
-      </c>
-      <c r="D159" t="s">
-        <v>18</v>
-      </c>
-      <c r="E159" t="s">
         <v>18</v>
       </c>
     </row>
@@ -10267,25 +10237,25 @@
         <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D10" t="s">
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D11" t="s">
         <v>18</v>
@@ -10297,10 +10267,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -10312,55 +10282,55 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D13" t="s">
         <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C14" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C15" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -10372,10 +10342,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -10387,10 +10357,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -10402,10 +10372,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -10417,25 +10387,25 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -10447,40 +10417,40 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C23" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C24" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -10492,10 +10462,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -10507,25 +10477,25 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C26" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -10537,10 +10507,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C28" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -10552,10 +10522,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C29" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -10567,10 +10537,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C30" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -10582,10 +10552,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -10597,10 +10567,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C32" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -10612,10 +10582,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C33" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -10627,10 +10597,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C34" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -10642,10 +10612,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -10657,10 +10627,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C36" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -10672,10 +10642,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C37" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -10687,10 +10657,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C38" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -10702,10 +10672,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C39" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -10717,10 +10687,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C40" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -10732,10 +10702,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C41" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -10747,10 +10717,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C42" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -10762,10 +10732,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -10777,10 +10747,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -10792,10 +10762,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -10807,10 +10777,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C46" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -10822,10 +10792,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C47" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -10837,10 +10807,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C48" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -10852,10 +10822,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -10867,10 +10837,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -10882,10 +10852,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C51" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -10897,10 +10867,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C52" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -10912,10 +10882,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C53" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -10927,10 +10897,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C54" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -10942,10 +10912,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -10957,10 +10927,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C56" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -10972,40 +10942,40 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C58" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
       </c>
       <c r="E58" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C59" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -11017,10 +10987,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C60" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -11032,10 +11002,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C61" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -11047,10 +11017,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -11062,10 +11032,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C63" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -11077,31 +11047,31 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
+        <v>263</v>
+      </c>
+      <c r="C65" t="s">
+        <v>264</v>
+      </c>
+      <c r="D65" t="s">
+        <v>18</v>
+      </c>
+      <c r="E65" t="s">
         <v>265</v>
-      </c>
-      <c r="C65" t="s">
-        <v>266</v>
-      </c>
-      <c r="D65" t="s">
-        <v>18</v>
-      </c>
-      <c r="E65" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -11350,7 +11320,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>42</v>
@@ -11369,7 +11339,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>46</v>
@@ -12191,25 +12161,25 @@
         <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C57" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
       </c>
       <c r="E57" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C58" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -12221,10 +12191,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C59" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -12236,55 +12206,55 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C60" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C62" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C63" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -12296,10 +12266,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C64" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -12311,10 +12281,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C65" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -12326,10 +12296,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C66" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -12341,25 +12311,25 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C68" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -12371,40 +12341,40 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C69" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C70" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
       </c>
       <c r="E70" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C71" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -12416,10 +12386,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C72" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -12431,25 +12401,25 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C73" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C74" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -12461,10 +12431,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C75" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -12476,10 +12446,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C76" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -12491,10 +12461,10 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C77" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -12506,10 +12476,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C78" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -12521,10 +12491,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C79" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -12536,10 +12506,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C80" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -12551,10 +12521,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C81" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -12566,10 +12536,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C82" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -12581,10 +12551,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C83" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -12596,10 +12566,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C84" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -12611,10 +12581,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C85" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -12626,10 +12596,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C86" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -12641,10 +12611,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C87" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -12656,10 +12626,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C88" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -12671,10 +12641,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C89" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -12686,10 +12656,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C90" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -12701,10 +12671,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C91" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -12716,10 +12686,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C92" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -12731,10 +12701,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C93" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -12746,10 +12716,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C94" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -12761,10 +12731,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C95" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -12776,10 +12746,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C96" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -12791,10 +12761,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C97" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -12806,10 +12776,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C98" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -12821,10 +12791,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C99" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
@@ -12836,10 +12806,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C100" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -12851,10 +12821,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C101" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -12866,10 +12836,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C102" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -12881,10 +12851,10 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C103" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D103" t="s">
         <v>18</v>
@@ -12896,40 +12866,40 @@
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C104" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
       </c>
       <c r="E104" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C105" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
       </c>
       <c r="E105" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C106" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
@@ -12941,10 +12911,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C107" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -12956,10 +12926,10 @@
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -12971,10 +12941,10 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C109" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -12986,10 +12956,10 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C110" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
@@ -13001,31 +12971,31 @@
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C111" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
       </c>
       <c r="E111" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
+        <v>263</v>
+      </c>
+      <c r="C112" t="s">
+        <v>264</v>
+      </c>
+      <c r="D112" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" t="s">
         <v>265</v>
-      </c>
-      <c r="C112" t="s">
-        <v>266</v>
-      </c>
-      <c r="D112" t="s">
-        <v>18</v>
-      </c>
-      <c r="E112" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="114">
@@ -13095,10 +13065,10 @@
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C118" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
         <v>18</v>
@@ -13110,10 +13080,10 @@
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C119" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D119" t="s">
         <v>18</v>
@@ -13159,10 +13129,10 @@
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C123" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>18</v>
@@ -13174,10 +13144,10 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C124" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
@@ -13813,10 +13783,10 @@
     <row r="171">
       <c r="A171"/>
       <c r="B171" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C171" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D171" t="s">
         <v>18</v>
@@ -13877,10 +13847,10 @@
     <row r="176">
       <c r="A176"/>
       <c r="B176" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C176" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D176" t="s">
         <v>18</v>
@@ -13941,7 +13911,7 @@
     <row r="181">
       <c r="A181"/>
       <c r="B181" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C181" t="s">
         <v>602</v>
@@ -13956,10 +13926,10 @@
     <row r="182">
       <c r="A182"/>
       <c r="B182" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C182" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D182" t="s">
         <v>18</v>
@@ -13971,10 +13941,10 @@
     <row r="183">
       <c r="A183"/>
       <c r="B183" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C183" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D183" t="s">
         <v>18</v>
@@ -14263,25 +14233,25 @@
         <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C14" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D14" t="s">
         <v>18</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -14293,10 +14263,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C16" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -14308,55 +14278,55 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C17" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
       </c>
       <c r="E17" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
       </c>
       <c r="E18" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -14368,10 +14338,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -14383,10 +14353,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C22" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -14398,10 +14368,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -14413,25 +14383,25 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -14443,40 +14413,40 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
       </c>
       <c r="E27" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C28" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -14488,10 +14458,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C29" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -14503,25 +14473,25 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
       </c>
       <c r="E30" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -14533,10 +14503,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C32" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -14548,10 +14518,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C33" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -14563,10 +14533,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C34" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -14578,10 +14548,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -14593,10 +14563,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C36" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -14608,10 +14578,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C37" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -14623,10 +14593,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C38" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -14638,10 +14608,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C39" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -14653,10 +14623,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -14668,10 +14638,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C41" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -14683,10 +14653,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C42" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -14698,10 +14668,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -14713,10 +14683,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C44" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -14728,10 +14698,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C45" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -14743,10 +14713,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -14758,10 +14728,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -14773,10 +14743,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C48" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -14788,10 +14758,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C49" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -14803,10 +14773,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C50" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -14818,10 +14788,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C51" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -14833,10 +14803,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C52" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -14848,10 +14818,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C53" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -14863,10 +14833,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C54" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -14878,10 +14848,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C55" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -14893,10 +14863,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C56" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -14908,10 +14878,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C57" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -14923,10 +14893,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C58" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -14938,10 +14908,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C59" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -14953,10 +14923,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C60" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -14968,40 +14938,40 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C61" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C62" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
       </c>
       <c r="E62" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C63" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -15013,10 +14983,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C64" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -15028,10 +14998,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -15043,10 +15013,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C66" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -15058,10 +15028,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C67" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -15073,31 +15043,31 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C68" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
+        <v>263</v>
+      </c>
+      <c r="C69" t="s">
+        <v>264</v>
+      </c>
+      <c r="D69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" t="s">
         <v>265</v>
-      </c>
-      <c r="C69" t="s">
-        <v>266</v>
-      </c>
-      <c r="D69" t="s">
-        <v>18</v>
-      </c>
-      <c r="E69" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="71">
@@ -16157,10 +16127,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C56" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -16789,25 +16759,25 @@
         <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
       </c>
       <c r="E19" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -16819,10 +16789,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -16834,55 +16804,55 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -16894,10 +16864,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -16909,10 +16879,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -16924,10 +16894,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -16939,25 +16909,25 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
       </c>
       <c r="E29" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C30" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -16969,40 +16939,40 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C32" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
       </c>
       <c r="E32" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C33" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -17014,10 +16984,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -17029,25 +16999,25 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C35" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
       </c>
       <c r="E35" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C36" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -17059,10 +17029,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -17074,10 +17044,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C38" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -17089,10 +17059,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -17104,10 +17074,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -17119,10 +17089,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -17134,10 +17104,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C42" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -17149,10 +17119,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -17164,10 +17134,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C44" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -17179,10 +17149,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C45" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -17194,10 +17164,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C46" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -17209,10 +17179,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -17224,10 +17194,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C48" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -17239,10 +17209,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C49" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -17254,10 +17224,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C50" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -17269,10 +17239,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C51" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -17284,10 +17254,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C52" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -17299,10 +17269,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C53" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -17314,10 +17284,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C54" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -17329,10 +17299,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C55" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -17344,10 +17314,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C56" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -17359,10 +17329,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C57" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -17374,10 +17344,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -17389,10 +17359,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C59" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -17404,10 +17374,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C60" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -17419,10 +17389,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C61" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -17434,10 +17404,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C62" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -17449,10 +17419,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C63" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -17464,10 +17434,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C64" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -17479,10 +17449,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C65" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -17494,40 +17464,40 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C66" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C67" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C68" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -17539,10 +17509,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C69" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -17554,10 +17524,10 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -17569,10 +17539,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -17584,10 +17554,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -17599,31 +17569,31 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C73" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
+        <v>263</v>
+      </c>
+      <c r="C74" t="s">
+        <v>264</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" t="s">
         <v>265</v>
-      </c>
-      <c r="C74" t="s">
-        <v>266</v>
-      </c>
-      <c r="D74" t="s">
-        <v>18</v>
-      </c>
-      <c r="E74" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="76">
@@ -17918,10 +17888,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C95" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -19299,7 +19269,7 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C45" t="s">
         <v>1838</v>
@@ -20181,10 +20151,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C38" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -20245,10 +20215,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C43" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -20290,10 +20260,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C46" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -20305,10 +20275,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -20418,25 +20388,25 @@
         <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
       </c>
       <c r="E56" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C57" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -20448,10 +20418,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C58" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -20463,55 +20433,55 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C59" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
       </c>
       <c r="E59" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
       </c>
       <c r="E60" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C61" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
       </c>
       <c r="E61" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C62" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -20523,10 +20493,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -20538,10 +20508,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -20553,10 +20523,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C65" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -20568,25 +20538,25 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -20598,40 +20568,40 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C69" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C70" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -20643,10 +20613,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C71" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -20658,25 +20628,25 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C72" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
       </c>
       <c r="E72" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C73" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -20688,10 +20658,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C74" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -20703,10 +20673,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C75" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -20718,10 +20688,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C76" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -20733,10 +20703,10 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -20748,10 +20718,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C78" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -20763,10 +20733,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C79" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -20778,10 +20748,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C80" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -20793,10 +20763,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -20808,10 +20778,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C82" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -20823,10 +20793,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C83" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -20838,10 +20808,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C84" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -20853,10 +20823,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C85" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -20868,10 +20838,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C86" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -20883,10 +20853,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C87" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -20898,10 +20868,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C88" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -20913,10 +20883,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C89" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -20928,10 +20898,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C90" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -20943,10 +20913,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C91" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -20958,10 +20928,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C92" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -20973,10 +20943,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C93" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -20988,10 +20958,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C94" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -21003,10 +20973,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C95" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
@@ -21018,10 +20988,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C96" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -21033,10 +21003,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C97" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -21048,10 +21018,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C98" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -21063,10 +21033,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C99" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
@@ -21078,10 +21048,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C100" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -21093,10 +21063,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C101" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -21108,10 +21078,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C102" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -21123,40 +21093,40 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C103" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D103" t="s">
         <v>18</v>
       </c>
       <c r="E103" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C104" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
       </c>
       <c r="E104" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C105" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
@@ -21168,10 +21138,10 @@
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C106" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
@@ -21183,10 +21153,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -21198,10 +21168,10 @@
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C108" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -21213,10 +21183,10 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C109" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -21228,31 +21198,31 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C110" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
       </c>
       <c r="E110" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
+        <v>263</v>
+      </c>
+      <c r="C111" t="s">
+        <v>264</v>
+      </c>
+      <c r="D111" t="s">
+        <v>18</v>
+      </c>
+      <c r="E111" t="s">
         <v>265</v>
-      </c>
-      <c r="C111" t="s">
-        <v>266</v>
-      </c>
-      <c r="D111" t="s">
-        <v>18</v>
-      </c>
-      <c r="E111" t="s">
-        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -21459,13 +21429,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>18</v>
@@ -21478,13 +21448,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>18</v>
@@ -21497,13 +21467,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>18</v>
@@ -21516,13 +21486,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>18</v>
@@ -21535,7 +21505,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>29</v>
@@ -21554,7 +21524,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>29</v>
@@ -21669,10 +21639,10 @@
         <v>1932</v>
       </c>
       <c r="B15" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -21684,10 +21654,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C16" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -21699,10 +21669,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C17" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -21778,13 +21748,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>18</v>
@@ -21797,13 +21767,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>18</v>
@@ -21816,13 +21786,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
@@ -21841,7 +21811,7 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
@@ -21854,13 +21824,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
@@ -21873,13 +21843,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
@@ -21892,16 +21862,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>322</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" t="s">
         <v>324</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="C8" t="s">
-        <v>326</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="E8"/>
       <c r="G8" s="2" t="s">
@@ -21911,16 +21881,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="2" t="s">
@@ -21930,16 +21900,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E10"/>
       <c r="G10" s="2" t="s">
@@ -21949,16 +21919,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E11"/>
       <c r="G11" s="2" t="s">
@@ -21968,13 +21938,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>18</v>
@@ -22004,13 +21974,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B15" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C15" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -22022,10 +21992,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C16" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -22037,10 +22007,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -22321,13 +22291,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D5" s="21" t="s">
         <v>18</v>
@@ -22446,13 +22416,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D3" s="22" t="s">
         <v>18</v>
@@ -22465,13 +22435,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D4" s="22" t="s">
         <v>18</v>
@@ -22721,13 +22691,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B10" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>18</v>
@@ -22740,13 +22710,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B11" s="23" t="s">
         <v>46</v>
       </c>
       <c r="C11" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>18</v>
@@ -22759,13 +22729,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B12" s="23" t="s">
         <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>18</v>
@@ -22912,25 +22882,25 @@
         <v>71</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
       </c>
       <c r="E21" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C22" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -22942,10 +22912,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C23" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -22957,55 +22927,55 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C24" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
       </c>
       <c r="E24" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -23017,10 +22987,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C28" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -23032,10 +23002,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C29" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -23047,10 +23017,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -23062,25 +23032,25 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C31" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -23092,40 +23062,40 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
       </c>
       <c r="E33" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C34" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C35" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -23137,10 +23107,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -23152,25 +23122,25 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C37" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -23182,10 +23152,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -23197,10 +23167,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C40" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -23212,10 +23182,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -23227,10 +23197,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -23242,10 +23212,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C43" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -23257,10 +23227,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -23272,10 +23242,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C45" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -23287,10 +23257,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -23302,10 +23272,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C47" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -23317,10 +23287,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C48" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -23332,10 +23302,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C49" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -23347,10 +23317,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C50" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -23362,10 +23332,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -23377,10 +23347,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C52" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -23392,10 +23362,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -23407,10 +23377,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C54" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -23422,10 +23392,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C55" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -23437,10 +23407,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C56" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -23452,10 +23422,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C57" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -23467,10 +23437,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C58" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -23482,10 +23452,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C59" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -23497,10 +23467,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C60" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -23512,10 +23482,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C61" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D61" t="s">
         <v>18</v>
@@ -23527,10 +23497,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C62" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D62" t="s">
         <v>18</v>
@@ -23542,10 +23512,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C63" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -23557,10 +23527,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -23572,10 +23542,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C65" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D65" t="s">
         <v>18</v>
@@ -23587,10 +23557,10 @@
     <row r="66">
       <c r="A66"/>
       <c r="B66" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C66" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -23602,10 +23572,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C67" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -23617,40 +23587,40 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C68" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
       </c>
       <c r="E68" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C69" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
       </c>
       <c r="E69" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C70" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -23662,10 +23632,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C71" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D71" t="s">
         <v>18</v>
@@ -23677,10 +23647,10 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -23692,10 +23662,10 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -23707,10 +23677,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -23722,31 +23692,31 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C75" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
       </c>
       <c r="E75" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
+        <v>263</v>
+      </c>
+      <c r="C76" t="s">
+        <v>264</v>
+      </c>
+      <c r="D76" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" t="s">
         <v>265</v>
-      </c>
-      <c r="C76" t="s">
-        <v>266</v>
-      </c>
-      <c r="D76" t="s">
-        <v>18</v>
-      </c>
-      <c r="E76" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="78">
@@ -24078,7 +24048,7 @@
       </c>
       <c r="E4"/>
       <c r="G4" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -24099,7 +24069,7 @@
       </c>
       <c r="E5"/>
       <c r="G5" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -24120,7 +24090,7 @@
       </c>
       <c r="E6"/>
       <c r="G6" s="3" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -24542,13 +24512,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>18</v>
@@ -24565,13 +24535,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>46</v>
       </c>
       <c r="C28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>18</v>
@@ -24588,13 +24558,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>18</v>
@@ -24788,7 +24758,7 @@
       </c>
       <c r="E38"/>
       <c r="G38" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H38"/>
     </row>
@@ -24807,7 +24777,7 @@
       </c>
       <c r="E39"/>
       <c r="G39" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H39"/>
     </row>
@@ -25595,25 +25565,25 @@
         <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C82" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
       </c>
       <c r="E82" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C83" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -25625,10 +25595,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C84" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -25640,55 +25610,55 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C85" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
       </c>
       <c r="E85" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C86" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
       </c>
       <c r="E86" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C87" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
       </c>
       <c r="E87" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C88" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -25700,10 +25670,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C89" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -25715,10 +25685,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C90" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -25730,10 +25700,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C91" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -25745,25 +25715,25 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C92" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
       </c>
       <c r="E92" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C93" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -25775,40 +25745,40 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C94" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C95" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D95" t="s">
         <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C96" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D96" t="s">
         <v>18</v>
@@ -25820,10 +25790,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C97" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="D97" t="s">
         <v>18</v>
@@ -25835,25 +25805,25 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C98" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
       </c>
       <c r="E98" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C99" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D99" t="s">
         <v>18</v>
@@ -25865,10 +25835,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C100" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -25880,10 +25850,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C101" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -25895,10 +25865,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C102" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D102" t="s">
         <v>18</v>
@@ -25910,10 +25880,10 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C103" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D103" t="s">
         <v>18</v>
@@ -25925,10 +25895,10 @@
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C104" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D104" t="s">
         <v>18</v>
@@ -25940,10 +25910,10 @@
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C105" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D105" t="s">
         <v>18</v>
@@ -25955,10 +25925,10 @@
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C106" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D106" t="s">
         <v>18</v>
@@ -25970,10 +25940,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C107" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D107" t="s">
         <v>18</v>
@@ -25985,10 +25955,10 @@
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C108" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D108" t="s">
         <v>18</v>
@@ -26000,10 +25970,10 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C109" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D109" t="s">
         <v>18</v>
@@ -26015,10 +25985,10 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C110" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D110" t="s">
         <v>18</v>
@@ -26030,10 +26000,10 @@
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C111" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D111" t="s">
         <v>18</v>
@@ -26045,10 +26015,10 @@
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C112" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D112" t="s">
         <v>18</v>
@@ -26060,10 +26030,10 @@
     <row r="113">
       <c r="A113"/>
       <c r="B113" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C113" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D113" t="s">
         <v>18</v>
@@ -26075,10 +26045,10 @@
     <row r="114">
       <c r="A114"/>
       <c r="B114" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C114" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D114" t="s">
         <v>18</v>
@@ -26090,10 +26060,10 @@
     <row r="115">
       <c r="A115"/>
       <c r="B115" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C115" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D115" t="s">
         <v>18</v>
@@ -26105,10 +26075,10 @@
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C116" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D116" t="s">
         <v>18</v>
@@ -26120,10 +26090,10 @@
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C117" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D117" t="s">
         <v>18</v>
@@ -26135,10 +26105,10 @@
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C118" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D118" t="s">
         <v>18</v>
@@ -26150,10 +26120,10 @@
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C119" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D119" t="s">
         <v>18</v>
@@ -26165,10 +26135,10 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C120" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D120" t="s">
         <v>18</v>
@@ -26180,10 +26150,10 @@
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C121" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D121" t="s">
         <v>18</v>
@@ -26195,10 +26165,10 @@
     <row r="122">
       <c r="A122"/>
       <c r="B122" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D122" t="s">
         <v>18</v>
@@ -26210,10 +26180,10 @@
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C123" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D123" t="s">
         <v>18</v>
@@ -26225,10 +26195,10 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C124" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D124" t="s">
         <v>18</v>
@@ -26240,10 +26210,10 @@
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C125" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D125" t="s">
         <v>18</v>
@@ -26255,10 +26225,10 @@
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C126" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D126" t="s">
         <v>18</v>
@@ -26270,10 +26240,10 @@
     <row r="127">
       <c r="A127"/>
       <c r="B127" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C127" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D127" t="s">
         <v>18</v>
@@ -26285,10 +26255,10 @@
     <row r="128">
       <c r="A128"/>
       <c r="B128" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C128" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D128" t="s">
         <v>18</v>
@@ -26300,40 +26270,40 @@
     <row r="129">
       <c r="A129"/>
       <c r="B129" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C129" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D129" t="s">
         <v>18</v>
       </c>
       <c r="E129" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="130">
       <c r="A130"/>
       <c r="B130" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C130" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D130" t="s">
         <v>18</v>
       </c>
       <c r="E130" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="131">
       <c r="A131"/>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C131" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D131" t="s">
         <v>18</v>
@@ -26345,10 +26315,10 @@
     <row r="132">
       <c r="A132"/>
       <c r="B132" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C132" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D132" t="s">
         <v>18</v>
@@ -26360,10 +26330,10 @@
     <row r="133">
       <c r="A133"/>
       <c r="B133" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C133" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D133" t="s">
         <v>18</v>
@@ -26375,10 +26345,10 @@
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C134" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
@@ -26390,10 +26360,10 @@
     <row r="135">
       <c r="A135"/>
       <c r="B135" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C135" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
         <v>18</v>
@@ -26405,31 +26375,31 @@
     <row r="136">
       <c r="A136"/>
       <c r="B136" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C136" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>18</v>
       </c>
       <c r="E136" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
     </row>
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
+        <v>263</v>
+      </c>
+      <c r="C137" t="s">
+        <v>264</v>
+      </c>
+      <c r="D137" t="s">
+        <v>18</v>
+      </c>
+      <c r="E137" t="s">
         <v>265</v>
-      </c>
-      <c r="C137" t="s">
-        <v>266</v>
-      </c>
-      <c r="D137" t="s">
-        <v>18</v>
-      </c>
-      <c r="E137" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="139">
@@ -26521,7 +26491,7 @@
         <v>527</v>
       </c>
       <c r="C145" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D145" t="s">
         <v>18</v>
@@ -26785,10 +26755,10 @@
     <row r="165">
       <c r="A165"/>
       <c r="B165" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C165" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D165" t="s">
         <v>18</v>
@@ -26928,10 +26898,10 @@
     <row r="176">
       <c r="A176"/>
       <c r="B176" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C176" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D176" t="s">
         <v>18</v>
@@ -26992,10 +26962,10 @@
     <row r="181">
       <c r="A181"/>
       <c r="B181" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C181" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D181" t="s">
         <v>18</v>
@@ -27090,10 +27060,10 @@
     <row r="189">
       <c r="A189"/>
       <c r="B189" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C189" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D189" t="s">
         <v>18</v>
@@ -27195,10 +27165,10 @@
     <row r="196">
       <c r="A196"/>
       <c r="B196" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C196" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D196" t="s">
         <v>18</v>
@@ -27308,7 +27278,7 @@
     <row r="205">
       <c r="A205"/>
       <c r="B205" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C205" t="s">
         <v>602</v>
@@ -27323,10 +27293,10 @@
     <row r="206">
       <c r="A206"/>
       <c r="B206" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C206" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D206" t="s">
         <v>18</v>
@@ -27338,10 +27308,10 @@
     <row r="207">
       <c r="A207"/>
       <c r="B207" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C207" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D207" t="s">
         <v>18</v>
@@ -27492,10 +27462,10 @@
     <row r="218">
       <c r="A218"/>
       <c r="B218" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C218" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D218" t="s">
         <v>18</v>
@@ -27571,10 +27541,10 @@
     <row r="224">
       <c r="A224"/>
       <c r="B224" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C224" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D224" t="s">
         <v>18</v>
@@ -27908,10 +27878,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C17" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -28318,7 +28288,7 @@
       </c>
       <c r="E19"/>
       <c r="G19" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H19"/>
     </row>
@@ -28337,7 +28307,7 @@
       </c>
       <c r="E20"/>
       <c r="G20" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H20"/>
     </row>
@@ -28978,7 +28948,7 @@
       </c>
       <c r="E53"/>
       <c r="G53" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H53"/>
     </row>
@@ -28997,7 +28967,7 @@
       </c>
       <c r="E54"/>
       <c r="G54" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H54"/>
     </row>
@@ -29016,7 +28986,7 @@
       </c>
       <c r="E55"/>
       <c r="G55" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H55"/>
     </row>
@@ -29035,7 +29005,7 @@
       </c>
       <c r="E56"/>
       <c r="G56" s="5" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H56"/>
     </row>
@@ -30311,7 +30281,7 @@
       </c>
       <c r="E122"/>
       <c r="G122" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H122"/>
     </row>
@@ -30330,7 +30300,7 @@
       </c>
       <c r="E123"/>
       <c r="G123" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H123"/>
     </row>
@@ -30349,7 +30319,7 @@
       </c>
       <c r="E124"/>
       <c r="G124" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H124"/>
     </row>
@@ -30368,7 +30338,7 @@
       </c>
       <c r="E125"/>
       <c r="G125" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H125"/>
     </row>
@@ -30387,7 +30357,7 @@
       </c>
       <c r="E126"/>
       <c r="G126" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H126"/>
     </row>
@@ -30406,7 +30376,7 @@
       </c>
       <c r="E127"/>
       <c r="G127" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H127"/>
     </row>
@@ -30425,7 +30395,7 @@
       </c>
       <c r="E128"/>
       <c r="G128" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H128"/>
     </row>
@@ -30444,7 +30414,7 @@
       </c>
       <c r="E129"/>
       <c r="G129" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H129"/>
     </row>
@@ -30463,7 +30433,7 @@
       </c>
       <c r="E130"/>
       <c r="G130" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H130"/>
     </row>
@@ -30482,7 +30452,7 @@
       </c>
       <c r="E131"/>
       <c r="G131" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H131"/>
     </row>
@@ -30501,7 +30471,7 @@
       </c>
       <c r="E132"/>
       <c r="G132" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H132"/>
     </row>
@@ -30520,7 +30490,7 @@
       </c>
       <c r="E133"/>
       <c r="G133" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H133"/>
     </row>
@@ -30539,7 +30509,7 @@
       </c>
       <c r="E134"/>
       <c r="G134" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H134"/>
     </row>
@@ -30558,7 +30528,7 @@
       </c>
       <c r="E135"/>
       <c r="G135" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H135"/>
     </row>
@@ -30577,7 +30547,7 @@
       </c>
       <c r="E136"/>
       <c r="G136" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H136"/>
     </row>
@@ -30596,7 +30566,7 @@
       </c>
       <c r="E137"/>
       <c r="G137" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H137"/>
     </row>
@@ -30615,7 +30585,7 @@
       </c>
       <c r="E138"/>
       <c r="G138" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H138"/>
     </row>
@@ -30653,7 +30623,7 @@
       </c>
       <c r="E140"/>
       <c r="G140" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H140"/>
     </row>
@@ -31259,10 +31229,10 @@
     <row r="173">
       <c r="A173"/>
       <c r="B173" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C173" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D173" t="s">
         <v>18</v>
@@ -31323,10 +31293,10 @@
     <row r="178">
       <c r="A178"/>
       <c r="B178" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C178" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D178" t="s">
         <v>18</v>
@@ -31481,7 +31451,7 @@
     <row r="190">
       <c r="A190"/>
       <c r="B190" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C190" t="s">
         <v>1073</v>
@@ -32384,7 +32354,7 @@
         <v>383</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>18</v>
@@ -32675,10 +32645,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C63" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -32769,10 +32739,10 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C70" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D70" t="s">
         <v>18</v>
@@ -32803,10 +32773,10 @@
         <v>1206</v>
       </c>
       <c r="B73" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
@@ -32818,10 +32788,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C74" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -32848,10 +32818,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C76" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D76" t="s">
         <v>18</v>
@@ -32912,10 +32882,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C81" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -32985,7 +32955,7 @@
         <v>383</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>18</v>
@@ -33061,7 +33031,7 @@
         <v>383</v>
       </c>
       <c r="C6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>18</v>
@@ -33466,10 +33436,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>342</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -33917,10 +33887,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -33981,10 +33951,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -34075,10 +34045,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C37" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -34490,10 +34460,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -34554,10 +34524,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -34648,10 +34618,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>129</v>
+        <v>260</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>262</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -6001,7 +6001,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.46.0-SNAPSHOT</t>
+    <t>1.47.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7849" uniqueCount="2150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7849" uniqueCount="2152">
   <si>
     <t>Field</t>
   </si>
@@ -6331,7 +6331,13 @@
     <t>publicOwnership</t>
   </si>
   <si>
+    <t>Public ownership</t>
+  </si>
+  <si>
     <t>archived</t>
+  </si>
+  <si>
+    <t>Archived</t>
   </si>
   <si>
     <t>epidCode</t>
@@ -12776,7 +12782,7 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>584</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>18</v>
@@ -12795,7 +12801,7 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>587</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>18</v>
@@ -12814,7 +12820,7 @@
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>590</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>18</v>
@@ -23223,7 +23229,7 @@
         <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>2098</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>18</v>
@@ -23236,13 +23242,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>133</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>2100</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>18</v>
@@ -24486,13 +24492,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>18</v>
@@ -24505,13 +24511,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>18</v>
@@ -24524,13 +24530,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>2100</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>18</v>
@@ -24562,10 +24568,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -24649,13 +24655,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>18</v>
@@ -24668,13 +24674,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
@@ -24706,13 +24712,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>2100</v>
       </c>
       <c r="D6" s="21" t="s">
         <v>18</v>
@@ -24850,13 +24856,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>2100</v>
       </c>
       <c r="D5" s="22" t="s">
         <v>18</v>
@@ -24937,13 +24943,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>18</v>
@@ -24956,13 +24962,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>18</v>
@@ -25013,7 +25019,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>9</v>
@@ -25057,7 +25063,7 @@
         <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>18</v>
@@ -25070,11 +25076,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>18</v>
@@ -25087,10 +25093,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -25182,7 +25188,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>58</v>
@@ -25207,7 +25213,7 @@
         <v>615</v>
       </c>
       <c r="C16" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>18</v>
@@ -25220,13 +25226,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>498</v>
       </c>
       <c r="C17" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>18</v>
@@ -25239,16 +25245,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="E18"/>
       <c r="G18" s="23" t="s">
@@ -25258,10 +25264,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -26153,13 +26159,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="B80" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="C80" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -26171,10 +26177,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="C81" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -26186,10 +26192,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="C82" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -26201,10 +26207,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="C83" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -26216,10 +26222,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="C84" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -26231,10 +26237,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="C85" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -26246,10 +26252,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="C86" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -26261,10 +26267,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="C87" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -26276,10 +26282,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C88" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -26291,10 +26297,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="C89" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -26306,10 +26312,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="C90" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -26321,10 +26327,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="C91" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -26336,10 +26342,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="C92" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -26365,12 +26371,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7849" uniqueCount="2149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7849" uniqueCount="2150">
   <si>
     <t>Field</t>
   </si>
@@ -3964,13 +3964,16 @@
     <t>Exposure (e.g. handling, butchering) to animals (or their remains) in an area where infected animals have been confirmed in the past month</t>
   </si>
   <si>
+    <t>AFP, Guinea Worm, New Flu, Anthrax, Polio, Undefined, Other</t>
+  </si>
+  <si>
     <t>sickDeadAnimals</t>
   </si>
   <si>
     <t>Exposure to sick/unxeplainedly dead animals</t>
   </si>
   <si>
-    <t>AFP, Guinea Worm, New Flu, Polio, Rabies, Anthrax, COVID-19, Undefined, Other</t>
+    <t>AFP, Guinea Worm, New Flu, Polio, Rabies, Anthrax, Undefined, Other</t>
   </si>
   <si>
     <t>sickDeadAnimalsDetails</t>
@@ -4030,7 +4033,7 @@
     <t>Did you have contact with live or dead bats or their excreta during the incubation period?</t>
   </si>
   <si>
-    <t>AFP, EVD, Guinea Worm, Lassa, Polio, VHF, Rabies, COVID-19, Undefined, Other</t>
+    <t>AFP, EVD, Guinea Worm, Lassa, Polio, VHF, Rabies, Undefined, Other</t>
   </si>
   <si>
     <t>primates</t>
@@ -4111,9 +4114,6 @@
     <t>Did you have contact with other animals during the incubation period?</t>
   </si>
   <si>
-    <t>AFP, EVD, Guinea Worm, Lassa, Monkeypox, Polio, VHF, Rabies, Anthrax, COVID-19, Undefined, Other</t>
-  </si>
-  <si>
     <t>otherAnimalsDetails</t>
   </si>
   <si>
@@ -4289,6 +4289,9 @@
   </si>
   <si>
     <t>Did you have contact with live, dead or consume camel products during the incubation period?</t>
+  </si>
+  <si>
+    <t>Undefined, Other</t>
   </si>
   <si>
     <t>snakes</t>
@@ -11610,7 +11613,7 @@
         <v>601</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -11664,13 +11667,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>18</v>
@@ -11683,13 +11686,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>18</v>
@@ -11702,13 +11705,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>18</v>
@@ -12630,13 +12633,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="C2" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>18</v>
@@ -12649,13 +12652,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>18</v>
@@ -12668,13 +12671,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>18</v>
@@ -12693,7 +12696,7 @@
         <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>18</v>
@@ -12725,13 +12728,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>18</v>
@@ -12833,7 +12836,7 @@
         <v>537</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="E12"/>
       <c r="G12" s="11" t="s">
@@ -12852,7 +12855,7 @@
         <v>538</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="E13"/>
       <c r="G13" s="11" t="s">
@@ -12871,7 +12874,7 @@
         <v>539</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="11" t="s">
@@ -12881,13 +12884,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>18</v>
@@ -12902,13 +12905,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C16" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>18</v>
@@ -12921,13 +12924,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>18</v>
@@ -12940,13 +12943,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="C18" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>18</v>
@@ -12959,13 +12962,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>18</v>
@@ -12978,16 +12981,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="C20" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="E20"/>
       <c r="G20" s="11" t="s">
@@ -12997,13 +13000,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>18</v>
@@ -13016,13 +13019,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C22" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>18</v>
@@ -13035,13 +13038,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="C23" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>18</v>
@@ -13054,13 +13057,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="C24" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>18</v>
@@ -13082,7 +13085,7 @@
         <v>668</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="E25"/>
       <c r="G25" s="11" t="s">
@@ -13149,13 +13152,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>18</v>
@@ -13168,16 +13171,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="C30" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="E30"/>
       <c r="G30" s="11" t="s">
@@ -13187,13 +13190,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>18</v>
@@ -13225,13 +13228,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>133</v>
       </c>
       <c r="C33" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>18</v>
@@ -13244,13 +13247,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>517</v>
       </c>
       <c r="C34" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>18</v>
@@ -13263,7 +13266,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>9</v>
@@ -13282,13 +13285,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>517</v>
       </c>
       <c r="C36" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>18</v>
@@ -13383,7 +13386,7 @@
         <v>491</v>
       </c>
       <c r="C41" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>18</v>
@@ -13398,13 +13401,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>498</v>
       </c>
       <c r="C42" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>18</v>
@@ -13417,13 +13420,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="C43" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>18</v>
@@ -13436,13 +13439,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>498</v>
       </c>
       <c r="C44" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>18</v>
@@ -13740,10 +13743,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
@@ -14635,10 +14638,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B121" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="C121" t="s">
         <v>492</v>
@@ -14653,10 +14656,10 @@
     <row r="122">
       <c r="A122"/>
       <c r="B122" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="C122" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="D122" t="s">
         <v>18</v>
@@ -14668,10 +14671,10 @@
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="C123" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="D123" t="s">
         <v>18</v>
@@ -14729,13 +14732,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B128" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="C128" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="D128" t="s">
         <v>18</v>
@@ -14793,13 +14796,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B133" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="C133" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="D133" t="s">
         <v>18</v>
@@ -14811,10 +14814,10 @@
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="C134" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="D134" t="s">
         <v>18</v>
@@ -14826,10 +14829,10 @@
     <row r="135">
       <c r="A135"/>
       <c r="B135" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="C135" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="D135" t="s">
         <v>18</v>
@@ -14841,10 +14844,10 @@
     <row r="136">
       <c r="A136"/>
       <c r="B136" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="C136" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="D136" t="s">
         <v>18</v>
@@ -14856,10 +14859,10 @@
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="C137" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="D137" t="s">
         <v>18</v>
@@ -14871,10 +14874,10 @@
     <row r="138">
       <c r="A138"/>
       <c r="B138" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="C138" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="D138" t="s">
         <v>18</v>
@@ -14886,10 +14889,10 @@
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="C139" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="D139" t="s">
         <v>18</v>
@@ -14901,10 +14904,10 @@
     <row r="140">
       <c r="A140"/>
       <c r="B140" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="C140" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="D140" t="s">
         <v>18</v>
@@ -14916,10 +14919,10 @@
     <row r="141">
       <c r="A141"/>
       <c r="B141" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="C141" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="D141" t="s">
         <v>18</v>
@@ -14931,10 +14934,10 @@
     <row r="142">
       <c r="A142"/>
       <c r="B142" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="C142" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="D142" t="s">
         <v>18</v>
@@ -14946,10 +14949,10 @@
     <row r="143">
       <c r="A143"/>
       <c r="B143" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="C143" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="D143" t="s">
         <v>18</v>
@@ -14961,10 +14964,10 @@
     <row r="144">
       <c r="A144"/>
       <c r="B144" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="C144" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="D144" t="s">
         <v>18</v>
@@ -14976,10 +14979,10 @@
     <row r="145">
       <c r="A145"/>
       <c r="B145" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="C145" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="D145" t="s">
         <v>18</v>
@@ -14991,10 +14994,10 @@
     <row r="146">
       <c r="A146"/>
       <c r="B146" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="C146" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="D146" t="s">
         <v>18</v>
@@ -15022,13 +15025,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B149" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="C149" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="D149" t="s">
         <v>18</v>
@@ -15040,10 +15043,10 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="C150" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="D150" t="s">
         <v>18</v>
@@ -15055,10 +15058,10 @@
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="C151" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="D151" t="s">
         <v>18</v>
@@ -15070,10 +15073,10 @@
     <row r="152">
       <c r="A152"/>
       <c r="B152" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="C152" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="D152" t="s">
         <v>18</v>
@@ -15085,10 +15088,10 @@
     <row r="153">
       <c r="A153"/>
       <c r="B153" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="C153" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="D153" t="s">
         <v>18</v>
@@ -15116,19 +15119,19 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B156" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="C156" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="D156" t="s">
         <v>18</v>
       </c>
       <c r="E156" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="157">
@@ -15137,7 +15140,7 @@
         <v>699</v>
       </c>
       <c r="C157" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="D157" t="s">
         <v>18</v>
@@ -15149,16 +15152,16 @@
     <row r="158">
       <c r="A158"/>
       <c r="B158" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="C158" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="D158" t="s">
         <v>18</v>
       </c>
       <c r="E158" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="160">
@@ -15180,13 +15183,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B161" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C161" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="D161" t="s">
         <v>18</v>
@@ -15198,10 +15201,10 @@
     <row r="162">
       <c r="A162"/>
       <c r="B162" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="C162" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D162" t="s">
         <v>18</v>
@@ -15213,10 +15216,10 @@
     <row r="163">
       <c r="A163"/>
       <c r="B163" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="C163" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="D163" t="s">
         <v>18</v>
@@ -15338,13 +15341,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B173" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="C173" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D173" t="s">
         <v>18</v>
@@ -15356,10 +15359,10 @@
     <row r="174">
       <c r="A174"/>
       <c r="B174" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="C174" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D174" t="s">
         <v>18</v>
@@ -15371,10 +15374,10 @@
     <row r="175">
       <c r="A175"/>
       <c r="B175" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="C175" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D175" t="s">
         <v>18</v>
@@ -15386,10 +15389,10 @@
     <row r="176">
       <c r="A176"/>
       <c r="B176" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C176" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D176" t="s">
         <v>18</v>
@@ -15639,7 +15642,7 @@
         <v>491</v>
       </c>
       <c r="C2" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>18</v>
@@ -15673,16 +15676,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -15694,13 +15697,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>498</v>
       </c>
       <c r="C5" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>18</v>
@@ -15715,16 +15718,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="C6" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -15736,16 +15739,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="E7"/>
       <c r="G7" s="12" t="s">
@@ -15780,7 +15783,7 @@
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>18</v>
@@ -15799,7 +15802,7 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>18</v>
@@ -16707,13 +16710,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B72" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="C72" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -16725,31 +16728,31 @@
     <row r="73">
       <c r="A73"/>
       <c r="B73" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="C73" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="D73" t="s">
         <v>18</v>
       </c>
       <c r="E73" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="C74" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
       </c>
       <c r="E74" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
   </sheetData>
@@ -16805,13 +16808,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="C2" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>18</v>
@@ -16824,10 +16827,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
@@ -16843,10 +16846,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
@@ -16862,13 +16865,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>18</v>
@@ -16881,13 +16884,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>18</v>
@@ -16900,16 +16903,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -16921,7 +16924,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>42</v>
@@ -17020,13 +17023,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="C13" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>18</v>
@@ -17041,13 +17044,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>18</v>
@@ -17060,13 +17063,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="C15" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>18</v>
@@ -17081,7 +17084,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>58</v>
@@ -17102,13 +17105,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>18</v>
@@ -17121,13 +17124,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>18</v>
@@ -17140,13 +17143,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>18</v>
@@ -17159,13 +17162,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>18</v>
@@ -17178,13 +17181,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="C21" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="D21" s="13" t="s">
         <v>18</v>
@@ -17197,13 +17200,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>18</v>
@@ -17216,7 +17219,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B23" s="13" t="s">
         <v>9</v>
@@ -17235,13 +17238,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="C24" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="D24" s="13" t="s">
         <v>18</v>
@@ -17254,10 +17257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
@@ -17273,13 +17276,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="D26" s="13" t="s">
         <v>18</v>
@@ -17292,13 +17295,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>18</v>
@@ -17311,13 +17314,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="C28" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>18</v>
@@ -17330,13 +17333,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>18</v>
@@ -17349,13 +17352,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>18</v>
@@ -17368,11 +17371,11 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>18</v>
@@ -17385,11 +17388,11 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>18</v>
@@ -17402,13 +17405,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>18</v>
@@ -17421,13 +17424,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>18</v>
@@ -17457,13 +17460,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B37" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C37" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -17475,10 +17478,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="C38" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -17490,10 +17493,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="C39" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -17505,10 +17508,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="C40" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -17520,10 +17523,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="C41" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -17535,10 +17538,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="C42" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -17550,10 +17553,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="C43" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -17565,10 +17568,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="C44" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -17580,10 +17583,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C45" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -17595,10 +17598,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="C46" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -17610,10 +17613,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="C47" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -17625,10 +17628,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C48" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -17640,10 +17643,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="C49" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="D49" t="s">
         <v>18</v>
@@ -17655,10 +17658,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C50" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="D50" t="s">
         <v>18</v>
@@ -17670,10 +17673,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="C51" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -17685,10 +17688,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C52" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -17700,10 +17703,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="C53" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -17715,10 +17718,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C54" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -17730,10 +17733,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="C55" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="D55" t="s">
         <v>18</v>
@@ -17776,13 +17779,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B59" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C59" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -17794,10 +17797,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C60" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -17825,13 +17828,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B63" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C63" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="D63" t="s">
         <v>18</v>
@@ -17843,10 +17846,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="C64" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="D64" t="s">
         <v>18</v>
@@ -17874,13 +17877,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B67" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="C67" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -17892,10 +17895,10 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="C68" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -17907,10 +17910,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C69" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -17938,13 +17941,13 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B72" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C72" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D72" t="s">
         <v>18</v>
@@ -17971,10 +17974,10 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C74" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="D74" t="s">
         <v>18</v>
@@ -17986,10 +17989,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="C75" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -18054,10 +18057,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -18075,16 +18078,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -18096,16 +18099,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="E4"/>
       <c r="G4" s="14" t="s">
@@ -18115,16 +18118,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="C5" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -18136,16 +18139,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="E6"/>
       <c r="G6" s="14" t="s">
@@ -18155,16 +18158,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -18176,7 +18179,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>58</v>
@@ -18185,7 +18188,7 @@
         <v>197</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -18197,16 +18200,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="E9"/>
       <c r="G9" s="14" t="s">
@@ -18216,7 +18219,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>498</v>
@@ -18237,16 +18240,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="C11" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
@@ -18258,16 +18261,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B12" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -18279,16 +18282,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B13" s="14" t="s">
         <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -18300,16 +18303,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="14" t="s">
@@ -18319,16 +18322,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="B15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="E15"/>
       <c r="G15" s="14" t="s">
@@ -18338,13 +18341,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>18</v>
@@ -19233,13 +19236,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B77" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="C77" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="D77" t="s">
         <v>18</v>
@@ -19251,10 +19254,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="C78" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="D78" t="s">
         <v>18</v>
@@ -19266,10 +19269,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="C79" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="D79" t="s">
         <v>18</v>
@@ -19281,10 +19284,10 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="C80" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -19296,10 +19299,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C81" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -19311,7 +19314,7 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C82" t="s">
         <v>802</v>
@@ -19326,10 +19329,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="C83" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -19341,10 +19344,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="C84" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -19356,10 +19359,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="C85" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -19371,10 +19374,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="C86" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -19386,10 +19389,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C87" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -19401,10 +19404,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="C88" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -19416,10 +19419,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C89" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -19431,10 +19434,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C90" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -19446,10 +19449,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="C91" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -19461,10 +19464,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="C92" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -19476,10 +19479,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="C93" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="D93" t="s">
         <v>18</v>
@@ -19491,10 +19494,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="C94" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="D94" t="s">
         <v>18</v>
@@ -19537,13 +19540,13 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B98" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C98" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D98" t="s">
         <v>18</v>
@@ -19570,10 +19573,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C100" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="D100" t="s">
         <v>18</v>
@@ -19585,10 +19588,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="C101" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D101" t="s">
         <v>18</v>
@@ -19651,10 +19654,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -19670,13 +19673,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>18</v>
@@ -19689,13 +19692,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C4" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>18</v>
@@ -19708,13 +19711,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C5" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>18</v>
@@ -19727,13 +19730,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="C6" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>18</v>
@@ -19746,13 +19749,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>18</v>
@@ -19765,13 +19768,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>18</v>
@@ -19784,13 +19787,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>18</v>
@@ -19803,13 +19806,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>18</v>
@@ -19822,13 +19825,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>18</v>
@@ -19841,13 +19844,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>18</v>
@@ -19860,13 +19863,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>18</v>
@@ -19879,13 +19882,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>18</v>
@@ -19898,13 +19901,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C15" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="D15" s="15" t="s">
         <v>18</v>
@@ -19917,13 +19920,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>18</v>
@@ -19936,13 +19939,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C17" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>18</v>
@@ -19955,13 +19958,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>18</v>
@@ -19974,13 +19977,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>18</v>
@@ -19993,13 +19996,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>18</v>
@@ -20012,13 +20015,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>18</v>
@@ -20031,13 +20034,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>18</v>
@@ -20050,13 +20053,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B23" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>18</v>
@@ -20086,13 +20089,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B26" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="C26" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -20104,10 +20107,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C27" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -20119,10 +20122,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C28" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -20183,13 +20186,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="C2" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="D2" s="16" t="s">
         <v>18</v>
@@ -20204,13 +20207,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="C3" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="D3" s="16" t="s">
         <v>18</v>
@@ -20223,13 +20226,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="C4" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>18</v>
@@ -20242,13 +20245,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="C5" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>18</v>
@@ -20261,16 +20264,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="C6" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -20282,13 +20285,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="C7" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="D7" s="16" t="s">
         <v>18</v>
@@ -20301,13 +20304,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>18</v>
@@ -20322,13 +20325,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="D9" s="16" t="s">
         <v>18</v>
@@ -20341,13 +20344,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C10" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>18</v>
@@ -20360,13 +20363,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>18</v>
@@ -20379,13 +20382,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>18</v>
@@ -20398,13 +20401,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>498</v>
       </c>
       <c r="C13" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>18</v>
@@ -20417,13 +20420,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="D14" s="16" t="s">
         <v>18</v>
@@ -20436,13 +20439,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>498</v>
       </c>
       <c r="C15" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="D15" s="16" t="s">
         <v>18</v>
@@ -20457,13 +20460,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D16" s="16" t="s">
         <v>18</v>
@@ -20476,7 +20479,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>29</v>
@@ -20495,7 +20498,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>29</v>
@@ -20514,7 +20517,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>29</v>
@@ -20550,13 +20553,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B22" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="C22" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -20568,10 +20571,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="C23" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -20583,10 +20586,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C24" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -20598,10 +20601,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="C25" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="D25" t="s">
         <v>18</v>
@@ -20629,13 +20632,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B28" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="C28" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -20647,10 +20650,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="C29" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -20662,10 +20665,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="C30" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -20677,10 +20680,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="C31" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -20692,10 +20695,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="C32" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -20707,10 +20710,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -20722,10 +20725,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="C34" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -20737,10 +20740,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="C35" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -20752,10 +20755,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C36" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -20767,10 +20770,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C37" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="D37" t="s">
         <v>18</v>
@@ -20782,10 +20785,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C38" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D38" t="s">
         <v>18</v>
@@ -20797,10 +20800,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C39" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="D39" t="s">
         <v>18</v>
@@ -20812,10 +20815,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C40" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -20827,10 +20830,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="C41" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="D41" t="s">
         <v>18</v>
@@ -20842,10 +20845,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C42" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -20857,10 +20860,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C43" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D43" t="s">
         <v>18</v>
@@ -20872,10 +20875,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C44" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D44" t="s">
         <v>18</v>
@@ -20890,7 +20893,7 @@
         <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -20902,10 +20905,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="C46" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -20917,10 +20920,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C47" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D47" t="s">
         <v>18</v>
@@ -20932,10 +20935,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="C48" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="D48" t="s">
         <v>18</v>
@@ -20963,13 +20966,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B51" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="C51" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -20981,10 +20984,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C52" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -20996,10 +20999,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C53" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -21027,13 +21030,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B56" t="s">
         <v>715</v>
       </c>
       <c r="C56" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -21048,7 +21051,7 @@
         <v>718</v>
       </c>
       <c r="C57" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D57" t="s">
         <v>18</v>
@@ -21060,10 +21063,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C58" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D58" t="s">
         <v>18</v>
@@ -21075,10 +21078,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C59" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D59" t="s">
         <v>18</v>
@@ -21142,16 +21145,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -21163,7 +21166,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>9</v>
@@ -21182,7 +21185,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="B4" s="17" t="s">
         <v>9</v>
@@ -21191,7 +21194,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -21203,13 +21206,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>517</v>
       </c>
       <c r="C5" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>18</v>
@@ -21222,16 +21225,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="B6" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="E6"/>
       <c r="G6" s="17" t="s">
@@ -21241,16 +21244,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="E7"/>
       <c r="G7" s="17" t="s">
@@ -21260,7 +21263,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>42</v>
@@ -21302,7 +21305,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>101</v>
@@ -21321,16 +21324,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="C11" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="E11"/>
       <c r="G11" s="17" t="s">
@@ -21340,13 +21343,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="C12" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>18</v>
@@ -21359,16 +21362,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="E13"/>
       <c r="G13" s="17" t="s">
@@ -21378,16 +21381,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="E14"/>
       <c r="G14" s="17" t="s">
@@ -21397,16 +21400,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="E15"/>
       <c r="G15" s="17" t="s">
@@ -21416,16 +21419,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="E16"/>
       <c r="G16" s="17" t="s">
@@ -21435,16 +21438,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="E17"/>
       <c r="G17" s="17" t="s">
@@ -21454,16 +21457,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="E18"/>
       <c r="G18" s="17" t="s">
@@ -21473,16 +21476,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="E19"/>
       <c r="G19" s="17" t="s">
@@ -21549,13 +21552,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="D23" s="17" t="s">
         <v>18</v>
@@ -21642,13 +21645,13 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B29" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="C29" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -21660,10 +21663,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C30" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -21675,10 +21678,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="C31" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -21690,10 +21693,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="C32" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -21705,10 +21708,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="C33" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -21800,10 +21803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="B41" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="C41" t="s">
         <v>542</v>
@@ -21818,10 +21821,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="C42" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="D42" t="s">
         <v>18</v>
@@ -21863,10 +21866,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="C45" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="D45" t="s">
         <v>18</v>
@@ -21881,7 +21884,7 @@
         <v>224</v>
       </c>
       <c r="C46" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="D46" t="s">
         <v>18</v>
@@ -21939,13 +21942,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="B51" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="C51" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="D51" t="s">
         <v>18</v>
@@ -21957,10 +21960,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="C52" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="D52" t="s">
         <v>18</v>
@@ -21972,10 +21975,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="C53" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="D53" t="s">
         <v>18</v>
@@ -21987,10 +21990,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="C54" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="D54" t="s">
         <v>18</v>
@@ -22933,13 +22936,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="C3" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>18</v>
@@ -22957,10 +22960,10 @@
         <v>490</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="C4" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>18</v>
@@ -22975,13 +22978,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D5" s="18" t="s">
         <v>18</v>
@@ -22994,10 +22997,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -23062,13 +23065,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B2" s="19" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="D2" s="19" t="s">
         <v>18</v>
@@ -23163,7 +23166,7 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>18</v>
@@ -23182,7 +23185,7 @@
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>18</v>
@@ -23195,7 +23198,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>55</v>
@@ -23214,7 +23217,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>133</v>
@@ -23233,7 +23236,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>133</v>
@@ -24464,13 +24467,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="D2" s="20" t="s">
         <v>18</v>
@@ -24483,13 +24486,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>18</v>
@@ -24502,13 +24505,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="D4" s="20" t="s">
         <v>18</v>
@@ -24521,7 +24524,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>133</v>
@@ -24559,10 +24562,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
@@ -24627,13 +24630,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="D2" s="21" t="s">
         <v>18</v>
@@ -24646,13 +24649,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="D3" s="21" t="s">
         <v>18</v>
@@ -24665,13 +24668,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="D4" s="21" t="s">
         <v>18</v>
@@ -24703,7 +24706,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>133</v>
@@ -24790,13 +24793,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>18</v>
@@ -24847,7 +24850,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>133</v>
@@ -24934,13 +24937,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>18</v>
@@ -24953,13 +24956,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>18</v>
@@ -25010,13 +25013,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>18</v>
@@ -25054,7 +25057,7 @@
         <v>101</v>
       </c>
       <c r="C8" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>18</v>
@@ -25067,11 +25070,11 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="B9" s="23"/>
       <c r="C9" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>18</v>
@@ -25084,10 +25087,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
@@ -25179,7 +25182,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="B15" s="23" t="s">
         <v>58</v>
@@ -25204,7 +25207,7 @@
         <v>615</v>
       </c>
       <c r="C16" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>18</v>
@@ -25217,13 +25220,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="B17" s="23" t="s">
         <v>498</v>
       </c>
       <c r="C17" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>18</v>
@@ -25236,16 +25239,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="B18" s="23" t="s">
         <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="E18"/>
       <c r="G18" s="23" t="s">
@@ -25255,10 +25258,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
@@ -26150,13 +26153,13 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="B80" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="C80" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="D80" t="s">
         <v>18</v>
@@ -26168,10 +26171,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="C81" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="D81" t="s">
         <v>18</v>
@@ -26183,10 +26186,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="C82" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="D82" t="s">
         <v>18</v>
@@ -26198,10 +26201,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="C83" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="D83" t="s">
         <v>18</v>
@@ -26213,10 +26216,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="C84" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="D84" t="s">
         <v>18</v>
@@ -26228,10 +26231,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="C85" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="D85" t="s">
         <v>18</v>
@@ -26243,10 +26246,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="C86" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="D86" t="s">
         <v>18</v>
@@ -26258,10 +26261,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="C87" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="D87" t="s">
         <v>18</v>
@@ -26273,10 +26276,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="C88" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="D88" t="s">
         <v>18</v>
@@ -26288,10 +26291,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="C89" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="D89" t="s">
         <v>18</v>
@@ -26303,10 +26306,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="C90" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="D90" t="s">
         <v>18</v>
@@ -26318,10 +26321,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="C91" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="D91" t="s">
         <v>18</v>
@@ -26333,10 +26336,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="C92" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="D92" t="s">
         <v>18</v>
@@ -26362,12 +26365,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
   </sheetData>
@@ -35388,231 +35391,231 @@
       </c>
       <c r="E16"/>
       <c r="G16" s="6" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="H16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C17" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E17"/>
       <c r="G17" s="6" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E18"/>
       <c r="G18" s="6" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E19"/>
       <c r="G19" s="6" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E20"/>
       <c r="G20" s="6" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="H20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C21" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E21"/>
       <c r="G21" s="6" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="H21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C22" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E22"/>
       <c r="G22" s="6" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="H22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E23"/>
       <c r="G23" s="6" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="H23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C24" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="E24"/>
       <c r="G24" s="6" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C25" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="E25"/>
       <c r="G25" s="6" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C26" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="E26"/>
       <c r="G26" s="6" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C27" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="E27"/>
       <c r="G27" s="6" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C28" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="E28"/>
       <c r="G28" s="6" t="s">
@@ -35622,115 +35625,115 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C29" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E29"/>
       <c r="G29" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C30" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="E30"/>
       <c r="G30" s="6" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C31" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E31"/>
       <c r="G31" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C32" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E32"/>
       <c r="G32" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C33" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="E33"/>
       <c r="G33" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C34" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="E34"/>
       <c r="G34" s="6" t="s">
-        <v>1358</v>
+        <v>1336</v>
       </c>
       <c r="H34"/>
     </row>
@@ -35749,7 +35752,7 @@
       </c>
       <c r="E35"/>
       <c r="G35" s="6" t="s">
-        <v>1358</v>
+        <v>1336</v>
       </c>
       <c r="H35"/>
     </row>
@@ -36053,7 +36056,7 @@
       </c>
       <c r="E51"/>
       <c r="G51" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H51"/>
     </row>
@@ -36072,7 +36075,7 @@
       </c>
       <c r="E52"/>
       <c r="G52" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H52"/>
     </row>
@@ -36091,7 +36094,7 @@
       </c>
       <c r="E53"/>
       <c r="G53" s="6" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H53"/>
     </row>
@@ -36167,26 +36170,26 @@
       </c>
       <c r="E57"/>
       <c r="G57" s="6" t="s">
-        <v>976</v>
+        <v>1418</v>
       </c>
       <c r="H57"/>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>517</v>
       </c>
       <c r="C58" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E58"/>
       <c r="G58" s="6" t="s">
-        <v>976</v>
+        <v>1418</v>
       </c>
       <c r="H58"/>
     </row>
@@ -36276,10 +36279,10 @@
         <v>1363</v>
       </c>
       <c r="B66" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C66" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D66" t="s">
         <v>18</v>
@@ -36291,10 +36294,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="C67" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="D67" t="s">
         <v>18</v>
@@ -36306,10 +36309,10 @@
     <row r="68">
       <c r="A68"/>
       <c r="B68" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C68" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="D68" t="s">
         <v>18</v>
@@ -36321,10 +36324,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="C69" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="D69" t="s">
         <v>18</v>
@@ -36400,10 +36403,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C75" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="D75" t="s">
         <v>18</v>
@@ -36546,7 +36549,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>517</v>
@@ -36565,13 +36568,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C3" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>18</v>
@@ -36584,13 +36587,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C4" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>18</v>
@@ -36603,13 +36606,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C5" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>18</v>
@@ -36622,7 +36625,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>517</v>
@@ -36641,13 +36644,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C7" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>18</v>
@@ -36660,13 +36663,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C8" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>18</v>
@@ -36679,13 +36682,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C9" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>18</v>
@@ -36698,13 +36701,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C10" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>18</v>
@@ -36717,13 +36720,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C11" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>18</v>
@@ -36736,13 +36739,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C12" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>18</v>
@@ -36755,13 +36758,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C13" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>18</v>
@@ -36774,13 +36777,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C14" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>18</v>
@@ -36793,13 +36796,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C15" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>18</v>
@@ -36812,13 +36815,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C16" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>18</v>
@@ -36831,13 +36834,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C17" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>18</v>
@@ -36850,13 +36853,13 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C18" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>18</v>
@@ -36869,13 +36872,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C19" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>18</v>
@@ -36888,13 +36891,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C20" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>18</v>
@@ -36907,13 +36910,13 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C21" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>18</v>
@@ -36926,13 +36929,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C22" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>18</v>
@@ -36945,13 +36948,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>517</v>
       </c>
       <c r="C23" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="D23" s="7" t="s">
         <v>18</v>
@@ -36964,13 +36967,13 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>18</v>
@@ -37100,7 +37103,7 @@
         <v>599</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -37116,13 +37119,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>18</v>
@@ -37135,13 +37138,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>18</v>
@@ -37154,13 +37157,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>18</v>
@@ -37173,13 +37176,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>18</v>
@@ -37192,13 +37195,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C7" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>18</v>
@@ -37211,13 +37214,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>18</v>
@@ -37230,13 +37233,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C9" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>18</v>
@@ -37249,13 +37252,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>18</v>
@@ -37268,13 +37271,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>18</v>
@@ -37287,13 +37290,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C12" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>18</v>
@@ -37306,13 +37309,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>18</v>
@@ -37325,13 +37328,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>18</v>
@@ -37361,13 +37364,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B17" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C17" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -37379,10 +37382,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C18" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -37394,10 +37397,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C19" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -37409,10 +37412,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="C20" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -37424,10 +37427,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C21" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -37439,10 +37442,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C22" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -37454,10 +37457,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="C23" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="D23" t="s">
         <v>18</v>
@@ -37469,10 +37472,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C24" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D24" t="s">
         <v>18</v>
@@ -37515,13 +37518,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B28" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="C28" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="D28" t="s">
         <v>18</v>
@@ -37533,10 +37536,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C29" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="D29" t="s">
         <v>18</v>
@@ -37579,13 +37582,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B33" t="s">
         <v>1254</v>
       </c>
       <c r="C33" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -37597,10 +37600,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C34" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>
@@ -37615,7 +37618,7 @@
         <v>1256</v>
       </c>
       <c r="C35" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="D35" t="s">
         <v>18</v>
@@ -37627,10 +37630,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C36" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="D36" t="s">
         <v>18</v>
@@ -37711,7 +37714,7 @@
         <v>599</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -37727,13 +37730,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>18</v>
@@ -37746,13 +37749,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>18</v>
@@ -37765,13 +37768,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C5" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>18</v>
@@ -37784,13 +37787,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>18</v>
@@ -37803,13 +37806,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C7" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>18</v>
@@ -37822,13 +37825,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>18</v>
@@ -37841,13 +37844,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C9" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="D9" s="9" t="s">
         <v>18</v>
@@ -37860,13 +37863,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="D10" s="9" t="s">
         <v>18</v>
@@ -37879,13 +37882,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>18</v>
@@ -37898,10 +37901,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
@@ -37934,13 +37937,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B15" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="C15" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="D15" t="s">
         <v>18</v>
@@ -37952,10 +37955,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="C16" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="D16" t="s">
         <v>18</v>
@@ -37967,10 +37970,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C17" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="D17" t="s">
         <v>18</v>
@@ -37982,10 +37985,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="C18" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="D18" t="s">
         <v>18</v>
@@ -37997,10 +38000,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C19" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D19" t="s">
         <v>18</v>
@@ -38012,10 +38015,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="C20" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -38027,10 +38030,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="C21" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="D21" t="s">
         <v>18</v>
@@ -38042,10 +38045,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C22" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D22" t="s">
         <v>18</v>
@@ -38088,13 +38091,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B26" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="C26" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="D26" t="s">
         <v>18</v>
@@ -38106,10 +38109,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C27" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="D27" t="s">
         <v>18</v>
@@ -38152,13 +38155,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B31" t="s">
         <v>1254</v>
       </c>
       <c r="C31" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="D31" t="s">
         <v>18</v>
@@ -38170,10 +38173,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C32" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="D32" t="s">
         <v>18</v>
@@ -38188,7 +38191,7 @@
         <v>1256</v>
       </c>
       <c r="C33" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="D33" t="s">
         <v>18</v>
@@ -38200,10 +38203,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="C34" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="D34" t="s">
         <v>18</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -6820,7 +6820,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.50.0-SNAPSHOT</t>
+    <t>${project.version}</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -6871,7 +6871,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.51.0-SNAPSHOT</t>
+    <t>${project.version}</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -6437,7 +6437,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.52.0-SNAPSHOT</t>
+    <t>1.53.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9601" uniqueCount="2467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9648" uniqueCount="2483">
   <si>
     <t>Field</t>
   </si>
@@ -1656,7 +1656,7 @@
     <t>addressTypeDetails</t>
   </si>
   <si>
-    <t>Address Type specification</t>
+    <t>Address name / description</t>
   </si>
   <si>
     <t>facilityType</t>
@@ -4914,6 +4914,12 @@
     <t>Public place</t>
   </si>
   <si>
+    <t>SCATTERED</t>
+  </si>
+  <si>
+    <t>Scattered</t>
+  </si>
+  <si>
     <t>BUS</t>
   </si>
   <si>
@@ -6957,6 +6963,9 @@
     <t>not executable</t>
   </si>
   <si>
+    <t>superordinateEvent</t>
+  </si>
+  <si>
     <t>eventStatus</t>
   </si>
   <si>
@@ -7131,6 +7140,21 @@
     <t>Specify other event place</t>
   </si>
   <si>
+    <t>transregionalOutbreak</t>
+  </si>
+  <si>
+    <t>Transregional outbreak</t>
+  </si>
+  <si>
+    <t>diseaseTransmissionMode</t>
+  </si>
+  <si>
+    <t>DiseaseTransmissionMode</t>
+  </si>
+  <si>
+    <t>Primary mode of transmission</t>
+  </si>
+  <si>
     <t>SIGNAL</t>
   </si>
   <si>
@@ -7225,6 +7249,30 @@
   </si>
   <si>
     <t>Medico-social establishments</t>
+  </si>
+  <si>
+    <t>HUMAN_TO_HUMAN</t>
+  </si>
+  <si>
+    <t>Primarily via human to human</t>
+  </si>
+  <si>
+    <t>Primarily via animal</t>
+  </si>
+  <si>
+    <t>Primarily via environment</t>
+  </si>
+  <si>
+    <t>FOOD</t>
+  </si>
+  <si>
+    <t>Primarily via food</t>
+  </si>
+  <si>
+    <t>VECTOR_BORNE</t>
+  </si>
+  <si>
+    <t>Primarily vector-borne</t>
   </si>
   <si>
     <t>Person</t>
@@ -7817,7 +7865,7 @@
 </file>
 
 <file path=xl/tables/table114.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="114" name="Event" displayName="Event" ref="A1:K39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="114" name="Event" displayName="Event" ref="A1:K41">
   <autoFilter/>
   <tableColumns count="11">
     <tableColumn id="1" name="Field"/>
@@ -7837,7 +7885,7 @@
 </file>
 
 <file path=xl/tables/table115.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="115" name="EventEventStatus" displayName="EventEventStatus" ref="A41:E46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="115" name="EventEventStatus" displayName="EventEventStatus" ref="A43:E48">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7851,7 +7899,7 @@
 </file>
 
 <file path=xl/tables/table116.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="116" name="EventRiskLevel" displayName="EventRiskLevel" ref="A48:E52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="116" name="EventRiskLevel" displayName="EventRiskLevel" ref="A50:E54">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7865,7 +7913,7 @@
 </file>
 
 <file path=xl/tables/table117.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="117" name="EventEventInvestigationStatus" displayName="EventEventInvestigationStatus" ref="A54:E58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="117" name="EventEventInvestigationStatus" displayName="EventEventInvestigationStatus" ref="A56:E60">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7879,7 +7927,7 @@
 </file>
 
 <file path=xl/tables/table118.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="118" name="EventYesNoUnknown" displayName="EventYesNoUnknown" ref="A60:E63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="118" name="EventYesNoUnknown" displayName="EventYesNoUnknown" ref="A62:E65">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7893,7 +7941,7 @@
 </file>
 
 <file path=xl/tables/table119.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="119" name="EventTypeOfPlace" displayName="EventTypeOfPlace" ref="A65:E72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="119" name="EventTypeOfPlace" displayName="EventTypeOfPlace" ref="A67:E75">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7921,7 +7969,7 @@
 </file>
 
 <file path=xl/tables/table120.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="120" name="EventMeansOfTransport" displayName="EventMeansOfTransport" ref="A74:E79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="120" name="EventMeansOfTransport" displayName="EventMeansOfTransport" ref="A77:E82">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7935,7 +7983,7 @@
 </file>
 
 <file path=xl/tables/table121.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="121" name="EventEventSourceType" displayName="EventEventSourceType" ref="A81:E86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="121" name="EventEventSourceType" displayName="EventEventSourceType" ref="A84:E89">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7949,7 +7997,7 @@
 </file>
 
 <file path=xl/tables/table122.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="122" name="EventInstitutionalPartnerType" displayName="EventInstitutionalPartnerType" ref="A88:E94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="122" name="EventInstitutionalPartnerType" displayName="EventInstitutionalPartnerType" ref="A91:E97">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7963,7 +8011,7 @@
 </file>
 
 <file path=xl/tables/table123.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="123" name="EventDisease" displayName="EventDisease" ref="A96:E152">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="123" name="EventDisease" displayName="EventDisease" ref="A99:E155">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -7977,27 +8025,21 @@
 </file>
 
 <file path=xl/tables/table124.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="124" name="Event_participant" displayName="Event_participant" ref="A1:K8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="124" name="EventDiseaseTransmissionMode" displayName="EventDiseaseTransmissionMode" ref="A157:E163">
   <autoFilter/>
-  <tableColumns count="11">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Type"/>
-    <tableColumn id="3" name="Data protection"/>
-    <tableColumn id="4" name="Caption"/>
-    <tableColumn id="5" name="Description"/>
-    <tableColumn id="6" name="Required"/>
-    <tableColumn id="7" name="New disease"/>
-    <tableColumn id="8" name="Diseases"/>
-    <tableColumn id="9" name="Outbreaks"/>
-    <tableColumn id="10" name="Ignored countries"/>
-    <tableColumn id="11" name="Exclusive countries"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
 </table>
 </file>
 
 <file path=xl/tables/table125.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="125" name="Facility" displayName="Facility" ref="A1:K12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="125" name="Event_participant" displayName="Event_participant" ref="A1:K8">
   <autoFilter/>
   <tableColumns count="11">
     <tableColumn id="1" name="Field"/>
@@ -8017,21 +8059,7 @@
 </file>
 
 <file path=xl/tables/table126.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="126" name="FacilityFacilityType" displayName="FacilityFacilityType" ref="A14:E55">
-  <autoFilter/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Type"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Caption"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Short"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
-</table>
-</file>
-
-<file path=xl/tables/table127.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="127" name="Country" displayName="Country" ref="A1:K6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="126" name="Facility" displayName="Facility" ref="A1:K12">
   <autoFilter/>
   <tableColumns count="11">
     <tableColumn id="1" name="Field"/>
@@ -8050,8 +8078,22 @@
 </table>
 </file>
 
+<file path=xl/tables/table127.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="127" name="FacilityFacilityType" displayName="FacilityFacilityType" ref="A14:E55">
+  <autoFilter/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="Type"/>
+    <tableColumn id="2" name="Value"/>
+    <tableColumn id="3" name="Caption"/>
+    <tableColumn id="4" name="Description"/>
+    <tableColumn id="5" name="Short"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
 <file path=xl/tables/table128.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="128" name="Region" displayName="Region" ref="A1:K7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="128" name="Country" displayName="Country" ref="A1:K6">
   <autoFilter/>
   <tableColumns count="11">
     <tableColumn id="1" name="Field"/>
@@ -8071,7 +8113,7 @@
 </file>
 
 <file path=xl/tables/table129.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="129" name="District" displayName="District" ref="A1:K7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="129" name="Region" displayName="Region" ref="A1:K7">
   <autoFilter/>
   <tableColumns count="11">
     <tableColumn id="1" name="Field"/>
@@ -8105,7 +8147,7 @@
 </file>
 
 <file path=xl/tables/table130.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="130" name="Community" displayName="Community" ref="A1:K6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="130" name="District" displayName="District" ref="A1:K7">
   <autoFilter/>
   <tableColumns count="11">
     <tableColumn id="1" name="Field"/>
@@ -8125,7 +8167,7 @@
 </file>
 
 <file path=xl/tables/table131.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="131" name="User" displayName="User" ref="A1:K19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="131" name="Community" displayName="Community" ref="A1:K6">
   <autoFilter/>
   <tableColumns count="11">
     <tableColumn id="1" name="Field"/>
@@ -8145,7 +8187,27 @@
 </file>
 
 <file path=xl/tables/table132.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="132" name="UserFacilityReference" displayName="UserFacilityReference" ref="A21:D24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="132" name="User" displayName="User" ref="A1:K19">
+  <autoFilter/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="Field"/>
+    <tableColumn id="2" name="Type"/>
+    <tableColumn id="3" name="Data protection"/>
+    <tableColumn id="4" name="Caption"/>
+    <tableColumn id="5" name="Description"/>
+    <tableColumn id="6" name="Required"/>
+    <tableColumn id="7" name="New disease"/>
+    <tableColumn id="8" name="Diseases"/>
+    <tableColumn id="9" name="Outbreaks"/>
+    <tableColumn id="10" name="Ignored countries"/>
+    <tableColumn id="11" name="Exclusive countries"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="false" showLastColumn="false" showRowStripes="true" showColumnStripes="false"/>
+</table>
+</file>
+
+<file path=xl/tables/table133.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="133" name="UserFacilityReference" displayName="UserFacilityReference" ref="A21:D24">
   <autoFilter/>
   <tableColumns count="4">
     <tableColumn id="1" name="Type"/>
@@ -8157,8 +8219,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table133.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="133" name="UserDisease" displayName="UserDisease" ref="A26:E82">
+<file path=xl/tables/table134.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="134" name="UserDisease" displayName="UserDisease" ref="A26:E82">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8171,8 +8233,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table134.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="134" name="UserLanguage" displayName="UserLanguage" ref="A84:E97">
+<file path=xl/tables/table135.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="135" name="UserLanguage" displayName="UserLanguage" ref="A84:E97">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8877,7 +8939,7 @@
 </file>
 
 <file path=xl/tables/table57.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ExposureTypeOfPlace" displayName="ExposureTypeOfPlace" ref="A73:E80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="57" name="ExposureTypeOfPlace" displayName="ExposureTypeOfPlace" ref="A73:E81">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8891,7 +8953,7 @@
 </file>
 
 <file path=xl/tables/table58.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ExposureMeansOfTransport" displayName="ExposureMeansOfTransport" ref="A82:E87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="58" name="ExposureMeansOfTransport" displayName="ExposureMeansOfTransport" ref="A83:E88">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8905,7 +8967,7 @@
 </file>
 
 <file path=xl/tables/table59.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ExposureYesNoUnknown" displayName="ExposureYesNoUnknown" ref="A89:E92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="59" name="ExposureYesNoUnknown" displayName="ExposureYesNoUnknown" ref="A90:E93">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8933,7 +8995,7 @@
 </file>
 
 <file path=xl/tables/table60.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ExposureAnimalCondition" displayName="ExposureAnimalCondition" ref="A94:E98">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="60" name="ExposureAnimalCondition" displayName="ExposureAnimalCondition" ref="A95:E99">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8947,7 +9009,7 @@
 </file>
 
 <file path=xl/tables/table61.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ExposureAnimalContactType" displayName="ExposureAnimalContactType" ref="A100:E105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="61" name="ExposureAnimalContactType" displayName="ExposureAnimalContactType" ref="A101:E106">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8961,7 +9023,7 @@
 </file>
 
 <file path=xl/tables/table62.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="ExposureWaterSource" displayName="ExposureWaterSource" ref="A107:E112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="62" name="ExposureWaterSource" displayName="ExposureWaterSource" ref="A108:E113">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8975,7 +9037,7 @@
 </file>
 
 <file path=xl/tables/table63.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="63" name="ExposureGatheringType" displayName="ExposureGatheringType" ref="A114:E118">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="63" name="ExposureGatheringType" displayName="ExposureGatheringType" ref="A115:E119">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8989,7 +9051,7 @@
 </file>
 
 <file path=xl/tables/table64.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="ExposureHabitationType" displayName="ExposureHabitationType" ref="A120:E122">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="64" name="ExposureHabitationType" displayName="ExposureHabitationType" ref="A121:E123">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -9003,7 +9065,7 @@
 </file>
 
 <file path=xl/tables/table65.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="ExposureTypeOfAnimal" displayName="ExposureTypeOfAnimal" ref="A124:E139">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="65" name="ExposureTypeOfAnimal" displayName="ExposureTypeOfAnimal" ref="A125:E140">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -13893,7 +13955,7 @@
         <v>683</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
@@ -13912,14 +13974,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>55</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>22</v>
@@ -13934,7 +13996,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>12</v>
@@ -13943,7 +14005,7 @@
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>22</v>
@@ -13958,14 +14020,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>22</v>
@@ -13980,7 +14042,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>12</v>
@@ -13989,7 +14051,7 @@
         <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>22</v>
@@ -14004,14 +14066,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>22</v>
@@ -14026,14 +14088,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>12</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>22</v>
@@ -14048,14 +14110,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>22</v>
@@ -14070,7 +14132,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>12</v>
@@ -14079,7 +14141,7 @@
         <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>22</v>
@@ -14094,7 +14156,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>12</v>
@@ -14103,7 +14165,7 @@
         <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>22</v>
@@ -14118,10 +14180,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
@@ -14157,13 +14219,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B15" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="C15" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
@@ -14175,10 +14237,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="C16" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -14190,10 +14252,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="C17" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
@@ -14205,10 +14267,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="C18" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
@@ -14220,10 +14282,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="C19" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
@@ -14235,10 +14297,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="C20" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -14250,10 +14312,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="C21" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -14265,10 +14327,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="C22" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
@@ -14311,13 +14373,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B26" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="C26" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
@@ -14329,10 +14391,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="C27" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
@@ -14375,13 +14437,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="B31" t="s">
         <v>1457</v>
       </c>
       <c r="C31" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
@@ -14393,10 +14455,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="C32" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="D32" t="s">
         <v>22</v>
@@ -14411,7 +14473,7 @@
         <v>1459</v>
       </c>
       <c r="C33" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="D33" t="s">
         <v>22</v>
@@ -14423,10 +14485,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C34" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
@@ -14519,7 +14581,7 @@
         <v>685</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
@@ -14582,14 +14644,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>55</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>22</v>
@@ -14604,7 +14666,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>12</v>
@@ -14613,7 +14675,7 @@
         <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>22</v>
@@ -14628,7 +14690,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>12</v>
@@ -14637,7 +14699,7 @@
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>22</v>
@@ -15573,14 +15635,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>22</v>
@@ -15595,14 +15657,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>12</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>22</v>
@@ -15617,7 +15679,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>12</v>
@@ -15626,7 +15688,7 @@
         <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>22</v>
@@ -15648,7 +15710,7 @@
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>22</v>
@@ -15685,14 +15747,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>22</v>
@@ -15813,7 +15875,7 @@
         <v>623</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="F12"/>
       <c r="H12" s="12" t="s">
@@ -15835,7 +15897,7 @@
         <v>624</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="F13"/>
       <c r="H13" s="12" t="s">
@@ -15857,7 +15919,7 @@
         <v>625</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="F14"/>
       <c r="H14" s="12" t="s">
@@ -15869,14 +15931,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>140</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>22</v>
@@ -15893,14 +15955,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="E16" s="12" t="s">
         <v>22</v>
@@ -15915,14 +15977,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>55</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>22</v>
@@ -15939,14 +16001,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>22</v>
@@ -15963,7 +16025,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>12</v>
@@ -15972,7 +16034,7 @@
         <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>22</v>
@@ -15989,14 +16051,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>22</v>
@@ -16013,7 +16075,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>12</v>
@@ -16022,7 +16084,7 @@
         <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>22</v>
@@ -16039,17 +16101,17 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="F22"/>
       <c r="H22" s="12" t="s">
@@ -16061,7 +16123,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>12</v>
@@ -16070,7 +16132,7 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>22</v>
@@ -16085,14 +16147,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>22</v>
@@ -16107,14 +16169,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>22</v>
@@ -16129,14 +16191,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>22</v>
@@ -16161,7 +16223,7 @@
         <v>756</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="F27"/>
       <c r="H27" s="12" t="s">
@@ -16250,7 +16312,7 @@
         <v>66</v>
       </c>
       <c r="D31" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>22</v>
@@ -16265,17 +16327,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="F32"/>
       <c r="H32" s="12" t="s">
@@ -16287,7 +16349,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>12</v>
@@ -16296,7 +16358,7 @@
         <v>66</v>
       </c>
       <c r="D33" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>22</v>
@@ -16359,14 +16421,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>140</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>22</v>
@@ -16381,14 +16443,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>603</v>
       </c>
       <c r="C37"/>
       <c r="D37" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>22</v>
@@ -16403,7 +16465,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>12</v>
@@ -16412,7 +16474,7 @@
         <v>66</v>
       </c>
       <c r="D38" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>22</v>
@@ -16427,14 +16489,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>603</v>
       </c>
       <c r="C39"/>
       <c r="D39" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>22</v>
@@ -16546,7 +16608,7 @@
       </c>
       <c r="C44"/>
       <c r="D44" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>22</v>
@@ -16563,7 +16625,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>584</v>
@@ -16572,7 +16634,7 @@
         <v>66</v>
       </c>
       <c r="D45" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>22</v>
@@ -16587,14 +16649,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="C46"/>
       <c r="D46" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>22</v>
@@ -16609,7 +16671,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>584</v>
@@ -16618,7 +16680,7 @@
         <v>66</v>
       </c>
       <c r="D47" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>22</v>
@@ -16991,10 +17053,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C63"/>
       <c r="D63" t="s">
@@ -17057,14 +17119,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>603</v>
       </c>
       <c r="C66"/>
       <c r="D66" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>22</v>
@@ -17079,14 +17141,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="C67"/>
       <c r="D67" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>22</v>
@@ -17103,7 +17165,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>12</v>
@@ -18101,10 +18163,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B133" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="C133" t="s">
         <v>577</v>
@@ -18119,10 +18181,10 @@
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="C134" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="D134" t="s">
         <v>22</v>
@@ -18134,10 +18196,10 @@
     <row r="135">
       <c r="A135"/>
       <c r="B135" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C135" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="D135" t="s">
         <v>22</v>
@@ -18195,13 +18257,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="B140" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="C140" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D140" t="s">
         <v>22</v>
@@ -18259,13 +18321,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="B145" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C145" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="D145" t="s">
         <v>22</v>
@@ -18277,10 +18339,10 @@
     <row r="146">
       <c r="A146"/>
       <c r="B146" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C146" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="D146" t="s">
         <v>22</v>
@@ -18292,10 +18354,10 @@
     <row r="147">
       <c r="A147"/>
       <c r="B147" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="C147" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="D147" t="s">
         <v>22</v>
@@ -18307,10 +18369,10 @@
     <row r="148">
       <c r="A148"/>
       <c r="B148" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="C148" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="D148" t="s">
         <v>22</v>
@@ -18322,10 +18384,10 @@
     <row r="149">
       <c r="A149"/>
       <c r="B149" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="C149" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="D149" t="s">
         <v>22</v>
@@ -18337,10 +18399,10 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="C150" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="D150" t="s">
         <v>22</v>
@@ -18352,10 +18414,10 @@
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="C151" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="D151" t="s">
         <v>22</v>
@@ -18367,10 +18429,10 @@
     <row r="152">
       <c r="A152"/>
       <c r="B152" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="C152" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D152" t="s">
         <v>22</v>
@@ -18382,10 +18444,10 @@
     <row r="153">
       <c r="A153"/>
       <c r="B153" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C153" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="D153" t="s">
         <v>22</v>
@@ -18397,10 +18459,10 @@
     <row r="154">
       <c r="A154"/>
       <c r="B154" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C154" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="D154" t="s">
         <v>22</v>
@@ -18412,10 +18474,10 @@
     <row r="155">
       <c r="A155"/>
       <c r="B155" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C155" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="D155" t="s">
         <v>22</v>
@@ -18427,10 +18489,10 @@
     <row r="156">
       <c r="A156"/>
       <c r="B156" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C156" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="D156" t="s">
         <v>22</v>
@@ -18442,10 +18504,10 @@
     <row r="157">
       <c r="A157"/>
       <c r="B157" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C157" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="D157" t="s">
         <v>22</v>
@@ -18457,10 +18519,10 @@
     <row r="158">
       <c r="A158"/>
       <c r="B158" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C158" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="D158" t="s">
         <v>22</v>
@@ -18488,13 +18550,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="B161" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="C161" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="D161" t="s">
         <v>22</v>
@@ -18506,10 +18568,10 @@
     <row r="162">
       <c r="A162"/>
       <c r="B162" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="C162" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="D162" t="s">
         <v>22</v>
@@ -18521,10 +18583,10 @@
     <row r="163">
       <c r="A163"/>
       <c r="B163" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="C163" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="D163" t="s">
         <v>22</v>
@@ -18536,10 +18598,10 @@
     <row r="164">
       <c r="A164"/>
       <c r="B164" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="C164" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="D164" t="s">
         <v>22</v>
@@ -18551,10 +18613,10 @@
     <row r="165">
       <c r="A165"/>
       <c r="B165" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="C165" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="D165" t="s">
         <v>22</v>
@@ -18582,19 +18644,19 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B168" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C168" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="D168" t="s">
         <v>22</v>
       </c>
       <c r="E168" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="169">
@@ -18603,7 +18665,7 @@
         <v>821</v>
       </c>
       <c r="C169" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="D169" t="s">
         <v>22</v>
@@ -18615,16 +18677,16 @@
     <row r="170">
       <c r="A170"/>
       <c r="B170" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="C170" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="D170" t="s">
         <v>22</v>
       </c>
       <c r="E170" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="172">
@@ -18646,13 +18708,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="B173" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="C173" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="D173" t="s">
         <v>22</v>
@@ -18664,10 +18726,10 @@
     <row r="174">
       <c r="A174"/>
       <c r="B174" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="C174" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="D174" t="s">
         <v>22</v>
@@ -18679,10 +18741,10 @@
     <row r="175">
       <c r="A175"/>
       <c r="B175" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="C175" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="D175" t="s">
         <v>22</v>
@@ -18804,13 +18866,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="B185" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C185" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="D185" t="s">
         <v>22</v>
@@ -18822,10 +18884,10 @@
     <row r="186">
       <c r="A186"/>
       <c r="B186" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="C186" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="D186" t="s">
         <v>22</v>
@@ -18837,10 +18899,10 @@
     <row r="187">
       <c r="A187"/>
       <c r="B187" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="C187" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="D187" t="s">
         <v>22</v>
@@ -18852,10 +18914,10 @@
     <row r="188">
       <c r="A188"/>
       <c r="B188" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="C188" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="D188" t="s">
         <v>22</v>
@@ -19101,13 +19163,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B207" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="C207" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="D207" t="s">
         <v>22</v>
@@ -19119,10 +19181,10 @@
     <row r="208">
       <c r="A208"/>
       <c r="B208" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="C208" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="D208" t="s">
         <v>22</v>
@@ -19134,7 +19196,7 @@
     <row r="209">
       <c r="A209"/>
       <c r="B209" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="C209" t="s">
         <v>962</v>
@@ -19243,7 +19305,7 @@
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="E2" s="13" t="s">
         <v>22</v>
@@ -19282,17 +19344,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>55</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -19306,7 +19368,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>584</v>
@@ -19315,7 +19377,7 @@
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>22</v>
@@ -19332,17 +19394,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -19356,7 +19418,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>12</v>
@@ -19365,10 +19427,10 @@
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="F7"/>
       <c r="H7" s="13" t="s">
@@ -19411,7 +19473,7 @@
         <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>22</v>
@@ -19435,7 +19497,7 @@
         <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>22</v>
@@ -19472,14 +19534,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>22</v>
@@ -20370,13 +20432,13 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="B73" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="C73" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="D73" t="s">
         <v>22</v>
@@ -20388,31 +20450,31 @@
     <row r="74">
       <c r="A74"/>
       <c r="B74" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="C74" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="D74" t="s">
         <v>22</v>
       </c>
       <c r="E74" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="C75" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="D75" t="s">
         <v>22</v>
       </c>
       <c r="E75" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="77">
@@ -20434,13 +20496,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="B78" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C78" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="D78" t="s">
         <v>22</v>
@@ -20452,10 +20514,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C79" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="D79" t="s">
         <v>22</v>
@@ -20530,14 +20592,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>22</v>
@@ -20552,14 +20614,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>1561</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>22</v>
@@ -20574,14 +20636,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>22</v>
@@ -20596,14 +20658,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="E5" s="14" t="s">
         <v>22</v>
@@ -20618,14 +20680,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="B6" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>22</v>
@@ -20640,17 +20702,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -20664,7 +20726,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B8" s="14" t="s">
         <v>55</v>
@@ -20782,14 +20844,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>22</v>
@@ -20806,7 +20868,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="B14" s="14" t="s">
         <v>12</v>
@@ -20815,7 +20877,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>22</v>
@@ -20830,14 +20892,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>22</v>
@@ -20854,7 +20916,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="B16" s="14" t="s">
         <v>72</v>
@@ -20878,7 +20940,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>12</v>
@@ -20887,7 +20949,7 @@
         <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="E17" s="14" t="s">
         <v>22</v>
@@ -20902,14 +20964,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="B18" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>22</v>
@@ -20924,7 +20986,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B19" s="14" t="s">
         <v>12</v>
@@ -20933,7 +20995,7 @@
         <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>22</v>
@@ -20948,14 +21010,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B20" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>22</v>
@@ -20970,14 +21032,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>22</v>
@@ -20992,7 +21054,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>12</v>
@@ -21001,7 +21063,7 @@
         <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>22</v>
@@ -21016,7 +21078,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>12</v>
@@ -21040,14 +21102,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>22</v>
@@ -21062,10 +21124,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B25" s="14" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="s">
@@ -21084,14 +21146,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>140</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>22</v>
@@ -21106,14 +21168,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>140</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>22</v>
@@ -21128,14 +21190,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>22</v>
@@ -21150,14 +21212,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>140</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>22</v>
@@ -21172,14 +21234,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>140</v>
       </c>
       <c r="C30"/>
       <c r="D30" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>22</v>
@@ -21194,12 +21256,12 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B31" s="14"/>
       <c r="C31"/>
       <c r="D31" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>22</v>
@@ -21214,12 +21276,12 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B32" s="14"/>
       <c r="C32"/>
       <c r="D32" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>22</v>
@@ -21234,14 +21296,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>22</v>
@@ -21256,14 +21318,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="B34" s="14" t="s">
         <v>12</v>
       </c>
       <c r="C34"/>
       <c r="D34" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>22</v>
@@ -21391,13 +21453,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="B44" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="C44" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="D44" t="s">
         <v>22</v>
@@ -21409,10 +21471,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="C45" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -21424,10 +21486,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="C46" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="D46" t="s">
         <v>22</v>
@@ -21439,10 +21501,10 @@
     <row r="47">
       <c r="A47"/>
       <c r="B47" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="C47" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="D47" t="s">
         <v>22</v>
@@ -21454,10 +21516,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="C48" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="D48" t="s">
         <v>22</v>
@@ -21469,10 +21531,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="C49" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="D49" t="s">
         <v>22</v>
@@ -21484,10 +21546,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="C50" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="D50" t="s">
         <v>22</v>
@@ -21499,10 +21561,10 @@
     <row r="51">
       <c r="A51"/>
       <c r="B51" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="C51" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="D51" t="s">
         <v>22</v>
@@ -21514,10 +21576,10 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="C52" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="D52" t="s">
         <v>22</v>
@@ -21529,10 +21591,10 @@
     <row r="53">
       <c r="A53"/>
       <c r="B53" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="C53" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="D53" t="s">
         <v>22</v>
@@ -21544,10 +21606,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="C54" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="D54" t="s">
         <v>22</v>
@@ -21559,10 +21621,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="C55" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="D55" t="s">
         <v>22</v>
@@ -21574,10 +21636,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C56" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="D56" t="s">
         <v>22</v>
@@ -21589,10 +21651,10 @@
     <row r="57">
       <c r="A57"/>
       <c r="B57" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C57" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="D57" t="s">
         <v>22</v>
@@ -21604,10 +21666,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C58" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="D58" t="s">
         <v>22</v>
@@ -21619,10 +21681,10 @@
     <row r="59">
       <c r="A59"/>
       <c r="B59" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C59" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="D59" t="s">
         <v>22</v>
@@ -21634,10 +21696,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="C60" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="D60" t="s">
         <v>22</v>
@@ -21649,10 +21711,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="C61" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D61" t="s">
         <v>22</v>
@@ -21664,10 +21726,10 @@
     <row r="62">
       <c r="A62"/>
       <c r="B62" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="C62" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="D62" t="s">
         <v>22</v>
@@ -21710,13 +21772,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="B66" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="C66" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="D66" t="s">
         <v>22</v>
@@ -21728,10 +21790,10 @@
     <row r="67">
       <c r="A67"/>
       <c r="B67" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="C67" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="D67" t="s">
         <v>22</v>
@@ -21759,13 +21821,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B70" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="C70" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="D70" t="s">
         <v>22</v>
@@ -21777,10 +21839,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="C71" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="D71" t="s">
         <v>22</v>
@@ -21808,13 +21870,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="B74" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="C74" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="D74" t="s">
         <v>22</v>
@@ -21826,10 +21888,10 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="C75" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="D75" t="s">
         <v>22</v>
@@ -21841,10 +21903,10 @@
     <row r="76">
       <c r="A76"/>
       <c r="B76" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="C76" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="D76" t="s">
         <v>22</v>
@@ -21872,13 +21934,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B79" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="C79" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="D79" t="s">
         <v>22</v>
@@ -21905,10 +21967,10 @@
     <row r="81">
       <c r="A81"/>
       <c r="B81" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C81" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="D81" t="s">
         <v>22</v>
@@ -21920,10 +21982,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C82" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="D82" t="s">
         <v>22</v>
@@ -22001,10 +22063,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
@@ -22025,17 +22087,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -22049,17 +22111,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="F4"/>
       <c r="H4" s="15" t="s">
@@ -22071,17 +22133,17 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -22095,7 +22157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>12</v>
@@ -22104,10 +22166,10 @@
         <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="F6"/>
       <c r="H6" s="15" t="s">
@@ -22119,17 +22181,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>55</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -22143,7 +22205,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>72</v>
@@ -22153,7 +22215,7 @@
         <v>228</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -22167,7 +22229,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>12</v>
@@ -22176,10 +22238,10 @@
         <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="F9"/>
       <c r="H9" s="15" t="s">
@@ -22191,7 +22253,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>584</v>
@@ -22217,17 +22279,17 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -22241,7 +22303,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B12" s="15" t="s">
         <v>12</v>
@@ -22250,10 +22312,10 @@
         <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -22267,17 +22329,17 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="B13" s="15" t="s">
         <v>140</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -22291,17 +22353,17 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>140</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="F14"/>
       <c r="H14" s="15" t="s">
@@ -22313,7 +22375,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>12</v>
@@ -22322,10 +22384,10 @@
         <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="F15"/>
       <c r="H15" s="15" t="s">
@@ -22337,14 +22399,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>42</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="E16" s="15" t="s">
         <v>22</v>
@@ -23287,13 +23349,13 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="B82" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="C82" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="D82" t="s">
         <v>22</v>
@@ -23305,10 +23367,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="C83" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="D83" t="s">
         <v>22</v>
@@ -23320,10 +23382,10 @@
     <row r="84">
       <c r="A84"/>
       <c r="B84" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="C84" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="D84" t="s">
         <v>22</v>
@@ -23335,10 +23397,10 @@
     <row r="85">
       <c r="A85"/>
       <c r="B85" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="C85" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="D85" t="s">
         <v>22</v>
@@ -23350,10 +23412,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="C86" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="D86" t="s">
         <v>22</v>
@@ -23365,7 +23427,7 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="C87" t="s">
         <v>1003</v>
@@ -23380,10 +23442,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C88" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D88" t="s">
         <v>22</v>
@@ -23395,10 +23457,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="C89" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
@@ -23410,10 +23472,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="C90" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="D90" t="s">
         <v>22</v>
@@ -23425,10 +23487,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="C91" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="D91" t="s">
         <v>22</v>
@@ -23440,10 +23502,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="C92" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="D92" t="s">
         <v>22</v>
@@ -23455,10 +23517,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="C93" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="D93" t="s">
         <v>22</v>
@@ -23470,10 +23532,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="C94" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="D94" t="s">
         <v>22</v>
@@ -23485,10 +23547,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="C95" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="D95" t="s">
         <v>22</v>
@@ -23500,10 +23562,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="C96" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="D96" t="s">
         <v>22</v>
@@ -23515,10 +23577,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="C97" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="D97" t="s">
         <v>22</v>
@@ -23530,10 +23592,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="C98" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="D98" t="s">
         <v>22</v>
@@ -23545,10 +23607,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="C99" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="D99" t="s">
         <v>22</v>
@@ -23560,10 +23622,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="C100" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="D100" t="s">
         <v>22</v>
@@ -23606,13 +23668,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B104" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="C104" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="D104" t="s">
         <v>22</v>
@@ -23639,10 +23701,10 @@
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C106" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="D106" t="s">
         <v>22</v>
@@ -23654,10 +23716,10 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C107" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="D107" t="s">
         <v>22</v>
@@ -23733,10 +23795,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
@@ -23755,14 +23817,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>55</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>22</v>
@@ -23777,14 +23839,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>22</v>
@@ -23799,14 +23861,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>2167</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>2165</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -23821,14 +23883,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>22</v>
@@ -23843,14 +23905,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>22</v>
@@ -23865,14 +23927,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>22</v>
@@ -23887,14 +23949,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>22</v>
@@ -23909,14 +23971,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>22</v>
@@ -23931,14 +23993,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>22</v>
@@ -23953,14 +24015,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>22</v>
@@ -23975,14 +24037,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>22</v>
@@ -23997,14 +24059,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>22</v>
@@ -24019,14 +24081,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>22</v>
@@ -24041,14 +24103,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>22</v>
@@ -24063,14 +24125,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>22</v>
@@ -24085,14 +24147,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>22</v>
@@ -24107,14 +24169,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>22</v>
@@ -24129,14 +24191,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>22</v>
@@ -24151,14 +24213,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>22</v>
@@ -24173,14 +24235,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>22</v>
@@ -24195,14 +24257,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>22</v>
@@ -24234,13 +24296,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="B26" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C26" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
@@ -24252,10 +24314,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C27" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
@@ -24267,10 +24329,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="C28" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
@@ -24343,14 +24405,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="E2" s="17" t="s">
         <v>22</v>
@@ -24367,14 +24429,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>22</v>
@@ -24389,14 +24451,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>22</v>
@@ -24411,14 +24473,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="B5" s="17" t="s">
         <v>1561</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>22</v>
@@ -24433,17 +24495,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -24457,14 +24519,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>22</v>
@@ -24479,14 +24541,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>22</v>
@@ -24503,14 +24565,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>22</v>
@@ -24525,14 +24587,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>22</v>
@@ -24547,14 +24609,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>22</v>
@@ -24569,14 +24631,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>22</v>
@@ -24591,14 +24653,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>584</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>22</v>
@@ -24613,14 +24675,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>22</v>
@@ -24635,14 +24697,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>584</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>22</v>
@@ -24659,14 +24721,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>22</v>
@@ -24681,7 +24743,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>42</v>
@@ -24703,7 +24765,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>42</v>
@@ -24725,7 +24787,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>42</v>
@@ -24764,13 +24826,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="B22" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="C22" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
@@ -24782,10 +24844,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C23" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="D23" t="s">
         <v>22</v>
@@ -24797,10 +24859,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="C24" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -24812,10 +24874,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="C25" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -24843,13 +24905,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="B28" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="C28" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
@@ -24861,10 +24923,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="C29" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
@@ -24876,10 +24938,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C30" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="D30" t="s">
         <v>22</v>
@@ -24891,10 +24953,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="C31" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
@@ -24906,10 +24968,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="C32" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="D32" t="s">
         <v>22</v>
@@ -24921,10 +24983,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="C33" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="D33" t="s">
         <v>22</v>
@@ -24936,10 +24998,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="C34" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
@@ -24951,10 +25013,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="C35" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
@@ -24966,10 +25028,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="C36" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="D36" t="s">
         <v>22</v>
@@ -24981,10 +25043,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="C37" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="D37" t="s">
         <v>22</v>
@@ -24996,10 +25058,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="C38" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="D38" t="s">
         <v>22</v>
@@ -25011,10 +25073,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="C39" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="D39" t="s">
         <v>22</v>
@@ -25026,10 +25088,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="C40" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="D40" t="s">
         <v>22</v>
@@ -25041,10 +25103,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="C41" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="D41" t="s">
         <v>22</v>
@@ -25056,10 +25118,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="C42" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="D42" t="s">
         <v>22</v>
@@ -25071,10 +25133,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="C43" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="D43" t="s">
         <v>22</v>
@@ -25086,10 +25148,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="C44" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D44" t="s">
         <v>22</v>
@@ -25101,10 +25163,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="C45" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -25116,10 +25178,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="C46" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D46" t="s">
         <v>22</v>
@@ -25134,7 +25196,7 @@
         <v>179</v>
       </c>
       <c r="C47" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="D47" t="s">
         <v>22</v>
@@ -25146,10 +25208,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="C48" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="D48" t="s">
         <v>22</v>
@@ -25161,10 +25223,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="C49" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="D49" t="s">
         <v>22</v>
@@ -25176,10 +25238,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="C50" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="D50" t="s">
         <v>22</v>
@@ -25207,13 +25269,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="B53" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="C53" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="D53" t="s">
         <v>22</v>
@@ -25225,10 +25287,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="C54" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="D54" t="s">
         <v>22</v>
@@ -25240,10 +25302,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="C55" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D55" t="s">
         <v>22</v>
@@ -25271,13 +25333,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="B58" t="s">
         <v>837</v>
       </c>
       <c r="C58" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="D58" t="s">
         <v>22</v>
@@ -25292,7 +25354,7 @@
         <v>840</v>
       </c>
       <c r="C59" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="D59" t="s">
         <v>22</v>
@@ -25304,10 +25366,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="C60" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="D60" t="s">
         <v>22</v>
@@ -25319,10 +25381,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="C61" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="D61" t="s">
         <v>22</v>
@@ -25345,7 +25407,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L152"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -25398,21 +25460,19 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>2307</v>
+        <v>2211</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2308</v>
+        <v>22</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>2309</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F2"/>
       <c r="H2" s="18" t="s">
         <v>16</v>
       </c>
@@ -25422,19 +25482,21 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>2310</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>2311</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
+        <v>2311</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>2312</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3"/>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
       <c r="H3" s="18" t="s">
         <v>16</v>
       </c>
@@ -25451,7 +25513,7 @@
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>611</v>
+        <v>2315</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>22</v>
@@ -25466,14 +25528,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>55</v>
+        <v>2317</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2316</v>
+        <v>611</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>22</v>
@@ -25488,14 +25550,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="B6" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>22</v>
@@ -25510,14 +25572,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>2320</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>2321</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>22</v>
@@ -25532,14 +25594,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>22</v>
@@ -25554,14 +25616,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2319</v>
+        <v>151</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2320</v>
+        <v>152</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>22</v>
@@ -25576,21 +25638,19 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="B10" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>4</v>
+        <v>2323</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>2322</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="F10"/>
       <c r="H10" s="18" t="s">
         <v>16</v>
       </c>
@@ -25600,19 +25660,21 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>603</v>
+        <v>12</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2324</v>
+        <v>4</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11"/>
+        <v>2325</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
       <c r="H11" s="18" t="s">
         <v>16</v>
       </c>
@@ -25622,17 +25684,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1483</v>
+        <v>2326</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>55</v>
+        <v>603</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>2326</v>
+        <v>22</v>
       </c>
       <c r="F12"/>
       <c r="H12" s="18" t="s">
@@ -25644,17 +25706,17 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="F13"/>
       <c r="H13" s="18" t="s">
@@ -25666,21 +25728,19 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1809</v>
+        <v>1485</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>582</v>
+        <v>2330</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
+        <v>2331</v>
+      </c>
+      <c r="F14"/>
       <c r="H14" s="18" t="s">
         <v>16</v>
       </c>
@@ -25690,14 +25750,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>583</v>
+        <v>1811</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>584</v>
+        <v>55</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E15" s="18" t="s">
         <v>22</v>
@@ -25714,19 +25774,21 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2329</v>
+        <v>583</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>115</v>
+        <v>584</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>559</v>
+        <v>585</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F16"/>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
       <c r="H16" s="18" t="s">
         <v>16</v>
       </c>
@@ -25736,17 +25798,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1497</v>
+        <v>2332</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>1498</v>
+        <v>115</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>1499</v>
+        <v>559</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>2330</v>
+        <v>22</v>
       </c>
       <c r="F17"/>
       <c r="H17" s="18" t="s">
@@ -25758,17 +25820,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>22</v>
+        <v>2333</v>
       </c>
       <c r="F18"/>
       <c r="H18" s="18" t="s">
@@ -25780,14 +25842,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>12</v>
+        <v>1503</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="E19" s="18" t="s">
         <v>22</v>
@@ -25802,16 +25864,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C20" t="s">
-        <v>66</v>
-      </c>
+      <c r="C20"/>
       <c r="D20" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="E20" s="18" t="s">
         <v>22</v>
@@ -25826,7 +25886,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>12</v>
@@ -25835,7 +25895,7 @@
         <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="E21" s="18" t="s">
         <v>22</v>
@@ -25850,14 +25910,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="E22" s="18" t="s">
         <v>22</v>
@@ -25872,14 +25932,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
       <c r="E23" s="18" t="s">
         <v>22</v>
@@ -25894,14 +25954,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="E24" s="18" t="s">
         <v>22</v>
@@ -25916,14 +25976,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
       <c r="E25" s="18" t="s">
         <v>22</v>
@@ -25938,17 +25998,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
       <c r="F26"/>
       <c r="H26" s="18" t="s">
@@ -25960,17 +26020,17 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="E27" s="18" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
       <c r="F27"/>
       <c r="H27" s="18" t="s">
@@ -25982,17 +26042,17 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="B28" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="F28"/>
       <c r="H28" s="18" t="s">
@@ -26004,17 +26064,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="F29"/>
       <c r="H29" s="18" t="s">
@@ -26026,17 +26086,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="B30" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C30"/>
       <c r="D30" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="F30"/>
       <c r="H30" s="18" t="s">
@@ -26048,17 +26108,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C31"/>
       <c r="D31" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="F31"/>
       <c r="H31" s="18" t="s">
@@ -26070,17 +26130,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="B32" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="F32"/>
       <c r="H32" s="18" t="s">
@@ -26160,14 +26220,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
       <c r="B36" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
       <c r="E36" s="18" t="s">
         <v>22</v>
@@ -26246,62 +26306,76 @@
       <c r="J39"/>
       <c r="K39"/>
     </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>603</v>
+      </c>
+      <c r="C40"/>
+      <c r="D40" t="s">
+        <v>2368</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40"/>
+      <c r="H40" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+    </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C41"/>
+      <c r="D41" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41"/>
+      <c r="H41" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
         <v>1</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B43" t="s">
         <v>158</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C43" t="s">
         <v>3</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D43" t="s">
         <v>4</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E43" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>2307</v>
-      </c>
-      <c r="B42" t="s">
-        <v>2364</v>
-      </c>
-      <c r="C42" t="s">
-        <v>2365</v>
-      </c>
-      <c r="D42" t="s">
-        <v>22</v>
-      </c>
-      <c r="E42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43"/>
-      <c r="B43" t="s">
-        <v>2245</v>
-      </c>
-      <c r="C43" t="s">
-        <v>2246</v>
-      </c>
-      <c r="D43" t="s">
-        <v>22</v>
-      </c>
-      <c r="E43" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="44">
-      <c r="A44"/>
+      <c r="A44" t="s">
+        <v>2310</v>
+      </c>
       <c r="B44" t="s">
-        <v>2366</v>
+        <v>2372</v>
       </c>
       <c r="C44" t="s">
-        <v>2367</v>
+        <v>2373</v>
       </c>
       <c r="D44" t="s">
         <v>22</v>
@@ -26313,10 +26387,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>2368</v>
+        <v>2247</v>
       </c>
       <c r="C45" t="s">
-        <v>2369</v>
+        <v>2248</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -26328,10 +26402,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>1929</v>
+        <v>2374</v>
       </c>
       <c r="C46" t="s">
-        <v>1930</v>
+        <v>2375</v>
       </c>
       <c r="D46" t="s">
         <v>22</v>
@@ -26340,62 +26414,62 @@
         <v>22</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47"/>
+      <c r="B47" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C47" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" t="s">
+      <c r="A48"/>
+      <c r="B48" t="s">
+        <v>1931</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1932</v>
+      </c>
+      <c r="D48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
         <v>1</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B50" t="s">
         <v>158</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C50" t="s">
         <v>3</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" t="s">
         <v>4</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E50" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>2311</v>
-      </c>
-      <c r="B49" t="s">
-        <v>2298</v>
-      </c>
-      <c r="C49" t="s">
-        <v>2370</v>
-      </c>
-      <c r="D49" t="s">
-        <v>22</v>
-      </c>
-      <c r="E49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50"/>
-      <c r="B50" t="s">
-        <v>2371</v>
-      </c>
-      <c r="C50" t="s">
-        <v>2372</v>
-      </c>
-      <c r="D50" t="s">
-        <v>22</v>
-      </c>
-      <c r="E50" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="51">
-      <c r="A51"/>
+      <c r="A51" t="s">
+        <v>2314</v>
+      </c>
       <c r="B51" t="s">
-        <v>2294</v>
+        <v>2300</v>
       </c>
       <c r="C51" t="s">
-        <v>2373</v>
+        <v>2378</v>
       </c>
       <c r="D51" t="s">
         <v>22</v>
@@ -26407,217 +26481,217 @@
     <row r="52">
       <c r="A52"/>
       <c r="B52" t="s">
+        <v>2379</v>
+      </c>
+      <c r="C52" t="s">
+        <v>2380</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53"/>
+      <c r="B53" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54"/>
+      <c r="B54" t="s">
         <v>185</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C54" t="s">
         <v>186</v>
       </c>
-      <c r="D52" t="s">
-        <v>22</v>
-      </c>
-      <c r="E52" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
         <v>1</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B56" t="s">
         <v>158</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C56" t="s">
         <v>3</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D56" t="s">
         <v>4</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E56" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>2314</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="57">
+      <c r="A57" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B57" t="s">
         <v>837</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C57" t="s">
         <v>838</v>
       </c>
-      <c r="D55" t="s">
-        <v>22</v>
-      </c>
-      <c r="E55" t="s">
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" t="s">
         <v>839</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56"/>
-      <c r="B56" t="s">
-        <v>2374</v>
-      </c>
-      <c r="C56" t="s">
-        <v>2375</v>
-      </c>
-      <c r="D56" t="s">
-        <v>22</v>
-      </c>
-      <c r="E56" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57"/>
-      <c r="B57" t="s">
-        <v>840</v>
-      </c>
-      <c r="C57" t="s">
-        <v>841</v>
-      </c>
-      <c r="D57" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
+        <v>2382</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2383</v>
+      </c>
+      <c r="D58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59"/>
+      <c r="B59" t="s">
+        <v>840</v>
+      </c>
+      <c r="C59" t="s">
+        <v>841</v>
+      </c>
+      <c r="D59" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60"/>
+      <c r="B60" t="s">
         <v>843</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C60" t="s">
         <v>844</v>
       </c>
-      <c r="D58" t="s">
-        <v>22</v>
-      </c>
-      <c r="E58" t="s">
+      <c r="D60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="s">
+    <row r="62">
+      <c r="A62" t="s">
         <v>1</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B62" t="s">
         <v>158</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C62" t="s">
         <v>3</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D62" t="s">
         <v>4</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E62" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="s">
+    <row r="63">
+      <c r="A63" t="s">
         <v>603</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B63" t="s">
         <v>833</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C63" t="s">
         <v>834</v>
       </c>
-      <c r="D61" t="s">
-        <v>22</v>
-      </c>
-      <c r="E61" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62"/>
-      <c r="B62" t="s">
+      <c r="D63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64"/>
+      <c r="B64" t="s">
         <v>835</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C64" t="s">
         <v>836</v>
       </c>
-      <c r="D62" t="s">
-        <v>22</v>
-      </c>
-      <c r="E62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63"/>
-      <c r="B63" t="s">
+      <c r="D64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65"/>
+      <c r="B65" t="s">
         <v>185</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C65" t="s">
         <v>186</v>
       </c>
-      <c r="D63" t="s">
-        <v>22</v>
-      </c>
-      <c r="E63" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
+      <c r="D65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
         <v>1</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B67" t="s">
         <v>158</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C67" t="s">
         <v>3</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D67" t="s">
         <v>4</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E67" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="s">
+    <row r="68">
+      <c r="A68" t="s">
         <v>1498</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B68" t="s">
         <v>1620</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C68" t="s">
         <v>542</v>
-      </c>
-      <c r="D66" t="s">
-        <v>22</v>
-      </c>
-      <c r="E66" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67"/>
-      <c r="B67" t="s">
-        <v>1621</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1622</v>
-      </c>
-      <c r="D67" t="s">
-        <v>22</v>
-      </c>
-      <c r="E67" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68"/>
-      <c r="B68" t="s">
-        <v>548</v>
-      </c>
-      <c r="C68" t="s">
-        <v>549</v>
       </c>
       <c r="D68" t="s">
         <v>22</v>
@@ -26629,10 +26703,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="C69" t="s">
-        <v>1504</v>
+        <v>1622</v>
       </c>
       <c r="D69" t="s">
         <v>22</v>
@@ -26644,10 +26718,10 @@
     <row r="70">
       <c r="A70"/>
       <c r="B70" t="s">
-        <v>255</v>
+        <v>548</v>
       </c>
       <c r="C70" t="s">
-        <v>1624</v>
+        <v>549</v>
       </c>
       <c r="D70" t="s">
         <v>22</v>
@@ -26659,10 +26733,10 @@
     <row r="71">
       <c r="A71"/>
       <c r="B71" t="s">
-        <v>185</v>
+        <v>1623</v>
       </c>
       <c r="C71" t="s">
-        <v>186</v>
+        <v>1504</v>
       </c>
       <c r="D71" t="s">
         <v>22</v>
@@ -26674,89 +26748,89 @@
     <row r="72">
       <c r="A72"/>
       <c r="B72" t="s">
+        <v>255</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1624</v>
+      </c>
+      <c r="D72" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73"/>
+      <c r="B73" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D73" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74"/>
+      <c r="B74" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" t="s">
+        <v>186</v>
+      </c>
+      <c r="D74" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75"/>
+      <c r="B75" t="s">
         <v>179</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C75" t="s">
         <v>180</v>
       </c>
-      <c r="D72" t="s">
-        <v>22</v>
-      </c>
-      <c r="E72" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
+      <c r="D75" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
         <v>1</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B77" t="s">
         <v>158</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C77" t="s">
         <v>3</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D77" t="s">
         <v>4</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E77" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="s">
+    <row r="78">
+      <c r="A78" t="s">
         <v>1503</v>
       </c>
-      <c r="B75" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D75" t="s">
-        <v>22</v>
-      </c>
-      <c r="E75" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76"/>
-      <c r="B76" t="s">
+      <c r="B78" t="s">
         <v>1627</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C78" t="s">
         <v>1628</v>
-      </c>
-      <c r="D76" t="s">
-        <v>22</v>
-      </c>
-      <c r="E76" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77"/>
-      <c r="B77" t="s">
-        <v>1629</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1630</v>
-      </c>
-      <c r="D77" t="s">
-        <v>22</v>
-      </c>
-      <c r="E77" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78"/>
-      <c r="B78" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1632</v>
       </c>
       <c r="D78" t="s">
         <v>22</v>
@@ -26768,89 +26842,89 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
+        <v>1629</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80"/>
+      <c r="B80" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1632</v>
+      </c>
+      <c r="D80" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81"/>
+      <c r="B81" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D81" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82"/>
+      <c r="B82" t="s">
         <v>179</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C82" t="s">
         <v>180</v>
       </c>
-      <c r="D79" t="s">
-        <v>22</v>
-      </c>
-      <c r="E79" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
+      <c r="D82" t="s">
+        <v>22</v>
+      </c>
+      <c r="E82" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
         <v>1</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B84" t="s">
         <v>158</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C84" t="s">
         <v>3</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D84" t="s">
         <v>4</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E84" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>2334</v>
-      </c>
-      <c r="B82" t="s">
-        <v>2376</v>
-      </c>
-      <c r="C82" t="s">
-        <v>2377</v>
-      </c>
-      <c r="D82" t="s">
-        <v>22</v>
-      </c>
-      <c r="E82" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83"/>
-      <c r="B83" t="s">
-        <v>2378</v>
-      </c>
-      <c r="C83" t="s">
-        <v>2379</v>
-      </c>
-      <c r="D83" t="s">
-        <v>22</v>
-      </c>
-      <c r="E83" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84"/>
-      <c r="B84" t="s">
-        <v>2380</v>
-      </c>
-      <c r="C84" t="s">
-        <v>2381</v>
-      </c>
-      <c r="D84" t="s">
-        <v>22</v>
-      </c>
-      <c r="E84" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="85">
-      <c r="A85"/>
+      <c r="A85" t="s">
+        <v>2337</v>
+      </c>
       <c r="B85" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="C85" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="D85" t="s">
         <v>22</v>
@@ -26862,10 +26936,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="C86" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="D86" t="s">
         <v>22</v>
@@ -26874,77 +26948,77 @@
         <v>22</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87"/>
+      <c r="B87" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D87" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="88">
-      <c r="A88" t="s">
+      <c r="A88"/>
+      <c r="B88" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D88" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89"/>
+      <c r="B89" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2393</v>
+      </c>
+      <c r="D89" t="s">
+        <v>22</v>
+      </c>
+      <c r="E89" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
         <v>1</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B91" t="s">
         <v>158</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C91" t="s">
         <v>3</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D91" t="s">
         <v>4</v>
       </c>
-      <c r="E88" t="s">
+      <c r="E91" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>2337</v>
-      </c>
-      <c r="B89" t="s">
-        <v>2386</v>
-      </c>
-      <c r="C89" t="s">
-        <v>2387</v>
-      </c>
-      <c r="D89" t="s">
-        <v>22</v>
-      </c>
-      <c r="E89" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90"/>
-      <c r="B90" t="s">
-        <v>2388</v>
-      </c>
-      <c r="C90" t="s">
-        <v>2389</v>
-      </c>
-      <c r="D90" t="s">
-        <v>22</v>
-      </c>
-      <c r="E90" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91"/>
-      <c r="B91" t="s">
-        <v>2390</v>
-      </c>
-      <c r="C91" t="s">
-        <v>2391</v>
-      </c>
-      <c r="D91" t="s">
-        <v>22</v>
-      </c>
-      <c r="E91" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="92">
-      <c r="A92"/>
+      <c r="A92" t="s">
+        <v>2340</v>
+      </c>
       <c r="B92" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="C92" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="D92" t="s">
         <v>22</v>
@@ -26956,10 +27030,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="C93" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="D93" t="s">
         <v>22</v>
@@ -26971,179 +27045,179 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D94" t="s">
+        <v>22</v>
+      </c>
+      <c r="E94" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95"/>
+      <c r="B95" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2401</v>
+      </c>
+      <c r="D95" t="s">
+        <v>22</v>
+      </c>
+      <c r="E95" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96"/>
+      <c r="B96" t="s">
+        <v>2402</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D96" t="s">
+        <v>22</v>
+      </c>
+      <c r="E96" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97"/>
+      <c r="B97" t="s">
         <v>179</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C97" t="s">
         <v>180</v>
       </c>
-      <c r="D94" t="s">
-        <v>22</v>
-      </c>
-      <c r="E94" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
+      <c r="D97" t="s">
+        <v>22</v>
+      </c>
+      <c r="E97" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
         <v>1</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B99" t="s">
         <v>158</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C99" t="s">
         <v>3</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D99" t="s">
         <v>4</v>
       </c>
-      <c r="E96" t="s">
+      <c r="E99" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="s">
+    <row r="100">
+      <c r="A100" t="s">
         <v>91</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B100" t="s">
         <v>285</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C100" t="s">
         <v>286</v>
       </c>
-      <c r="D97" t="s">
-        <v>22</v>
-      </c>
-      <c r="E97" t="s">
+      <c r="D100" t="s">
+        <v>22</v>
+      </c>
+      <c r="E100" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98"/>
-      <c r="B98" t="s">
-        <v>287</v>
-      </c>
-      <c r="C98" t="s">
-        <v>288</v>
-      </c>
-      <c r="D98" t="s">
-        <v>22</v>
-      </c>
-      <c r="E98" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99"/>
-      <c r="B99" t="s">
-        <v>289</v>
-      </c>
-      <c r="C99" t="s">
-        <v>290</v>
-      </c>
-      <c r="D99" t="s">
-        <v>22</v>
-      </c>
-      <c r="E99" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100"/>
-      <c r="B100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C100" t="s">
-        <v>292</v>
-      </c>
-      <c r="D100" t="s">
-        <v>22</v>
-      </c>
-      <c r="E100" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C101" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D101" t="s">
         <v>22</v>
       </c>
       <c r="E101" t="s">
-        <v>296</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C102" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D102" t="s">
         <v>22</v>
       </c>
       <c r="E102" t="s">
-        <v>297</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C103" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="D103" t="s">
         <v>22</v>
       </c>
       <c r="E103" t="s">
-        <v>22</v>
+        <v>293</v>
       </c>
     </row>
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C104" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D104" t="s">
         <v>22</v>
       </c>
       <c r="E104" t="s">
-        <v>22</v>
+        <v>296</v>
       </c>
     </row>
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C105" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="D105" t="s">
         <v>22</v>
       </c>
       <c r="E105" t="s">
-        <v>22</v>
+        <v>297</v>
       </c>
     </row>
     <row r="106">
       <c r="A106"/>
       <c r="B106" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C106" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="D106" t="s">
         <v>22</v>
@@ -27155,25 +27229,25 @@
     <row r="107">
       <c r="A107"/>
       <c r="B107" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C107" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D107" t="s">
         <v>22</v>
       </c>
       <c r="E107" t="s">
-        <v>309</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
       <c r="A108"/>
       <c r="B108" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C108" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D108" t="s">
         <v>22</v>
@@ -27185,40 +27259,40 @@
     <row r="109">
       <c r="A109"/>
       <c r="B109" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="C109" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D109" t="s">
         <v>22</v>
       </c>
       <c r="E109" t="s">
-        <v>314</v>
+        <v>22</v>
       </c>
     </row>
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="C110" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D110" t="s">
         <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="C111" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D111" t="s">
         <v>22</v>
@@ -27230,40 +27304,40 @@
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C112" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="D112" t="s">
         <v>22</v>
       </c>
       <c r="E112" t="s">
-        <v>22</v>
+        <v>314</v>
       </c>
     </row>
     <row r="113">
       <c r="A113"/>
       <c r="B113" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="C113" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="D113" t="s">
         <v>22</v>
       </c>
       <c r="E113" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="114">
       <c r="A114"/>
       <c r="B114" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C114" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="D114" t="s">
         <v>22</v>
@@ -27275,10 +27349,10 @@
     <row r="115">
       <c r="A115"/>
       <c r="B115" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="C115" t="s">
-        <v>142</v>
+        <v>321</v>
       </c>
       <c r="D115" t="s">
         <v>22</v>
@@ -27290,25 +27364,25 @@
     <row r="116">
       <c r="A116"/>
       <c r="B116" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="C116" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="D116" t="s">
         <v>22</v>
       </c>
       <c r="E116" t="s">
-        <v>22</v>
+        <v>324</v>
       </c>
     </row>
     <row r="117">
       <c r="A117"/>
       <c r="B117" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C117" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D117" t="s">
         <v>22</v>
@@ -27320,10 +27394,10 @@
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C118" t="s">
-        <v>333</v>
+        <v>142</v>
       </c>
       <c r="D118" t="s">
         <v>22</v>
@@ -27335,10 +27409,10 @@
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C119" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D119" t="s">
         <v>22</v>
@@ -27350,10 +27424,10 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="C120" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="D120" t="s">
         <v>22</v>
@@ -27365,10 +27439,10 @@
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C121" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D121" t="s">
         <v>22</v>
@@ -27380,10 +27454,10 @@
     <row r="122">
       <c r="A122"/>
       <c r="B122" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="C122" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D122" t="s">
         <v>22</v>
@@ -27395,10 +27469,10 @@
     <row r="123">
       <c r="A123"/>
       <c r="B123" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C123" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D123" t="s">
         <v>22</v>
@@ -27410,10 +27484,10 @@
     <row r="124">
       <c r="A124"/>
       <c r="B124" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C124" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D124" t="s">
         <v>22</v>
@@ -27425,10 +27499,10 @@
     <row r="125">
       <c r="A125"/>
       <c r="B125" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C125" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D125" t="s">
         <v>22</v>
@@ -27440,10 +27514,10 @@
     <row r="126">
       <c r="A126"/>
       <c r="B126" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C126" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D126" t="s">
         <v>22</v>
@@ -27455,10 +27529,10 @@
     <row r="127">
       <c r="A127"/>
       <c r="B127" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C127" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D127" t="s">
         <v>22</v>
@@ -27470,10 +27544,10 @@
     <row r="128">
       <c r="A128"/>
       <c r="B128" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C128" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D128" t="s">
         <v>22</v>
@@ -27485,10 +27559,10 @@
     <row r="129">
       <c r="A129"/>
       <c r="B129" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C129" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D129" t="s">
         <v>22</v>
@@ -27500,10 +27574,10 @@
     <row r="130">
       <c r="A130"/>
       <c r="B130" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="C130" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D130" t="s">
         <v>22</v>
@@ -27515,10 +27589,10 @@
     <row r="131">
       <c r="A131"/>
       <c r="B131" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="C131" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D131" t="s">
         <v>22</v>
@@ -27530,10 +27604,10 @@
     <row r="132">
       <c r="A132"/>
       <c r="B132" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C132" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D132" t="s">
         <v>22</v>
@@ -27545,10 +27619,10 @@
     <row r="133">
       <c r="A133"/>
       <c r="B133" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C133" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D133" t="s">
         <v>22</v>
@@ -27560,10 +27634,10 @@
     <row r="134">
       <c r="A134"/>
       <c r="B134" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C134" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D134" t="s">
         <v>22</v>
@@ -27575,10 +27649,10 @@
     <row r="135">
       <c r="A135"/>
       <c r="B135" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="C135" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D135" t="s">
         <v>22</v>
@@ -27590,10 +27664,10 @@
     <row r="136">
       <c r="A136"/>
       <c r="B136" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="C136" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="D136" t="s">
         <v>22</v>
@@ -27605,10 +27679,10 @@
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C137" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D137" t="s">
         <v>22</v>
@@ -27620,10 +27694,10 @@
     <row r="138">
       <c r="A138"/>
       <c r="B138" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C138" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="D138" t="s">
         <v>22</v>
@@ -27635,10 +27709,10 @@
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C139" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="D139" t="s">
         <v>22</v>
@@ -27650,10 +27724,10 @@
     <row r="140">
       <c r="A140"/>
       <c r="B140" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C140" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="D140" t="s">
         <v>22</v>
@@ -27665,10 +27739,10 @@
     <row r="141">
       <c r="A141"/>
       <c r="B141" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C141" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="D141" t="s">
         <v>22</v>
@@ -27680,10 +27754,10 @@
     <row r="142">
       <c r="A142"/>
       <c r="B142" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C142" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="D142" t="s">
         <v>22</v>
@@ -27695,10 +27769,10 @@
     <row r="143">
       <c r="A143"/>
       <c r="B143" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C143" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D143" t="s">
         <v>22</v>
@@ -27710,40 +27784,40 @@
     <row r="144">
       <c r="A144"/>
       <c r="B144" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C144" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D144" t="s">
         <v>22</v>
       </c>
       <c r="E144" t="s">
-        <v>385</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145">
       <c r="A145"/>
       <c r="B145" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="C145" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="D145" t="s">
         <v>22</v>
       </c>
       <c r="E145" t="s">
-        <v>388</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146">
       <c r="A146"/>
       <c r="B146" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C146" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="D146" t="s">
         <v>22</v>
@@ -27755,40 +27829,40 @@
     <row r="147">
       <c r="A147"/>
       <c r="B147" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C147" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D147" t="s">
         <v>22</v>
       </c>
       <c r="E147" t="s">
-        <v>22</v>
+        <v>385</v>
       </c>
     </row>
     <row r="148">
       <c r="A148"/>
       <c r="B148" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="C148" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D148" t="s">
         <v>22</v>
       </c>
       <c r="E148" t="s">
-        <v>22</v>
+        <v>388</v>
       </c>
     </row>
     <row r="149">
       <c r="A149"/>
       <c r="B149" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C149" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D149" t="s">
         <v>22</v>
@@ -27800,10 +27874,10 @@
     <row r="150">
       <c r="A150"/>
       <c r="B150" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C150" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D150" t="s">
         <v>22</v>
@@ -27815,31 +27889,185 @@
     <row r="151">
       <c r="A151"/>
       <c r="B151" t="s">
-        <v>179</v>
+        <v>393</v>
       </c>
       <c r="C151" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D151" t="s">
         <v>22</v>
       </c>
       <c r="E151" t="s">
-        <v>180</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152">
       <c r="A152"/>
       <c r="B152" t="s">
+        <v>395</v>
+      </c>
+      <c r="C152" t="s">
+        <v>396</v>
+      </c>
+      <c r="D152" t="s">
+        <v>22</v>
+      </c>
+      <c r="E152" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153"/>
+      <c r="B153" t="s">
+        <v>397</v>
+      </c>
+      <c r="C153" t="s">
+        <v>398</v>
+      </c>
+      <c r="D153" t="s">
+        <v>22</v>
+      </c>
+      <c r="E153" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154"/>
+      <c r="B154" t="s">
+        <v>179</v>
+      </c>
+      <c r="C154" t="s">
+        <v>399</v>
+      </c>
+      <c r="D154" t="s">
+        <v>22</v>
+      </c>
+      <c r="E154" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155"/>
+      <c r="B155" t="s">
         <v>400</v>
       </c>
-      <c r="C152" t="s">
+      <c r="C155" t="s">
         <v>401</v>
       </c>
-      <c r="D152" t="s">
-        <v>22</v>
-      </c>
-      <c r="E152" t="s">
+      <c r="D155" t="s">
+        <v>22</v>
+      </c>
+      <c r="E155" t="s">
         <v>402</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>1</v>
+      </c>
+      <c r="B157" t="s">
+        <v>158</v>
+      </c>
+      <c r="C157" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" t="s">
+        <v>4</v>
+      </c>
+      <c r="E157" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B158" t="s">
+        <v>2404</v>
+      </c>
+      <c r="C158" t="s">
+        <v>2405</v>
+      </c>
+      <c r="D158" t="s">
+        <v>22</v>
+      </c>
+      <c r="E158" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159"/>
+      <c r="B159" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C159" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D159" t="s">
+        <v>22</v>
+      </c>
+      <c r="E159" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160"/>
+      <c r="B160" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C160" t="s">
+        <v>2407</v>
+      </c>
+      <c r="D160" t="s">
+        <v>22</v>
+      </c>
+      <c r="E160" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161"/>
+      <c r="B161" t="s">
+        <v>2408</v>
+      </c>
+      <c r="C161" t="s">
+        <v>2409</v>
+      </c>
+      <c r="D161" t="s">
+        <v>22</v>
+      </c>
+      <c r="E161" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162"/>
+      <c r="B162" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C162" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D162" t="s">
+        <v>22</v>
+      </c>
+      <c r="E162" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163"/>
+      <c r="B163" t="s">
+        <v>185</v>
+      </c>
+      <c r="C163" t="s">
+        <v>186</v>
+      </c>
+      <c r="D163" t="s">
+        <v>22</v>
+      </c>
+      <c r="E163" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -27855,6 +28083,7 @@
     <tablePart r:id="rId8"/>
     <tablePart r:id="rId9"/>
     <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
@@ -27936,14 +28165,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="E3" s="19" t="s">
         <v>22</v>
@@ -27963,11 +28192,11 @@
         <v>575</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>2396</v>
+        <v>2412</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2396</v>
+        <v>2412</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>22</v>
@@ -27984,7 +28213,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2397</v>
+        <v>2413</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>12</v>
@@ -27993,7 +28222,7 @@
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>2398</v>
+        <v>2414</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>22</v>
@@ -28008,10 +28237,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
@@ -29496,14 +29725,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2399</v>
+        <v>2415</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2400</v>
+        <v>2416</v>
       </c>
       <c r="E2" s="20" t="s">
         <v>22</v>
@@ -29613,7 +29842,7 @@
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2401</v>
+        <v>2417</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>22</v>
@@ -29635,7 +29864,7 @@
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2402</v>
+        <v>2418</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>22</v>
@@ -29650,7 +29879,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2403</v>
+        <v>2419</v>
       </c>
       <c r="B9" s="20" t="s">
         <v>69</v>
@@ -29672,14 +29901,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2404</v>
+        <v>2420</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>140</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>2405</v>
+        <v>2421</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>22</v>
@@ -29694,14 +29923,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2406</v>
+        <v>2422</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>140</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2407</v>
+        <v>2423</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>22</v>
@@ -30434,14 +30663,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2408</v>
+        <v>2424</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2409</v>
+        <v>2425</v>
       </c>
       <c r="E2" s="21" t="s">
         <v>22</v>
@@ -30478,14 +30707,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2410</v>
+        <v>2426</v>
       </c>
       <c r="B4" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2411</v>
+        <v>2427</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>22</v>
@@ -30500,14 +30729,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2412</v>
+        <v>2428</v>
       </c>
       <c r="B5" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2413</v>
+        <v>2429</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>22</v>
@@ -30522,14 +30751,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2406</v>
+        <v>2422</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>140</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2407</v>
+        <v>2423</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>22</v>
@@ -30605,14 +30834,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2399</v>
+        <v>2415</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2400</v>
+        <v>2416</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>22</v>
@@ -30627,14 +30856,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2414</v>
+        <v>2430</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2415</v>
+        <v>2431</v>
       </c>
       <c r="E3" s="22" t="s">
         <v>22</v>
@@ -30649,14 +30878,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2416</v>
+        <v>2432</v>
       </c>
       <c r="B4" s="22" t="s">
         <v>42</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2417</v>
+        <v>2433</v>
       </c>
       <c r="E4" s="22" t="s">
         <v>22</v>
@@ -30671,14 +30900,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2406</v>
+        <v>2422</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>140</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2407</v>
+        <v>2423</v>
       </c>
       <c r="E5" s="22" t="s">
         <v>22</v>
@@ -30715,10 +30944,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2418</v>
+        <v>2434</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>2419</v>
+        <v>2435</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
@@ -30798,14 +31027,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2399</v>
+        <v>2415</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2400</v>
+        <v>2416</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>22</v>
@@ -30820,14 +31049,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2414</v>
+        <v>2430</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2415</v>
+        <v>2431</v>
       </c>
       <c r="E3" s="23" t="s">
         <v>22</v>
@@ -30842,14 +31071,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2416</v>
+        <v>2432</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2417</v>
+        <v>2433</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>22</v>
@@ -30886,14 +31115,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2406</v>
+        <v>2422</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>140</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2407</v>
+        <v>2423</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>22</v>
@@ -30991,14 +31220,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2399</v>
+        <v>2415</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2400</v>
+        <v>2416</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>22</v>
@@ -31057,14 +31286,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2406</v>
+        <v>2422</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>140</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2407</v>
+        <v>2423</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>22</v>
@@ -31162,14 +31391,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2420</v>
+        <v>2436</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>140</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2421</v>
+        <v>2437</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>22</v>
@@ -31184,14 +31413,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2422</v>
+        <v>2438</v>
       </c>
       <c r="B3" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2423</v>
+        <v>2439</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>22</v>
@@ -31250,14 +31479,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2424</v>
+        <v>2440</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>22</v>
@@ -31301,7 +31530,7 @@
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2425</v>
+        <v>2441</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>22</v>
@@ -31316,12 +31545,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2426</v>
+        <v>2442</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2427</v>
+        <v>2443</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>22</v>
@@ -31424,7 +31653,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2428</v>
+        <v>2444</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>72</v>
@@ -31453,7 +31682,7 @@
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2429</v>
+        <v>2445</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>22</v>
@@ -31468,14 +31697,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2430</v>
+        <v>2446</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>584</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2431</v>
+        <v>2447</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>22</v>
@@ -31490,17 +31719,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2432</v>
+        <v>2448</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>91</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>2433</v>
+        <v>2449</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>2434</v>
+        <v>2450</v>
       </c>
       <c r="F17"/>
       <c r="H17" s="25" t="s">
@@ -31512,10 +31741,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2435</v>
+        <v>2451</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>2436</v>
+        <v>2452</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
@@ -31534,14 +31763,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2437</v>
+        <v>2453</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>140</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>2438</v>
+        <v>2454</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>22</v>
@@ -32484,13 +32713,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>2436</v>
+        <v>2452</v>
       </c>
       <c r="B85" t="s">
-        <v>2439</v>
+        <v>2455</v>
       </c>
       <c r="C85" t="s">
-        <v>2440</v>
+        <v>2456</v>
       </c>
       <c r="D85" t="s">
         <v>22</v>
@@ -32502,10 +32731,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>2441</v>
+        <v>2457</v>
       </c>
       <c r="C86" t="s">
-        <v>2442</v>
+        <v>2458</v>
       </c>
       <c r="D86" t="s">
         <v>22</v>
@@ -32517,10 +32746,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>2443</v>
+        <v>2459</v>
       </c>
       <c r="C87" t="s">
-        <v>2444</v>
+        <v>2460</v>
       </c>
       <c r="D87" t="s">
         <v>22</v>
@@ -32532,10 +32761,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>2445</v>
+        <v>2461</v>
       </c>
       <c r="C88" t="s">
-        <v>2446</v>
+        <v>2462</v>
       </c>
       <c r="D88" t="s">
         <v>22</v>
@@ -32547,10 +32776,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>2447</v>
+        <v>2463</v>
       </c>
       <c r="C89" t="s">
-        <v>2448</v>
+        <v>2464</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
@@ -32562,10 +32791,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>2449</v>
+        <v>2465</v>
       </c>
       <c r="C90" t="s">
-        <v>2450</v>
+        <v>2466</v>
       </c>
       <c r="D90" t="s">
         <v>22</v>
@@ -32577,10 +32806,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>2451</v>
+        <v>2467</v>
       </c>
       <c r="C91" t="s">
-        <v>2452</v>
+        <v>2468</v>
       </c>
       <c r="D91" t="s">
         <v>22</v>
@@ -32592,10 +32821,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>2453</v>
+        <v>2469</v>
       </c>
       <c r="C92" t="s">
-        <v>2454</v>
+        <v>2470</v>
       </c>
       <c r="D92" t="s">
         <v>22</v>
@@ -32607,10 +32836,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>2455</v>
+        <v>2471</v>
       </c>
       <c r="C93" t="s">
-        <v>2456</v>
+        <v>2472</v>
       </c>
       <c r="D93" t="s">
         <v>22</v>
@@ -32622,10 +32851,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>2457</v>
+        <v>2473</v>
       </c>
       <c r="C94" t="s">
-        <v>2458</v>
+        <v>2474</v>
       </c>
       <c r="D94" t="s">
         <v>22</v>
@@ -32637,10 +32866,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>2459</v>
+        <v>2475</v>
       </c>
       <c r="C95" t="s">
-        <v>2460</v>
+        <v>2476</v>
       </c>
       <c r="D95" t="s">
         <v>22</v>
@@ -32652,10 +32881,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>2461</v>
+        <v>2477</v>
       </c>
       <c r="C96" t="s">
-        <v>2462</v>
+        <v>2478</v>
       </c>
       <c r="D96" t="s">
         <v>22</v>
@@ -32667,10 +32896,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>2463</v>
+        <v>2479</v>
       </c>
       <c r="C97" t="s">
-        <v>2464</v>
+        <v>2480</v>
       </c>
       <c r="D97" t="s">
         <v>22</v>
@@ -32697,12 +32926,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2465</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2466</v>
+        <v>2482</v>
       </c>
     </row>
   </sheetData>
@@ -44123,7 +44352,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L140"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -45685,10 +45914,10 @@
     <row r="79">
       <c r="A79"/>
       <c r="B79" t="s">
-        <v>185</v>
+        <v>1625</v>
       </c>
       <c r="C79" t="s">
-        <v>186</v>
+        <v>1626</v>
       </c>
       <c r="D79" t="s">
         <v>22</v>
@@ -45700,54 +45929,54 @@
     <row r="80">
       <c r="A80"/>
       <c r="B80" t="s">
+        <v>185</v>
+      </c>
+      <c r="C80" t="s">
+        <v>186</v>
+      </c>
+      <c r="D80" t="s">
+        <v>22</v>
+      </c>
+      <c r="E80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81"/>
+      <c r="B81" t="s">
         <v>179</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C81" t="s">
         <v>180</v>
       </c>
-      <c r="D80" t="s">
-        <v>22</v>
-      </c>
-      <c r="E80" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>1</v>
-      </c>
-      <c r="B82" t="s">
-        <v>158</v>
-      </c>
-      <c r="C82" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" t="s">
-        <v>4</v>
-      </c>
-      <c r="E82" t="s">
-        <v>168</v>
+      <c r="D81" t="s">
+        <v>22</v>
+      </c>
+      <c r="E81" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
+        <v>1</v>
+      </c>
+      <c r="B83" t="s">
+        <v>158</v>
+      </c>
+      <c r="C83" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>4</v>
+      </c>
+      <c r="E83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
         <v>1503</v>
       </c>
-      <c r="B83" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1626</v>
-      </c>
-      <c r="D83" t="s">
-        <v>22</v>
-      </c>
-      <c r="E83" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84"/>
       <c r="B84" t="s">
         <v>1627</v>
       </c>
@@ -45794,59 +46023,59 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D87" t="s">
+        <v>22</v>
+      </c>
+      <c r="E87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88"/>
+      <c r="B88" t="s">
         <v>179</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C88" t="s">
         <v>180</v>
       </c>
-      <c r="D87" t="s">
-        <v>22</v>
-      </c>
-      <c r="E87" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>1</v>
-      </c>
-      <c r="B89" t="s">
-        <v>158</v>
-      </c>
-      <c r="C89" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" t="s">
-        <v>4</v>
-      </c>
-      <c r="E89" t="s">
-        <v>168</v>
+      <c r="D88" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90" t="s">
+        <v>158</v>
+      </c>
+      <c r="C90" t="s">
+        <v>3</v>
+      </c>
+      <c r="D90" t="s">
+        <v>4</v>
+      </c>
+      <c r="E90" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
         <v>603</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>833</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" t="s">
         <v>834</v>
-      </c>
-      <c r="D90" t="s">
-        <v>22</v>
-      </c>
-      <c r="E90" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91"/>
-      <c r="B91" t="s">
-        <v>835</v>
-      </c>
-      <c r="C91" t="s">
-        <v>836</v>
       </c>
       <c r="D91" t="s">
         <v>22</v>
@@ -45858,59 +46087,59 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
+        <v>835</v>
+      </c>
+      <c r="C92" t="s">
+        <v>836</v>
+      </c>
+      <c r="D92" t="s">
+        <v>22</v>
+      </c>
+      <c r="E92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93"/>
+      <c r="B93" t="s">
         <v>185</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C93" t="s">
         <v>186</v>
       </c>
-      <c r="D92" t="s">
-        <v>22</v>
-      </c>
-      <c r="E92" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>1</v>
-      </c>
-      <c r="B94" t="s">
-        <v>158</v>
-      </c>
-      <c r="C94" t="s">
-        <v>3</v>
-      </c>
-      <c r="D94" t="s">
-        <v>4</v>
-      </c>
-      <c r="E94" t="s">
-        <v>168</v>
+      <c r="D93" t="s">
+        <v>22</v>
+      </c>
+      <c r="E93" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
+        <v>1</v>
+      </c>
+      <c r="B95" t="s">
+        <v>158</v>
+      </c>
+      <c r="C95" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" t="s">
+        <v>4</v>
+      </c>
+      <c r="E95" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
         <v>1543</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>275</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C96" t="s">
         <v>276</v>
-      </c>
-      <c r="D95" t="s">
-        <v>22</v>
-      </c>
-      <c r="E95" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96"/>
-      <c r="B96" t="s">
-        <v>277</v>
-      </c>
-      <c r="C96" t="s">
-        <v>278</v>
       </c>
       <c r="D96" t="s">
         <v>22</v>
@@ -45922,10 +46151,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>1633</v>
+        <v>277</v>
       </c>
       <c r="C97" t="s">
-        <v>1634</v>
+        <v>278</v>
       </c>
       <c r="D97" t="s">
         <v>22</v>
@@ -45937,54 +46166,54 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
+        <v>1635</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1636</v>
+      </c>
+      <c r="D98" t="s">
+        <v>22</v>
+      </c>
+      <c r="E98" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99"/>
+      <c r="B99" t="s">
         <v>185</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C99" t="s">
         <v>186</v>
       </c>
-      <c r="D98" t="s">
-        <v>22</v>
-      </c>
-      <c r="E98" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>1</v>
-      </c>
-      <c r="B100" t="s">
-        <v>158</v>
-      </c>
-      <c r="C100" t="s">
-        <v>3</v>
-      </c>
-      <c r="D100" t="s">
-        <v>4</v>
-      </c>
-      <c r="E100" t="s">
-        <v>168</v>
+      <c r="D99" t="s">
+        <v>22</v>
+      </c>
+      <c r="E99" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
+        <v>1</v>
+      </c>
+      <c r="B101" t="s">
+        <v>158</v>
+      </c>
+      <c r="C101" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" t="s">
+        <v>4</v>
+      </c>
+      <c r="E101" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
         <v>1548</v>
       </c>
-      <c r="B101" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C101" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D101" t="s">
-        <v>22</v>
-      </c>
-      <c r="E101" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102"/>
       <c r="B102" t="s">
         <v>1637</v>
       </c>
@@ -46031,54 +46260,54 @@
     <row r="105">
       <c r="A105"/>
       <c r="B105" t="s">
+        <v>1643</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1644</v>
+      </c>
+      <c r="D105" t="s">
+        <v>22</v>
+      </c>
+      <c r="E105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106"/>
+      <c r="B106" t="s">
         <v>179</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C106" t="s">
         <v>180</v>
       </c>
-      <c r="D105" t="s">
-        <v>22</v>
-      </c>
-      <c r="E105" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>1</v>
-      </c>
-      <c r="B107" t="s">
-        <v>158</v>
-      </c>
-      <c r="C107" t="s">
-        <v>3</v>
-      </c>
-      <c r="D107" t="s">
-        <v>4</v>
-      </c>
-      <c r="E107" t="s">
-        <v>168</v>
+      <c r="D106" t="s">
+        <v>22</v>
+      </c>
+      <c r="E106" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>158</v>
+      </c>
+      <c r="C108" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" t="s">
+        <v>4</v>
+      </c>
+      <c r="E108" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
         <v>1556</v>
       </c>
-      <c r="B108" t="s">
-        <v>1643</v>
-      </c>
-      <c r="C108" t="s">
-        <v>1644</v>
-      </c>
-      <c r="D108" t="s">
-        <v>22</v>
-      </c>
-      <c r="E108" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109"/>
       <c r="B109" t="s">
         <v>1645</v>
       </c>
@@ -46125,54 +46354,54 @@
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D112" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113"/>
+      <c r="B113" t="s">
         <v>179</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C113" t="s">
         <v>180</v>
       </c>
-      <c r="D112" t="s">
-        <v>22</v>
-      </c>
-      <c r="E112" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>1</v>
-      </c>
-      <c r="B114" t="s">
-        <v>158</v>
-      </c>
-      <c r="C114" t="s">
-        <v>3</v>
-      </c>
-      <c r="D114" t="s">
-        <v>4</v>
-      </c>
-      <c r="E114" t="s">
-        <v>168</v>
+      <c r="D113" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>158</v>
+      </c>
+      <c r="C115" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>4</v>
+      </c>
+      <c r="E115" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
         <v>1570</v>
       </c>
-      <c r="B115" t="s">
-        <v>1651</v>
-      </c>
-      <c r="C115" t="s">
-        <v>1652</v>
-      </c>
-      <c r="D115" t="s">
-        <v>22</v>
-      </c>
-      <c r="E115" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116"/>
       <c r="B116" t="s">
         <v>1653</v>
       </c>
@@ -46204,103 +46433,103 @@
     <row r="118">
       <c r="A118"/>
       <c r="B118" t="s">
+        <v>1657</v>
+      </c>
+      <c r="C118" t="s">
+        <v>1658</v>
+      </c>
+      <c r="D118" t="s">
+        <v>22</v>
+      </c>
+      <c r="E118" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119"/>
+      <c r="B119" t="s">
         <v>179</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C119" t="s">
         <v>180</v>
       </c>
-      <c r="D118" t="s">
-        <v>22</v>
-      </c>
-      <c r="E118" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>1</v>
-      </c>
-      <c r="B120" t="s">
-        <v>158</v>
-      </c>
-      <c r="C120" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" t="s">
-        <v>4</v>
-      </c>
-      <c r="E120" t="s">
-        <v>168</v>
+      <c r="D119" t="s">
+        <v>22</v>
+      </c>
+      <c r="E119" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
+        <v>1</v>
+      </c>
+      <c r="B121" t="s">
+        <v>158</v>
+      </c>
+      <c r="C121" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" t="s">
+        <v>4</v>
+      </c>
+      <c r="E121" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
         <v>1575</v>
       </c>
-      <c r="B121" t="s">
-        <v>1657</v>
-      </c>
-      <c r="C121" t="s">
-        <v>1658</v>
-      </c>
-      <c r="D121" t="s">
-        <v>22</v>
-      </c>
-      <c r="E121" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122"/>
       <c r="B122" t="s">
+        <v>1659</v>
+      </c>
+      <c r="C122" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D122" t="s">
+        <v>22</v>
+      </c>
+      <c r="E122" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123"/>
+      <c r="B123" t="s">
         <v>179</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C123" t="s">
         <v>180</v>
       </c>
-      <c r="D122" t="s">
-        <v>22</v>
-      </c>
-      <c r="E122" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>1</v>
-      </c>
-      <c r="B124" t="s">
-        <v>158</v>
-      </c>
-      <c r="C124" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" t="s">
-        <v>4</v>
-      </c>
-      <c r="E124" t="s">
-        <v>168</v>
+      <c r="D123" t="s">
+        <v>22</v>
+      </c>
+      <c r="E123" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>158</v>
+      </c>
+      <c r="C125" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" t="s">
+        <v>4</v>
+      </c>
+      <c r="E125" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
         <v>1580</v>
       </c>
-      <c r="B125" t="s">
-        <v>1659</v>
-      </c>
-      <c r="C125" t="s">
-        <v>1660</v>
-      </c>
-      <c r="D125" t="s">
-        <v>22</v>
-      </c>
-      <c r="E125" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126"/>
       <c r="B126" t="s">
         <v>1661</v>
       </c>
@@ -46497,15 +46726,30 @@
     <row r="139">
       <c r="A139"/>
       <c r="B139" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C139" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D139" t="s">
+        <v>22</v>
+      </c>
+      <c r="E139" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140"/>
+      <c r="B140" t="s">
         <v>179</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C140" t="s">
         <v>180</v>
       </c>
-      <c r="D139" t="s">
-        <v>22</v>
-      </c>
-      <c r="E139" t="s">
+      <c r="D140" t="s">
+        <v>22</v>
+      </c>
+      <c r="E140" t="s">
         <v>22</v>
       </c>
     </row>
@@ -46583,7 +46827,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>603</v>
@@ -46607,14 +46851,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>22</v>
@@ -46631,14 +46875,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>22</v>
@@ -46655,14 +46899,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>22</v>
@@ -46677,7 +46921,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>603</v>
@@ -46701,14 +46945,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>22</v>
@@ -46725,14 +46969,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>22</v>
@@ -46747,14 +46991,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>22</v>
@@ -46769,14 +47013,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>22</v>
@@ -46793,14 +47037,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>22</v>
@@ -46815,14 +47059,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>22</v>
@@ -46837,14 +47081,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="E13" s="8" t="s">
         <v>22</v>
@@ -46859,14 +47103,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>22</v>
@@ -46883,14 +47127,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>22</v>
@@ -46907,14 +47151,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>22</v>
@@ -46931,14 +47175,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>22</v>
@@ -46953,14 +47197,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>22</v>
@@ -46977,14 +47221,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>22</v>
@@ -47001,14 +47245,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>22</v>
@@ -47025,14 +47269,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>22</v>
@@ -47049,14 +47293,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="E22" s="8" t="s">
         <v>22</v>
@@ -47073,14 +47317,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>603</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>22</v>
@@ -47097,7 +47341,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>12</v>
@@ -47106,7 +47350,7 @@
         <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>22</v>
@@ -47250,7 +47494,7 @@
         <v>683</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
@@ -47269,14 +47513,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>22</v>
@@ -47291,14 +47535,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>22</v>
@@ -47313,14 +47557,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>55</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>22</v>
@@ -47335,7 +47579,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>12</v>
@@ -47344,7 +47588,7 @@
         <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>22</v>
@@ -47359,14 +47603,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>22</v>
@@ -47381,7 +47625,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>12</v>
@@ -47390,7 +47634,7 @@
         <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>22</v>
@@ -47405,14 +47649,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>22</v>
@@ -47427,14 +47671,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>22</v>
@@ -47449,14 +47693,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>22</v>
@@ -47471,14 +47715,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>22</v>
@@ -47493,7 +47737,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="B13" s="9" t="s">
         <v>12</v>
@@ -47502,7 +47746,7 @@
         <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>22</v>
@@ -47517,7 +47761,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>12</v>
@@ -47526,7 +47770,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>22</v>
@@ -47558,13 +47802,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B17" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="C17" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="D17" t="s">
         <v>22</v>
@@ -47576,10 +47820,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="C18" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="D18" t="s">
         <v>22</v>
@@ -47591,10 +47835,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="C19" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
@@ -47606,10 +47850,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="C20" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -47621,10 +47865,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="C21" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -47636,10 +47880,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="C22" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
@@ -47651,10 +47895,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="C23" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="D23" t="s">
         <v>22</v>
@@ -47666,10 +47910,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="C24" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -47712,13 +47956,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B28" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="C28" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
@@ -47730,10 +47974,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="C29" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
@@ -47776,13 +48020,13 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="B33" t="s">
         <v>1457</v>
       </c>
       <c r="C33" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="D33" t="s">
         <v>22</v>
@@ -47794,10 +48038,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="C34" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
@@ -47812,7 +48056,7 @@
         <v>1459</v>
       </c>
       <c r="C35" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
@@ -47824,10 +48068,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C36" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D36" t="s">
         <v>22</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -7827,7 +7827,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.56.0-SNAPSHOT</t>
+    <t>1.57.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -7899,7 +7899,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.57.0-SNAPSHOT</t>
+    <t>1.58.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11215" uniqueCount="2782">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11235" uniqueCount="2792">
   <si>
     <t>Field</t>
   </si>
@@ -6789,6 +6789,36 @@
   </si>
   <si>
     <t>Brain tissue</t>
+  </si>
+  <si>
+    <t>ANTERIOR_NARES_SWAB</t>
+  </si>
+  <si>
+    <t>Anterior nares swab</t>
+  </si>
+  <si>
+    <t>OROPHARYNGEAL_ASPIRATE</t>
+  </si>
+  <si>
+    <t>Oropharyngeal aspirate</t>
+  </si>
+  <si>
+    <t>NASOPHARYNGEAL_ASPIRATE</t>
+  </si>
+  <si>
+    <t>Nasopharyngeal aspirate</t>
+  </si>
+  <si>
+    <t>LOWER_RESPIRATORY_SAMPLE</t>
+  </si>
+  <si>
+    <t>Lower respiratory sample</t>
+  </si>
+  <si>
+    <t>PLEURAL_FLUID_SPECIMEN</t>
+  </si>
+  <si>
+    <t>Pleural fluid specimen</t>
   </si>
   <si>
     <t>EXTERNAL</t>
@@ -8618,7 +8648,7 @@
 </file>
 
 <file path=xl/tables/table105.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="105" name="SampleSampleMaterial" displayName="SampleSampleMaterial" ref="A45:E65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="105" name="SampleSampleMaterial" displayName="SampleSampleMaterial" ref="A45:E70">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8632,7 +8662,7 @@
 </file>
 
 <file path=xl/tables/table106.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="106" name="SampleSamplePurpose" displayName="SampleSamplePurpose" ref="A67:E69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="106" name="SampleSamplePurpose" displayName="SampleSamplePurpose" ref="A72:E74">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8646,7 +8676,7 @@
 </file>
 
 <file path=xl/tables/table107.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="107" name="SampleSpecimenCondition" displayName="SampleSpecimenCondition" ref="A71:E73">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="107" name="SampleSpecimenCondition" displayName="SampleSpecimenCondition" ref="A76:E78">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8660,7 +8690,7 @@
 </file>
 
 <file path=xl/tables/table108.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="108" name="SampleSampleSource" displayName="SampleSampleSource" ref="A75:E78">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="108" name="SampleSampleSource" displayName="SampleSampleSource" ref="A80:E83">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8674,7 +8704,7 @@
 </file>
 
 <file path=xl/tables/table109.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="109" name="SamplePathogenTestResultType" displayName="SamplePathogenTestResultType" ref="A80:E85">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="109" name="SamplePathogenTestResultType" displayName="SamplePathogenTestResultType" ref="A85:E90">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -8702,7 +8732,7 @@
 </file>
 
 <file path=xl/tables/table110.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="110" name="SampleSamplingReason" displayName="SampleSamplingReason" ref="A87:E101">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="110" name="SampleSamplingReason" displayName="SampleSamplingReason" ref="A92:E106">
   <autoFilter/>
   <tableColumns count="5">
     <tableColumn id="1" name="Type"/>
@@ -22744,7 +22774,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.0" customWidth="true"/>
@@ -23990,10 +24020,10 @@
     <row r="65">
       <c r="A65"/>
       <c r="B65" t="s">
-        <v>179</v>
+        <v>2250</v>
       </c>
       <c r="C65" t="s">
-        <v>180</v>
+        <v>2251</v>
       </c>
       <c r="D65" t="s">
         <v>22</v>
@@ -24002,32 +24032,43 @@
         <v>22</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66"/>
+      <c r="B66" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2253</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" t="s">
+        <v>22</v>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" t="s">
-        <v>1</v>
-      </c>
+      <c r="A67"/>
       <c r="B67" t="s">
-        <v>158</v>
+        <v>2254</v>
       </c>
       <c r="C67" t="s">
-        <v>3</v>
+        <v>2255</v>
       </c>
       <c r="D67" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E67" t="s">
-        <v>168</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="s">
-        <v>2166</v>
-      </c>
+      <c r="A68"/>
       <c r="B68" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="C68" t="s">
-        <v>2251</v>
+        <v>2257</v>
       </c>
       <c r="D68" t="s">
         <v>22</v>
@@ -24039,10 +24080,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>2252</v>
+        <v>2258</v>
       </c>
       <c r="C69" t="s">
-        <v>2253</v>
+        <v>2259</v>
       </c>
       <c r="D69" t="s">
         <v>22</v>
@@ -24051,47 +24092,47 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>1</v>
-      </c>
-      <c r="B71" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" t="s">
-        <v>3</v>
-      </c>
-      <c r="D71" t="s">
-        <v>4</v>
-      </c>
-      <c r="E71" t="s">
-        <v>168</v>
+    <row r="70">
+      <c r="A70"/>
+      <c r="B70" t="s">
+        <v>179</v>
+      </c>
+      <c r="C70" t="s">
+        <v>180</v>
+      </c>
+      <c r="D70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>2178</v>
+        <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>2254</v>
+        <v>158</v>
       </c>
       <c r="C72" t="s">
-        <v>2255</v>
+        <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E72" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73"/>
+      <c r="A73" t="s">
+        <v>2166</v>
+      </c>
       <c r="B73" t="s">
-        <v>2256</v>
+        <v>2260</v>
       </c>
       <c r="C73" t="s">
-        <v>2257</v>
+        <v>2261</v>
       </c>
       <c r="D73" t="s">
         <v>22</v>
@@ -24100,47 +24141,47 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B75" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" t="s">
-        <v>4</v>
-      </c>
-      <c r="E75" t="s">
-        <v>168</v>
+    <row r="74">
+      <c r="A74"/>
+      <c r="B74" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D74" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>2184</v>
+        <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>2258</v>
+        <v>158</v>
       </c>
       <c r="C76" t="s">
-        <v>2259</v>
+        <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E76" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77"/>
+      <c r="A77" t="s">
+        <v>2178</v>
+      </c>
       <c r="B77" t="s">
-        <v>2260</v>
+        <v>2264</v>
       </c>
       <c r="C77" t="s">
-        <v>2261</v>
+        <v>2265</v>
       </c>
       <c r="D77" t="s">
         <v>22</v>
@@ -24152,10 +24193,10 @@
     <row r="78">
       <c r="A78"/>
       <c r="B78" t="s">
-        <v>2262</v>
+        <v>2266</v>
       </c>
       <c r="C78" t="s">
-        <v>2263</v>
+        <v>2267</v>
       </c>
       <c r="D78" t="s">
         <v>22</v>
@@ -24183,13 +24224,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>2193</v>
+        <v>2184</v>
       </c>
       <c r="B81" t="s">
-        <v>2264</v>
+        <v>2268</v>
       </c>
       <c r="C81" t="s">
-        <v>2265</v>
+        <v>2269</v>
       </c>
       <c r="D81" t="s">
         <v>22</v>
@@ -24201,10 +24242,10 @@
     <row r="82">
       <c r="A82"/>
       <c r="B82" t="s">
-        <v>936</v>
+        <v>2270</v>
       </c>
       <c r="C82" t="s">
-        <v>938</v>
+        <v>2271</v>
       </c>
       <c r="D82" t="s">
         <v>22</v>
@@ -24216,10 +24257,10 @@
     <row r="83">
       <c r="A83"/>
       <c r="B83" t="s">
-        <v>2266</v>
+        <v>2272</v>
       </c>
       <c r="C83" t="s">
-        <v>2267</v>
+        <v>2273</v>
       </c>
       <c r="D83" t="s">
         <v>22</v>
@@ -24228,62 +24269,62 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84"/>
-      <c r="B84" t="s">
-        <v>2268</v>
-      </c>
-      <c r="C84" t="s">
-        <v>2269</v>
-      </c>
-      <c r="D84" t="s">
-        <v>22</v>
-      </c>
-      <c r="E84" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="85">
-      <c r="A85"/>
+      <c r="A85" t="s">
+        <v>1</v>
+      </c>
       <c r="B85" t="s">
-        <v>2270</v>
+        <v>158</v>
       </c>
       <c r="C85" t="s">
-        <v>2271</v>
+        <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E85" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D86" t="s">
+        <v>22</v>
+      </c>
+      <c r="E86" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="s">
-        <v>1</v>
-      </c>
+      <c r="A87"/>
       <c r="B87" t="s">
-        <v>158</v>
+        <v>936</v>
       </c>
       <c r="C87" t="s">
-        <v>3</v>
+        <v>938</v>
       </c>
       <c r="D87" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E87" t="s">
-        <v>168</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s">
-        <v>2208</v>
-      </c>
+      <c r="A88"/>
       <c r="B88" t="s">
-        <v>2272</v>
+        <v>2276</v>
       </c>
       <c r="C88" t="s">
-        <v>2273</v>
+        <v>2277</v>
       </c>
       <c r="D88" t="s">
         <v>22</v>
@@ -24295,10 +24336,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>2274</v>
+        <v>2278</v>
       </c>
       <c r="C89" t="s">
-        <v>2275</v>
+        <v>2279</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
@@ -24310,10 +24351,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>919</v>
+        <v>2280</v>
       </c>
       <c r="C90" t="s">
-        <v>643</v>
+        <v>2281</v>
       </c>
       <c r="D90" t="s">
         <v>22</v>
@@ -24322,43 +24363,32 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91"/>
-      <c r="B91" t="s">
-        <v>2276</v>
-      </c>
-      <c r="C91" t="s">
-        <v>2277</v>
-      </c>
-      <c r="D91" t="s">
-        <v>22</v>
-      </c>
-      <c r="E91" t="s">
-        <v>22</v>
-      </c>
-    </row>
     <row r="92">
-      <c r="A92"/>
+      <c r="A92" t="s">
+        <v>1</v>
+      </c>
       <c r="B92" t="s">
-        <v>2278</v>
+        <v>158</v>
       </c>
       <c r="C92" t="s">
-        <v>2279</v>
+        <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E92" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93"/>
+      <c r="A93" t="s">
+        <v>2208</v>
+      </c>
       <c r="B93" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="C93" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="D93" t="s">
         <v>22</v>
@@ -24370,10 +24400,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="C94" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="D94" t="s">
         <v>22</v>
@@ -24385,10 +24415,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>2284</v>
+        <v>919</v>
       </c>
       <c r="C95" t="s">
-        <v>2285</v>
+        <v>643</v>
       </c>
       <c r="D95" t="s">
         <v>22</v>
@@ -24430,10 +24460,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>1071</v>
+        <v>2290</v>
       </c>
       <c r="C98" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="D98" t="s">
         <v>22</v>
@@ -24445,10 +24475,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="C99" t="s">
-        <v>791</v>
+        <v>2293</v>
       </c>
       <c r="D99" t="s">
         <v>22</v>
@@ -24460,10 +24490,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>185</v>
+        <v>2294</v>
       </c>
       <c r="C100" t="s">
-        <v>186</v>
+        <v>2295</v>
       </c>
       <c r="D100" t="s">
         <v>22</v>
@@ -24475,15 +24505,90 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
+        <v>2296</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2297</v>
+      </c>
+      <c r="D101" t="s">
+        <v>22</v>
+      </c>
+      <c r="E101" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102"/>
+      <c r="B102" t="s">
+        <v>2298</v>
+      </c>
+      <c r="C102" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D102" t="s">
+        <v>22</v>
+      </c>
+      <c r="E102" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103"/>
+      <c r="B103" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C103" t="s">
+        <v>2300</v>
+      </c>
+      <c r="D103" t="s">
+        <v>22</v>
+      </c>
+      <c r="E103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104"/>
+      <c r="B104" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C104" t="s">
+        <v>791</v>
+      </c>
+      <c r="D104" t="s">
+        <v>22</v>
+      </c>
+      <c r="E104" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105"/>
+      <c r="B105" t="s">
+        <v>185</v>
+      </c>
+      <c r="C105" t="s">
+        <v>186</v>
+      </c>
+      <c r="D105" t="s">
+        <v>22</v>
+      </c>
+      <c r="E105" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106"/>
+      <c r="B106" t="s">
         <v>1074</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C106" t="s">
         <v>847</v>
       </c>
-      <c r="D101" t="s">
-        <v>22</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="D106" t="s">
+        <v>22</v>
+      </c>
+      <c r="E106" t="s">
         <v>22</v>
       </c>
     </row>
@@ -24557,7 +24662,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>2187</v>
@@ -24581,17 +24686,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2293</v>
+        <v>2303</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>91</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2294</v>
+        <v>2304</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>2295</v>
+        <v>2305</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -24605,17 +24710,17 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2296</v>
+        <v>2306</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2297</v>
+        <v>2307</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>2298</v>
+        <v>2308</v>
       </c>
       <c r="F4"/>
       <c r="H4" s="16" t="s">
@@ -24627,14 +24732,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2299</v>
+        <v>2309</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>12</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2300</v>
+        <v>2310</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>22</v>
@@ -24649,17 +24754,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2301</v>
+        <v>2311</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2303</v>
+        <v>2313</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>2304</v>
+        <v>2314</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -24673,7 +24778,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="B7" s="16" t="s">
         <v>12</v>
@@ -24682,10 +24787,10 @@
         <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>2306</v>
+        <v>2316</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="F7"/>
       <c r="H7" s="16" t="s">
@@ -24697,17 +24802,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>55</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>2310</v>
+        <v>2320</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -24731,7 +24836,7 @@
         <v>230</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>2311</v>
+        <v>2321</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -24757,7 +24862,7 @@
         <v>2170</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>2312</v>
+        <v>2322</v>
       </c>
       <c r="F10"/>
       <c r="H10" s="16" t="s">
@@ -24769,7 +24874,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2313</v>
+        <v>2323</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>626</v>
@@ -24795,17 +24900,17 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2314</v>
+        <v>2324</v>
       </c>
       <c r="B12" s="16" t="s">
         <v>2193</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2315</v>
+        <v>2325</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>2316</v>
+        <v>2326</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -24819,7 +24924,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2317</v>
+        <v>2327</v>
       </c>
       <c r="B13" s="16" t="s">
         <v>12</v>
@@ -24828,10 +24933,10 @@
         <v>66</v>
       </c>
       <c r="D13" t="s">
-        <v>2318</v>
+        <v>2328</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>2319</v>
+        <v>2329</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -24845,17 +24950,17 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2320</v>
+        <v>2330</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>140</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>2321</v>
+        <v>2331</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>2322</v>
+        <v>2332</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -24869,17 +24974,17 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2323</v>
+        <v>2333</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>140</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2324</v>
+        <v>2334</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>2325</v>
+        <v>2335</v>
       </c>
       <c r="F15"/>
       <c r="H15" s="16" t="s">
@@ -24891,7 +24996,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2326</v>
+        <v>2336</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>12</v>
@@ -24900,10 +25005,10 @@
         <v>66</v>
       </c>
       <c r="D16" t="s">
-        <v>2327</v>
+        <v>2337</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>2328</v>
+        <v>2338</v>
       </c>
       <c r="F16"/>
       <c r="H16" s="16" t="s">
@@ -24915,14 +25020,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2329</v>
+        <v>2339</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>42</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>2330</v>
+        <v>2340</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>22</v>
@@ -24961,14 +25066,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2331</v>
+        <v>2341</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>140</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>2332</v>
+        <v>2342</v>
       </c>
       <c r="E19" s="16" t="s">
         <v>22</v>
@@ -25913,13 +26018,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>2302</v>
+        <v>2312</v>
       </c>
       <c r="B85" t="s">
-        <v>2333</v>
+        <v>2343</v>
       </c>
       <c r="C85" t="s">
-        <v>2334</v>
+        <v>2344</v>
       </c>
       <c r="D85" t="s">
         <v>22</v>
@@ -25931,10 +26036,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>2335</v>
+        <v>2345</v>
       </c>
       <c r="C86" t="s">
-        <v>2336</v>
+        <v>2346</v>
       </c>
       <c r="D86" t="s">
         <v>22</v>
@@ -25946,10 +26051,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>2337</v>
+        <v>2347</v>
       </c>
       <c r="C87" t="s">
-        <v>2338</v>
+        <v>2348</v>
       </c>
       <c r="D87" t="s">
         <v>22</v>
@@ -25961,10 +26066,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>2339</v>
+        <v>2349</v>
       </c>
       <c r="C88" t="s">
-        <v>2340</v>
+        <v>2350</v>
       </c>
       <c r="D88" t="s">
         <v>22</v>
@@ -25976,10 +26081,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>2341</v>
+        <v>2351</v>
       </c>
       <c r="C89" t="s">
-        <v>2342</v>
+        <v>2352</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
@@ -25991,7 +26096,7 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>2343</v>
+        <v>2353</v>
       </c>
       <c r="C90" t="s">
         <v>1087</v>
@@ -26006,10 +26111,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>2344</v>
+        <v>2354</v>
       </c>
       <c r="C91" t="s">
-        <v>2345</v>
+        <v>2355</v>
       </c>
       <c r="D91" t="s">
         <v>22</v>
@@ -26021,10 +26126,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>2346</v>
+        <v>2356</v>
       </c>
       <c r="C92" t="s">
-        <v>2347</v>
+        <v>2357</v>
       </c>
       <c r="D92" t="s">
         <v>22</v>
@@ -26036,10 +26141,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>2348</v>
+        <v>2358</v>
       </c>
       <c r="C93" t="s">
-        <v>2349</v>
+        <v>2359</v>
       </c>
       <c r="D93" t="s">
         <v>22</v>
@@ -26051,10 +26156,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>2350</v>
+        <v>2360</v>
       </c>
       <c r="C94" t="s">
-        <v>2351</v>
+        <v>2361</v>
       </c>
       <c r="D94" t="s">
         <v>22</v>
@@ -26066,10 +26171,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>2352</v>
+        <v>2362</v>
       </c>
       <c r="C95" t="s">
-        <v>2353</v>
+        <v>2363</v>
       </c>
       <c r="D95" t="s">
         <v>22</v>
@@ -26081,10 +26186,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>2354</v>
+        <v>2364</v>
       </c>
       <c r="C96" t="s">
-        <v>2355</v>
+        <v>2365</v>
       </c>
       <c r="D96" t="s">
         <v>22</v>
@@ -26096,10 +26201,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>2356</v>
+        <v>2366</v>
       </c>
       <c r="C97" t="s">
-        <v>2357</v>
+        <v>2367</v>
       </c>
       <c r="D97" t="s">
         <v>22</v>
@@ -26111,10 +26216,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>2358</v>
+        <v>2368</v>
       </c>
       <c r="C98" t="s">
-        <v>2359</v>
+        <v>2369</v>
       </c>
       <c r="D98" t="s">
         <v>22</v>
@@ -26126,10 +26231,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>2360</v>
+        <v>2370</v>
       </c>
       <c r="C99" t="s">
-        <v>2361</v>
+        <v>2371</v>
       </c>
       <c r="D99" t="s">
         <v>22</v>
@@ -26141,10 +26246,10 @@
     <row r="100">
       <c r="A100"/>
       <c r="B100" t="s">
-        <v>2362</v>
+        <v>2372</v>
       </c>
       <c r="C100" t="s">
-        <v>2363</v>
+        <v>2373</v>
       </c>
       <c r="D100" t="s">
         <v>22</v>
@@ -26156,10 +26261,10 @@
     <row r="101">
       <c r="A101"/>
       <c r="B101" t="s">
-        <v>2364</v>
+        <v>2374</v>
       </c>
       <c r="C101" t="s">
-        <v>2365</v>
+        <v>2375</v>
       </c>
       <c r="D101" t="s">
         <v>22</v>
@@ -26171,10 +26276,10 @@
     <row r="102">
       <c r="A102"/>
       <c r="B102" t="s">
-        <v>2366</v>
+        <v>2376</v>
       </c>
       <c r="C102" t="s">
-        <v>2367</v>
+        <v>2377</v>
       </c>
       <c r="D102" t="s">
         <v>22</v>
@@ -26186,10 +26291,10 @@
     <row r="103">
       <c r="A103"/>
       <c r="B103" t="s">
-        <v>2368</v>
+        <v>2378</v>
       </c>
       <c r="C103" t="s">
-        <v>2369</v>
+        <v>2379</v>
       </c>
       <c r="D103" t="s">
         <v>22</v>
@@ -26201,10 +26306,10 @@
     <row r="104">
       <c r="A104"/>
       <c r="B104" t="s">
-        <v>2370</v>
+        <v>2380</v>
       </c>
       <c r="C104" t="s">
-        <v>2371</v>
+        <v>2381</v>
       </c>
       <c r="D104" t="s">
         <v>22</v>
@@ -26250,10 +26355,10 @@
         <v>2193</v>
       </c>
       <c r="B108" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="C108" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="D108" t="s">
         <v>22</v>
@@ -26280,10 +26385,10 @@
     <row r="110">
       <c r="A110"/>
       <c r="B110" t="s">
-        <v>2266</v>
+        <v>2276</v>
       </c>
       <c r="C110" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
       <c r="D110" t="s">
         <v>22</v>
@@ -26295,10 +26400,10 @@
     <row r="111">
       <c r="A111"/>
       <c r="B111" t="s">
-        <v>2268</v>
+        <v>2278</v>
       </c>
       <c r="C111" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
       <c r="D111" t="s">
         <v>22</v>
@@ -26310,10 +26415,10 @@
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>2270</v>
+        <v>2280</v>
       </c>
       <c r="C112" t="s">
-        <v>2271</v>
+        <v>2281</v>
       </c>
       <c r="D112" t="s">
         <v>22</v>
@@ -26389,7 +26494,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2292</v>
+        <v>2302</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>2187</v>
@@ -26411,14 +26516,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2308</v>
+        <v>2318</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>55</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2309</v>
+        <v>2319</v>
       </c>
       <c r="E3" s="17" t="s">
         <v>22</v>
@@ -26433,14 +26538,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2372</v>
+        <v>2382</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>2373</v>
+        <v>2383</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2374</v>
+        <v>2384</v>
       </c>
       <c r="E4" s="17" t="s">
         <v>22</v>
@@ -26455,14 +26560,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2375</v>
+        <v>2385</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>2373</v>
+        <v>2383</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2376</v>
+        <v>2386</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>22</v>
@@ -26477,14 +26582,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2377</v>
+        <v>2387</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>2373</v>
+        <v>2383</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2378</v>
+        <v>2388</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>22</v>
@@ -26499,14 +26604,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2379</v>
+        <v>2389</v>
       </c>
       <c r="B7" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2380</v>
+        <v>2390</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>22</v>
@@ -26521,14 +26626,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2381</v>
+        <v>2391</v>
       </c>
       <c r="B8" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2382</v>
+        <v>2392</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>22</v>
@@ -26543,14 +26648,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2383</v>
+        <v>2393</v>
       </c>
       <c r="B9" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2384</v>
+        <v>2394</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>22</v>
@@ -26565,14 +26670,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2385</v>
+        <v>2395</v>
       </c>
       <c r="B10" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>2386</v>
+        <v>2396</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>22</v>
@@ -26587,14 +26692,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2387</v>
+        <v>2397</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2388</v>
+        <v>2398</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>22</v>
@@ -26609,14 +26714,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2389</v>
+        <v>2399</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2390</v>
+        <v>2400</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>22</v>
@@ -26631,14 +26736,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2391</v>
+        <v>2401</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2392</v>
+        <v>2402</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>22</v>
@@ -26653,14 +26758,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2393</v>
+        <v>2403</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>2394</v>
+        <v>2404</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>22</v>
@@ -26675,14 +26780,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2395</v>
+        <v>2405</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2396</v>
+        <v>2406</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>22</v>
@@ -26697,14 +26802,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2397</v>
+        <v>2407</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2398</v>
+        <v>2408</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>22</v>
@@ -26719,14 +26824,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2399</v>
+        <v>2409</v>
       </c>
       <c r="B17" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>2400</v>
+        <v>2410</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>22</v>
@@ -26741,14 +26846,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2401</v>
+        <v>2411</v>
       </c>
       <c r="B18" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>2402</v>
+        <v>2412</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>22</v>
@@ -26763,14 +26868,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2403</v>
+        <v>2413</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>2404</v>
+        <v>2414</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>22</v>
@@ -26785,14 +26890,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="B20" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C20"/>
       <c r="D20" t="s">
-        <v>2406</v>
+        <v>2416</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>22</v>
@@ -26807,14 +26912,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>2407</v>
+        <v>2417</v>
       </c>
       <c r="B21" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C21"/>
       <c r="D21" t="s">
-        <v>2408</v>
+        <v>2418</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>22</v>
@@ -26829,14 +26934,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2409</v>
+        <v>2419</v>
       </c>
       <c r="B22" s="17" t="s">
         <v>42</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>22</v>
@@ -26851,14 +26956,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>2411</v>
+        <v>2421</v>
       </c>
       <c r="B23" s="17" t="s">
         <v>12</v>
       </c>
       <c r="C23"/>
       <c r="D23" t="s">
-        <v>2412</v>
+        <v>2422</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>22</v>
@@ -26890,13 +26995,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>2373</v>
+        <v>2383</v>
       </c>
       <c r="B26" t="s">
-        <v>2268</v>
+        <v>2278</v>
       </c>
       <c r="C26" t="s">
-        <v>2269</v>
+        <v>2279</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
@@ -26908,10 +27013,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>2266</v>
+        <v>2276</v>
       </c>
       <c r="C27" t="s">
-        <v>2267</v>
+        <v>2277</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
@@ -26923,10 +27028,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>2264</v>
+        <v>2274</v>
       </c>
       <c r="C28" t="s">
-        <v>2265</v>
+        <v>2275</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
@@ -26999,14 +27104,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2413</v>
+        <v>2423</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>2414</v>
+        <v>2424</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2415</v>
+        <v>2425</v>
       </c>
       <c r="E2" s="18" t="s">
         <v>22</v>
@@ -27045,14 +27150,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2416</v>
+        <v>2426</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2418</v>
+        <v>2428</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>22</v>
@@ -27067,7 +27172,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2419</v>
+        <v>2429</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>1690</v>
@@ -27089,17 +27194,17 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2420</v>
+        <v>2430</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>2421</v>
+        <v>2431</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2422</v>
+        <v>2432</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>2423</v>
+        <v>2433</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -27113,14 +27218,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2424</v>
+        <v>2434</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>2425</v>
+        <v>2435</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2426</v>
+        <v>2436</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>22</v>
@@ -27135,14 +27240,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2427</v>
+        <v>2437</v>
       </c>
       <c r="B8" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2428</v>
+        <v>2438</v>
       </c>
       <c r="E8" s="18" t="s">
         <v>22</v>
@@ -27159,14 +27264,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2429</v>
+        <v>2439</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2430</v>
+        <v>2440</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>22</v>
@@ -27181,14 +27286,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2431</v>
+        <v>2441</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>2432</v>
+        <v>2442</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>2433</v>
+        <v>2443</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>22</v>
@@ -27203,14 +27308,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2434</v>
+        <v>2444</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2435</v>
+        <v>2445</v>
       </c>
       <c r="E11" s="18" t="s">
         <v>22</v>
@@ -27225,14 +27330,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2436</v>
+        <v>2446</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>55</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2437</v>
+        <v>2447</v>
       </c>
       <c r="E12" s="18" t="s">
         <v>22</v>
@@ -27247,14 +27352,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2438</v>
+        <v>2448</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>626</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2439</v>
+        <v>2449</v>
       </c>
       <c r="E13" s="18" t="s">
         <v>22</v>
@@ -27269,14 +27374,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2440</v>
+        <v>2450</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>2441</v>
+        <v>2451</v>
       </c>
       <c r="E14" s="18" t="s">
         <v>22</v>
@@ -27291,14 +27396,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2442</v>
+        <v>2452</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>626</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2443</v>
+        <v>2453</v>
       </c>
       <c r="E15" s="18" t="s">
         <v>22</v>
@@ -27315,14 +27420,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2444</v>
+        <v>2454</v>
       </c>
       <c r="B16" s="18" t="s">
         <v>12</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2445</v>
+        <v>2455</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>22</v>
@@ -27337,7 +27442,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2446</v>
+        <v>2456</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>42</v>
@@ -27359,7 +27464,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2447</v>
+        <v>2457</v>
       </c>
       <c r="B18" s="18" t="s">
         <v>42</v>
@@ -27381,7 +27486,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2448</v>
+        <v>2458</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>42</v>
@@ -27420,13 +27525,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>2414</v>
+        <v>2424</v>
       </c>
       <c r="B22" t="s">
-        <v>2449</v>
+        <v>2459</v>
       </c>
       <c r="C22" t="s">
-        <v>2450</v>
+        <v>2460</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
@@ -27438,10 +27543,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>2451</v>
+        <v>2461</v>
       </c>
       <c r="C23" t="s">
-        <v>2452</v>
+        <v>2462</v>
       </c>
       <c r="D23" t="s">
         <v>22</v>
@@ -27453,10 +27558,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>2453</v>
+        <v>2463</v>
       </c>
       <c r="C24" t="s">
-        <v>2454</v>
+        <v>2464</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -27468,10 +27573,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>2455</v>
+        <v>2465</v>
       </c>
       <c r="C25" t="s">
-        <v>2456</v>
+        <v>2466</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -27499,13 +27604,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2421</v>
+        <v>2431</v>
       </c>
       <c r="B28" t="s">
-        <v>2457</v>
+        <v>2467</v>
       </c>
       <c r="C28" t="s">
-        <v>2458</v>
+        <v>2468</v>
       </c>
       <c r="D28" t="s">
         <v>22</v>
@@ -27517,10 +27622,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>2459</v>
+        <v>2469</v>
       </c>
       <c r="C29" t="s">
-        <v>2460</v>
+        <v>2470</v>
       </c>
       <c r="D29" t="s">
         <v>22</v>
@@ -27532,10 +27637,10 @@
     <row r="30">
       <c r="A30"/>
       <c r="B30" t="s">
-        <v>2461</v>
+        <v>2471</v>
       </c>
       <c r="C30" t="s">
-        <v>2462</v>
+        <v>2472</v>
       </c>
       <c r="D30" t="s">
         <v>22</v>
@@ -27547,10 +27652,10 @@
     <row r="31">
       <c r="A31"/>
       <c r="B31" t="s">
-        <v>2463</v>
+        <v>2473</v>
       </c>
       <c r="C31" t="s">
-        <v>2464</v>
+        <v>2474</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
@@ -27562,10 +27667,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>2465</v>
+        <v>2475</v>
       </c>
       <c r="C32" t="s">
-        <v>2466</v>
+        <v>2476</v>
       </c>
       <c r="D32" t="s">
         <v>22</v>
@@ -27580,7 +27685,7 @@
         <v>917</v>
       </c>
       <c r="C33" t="s">
-        <v>2467</v>
+        <v>2477</v>
       </c>
       <c r="D33" t="s">
         <v>22</v>
@@ -27592,10 +27697,10 @@
     <row r="34">
       <c r="A34"/>
       <c r="B34" t="s">
-        <v>2468</v>
+        <v>2478</v>
       </c>
       <c r="C34" t="s">
-        <v>2469</v>
+        <v>2479</v>
       </c>
       <c r="D34" t="s">
         <v>22</v>
@@ -27607,10 +27712,10 @@
     <row r="35">
       <c r="A35"/>
       <c r="B35" t="s">
-        <v>2470</v>
+        <v>2480</v>
       </c>
       <c r="C35" t="s">
-        <v>2471</v>
+        <v>2481</v>
       </c>
       <c r="D35" t="s">
         <v>22</v>
@@ -27622,10 +27727,10 @@
     <row r="36">
       <c r="A36"/>
       <c r="B36" t="s">
-        <v>2472</v>
+        <v>2482</v>
       </c>
       <c r="C36" t="s">
-        <v>2473</v>
+        <v>2483</v>
       </c>
       <c r="D36" t="s">
         <v>22</v>
@@ -27637,10 +27742,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>2474</v>
+        <v>2484</v>
       </c>
       <c r="C37" t="s">
-        <v>2475</v>
+        <v>2485</v>
       </c>
       <c r="D37" t="s">
         <v>22</v>
@@ -27652,10 +27757,10 @@
     <row r="38">
       <c r="A38"/>
       <c r="B38" t="s">
-        <v>2476</v>
+        <v>2486</v>
       </c>
       <c r="C38" t="s">
-        <v>2477</v>
+        <v>2487</v>
       </c>
       <c r="D38" t="s">
         <v>22</v>
@@ -27667,10 +27772,10 @@
     <row r="39">
       <c r="A39"/>
       <c r="B39" t="s">
-        <v>2478</v>
+        <v>2488</v>
       </c>
       <c r="C39" t="s">
-        <v>2479</v>
+        <v>2489</v>
       </c>
       <c r="D39" t="s">
         <v>22</v>
@@ -27682,10 +27787,10 @@
     <row r="40">
       <c r="A40"/>
       <c r="B40" t="s">
-        <v>2480</v>
+        <v>2490</v>
       </c>
       <c r="C40" t="s">
-        <v>2481</v>
+        <v>2491</v>
       </c>
       <c r="D40" t="s">
         <v>22</v>
@@ -27697,10 +27802,10 @@
     <row r="41">
       <c r="A41"/>
       <c r="B41" t="s">
-        <v>2482</v>
+        <v>2492</v>
       </c>
       <c r="C41" t="s">
-        <v>2483</v>
+        <v>2493</v>
       </c>
       <c r="D41" t="s">
         <v>22</v>
@@ -27712,10 +27817,10 @@
     <row r="42">
       <c r="A42"/>
       <c r="B42" t="s">
-        <v>2484</v>
+        <v>2494</v>
       </c>
       <c r="C42" t="s">
-        <v>2485</v>
+        <v>2495</v>
       </c>
       <c r="D42" t="s">
         <v>22</v>
@@ -27727,10 +27832,10 @@
     <row r="43">
       <c r="A43"/>
       <c r="B43" t="s">
-        <v>2486</v>
+        <v>2496</v>
       </c>
       <c r="C43" t="s">
-        <v>2487</v>
+        <v>2497</v>
       </c>
       <c r="D43" t="s">
         <v>22</v>
@@ -27742,10 +27847,10 @@
     <row r="44">
       <c r="A44"/>
       <c r="B44" t="s">
-        <v>2488</v>
+        <v>2498</v>
       </c>
       <c r="C44" t="s">
-        <v>2489</v>
+        <v>2499</v>
       </c>
       <c r="D44" t="s">
         <v>22</v>
@@ -27757,10 +27862,10 @@
     <row r="45">
       <c r="A45"/>
       <c r="B45" t="s">
-        <v>2490</v>
+        <v>2500</v>
       </c>
       <c r="C45" t="s">
-        <v>2491</v>
+        <v>2501</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -27772,10 +27877,10 @@
     <row r="46">
       <c r="A46"/>
       <c r="B46" t="s">
-        <v>2492</v>
+        <v>2502</v>
       </c>
       <c r="C46" t="s">
-        <v>2493</v>
+        <v>2503</v>
       </c>
       <c r="D46" t="s">
         <v>22</v>
@@ -27790,7 +27895,7 @@
         <v>179</v>
       </c>
       <c r="C47" t="s">
-        <v>2494</v>
+        <v>2504</v>
       </c>
       <c r="D47" t="s">
         <v>22</v>
@@ -27802,10 +27907,10 @@
     <row r="48">
       <c r="A48"/>
       <c r="B48" t="s">
-        <v>2495</v>
+        <v>2505</v>
       </c>
       <c r="C48" t="s">
-        <v>2496</v>
+        <v>2506</v>
       </c>
       <c r="D48" t="s">
         <v>22</v>
@@ -27817,10 +27922,10 @@
     <row r="49">
       <c r="A49"/>
       <c r="B49" t="s">
-        <v>2497</v>
+        <v>2507</v>
       </c>
       <c r="C49" t="s">
-        <v>2498</v>
+        <v>2508</v>
       </c>
       <c r="D49" t="s">
         <v>22</v>
@@ -27832,10 +27937,10 @@
     <row r="50">
       <c r="A50"/>
       <c r="B50" t="s">
-        <v>2499</v>
+        <v>2509</v>
       </c>
       <c r="C50" t="s">
-        <v>2500</v>
+        <v>2510</v>
       </c>
       <c r="D50" t="s">
         <v>22</v>
@@ -27863,13 +27968,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>2425</v>
+        <v>2435</v>
       </c>
       <c r="B53" t="s">
-        <v>2501</v>
+        <v>2511</v>
       </c>
       <c r="C53" t="s">
-        <v>2502</v>
+        <v>2512</v>
       </c>
       <c r="D53" t="s">
         <v>22</v>
@@ -27881,10 +27986,10 @@
     <row r="54">
       <c r="A54"/>
       <c r="B54" t="s">
-        <v>2503</v>
+        <v>2513</v>
       </c>
       <c r="C54" t="s">
-        <v>2504</v>
+        <v>2514</v>
       </c>
       <c r="D54" t="s">
         <v>22</v>
@@ -27896,10 +28001,10 @@
     <row r="55">
       <c r="A55"/>
       <c r="B55" t="s">
-        <v>2505</v>
+        <v>2515</v>
       </c>
       <c r="C55" t="s">
-        <v>2506</v>
+        <v>2516</v>
       </c>
       <c r="D55" t="s">
         <v>22</v>
@@ -27927,13 +28032,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>2432</v>
+        <v>2442</v>
       </c>
       <c r="B58" t="s">
         <v>936</v>
       </c>
       <c r="C58" t="s">
-        <v>2507</v>
+        <v>2517</v>
       </c>
       <c r="D58" t="s">
         <v>22</v>
@@ -27948,7 +28053,7 @@
         <v>939</v>
       </c>
       <c r="C59" t="s">
-        <v>2508</v>
+        <v>2518</v>
       </c>
       <c r="D59" t="s">
         <v>22</v>
@@ -27960,10 +28065,10 @@
     <row r="60">
       <c r="A60"/>
       <c r="B60" t="s">
-        <v>2509</v>
+        <v>2519</v>
       </c>
       <c r="C60" t="s">
-        <v>2510</v>
+        <v>2520</v>
       </c>
       <c r="D60" t="s">
         <v>22</v>
@@ -27975,10 +28080,10 @@
     <row r="61">
       <c r="A61"/>
       <c r="B61" t="s">
-        <v>2511</v>
+        <v>2521</v>
       </c>
       <c r="C61" t="s">
-        <v>2512</v>
+        <v>2522</v>
       </c>
       <c r="D61" t="s">
         <v>22</v>
@@ -28054,10 +28159,10 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2513</v>
+        <v>2523</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
@@ -28076,17 +28181,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2514</v>
+        <v>2524</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>2515</v>
+        <v>2525</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2516</v>
+        <v>2526</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>2517</v>
+        <v>2527</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -28100,14 +28205,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2518</v>
+        <v>2528</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>2519</v>
+        <v>2529</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2520</v>
+        <v>2530</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>22</v>
@@ -28122,10 +28227,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2521</v>
+        <v>2531</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>2522</v>
+        <v>2532</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
@@ -28144,14 +28249,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2523</v>
+        <v>2533</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>55</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2524</v>
+        <v>2534</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>22</v>
@@ -28166,14 +28271,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2525</v>
+        <v>2535</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>55</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2526</v>
+        <v>2536</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>22</v>
@@ -28188,14 +28293,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2527</v>
+        <v>2537</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>2528</v>
+        <v>2538</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2529</v>
+        <v>2539</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>22</v>
@@ -28254,14 +28359,14 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2530</v>
+        <v>2540</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
-        <v>2531</v>
+        <v>2541</v>
       </c>
       <c r="E11" s="19" t="s">
         <v>22</v>
@@ -28276,7 +28381,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2532</v>
+        <v>2542</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>12</v>
@@ -28286,7 +28391,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>2533</v>
+        <v>2543</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -28300,14 +28405,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2534</v>
+        <v>2544</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>651</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2535</v>
+        <v>2545</v>
       </c>
       <c r="E13" s="19" t="s">
         <v>22</v>
@@ -28329,10 +28434,10 @@
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
-        <v>2536</v>
+        <v>2546</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>2537</v>
+        <v>2547</v>
       </c>
       <c r="F14"/>
       <c r="H14" s="19" t="s">
@@ -28351,10 +28456,10 @@
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2538</v>
+        <v>2548</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>2539</v>
+        <v>2549</v>
       </c>
       <c r="F15"/>
       <c r="H15" s="19" t="s">
@@ -28414,14 +28519,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2540</v>
+        <v>2550</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>55</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
-        <v>2541</v>
+        <v>2551</v>
       </c>
       <c r="E18" s="19" t="s">
         <v>22</v>
@@ -28436,14 +28541,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2542</v>
+        <v>2552</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>2543</v>
+        <v>2553</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>22</v>
@@ -28458,7 +28563,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>2544</v>
+        <v>2554</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>115</v>
@@ -28490,7 +28595,7 @@
         <v>1625</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>2545</v>
+        <v>2555</v>
       </c>
       <c r="F21"/>
       <c r="H21" s="19" t="s">
@@ -28570,14 +28675,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>2546</v>
+        <v>2556</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>55</v>
       </c>
       <c r="C25"/>
       <c r="D25" t="s">
-        <v>2547</v>
+        <v>2557</v>
       </c>
       <c r="E25" s="19" t="s">
         <v>22</v>
@@ -28614,14 +28719,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>2548</v>
+        <v>2558</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>2549</v>
+        <v>2559</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
-        <v>2550</v>
+        <v>2560</v>
       </c>
       <c r="E27" s="19" t="s">
         <v>22</v>
@@ -28636,14 +28741,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>2551</v>
+        <v>2561</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>2552</v>
+        <v>2562</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="s">
-        <v>2553</v>
+        <v>2563</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>22</v>
@@ -28658,14 +28763,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>2554</v>
+        <v>2564</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="s">
-        <v>2555</v>
+        <v>2565</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>22</v>
@@ -28680,17 +28785,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>2556</v>
+        <v>2566</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C30"/>
       <c r="D30" t="s">
-        <v>2557</v>
+        <v>2567</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>2558</v>
+        <v>2568</v>
       </c>
       <c r="F30"/>
       <c r="H30" s="19" t="s">
@@ -28702,17 +28807,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2559</v>
+        <v>2569</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C31"/>
       <c r="D31" t="s">
-        <v>2560</v>
+        <v>2570</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>2561</v>
+        <v>2571</v>
       </c>
       <c r="F31"/>
       <c r="H31" s="19" t="s">
@@ -28724,17 +28829,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>2562</v>
+        <v>2572</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="s">
-        <v>2563</v>
+        <v>2573</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>2564</v>
+        <v>2574</v>
       </c>
       <c r="F32"/>
       <c r="H32" s="19" t="s">
@@ -28746,17 +28851,17 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>2565</v>
+        <v>2575</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
-        <v>2566</v>
+        <v>2576</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>2567</v>
+        <v>2577</v>
       </c>
       <c r="F33"/>
       <c r="H33" s="19" t="s">
@@ -28768,17 +28873,17 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>2568</v>
+        <v>2578</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C34"/>
       <c r="D34" t="s">
-        <v>2569</v>
+        <v>2579</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>2570</v>
+        <v>2580</v>
       </c>
       <c r="F34"/>
       <c r="H34" s="19" t="s">
@@ -28790,17 +28895,17 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>2571</v>
+        <v>2581</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C35"/>
       <c r="D35" t="s">
-        <v>2572</v>
+        <v>2582</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>2573</v>
+        <v>2583</v>
       </c>
       <c r="F35"/>
       <c r="H35" s="19" t="s">
@@ -28812,17 +28917,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>2574</v>
+        <v>2584</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>2576</v>
+        <v>2586</v>
       </c>
       <c r="F36"/>
       <c r="H36" s="19" t="s">
@@ -28878,7 +28983,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>2577</v>
+        <v>2587</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>626</v>
@@ -28887,7 +28992,7 @@
         <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>2578</v>
+        <v>2588</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>22</v>
@@ -28902,14 +29007,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>2579</v>
+        <v>2589</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C40"/>
       <c r="D40" t="s">
-        <v>2580</v>
+        <v>2590</v>
       </c>
       <c r="E40" s="19" t="s">
         <v>22</v>
@@ -28990,14 +29095,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>2581</v>
+        <v>2591</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>651</v>
       </c>
       <c r="C44"/>
       <c r="D44" t="s">
-        <v>2582</v>
+        <v>2592</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>22</v>
@@ -29012,14 +29117,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>2583</v>
+        <v>2593</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>2584</v>
+        <v>2594</v>
       </c>
       <c r="C45"/>
       <c r="D45" t="s">
-        <v>2585</v>
+        <v>2595</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>22</v>
@@ -29034,17 +29139,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>2586</v>
+        <v>2596</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>2587</v>
+        <v>2597</v>
       </c>
       <c r="C46"/>
       <c r="D46" t="s">
-        <v>2588</v>
+        <v>2598</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>2589</v>
+        <v>2599</v>
       </c>
       <c r="F46"/>
       <c r="H46" s="19" t="s">
@@ -29058,14 +29163,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>2590</v>
+        <v>2600</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>2591</v>
+        <v>2601</v>
       </c>
       <c r="C47"/>
       <c r="D47" t="s">
-        <v>2592</v>
+        <v>2602</v>
       </c>
       <c r="E47" s="19" t="s">
         <v>22</v>
@@ -29082,14 +29187,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>2593</v>
+        <v>2603</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>2594</v>
+        <v>2604</v>
       </c>
       <c r="C48"/>
       <c r="D48" t="s">
-        <v>2595</v>
+        <v>2605</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>22</v>
@@ -29106,14 +29211,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>2596</v>
+        <v>2606</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>2597</v>
+        <v>2607</v>
       </c>
       <c r="C49"/>
       <c r="D49" t="s">
-        <v>2598</v>
+        <v>2608</v>
       </c>
       <c r="E49" s="19" t="s">
         <v>22</v>
@@ -29174,14 +29279,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>2599</v>
+        <v>2609</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C52"/>
       <c r="D52" t="s">
-        <v>2600</v>
+        <v>2610</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>22</v>
@@ -29215,13 +29320,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>2515</v>
+        <v>2525</v>
       </c>
       <c r="B55" t="s">
-        <v>2601</v>
+        <v>2611</v>
       </c>
       <c r="C55" t="s">
-        <v>2602</v>
+        <v>2612</v>
       </c>
       <c r="D55" t="s">
         <v>22</v>
@@ -29233,10 +29338,10 @@
     <row r="56">
       <c r="A56"/>
       <c r="B56" t="s">
-        <v>2453</v>
+        <v>2463</v>
       </c>
       <c r="C56" t="s">
-        <v>2454</v>
+        <v>2464</v>
       </c>
       <c r="D56" t="s">
         <v>22</v>
@@ -29263,10 +29368,10 @@
     <row r="58">
       <c r="A58"/>
       <c r="B58" t="s">
-        <v>2603</v>
+        <v>2613</v>
       </c>
       <c r="C58" t="s">
-        <v>2604</v>
+        <v>2614</v>
       </c>
       <c r="D58" t="s">
         <v>22</v>
@@ -29309,13 +29414,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>2519</v>
+        <v>2529</v>
       </c>
       <c r="B62" t="s">
-        <v>2505</v>
+        <v>2515</v>
       </c>
       <c r="C62" t="s">
-        <v>2605</v>
+        <v>2615</v>
       </c>
       <c r="D62" t="s">
         <v>22</v>
@@ -29327,10 +29432,10 @@
     <row r="63">
       <c r="A63"/>
       <c r="B63" t="s">
-        <v>2606</v>
+        <v>2616</v>
       </c>
       <c r="C63" t="s">
-        <v>2607</v>
+        <v>2617</v>
       </c>
       <c r="D63" t="s">
         <v>22</v>
@@ -29342,10 +29447,10 @@
     <row r="64">
       <c r="A64"/>
       <c r="B64" t="s">
-        <v>2501</v>
+        <v>2511</v>
       </c>
       <c r="C64" t="s">
-        <v>2608</v>
+        <v>2618</v>
       </c>
       <c r="D64" t="s">
         <v>22</v>
@@ -29388,7 +29493,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>2522</v>
+        <v>2532</v>
       </c>
       <c r="B68" t="s">
         <v>936</v>
@@ -29406,10 +29511,10 @@
     <row r="69">
       <c r="A69"/>
       <c r="B69" t="s">
-        <v>2609</v>
+        <v>2619</v>
       </c>
       <c r="C69" t="s">
-        <v>2610</v>
+        <v>2620</v>
       </c>
       <c r="D69" t="s">
         <v>22</v>
@@ -29467,7 +29572,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>2528</v>
+        <v>2538</v>
       </c>
       <c r="B74" t="s">
         <v>936</v>
@@ -29485,7 +29590,7 @@
     <row r="75">
       <c r="A75"/>
       <c r="B75" t="s">
-        <v>2609</v>
+        <v>2619</v>
       </c>
       <c r="C75" t="s">
         <v>1046</v>
@@ -29515,10 +29620,10 @@
     <row r="77">
       <c r="A77"/>
       <c r="B77" t="s">
-        <v>2611</v>
+        <v>2621</v>
       </c>
       <c r="C77" t="s">
-        <v>2612</v>
+        <v>2622</v>
       </c>
       <c r="D77" t="s">
         <v>22</v>
@@ -29967,13 +30072,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>2549</v>
+        <v>2559</v>
       </c>
       <c r="B111" t="s">
-        <v>2613</v>
+        <v>2623</v>
       </c>
       <c r="C111" t="s">
-        <v>2614</v>
+        <v>2624</v>
       </c>
       <c r="D111" t="s">
         <v>22</v>
@@ -29985,10 +30090,10 @@
     <row r="112">
       <c r="A112"/>
       <c r="B112" t="s">
-        <v>2615</v>
+        <v>2625</v>
       </c>
       <c r="C112" t="s">
-        <v>2616</v>
+        <v>2626</v>
       </c>
       <c r="D112" t="s">
         <v>22</v>
@@ -30000,10 +30105,10 @@
     <row r="113">
       <c r="A113"/>
       <c r="B113" t="s">
-        <v>2617</v>
+        <v>2627</v>
       </c>
       <c r="C113" t="s">
-        <v>2618</v>
+        <v>2628</v>
       </c>
       <c r="D113" t="s">
         <v>22</v>
@@ -30015,10 +30120,10 @@
     <row r="114">
       <c r="A114"/>
       <c r="B114" t="s">
-        <v>2619</v>
+        <v>2629</v>
       </c>
       <c r="C114" t="s">
-        <v>2620</v>
+        <v>2630</v>
       </c>
       <c r="D114" t="s">
         <v>22</v>
@@ -30030,10 +30135,10 @@
     <row r="115">
       <c r="A115"/>
       <c r="B115" t="s">
-        <v>2621</v>
+        <v>2631</v>
       </c>
       <c r="C115" t="s">
-        <v>2622</v>
+        <v>2632</v>
       </c>
       <c r="D115" t="s">
         <v>22</v>
@@ -30061,13 +30166,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>2552</v>
+        <v>2562</v>
       </c>
       <c r="B118" t="s">
-        <v>2623</v>
+        <v>2633</v>
       </c>
       <c r="C118" t="s">
-        <v>2624</v>
+        <v>2634</v>
       </c>
       <c r="D118" t="s">
         <v>22</v>
@@ -30079,10 +30184,10 @@
     <row r="119">
       <c r="A119"/>
       <c r="B119" t="s">
-        <v>2625</v>
+        <v>2635</v>
       </c>
       <c r="C119" t="s">
-        <v>2626</v>
+        <v>2636</v>
       </c>
       <c r="D119" t="s">
         <v>22</v>
@@ -30094,10 +30199,10 @@
     <row r="120">
       <c r="A120"/>
       <c r="B120" t="s">
-        <v>2627</v>
+        <v>2637</v>
       </c>
       <c r="C120" t="s">
-        <v>2628</v>
+        <v>2638</v>
       </c>
       <c r="D120" t="s">
         <v>22</v>
@@ -30109,10 +30214,10 @@
     <row r="121">
       <c r="A121"/>
       <c r="B121" t="s">
-        <v>2629</v>
+        <v>2639</v>
       </c>
       <c r="C121" t="s">
-        <v>2630</v>
+        <v>2640</v>
       </c>
       <c r="D121" t="s">
         <v>22</v>
@@ -30124,10 +30229,10 @@
     <row r="122">
       <c r="A122"/>
       <c r="B122" t="s">
-        <v>2631</v>
+        <v>2641</v>
       </c>
       <c r="C122" t="s">
-        <v>2632</v>
+        <v>2642</v>
       </c>
       <c r="D122" t="s">
         <v>22</v>
@@ -31029,13 +31134,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>2584</v>
+        <v>2594</v>
       </c>
       <c r="B184" t="s">
-        <v>2633</v>
+        <v>2643</v>
       </c>
       <c r="C184" t="s">
-        <v>2634</v>
+        <v>2644</v>
       </c>
       <c r="D184" t="s">
         <v>22</v>
@@ -31047,10 +31152,10 @@
     <row r="185">
       <c r="A185"/>
       <c r="B185" t="s">
-        <v>2260</v>
+        <v>2270</v>
       </c>
       <c r="C185" t="s">
-        <v>2635</v>
+        <v>2645</v>
       </c>
       <c r="D185" t="s">
         <v>22</v>
@@ -31062,10 +31167,10 @@
     <row r="186">
       <c r="A186"/>
       <c r="B186" t="s">
-        <v>2262</v>
+        <v>2272</v>
       </c>
       <c r="C186" t="s">
-        <v>2636</v>
+        <v>2646</v>
       </c>
       <c r="D186" t="s">
         <v>22</v>
@@ -31077,10 +31182,10 @@
     <row r="187">
       <c r="A187"/>
       <c r="B187" t="s">
-        <v>2637</v>
+        <v>2647</v>
       </c>
       <c r="C187" t="s">
-        <v>2638</v>
+        <v>2648</v>
       </c>
       <c r="D187" t="s">
         <v>22</v>
@@ -31092,10 +31197,10 @@
     <row r="188">
       <c r="A188"/>
       <c r="B188" t="s">
-        <v>2639</v>
+        <v>2649</v>
       </c>
       <c r="C188" t="s">
-        <v>2640</v>
+        <v>2650</v>
       </c>
       <c r="D188" t="s">
         <v>22</v>
@@ -31138,7 +31243,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>2587</v>
+        <v>2597</v>
       </c>
       <c r="B192" t="s">
         <v>893</v>
@@ -31217,13 +31322,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>2591</v>
+        <v>2601</v>
       </c>
       <c r="B198" t="s">
-        <v>2641</v>
+        <v>2651</v>
       </c>
       <c r="C198" t="s">
-        <v>2642</v>
+        <v>2652</v>
       </c>
       <c r="D198" t="s">
         <v>22</v>
@@ -31235,10 +31340,10 @@
     <row r="199">
       <c r="A199"/>
       <c r="B199" t="s">
-        <v>2643</v>
+        <v>2653</v>
       </c>
       <c r="C199" t="s">
-        <v>2644</v>
+        <v>2654</v>
       </c>
       <c r="D199" t="s">
         <v>22</v>
@@ -31250,10 +31355,10 @@
     <row r="200">
       <c r="A200"/>
       <c r="B200" t="s">
-        <v>2645</v>
+        <v>2655</v>
       </c>
       <c r="C200" t="s">
-        <v>2646</v>
+        <v>2656</v>
       </c>
       <c r="D200" t="s">
         <v>22</v>
@@ -31265,10 +31370,10 @@
     <row r="201">
       <c r="A201"/>
       <c r="B201" t="s">
-        <v>2647</v>
+        <v>2657</v>
       </c>
       <c r="C201" t="s">
-        <v>2648</v>
+        <v>2658</v>
       </c>
       <c r="D201" t="s">
         <v>22</v>
@@ -31280,10 +31385,10 @@
     <row r="202">
       <c r="A202"/>
       <c r="B202" t="s">
-        <v>2649</v>
+        <v>2659</v>
       </c>
       <c r="C202" t="s">
-        <v>2650</v>
+        <v>2660</v>
       </c>
       <c r="D202" t="s">
         <v>22</v>
@@ -31295,10 +31400,10 @@
     <row r="203">
       <c r="A203"/>
       <c r="B203" t="s">
-        <v>2651</v>
+        <v>2661</v>
       </c>
       <c r="C203" t="s">
-        <v>2652</v>
+        <v>2662</v>
       </c>
       <c r="D203" t="s">
         <v>22</v>
@@ -31341,13 +31446,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>2594</v>
+        <v>2604</v>
       </c>
       <c r="B207" t="s">
-        <v>2653</v>
+        <v>2663</v>
       </c>
       <c r="C207" t="s">
-        <v>2654</v>
+        <v>2664</v>
       </c>
       <c r="D207" t="s">
         <v>22</v>
@@ -31359,10 +31464,10 @@
     <row r="208">
       <c r="A208"/>
       <c r="B208" t="s">
-        <v>2655</v>
+        <v>2665</v>
       </c>
       <c r="C208" t="s">
-        <v>2656</v>
+        <v>2666</v>
       </c>
       <c r="D208" t="s">
         <v>22</v>
@@ -31374,10 +31479,10 @@
     <row r="209">
       <c r="A209"/>
       <c r="B209" t="s">
-        <v>2657</v>
+        <v>2667</v>
       </c>
       <c r="C209" t="s">
-        <v>2658</v>
+        <v>2668</v>
       </c>
       <c r="D209" t="s">
         <v>22</v>
@@ -31389,10 +31494,10 @@
     <row r="210">
       <c r="A210"/>
       <c r="B210" t="s">
-        <v>2659</v>
+        <v>2669</v>
       </c>
       <c r="C210" t="s">
-        <v>2660</v>
+        <v>2670</v>
       </c>
       <c r="D210" t="s">
         <v>22</v>
@@ -31404,10 +31509,10 @@
     <row r="211">
       <c r="A211"/>
       <c r="B211" t="s">
-        <v>2661</v>
+        <v>2671</v>
       </c>
       <c r="C211" t="s">
-        <v>2662</v>
+        <v>2672</v>
       </c>
       <c r="D211" t="s">
         <v>22</v>
@@ -31450,13 +31555,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>2597</v>
+        <v>2607</v>
       </c>
       <c r="B215" t="s">
-        <v>2663</v>
+        <v>2673</v>
       </c>
       <c r="C215" t="s">
-        <v>2664</v>
+        <v>2674</v>
       </c>
       <c r="D215" t="s">
         <v>22</v>
@@ -31468,10 +31573,10 @@
     <row r="216">
       <c r="A216"/>
       <c r="B216" t="s">
-        <v>2665</v>
+        <v>2675</v>
       </c>
       <c r="C216" t="s">
-        <v>2666</v>
+        <v>2676</v>
       </c>
       <c r="D216" t="s">
         <v>22</v>
@@ -31483,10 +31588,10 @@
     <row r="217">
       <c r="A217"/>
       <c r="B217" t="s">
-        <v>2667</v>
+        <v>2677</v>
       </c>
       <c r="C217" t="s">
-        <v>2668</v>
+        <v>2678</v>
       </c>
       <c r="D217" t="s">
         <v>22</v>
@@ -31498,10 +31603,10 @@
     <row r="218">
       <c r="A218"/>
       <c r="B218" t="s">
-        <v>2669</v>
+        <v>2679</v>
       </c>
       <c r="C218" t="s">
-        <v>2670</v>
+        <v>2680</v>
       </c>
       <c r="D218" t="s">
         <v>22</v>
@@ -31513,10 +31618,10 @@
     <row r="219">
       <c r="A219"/>
       <c r="B219" t="s">
-        <v>2671</v>
+        <v>2681</v>
       </c>
       <c r="C219" t="s">
-        <v>2672</v>
+        <v>2682</v>
       </c>
       <c r="D219" t="s">
         <v>22</v>
@@ -33294,14 +33399,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2416</v>
+        <v>2426</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2454</v>
+        <v>2464</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>22</v>
@@ -33321,11 +33426,11 @@
         <v>617</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>2673</v>
+        <v>2683</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2673</v>
+        <v>2683</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>22</v>
@@ -33342,7 +33447,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2674</v>
+        <v>2684</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>12</v>
@@ -33351,7 +33456,7 @@
         <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>2675</v>
+        <v>2685</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>22</v>
@@ -33476,7 +33581,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>2676</v>
+        <v>2686</v>
       </c>
       <c r="B11" s="20" t="s">
         <v>140</v>
@@ -33559,14 +33664,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2677</v>
+        <v>2687</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>2678</v>
+        <v>2688</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2679</v>
+        <v>2689</v>
       </c>
       <c r="E2" s="21" t="s">
         <v>22</v>
@@ -33583,14 +33688,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2416</v>
+        <v>2426</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>2417</v>
+        <v>2427</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2418</v>
+        <v>2428</v>
       </c>
       <c r="E3" s="21" t="s">
         <v>22</v>
@@ -33605,14 +33710,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2680</v>
+        <v>2690</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>2681</v>
+        <v>2691</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2682</v>
+        <v>2692</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>22</v>
@@ -33627,14 +33732,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2424</v>
+        <v>2434</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2683</v>
+        <v>2693</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2426</v>
+        <v>2436</v>
       </c>
       <c r="E5" s="21" t="s">
         <v>22</v>
@@ -33649,7 +33754,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2684</v>
+        <v>2694</v>
       </c>
       <c r="B6" s="21" t="s">
         <v>55</v>
@@ -33673,14 +33778,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2685</v>
+        <v>2695</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>2686</v>
+        <v>2696</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>2687</v>
+        <v>2697</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>22</v>
@@ -33695,7 +33800,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>2434</v>
+        <v>2444</v>
       </c>
       <c r="B8" s="21" t="s">
         <v>55</v>
@@ -33717,14 +33822,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2438</v>
+        <v>2448</v>
       </c>
       <c r="B9" s="21" t="s">
         <v>626</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2439</v>
+        <v>2449</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>22</v>
@@ -33739,14 +33844,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>2688</v>
+        <v>2698</v>
       </c>
       <c r="B10" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
-        <v>2531</v>
+        <v>2541</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>22</v>
@@ -33783,14 +33888,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>2689</v>
+        <v>2699</v>
       </c>
       <c r="B12" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2445</v>
+        <v>2455</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>22</v>
@@ -33805,14 +33910,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>2690</v>
+        <v>2700</v>
       </c>
       <c r="B13" s="21" t="s">
         <v>626</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2691</v>
+        <v>2701</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>22</v>
@@ -33844,13 +33949,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2678</v>
+        <v>2688</v>
       </c>
       <c r="B16" t="s">
-        <v>2453</v>
+        <v>2463</v>
       </c>
       <c r="C16" t="s">
-        <v>2454</v>
+        <v>2464</v>
       </c>
       <c r="D16" t="s">
         <v>22</v>
@@ -33878,13 +33983,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2681</v>
+        <v>2691</v>
       </c>
       <c r="B19" t="s">
-        <v>2692</v>
+        <v>2702</v>
       </c>
       <c r="C19" t="s">
-        <v>2693</v>
+        <v>2703</v>
       </c>
       <c r="D19" t="s">
         <v>22</v>
@@ -33896,10 +34001,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>2468</v>
+        <v>2478</v>
       </c>
       <c r="C20" t="s">
-        <v>2694</v>
+        <v>2704</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -33911,10 +34016,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>2695</v>
+        <v>2705</v>
       </c>
       <c r="C21" t="s">
-        <v>2696</v>
+        <v>2706</v>
       </c>
       <c r="D21" t="s">
         <v>22</v>
@@ -33926,10 +34031,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>2472</v>
+        <v>2482</v>
       </c>
       <c r="C22" t="s">
-        <v>2697</v>
+        <v>2707</v>
       </c>
       <c r="D22" t="s">
         <v>22</v>
@@ -33941,10 +34046,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>2698</v>
+        <v>2708</v>
       </c>
       <c r="C23" t="s">
-        <v>2699</v>
+        <v>2709</v>
       </c>
       <c r="D23" t="s">
         <v>22</v>
@@ -33956,10 +34061,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>2700</v>
+        <v>2710</v>
       </c>
       <c r="C24" t="s">
-        <v>2701</v>
+        <v>2711</v>
       </c>
       <c r="D24" t="s">
         <v>22</v>
@@ -33971,10 +34076,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>2702</v>
+        <v>2712</v>
       </c>
       <c r="C25" t="s">
-        <v>2703</v>
+        <v>2713</v>
       </c>
       <c r="D25" t="s">
         <v>22</v>
@@ -33986,10 +34091,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>2704</v>
+        <v>2714</v>
       </c>
       <c r="C26" t="s">
-        <v>2705</v>
+        <v>2715</v>
       </c>
       <c r="D26" t="s">
         <v>22</v>
@@ -34001,10 +34106,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>2706</v>
+        <v>2716</v>
       </c>
       <c r="C27" t="s">
-        <v>2707</v>
+        <v>2717</v>
       </c>
       <c r="D27" t="s">
         <v>22</v>
@@ -34047,13 +34152,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>2683</v>
+        <v>2693</v>
       </c>
       <c r="B31" t="s">
-        <v>2501</v>
+        <v>2511</v>
       </c>
       <c r="C31" t="s">
-        <v>2502</v>
+        <v>2512</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
@@ -34065,10 +34170,10 @@
     <row r="32">
       <c r="A32"/>
       <c r="B32" t="s">
-        <v>2503</v>
+        <v>2513</v>
       </c>
       <c r="C32" t="s">
-        <v>2504</v>
+        <v>2514</v>
       </c>
       <c r="D32" t="s">
         <v>22</v>
@@ -34080,10 +34185,10 @@
     <row r="33">
       <c r="A33"/>
       <c r="B33" t="s">
-        <v>2505</v>
+        <v>2515</v>
       </c>
       <c r="C33" t="s">
-        <v>2506</v>
+        <v>2516</v>
       </c>
       <c r="D33" t="s">
         <v>22</v>
@@ -34111,7 +34216,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>2686</v>
+        <v>2696</v>
       </c>
       <c r="B36" t="s">
         <v>936</v>
@@ -34129,10 +34234,10 @@
     <row r="37">
       <c r="A37"/>
       <c r="B37" t="s">
-        <v>2708</v>
+        <v>2718</v>
       </c>
       <c r="C37" t="s">
-        <v>2709</v>
+        <v>2719</v>
       </c>
       <c r="D37" t="s">
         <v>22</v>
@@ -34223,14 +34328,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2710</v>
+        <v>2720</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2711</v>
+        <v>2721</v>
       </c>
       <c r="E2" s="22" t="s">
         <v>22</v>
@@ -34450,7 +34555,7 @@
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
-        <v>2712</v>
+        <v>2722</v>
       </c>
       <c r="E12" s="22" t="s">
         <v>22</v>
@@ -34472,7 +34577,7 @@
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
-        <v>2713</v>
+        <v>2723</v>
       </c>
       <c r="E13" s="22" t="s">
         <v>22</v>
@@ -34487,7 +34592,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2714</v>
+        <v>2724</v>
       </c>
       <c r="B14" s="22" t="s">
         <v>69</v>
@@ -34509,14 +34614,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>2715</v>
+        <v>2725</v>
       </c>
       <c r="B15" s="22" t="s">
         <v>140</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2716</v>
+        <v>2726</v>
       </c>
       <c r="E15" s="22" t="s">
         <v>22</v>
@@ -34531,14 +34636,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2717</v>
+        <v>2727</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>140</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2718</v>
+        <v>2728</v>
       </c>
       <c r="E16" s="22" t="s">
         <v>22</v>
@@ -35621,14 +35726,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2719</v>
+        <v>2729</v>
       </c>
       <c r="B2" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2720</v>
+        <v>2730</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>22</v>
@@ -35665,14 +35770,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2721</v>
+        <v>2731</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2722</v>
+        <v>2732</v>
       </c>
       <c r="E4" s="23" t="s">
         <v>22</v>
@@ -35687,14 +35792,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2723</v>
+        <v>2733</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>12</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2724</v>
+        <v>2734</v>
       </c>
       <c r="E5" s="23" t="s">
         <v>22</v>
@@ -35709,14 +35814,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2717</v>
+        <v>2727</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>140</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2718</v>
+        <v>2728</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>22</v>
@@ -35792,14 +35897,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2710</v>
+        <v>2720</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2711</v>
+        <v>2721</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>22</v>
@@ -35814,14 +35919,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2725</v>
+        <v>2735</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>12</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2726</v>
+        <v>2736</v>
       </c>
       <c r="E3" s="24" t="s">
         <v>22</v>
@@ -35836,14 +35941,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2727</v>
+        <v>2737</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>42</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2728</v>
+        <v>2738</v>
       </c>
       <c r="E4" s="24" t="s">
         <v>22</v>
@@ -35858,14 +35963,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2717</v>
+        <v>2727</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>140</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2718</v>
+        <v>2728</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>22</v>
@@ -35902,10 +36007,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>2729</v>
+        <v>2739</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>2730</v>
+        <v>2740</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
@@ -35985,14 +36090,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2710</v>
+        <v>2720</v>
       </c>
       <c r="B2" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2711</v>
+        <v>2721</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>22</v>
@@ -36007,14 +36112,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2725</v>
+        <v>2735</v>
       </c>
       <c r="B3" s="25" t="s">
         <v>12</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2726</v>
+        <v>2736</v>
       </c>
       <c r="E3" s="25" t="s">
         <v>22</v>
@@ -36029,14 +36134,14 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2727</v>
+        <v>2737</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>42</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>2728</v>
+        <v>2738</v>
       </c>
       <c r="E4" s="25" t="s">
         <v>22</v>
@@ -36073,14 +36178,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2717</v>
+        <v>2727</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>140</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2718</v>
+        <v>2728</v>
       </c>
       <c r="E6" s="25" t="s">
         <v>22</v>
@@ -36178,14 +36283,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2710</v>
+        <v>2720</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>12</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2711</v>
+        <v>2721</v>
       </c>
       <c r="E2" s="26" t="s">
         <v>22</v>
@@ -36244,14 +36349,14 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2717</v>
+        <v>2727</v>
       </c>
       <c r="B5" s="26" t="s">
         <v>140</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
-        <v>2718</v>
+        <v>2728</v>
       </c>
       <c r="E5" s="26" t="s">
         <v>22</v>
@@ -36349,14 +36454,14 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2731</v>
+        <v>2741</v>
       </c>
       <c r="B2" s="27" t="s">
         <v>140</v>
       </c>
       <c r="C2"/>
       <c r="D2" t="s">
-        <v>2732</v>
+        <v>2742</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>22</v>
@@ -36371,14 +36476,14 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>2733</v>
+        <v>2743</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>12</v>
       </c>
       <c r="C3"/>
       <c r="D3" t="s">
-        <v>2734</v>
+        <v>2744</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>22</v>
@@ -36437,14 +36542,14 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>2735</v>
+        <v>2745</v>
       </c>
       <c r="B6" s="27" t="s">
         <v>12</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
-        <v>2566</v>
+        <v>2576</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>22</v>
@@ -36488,7 +36593,7 @@
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
-        <v>2736</v>
+        <v>2746</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>22</v>
@@ -36503,12 +36608,12 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>2737</v>
+        <v>2747</v>
       </c>
       <c r="B9" s="27"/>
       <c r="C9"/>
       <c r="D9" t="s">
-        <v>2738</v>
+        <v>2748</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>22</v>
@@ -36611,7 +36716,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>2739</v>
+        <v>2749</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>72</v>
@@ -36640,7 +36745,7 @@
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
-        <v>2740</v>
+        <v>2750</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>22</v>
@@ -36655,14 +36760,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>2741</v>
+        <v>2751</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>626</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>2742</v>
+        <v>2752</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>22</v>
@@ -36677,17 +36782,17 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>2743</v>
+        <v>2753</v>
       </c>
       <c r="B17" s="27" t="s">
         <v>91</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>2744</v>
+        <v>2754</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>2745</v>
+        <v>2755</v>
       </c>
       <c r="F17"/>
       <c r="H17" s="27" t="s">
@@ -36699,10 +36804,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>2746</v>
+        <v>2756</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>2747</v>
+        <v>2757</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
@@ -36721,14 +36826,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>2748</v>
+        <v>2758</v>
       </c>
       <c r="B19" s="27" t="s">
         <v>140</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
-        <v>2749</v>
+        <v>2759</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>22</v>
@@ -37671,13 +37776,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>2747</v>
+        <v>2757</v>
       </c>
       <c r="B85" t="s">
-        <v>2750</v>
+        <v>2760</v>
       </c>
       <c r="C85" t="s">
-        <v>2751</v>
+        <v>2761</v>
       </c>
       <c r="D85" t="s">
         <v>22</v>
@@ -37689,10 +37794,10 @@
     <row r="86">
       <c r="A86"/>
       <c r="B86" t="s">
-        <v>2752</v>
+        <v>2762</v>
       </c>
       <c r="C86" t="s">
-        <v>2753</v>
+        <v>2763</v>
       </c>
       <c r="D86" t="s">
         <v>22</v>
@@ -37704,10 +37809,10 @@
     <row r="87">
       <c r="A87"/>
       <c r="B87" t="s">
-        <v>2754</v>
+        <v>2764</v>
       </c>
       <c r="C87" t="s">
-        <v>2755</v>
+        <v>2765</v>
       </c>
       <c r="D87" t="s">
         <v>22</v>
@@ -37719,10 +37824,10 @@
     <row r="88">
       <c r="A88"/>
       <c r="B88" t="s">
-        <v>2756</v>
+        <v>2766</v>
       </c>
       <c r="C88" t="s">
-        <v>2757</v>
+        <v>2767</v>
       </c>
       <c r="D88" t="s">
         <v>22</v>
@@ -37734,10 +37839,10 @@
     <row r="89">
       <c r="A89"/>
       <c r="B89" t="s">
-        <v>2758</v>
+        <v>2768</v>
       </c>
       <c r="C89" t="s">
-        <v>2759</v>
+        <v>2769</v>
       </c>
       <c r="D89" t="s">
         <v>22</v>
@@ -37749,10 +37854,10 @@
     <row r="90">
       <c r="A90"/>
       <c r="B90" t="s">
-        <v>2760</v>
+        <v>2770</v>
       </c>
       <c r="C90" t="s">
-        <v>2761</v>
+        <v>2771</v>
       </c>
       <c r="D90" t="s">
         <v>22</v>
@@ -37764,10 +37869,10 @@
     <row r="91">
       <c r="A91"/>
       <c r="B91" t="s">
-        <v>2762</v>
+        <v>2772</v>
       </c>
       <c r="C91" t="s">
-        <v>2763</v>
+        <v>2773</v>
       </c>
       <c r="D91" t="s">
         <v>22</v>
@@ -37779,10 +37884,10 @@
     <row r="92">
       <c r="A92"/>
       <c r="B92" t="s">
-        <v>2764</v>
+        <v>2774</v>
       </c>
       <c r="C92" t="s">
-        <v>2765</v>
+        <v>2775</v>
       </c>
       <c r="D92" t="s">
         <v>22</v>
@@ -37794,10 +37899,10 @@
     <row r="93">
       <c r="A93"/>
       <c r="B93" t="s">
-        <v>2766</v>
+        <v>2776</v>
       </c>
       <c r="C93" t="s">
-        <v>2767</v>
+        <v>2777</v>
       </c>
       <c r="D93" t="s">
         <v>22</v>
@@ -37809,10 +37914,10 @@
     <row r="94">
       <c r="A94"/>
       <c r="B94" t="s">
-        <v>2768</v>
+        <v>2778</v>
       </c>
       <c r="C94" t="s">
-        <v>2769</v>
+        <v>2779</v>
       </c>
       <c r="D94" t="s">
         <v>22</v>
@@ -37824,10 +37929,10 @@
     <row r="95">
       <c r="A95"/>
       <c r="B95" t="s">
-        <v>2770</v>
+        <v>2780</v>
       </c>
       <c r="C95" t="s">
-        <v>2771</v>
+        <v>2781</v>
       </c>
       <c r="D95" t="s">
         <v>22</v>
@@ -37839,10 +37944,10 @@
     <row r="96">
       <c r="A96"/>
       <c r="B96" t="s">
-        <v>2772</v>
+        <v>2782</v>
       </c>
       <c r="C96" t="s">
-        <v>2773</v>
+        <v>2783</v>
       </c>
       <c r="D96" t="s">
         <v>22</v>
@@ -37854,10 +37959,10 @@
     <row r="97">
       <c r="A97"/>
       <c r="B97" t="s">
-        <v>2774</v>
+        <v>2784</v>
       </c>
       <c r="C97" t="s">
-        <v>2775</v>
+        <v>2785</v>
       </c>
       <c r="D97" t="s">
         <v>22</v>
@@ -37869,10 +37974,10 @@
     <row r="98">
       <c r="A98"/>
       <c r="B98" t="s">
-        <v>2776</v>
+        <v>2786</v>
       </c>
       <c r="C98" t="s">
-        <v>2777</v>
+        <v>2787</v>
       </c>
       <c r="D98" t="s">
         <v>22</v>
@@ -37884,10 +37989,10 @@
     <row r="99">
       <c r="A99"/>
       <c r="B99" t="s">
-        <v>2778</v>
+        <v>2788</v>
       </c>
       <c r="C99" t="s">
-        <v>2779</v>
+        <v>2789</v>
       </c>
       <c r="D99" t="s">
         <v>22</v>
@@ -37914,12 +38019,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2780</v>
+        <v>2790</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2781</v>
+        <v>2791</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_Data_Dictionary.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12411" uniqueCount="2878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12501" uniqueCount="2878">
   <si>
     <t>Field</t>
   </si>
@@ -89,6 +89,9 @@
     <t/>
   </si>
   <si>
+    <t>All</t>
+  </si>
+  <si>
     <t>changeDate</t>
   </si>
   <si>
@@ -111,9 +114,6 @@
   </si>
   <si>
     <t>Enter the first name of the person</t>
-  </si>
-  <si>
-    <t>All</t>
   </si>
   <si>
     <t>lastName</t>
@@ -11456,10 +11456,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>12</v>
@@ -11472,44 +11478,58 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -11522,10 +11542,10 @@
         <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -11537,7 +11557,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -11553,7 +11573,7 @@
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>28</v>
@@ -11563,7 +11583,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -11576,10 +11596,10 @@
         <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
@@ -11589,7 +11609,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -11600,10 +11620,10 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -11613,7 +11633,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -11626,10 +11646,10 @@
         <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>35</v>
@@ -11639,7 +11659,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -11650,10 +11670,10 @@
         <v>36</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>37</v>
@@ -11663,7 +11683,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -11674,10 +11694,10 @@
         <v>38</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>39</v>
@@ -11687,7 +11707,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -11698,10 +11718,10 @@
         <v>40</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
@@ -11711,7 +11731,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -11722,10 +11742,10 @@
         <v>42</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -11735,7 +11755,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -11759,7 +11779,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -11775,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
         <v>49</v>
@@ -11785,7 +11805,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -11809,7 +11829,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -11833,7 +11853,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -11857,7 +11877,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -11881,7 +11901,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -11905,7 +11925,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -12042,7 +12062,7 @@
         <v>79</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
         <v>71</v>
@@ -12127,7 +12147,7 @@
       </c>
       <c r="F30"/>
       <c r="H30" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I30" t="b">
         <v>1</v>
@@ -12151,7 +12171,7 @@
       </c>
       <c r="F31"/>
       <c r="H31" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -12173,7 +12193,7 @@
       </c>
       <c r="F32"/>
       <c r="H32" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -12195,7 +12215,7 @@
       </c>
       <c r="F33"/>
       <c r="H33" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -12206,7 +12226,7 @@
         <v>98</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34" t="s">
         <v>71</v>
@@ -12219,7 +12239,7 @@
       </c>
       <c r="F34"/>
       <c r="H34" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
@@ -12252,7 +12272,7 @@
         <v>104</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C36" t="s">
         <v>71</v>
@@ -12298,7 +12318,7 @@
         <v>109</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
         <v>71</v>
@@ -12355,7 +12375,7 @@
       </c>
       <c r="F40"/>
       <c r="H40" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I40"/>
       <c r="J40"/>
@@ -12377,7 +12397,7 @@
       </c>
       <c r="F41"/>
       <c r="H41" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
@@ -12388,7 +12408,7 @@
         <v>120</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
         <v>71</v>
@@ -12401,7 +12421,7 @@
       </c>
       <c r="F42"/>
       <c r="H42" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
@@ -12423,7 +12443,7 @@
       </c>
       <c r="F43"/>
       <c r="H43" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
@@ -12434,7 +12454,7 @@
         <v>125</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C44" t="s">
         <v>71</v>
@@ -12447,7 +12467,7 @@
       </c>
       <c r="F44"/>
       <c r="H44" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
@@ -12471,7 +12491,7 @@
       </c>
       <c r="F45"/>
       <c r="H45" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
@@ -12484,7 +12504,7 @@
         <v>129</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C46" t="s">
         <v>71</v>
@@ -12497,7 +12517,7 @@
       </c>
       <c r="F46"/>
       <c r="H46" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
@@ -12508,7 +12528,7 @@
         <v>131</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
         <v>71</v>
@@ -12521,7 +12541,7 @@
       </c>
       <c r="F47"/>
       <c r="H47" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
@@ -12541,7 +12561,7 @@
       </c>
       <c r="F48"/>
       <c r="H48" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
@@ -12561,7 +12581,7 @@
       </c>
       <c r="F49"/>
       <c r="H49" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -12631,7 +12651,7 @@
       </c>
       <c r="F52"/>
       <c r="H52" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
@@ -12642,7 +12662,7 @@
         <v>146</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C53" t="s">
         <v>71</v>
@@ -12655,7 +12675,7 @@
       </c>
       <c r="F53"/>
       <c r="H53" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
@@ -12668,7 +12688,7 @@
         <v>148</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54"/>
       <c r="D54" t="s">
@@ -12679,7 +12699,7 @@
       </c>
       <c r="F54"/>
       <c r="H54" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
@@ -12705,7 +12725,7 @@
       </c>
       <c r="F55"/>
       <c r="H55" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
@@ -12731,7 +12751,7 @@
       </c>
       <c r="F56"/>
       <c r="H56" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
@@ -12744,7 +12764,7 @@
         <v>155</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C57" t="s">
         <v>71</v>
@@ -12757,7 +12777,7 @@
       </c>
       <c r="F57"/>
       <c r="H57" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
@@ -16017,10 +16037,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="10" t="s">
         <v>12</v>
@@ -16033,13 +16059,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -16049,6 +16081,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -16066,7 +16106,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -16088,7 +16128,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -16110,7 +16150,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -16132,7 +16172,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -16154,7 +16194,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -16196,7 +16236,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -16216,7 +16256,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="10" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -16363,10 +16403,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>12</v>
@@ -16379,13 +16425,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -16395,6 +16447,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -16414,7 +16474,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -16436,7 +16496,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -16460,7 +16520,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -16482,7 +16542,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -16493,7 +16553,7 @@
         <v>1133</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>71</v>
@@ -16506,7 +16566,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -16530,7 +16590,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -16541,7 +16601,7 @@
         <v>1801</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>71</v>
@@ -16554,7 +16614,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -16576,7 +16636,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -16598,7 +16658,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -16620,7 +16680,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -16631,7 +16691,7 @@
         <v>1146</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>71</v>
@@ -16644,7 +16704,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -16666,7 +16726,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -16677,7 +16737,7 @@
         <v>1151</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>71</v>
@@ -16690,7 +16750,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -16701,7 +16761,7 @@
         <v>1153</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
@@ -16714,7 +16774,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -16725,7 +16785,7 @@
         <v>1155</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
         <v>71</v>
@@ -16738,7 +16798,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -16760,7 +16820,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -16782,7 +16842,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -16804,7 +16864,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -16826,7 +16886,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -16848,7 +16908,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -16870,7 +16930,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -16881,7 +16941,7 @@
         <v>1814</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>71</v>
@@ -16894,7 +16954,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -16916,7 +16976,7 @@
       </c>
       <c r="F27"/>
       <c r="H27" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -16938,7 +16998,7 @@
       </c>
       <c r="F28"/>
       <c r="H28" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -17092,7 +17152,7 @@
       </c>
       <c r="F35"/>
       <c r="H35" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
@@ -17114,7 +17174,7 @@
       </c>
       <c r="F36"/>
       <c r="H36" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
@@ -17136,7 +17196,7 @@
       </c>
       <c r="F37"/>
       <c r="H37" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I37"/>
       <c r="J37"/>
@@ -17147,7 +17207,7 @@
         <v>1843</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
         <v>71</v>
@@ -17160,7 +17220,7 @@
       </c>
       <c r="F38"/>
       <c r="H38" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I38"/>
       <c r="J38"/>
@@ -17215,7 +17275,7 @@
         <v>1851</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
         <v>71</v>
@@ -17242,7 +17302,7 @@
         <v>1854</v>
       </c>
       <c r="C42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
         <v>1855</v>
@@ -17252,7 +17312,7 @@
       </c>
       <c r="F42"/>
       <c r="H42" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
@@ -17274,7 +17334,7 @@
       </c>
       <c r="F43"/>
       <c r="H43" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
@@ -17296,7 +17356,7 @@
       </c>
       <c r="F44"/>
       <c r="H44" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
@@ -17318,7 +17378,7 @@
       </c>
       <c r="F45"/>
       <c r="H45" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
@@ -17340,7 +17400,7 @@
       </c>
       <c r="F46"/>
       <c r="H46" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
@@ -17351,7 +17411,7 @@
         <v>1163</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C47" t="s">
         <v>71</v>
@@ -17364,7 +17424,7 @@
       </c>
       <c r="F47"/>
       <c r="H47" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
@@ -17386,7 +17446,7 @@
       </c>
       <c r="F48"/>
       <c r="H48" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
@@ -17397,7 +17457,7 @@
         <v>1168</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
         <v>71</v>
@@ -17410,7 +17470,7 @@
       </c>
       <c r="F49"/>
       <c r="H49" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -17432,7 +17492,7 @@
       </c>
       <c r="F50"/>
       <c r="H50" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
@@ -17443,7 +17503,7 @@
         <v>1865</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C51" t="s">
         <v>71</v>
@@ -17456,7 +17516,7 @@
       </c>
       <c r="F51"/>
       <c r="H51" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I51"/>
       <c r="J51"/>
@@ -17478,7 +17538,7 @@
       </c>
       <c r="F52"/>
       <c r="H52" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
@@ -17500,7 +17560,7 @@
       </c>
       <c r="F53"/>
       <c r="H53" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
@@ -17522,7 +17582,7 @@
       </c>
       <c r="F54"/>
       <c r="H54" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
@@ -17533,10 +17593,10 @@
         <v>1873</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
         <v>1874</v>
@@ -17546,7 +17606,7 @@
       </c>
       <c r="F55"/>
       <c r="H55" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
@@ -17557,7 +17617,7 @@
         <v>1875</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
         <v>71</v>
@@ -17570,7 +17630,7 @@
       </c>
       <c r="F56"/>
       <c r="H56" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
@@ -17592,7 +17652,7 @@
       </c>
       <c r="F57"/>
       <c r="H57" s="11" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
@@ -19324,10 +19384,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>12</v>
@@ -19340,13 +19406,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -19356,6 +19428,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -19373,7 +19453,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5" t="s">
@@ -19397,7 +19477,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6" t="s">
@@ -19421,7 +19501,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7" t="s">
@@ -19445,7 +19525,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -19467,7 +19547,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9" t="s">
@@ -19491,7 +19571,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10" t="s">
@@ -19515,7 +19595,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -19537,7 +19617,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -19559,7 +19639,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13" t="s">
@@ -19583,7 +19663,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -19605,7 +19685,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -19627,7 +19707,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -19649,7 +19729,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17" t="s">
@@ -19673,7 +19753,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18" t="s">
@@ -19697,7 +19777,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19" t="s">
@@ -19721,7 +19801,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -19743,7 +19823,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21" t="s">
@@ -19767,7 +19847,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22" t="s">
@@ -19791,7 +19871,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23" t="s">
@@ -19815,7 +19895,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24" t="s">
@@ -19839,7 +19919,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25" t="s">
@@ -19863,7 +19943,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -19876,7 +19956,7 @@
         <v>1971</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
         <v>71</v>
@@ -19889,7 +19969,7 @@
       </c>
       <c r="F27"/>
       <c r="H27" s="12" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -20036,10 +20116,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>12</v>
@@ -20052,13 +20138,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -20068,6 +20160,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -20085,7 +20185,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -20107,7 +20207,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -20129,7 +20229,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -20151,7 +20251,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -20162,7 +20262,7 @@
         <v>1980</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>71</v>
@@ -20175,7 +20275,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -20197,7 +20297,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -20208,7 +20308,7 @@
         <v>1985</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>71</v>
@@ -20221,7 +20321,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -20243,7 +20343,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -20254,7 +20354,7 @@
         <v>1990</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
@@ -20265,7 +20365,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -20276,7 +20376,7 @@
         <v>1992</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
@@ -20287,7 +20387,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -20309,7 +20409,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -20320,7 +20420,7 @@
         <v>1997</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>71</v>
@@ -20333,7 +20433,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -20344,7 +20444,7 @@
         <v>1999</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>71</v>
@@ -20357,7 +20457,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="13" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -20754,10 +20854,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="14" t="s">
         <v>12</v>
@@ -20770,13 +20876,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -20786,6 +20898,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -20803,7 +20923,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -20825,7 +20945,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -20836,7 +20956,7 @@
         <v>2028</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -20849,7 +20969,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -20871,7 +20991,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -20882,7 +21002,7 @@
         <v>2032</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>71</v>
@@ -20895,7 +21015,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -20917,7 +21037,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -20928,7 +21048,7 @@
         <v>1992</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
@@ -20939,7 +21059,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -20961,7 +21081,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -20972,7 +21092,7 @@
         <v>1997</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>71</v>
@@ -20985,7 +21105,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -20996,7 +21116,7 @@
         <v>1999</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>71</v>
@@ -21009,7 +21129,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -21031,7 +21151,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -21428,10 +21548,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="15" t="s">
         <v>12</v>
@@ -21444,13 +21570,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -21460,6 +21592,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -21477,7 +21617,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -21499,7 +21639,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -21521,7 +21661,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -21543,7 +21683,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -21554,7 +21694,7 @@
         <v>2039</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>71</v>
@@ -21567,7 +21707,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -21578,7 +21718,7 @@
         <v>2041</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>71</v>
@@ -21591,7 +21731,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -22533,10 +22673,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="16" t="s">
         <v>12</v>
@@ -22549,13 +22695,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -22565,6 +22717,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -22582,7 +22742,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -22593,7 +22753,7 @@
         <v>2045</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
@@ -22604,7 +22764,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -22615,7 +22775,7 @@
         <v>2047</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -22628,7 +22788,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -22650,7 +22810,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -22661,7 +22821,7 @@
         <v>650</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
@@ -22672,7 +22832,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -22692,7 +22852,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -22716,7 +22876,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -22740,7 +22900,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -22764,7 +22924,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -22788,7 +22948,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -22810,7 +22970,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -22832,7 +22992,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -22854,7 +23014,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -22876,7 +23036,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -22900,7 +23060,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -22922,7 +23082,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -22946,7 +23106,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -22968,7 +23128,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -22981,7 +23141,7 @@
         <v>2062</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
         <v>71</v>
@@ -22994,7 +23154,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -23018,7 +23178,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -23031,7 +23191,7 @@
         <v>2067</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
@@ -23044,7 +23204,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -23068,7 +23228,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -23079,7 +23239,7 @@
         <v>2073</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
         <v>71</v>
@@ -23092,7 +23252,7 @@
       </c>
       <c r="F27"/>
       <c r="H27" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -23114,7 +23274,7 @@
       </c>
       <c r="F28"/>
       <c r="H28" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -23136,7 +23296,7 @@
       </c>
       <c r="F29"/>
       <c r="H29" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -23158,7 +23318,7 @@
       </c>
       <c r="F30"/>
       <c r="H30" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -23180,7 +23340,7 @@
       </c>
       <c r="F31"/>
       <c r="H31" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -23191,7 +23351,7 @@
         <v>867</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
         <v>71</v>
@@ -23204,7 +23364,7 @@
       </c>
       <c r="F32"/>
       <c r="H32" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -23226,7 +23386,7 @@
       </c>
       <c r="F33"/>
       <c r="H33" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -23248,7 +23408,7 @@
       </c>
       <c r="F34"/>
       <c r="H34" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
@@ -23259,7 +23419,7 @@
         <v>1133</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
         <v>71</v>
@@ -23272,7 +23432,7 @@
       </c>
       <c r="F35"/>
       <c r="H35" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
@@ -23294,7 +23454,7 @@
       </c>
       <c r="F36"/>
       <c r="H36" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
@@ -23305,7 +23465,7 @@
         <v>2090</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37" t="s">
         <v>71</v>
@@ -23318,7 +23478,7 @@
       </c>
       <c r="F37"/>
       <c r="H37" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I37"/>
       <c r="J37"/>
@@ -23329,7 +23489,7 @@
         <v>818</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38"/>
       <c r="D38" t="s">
@@ -23340,7 +23500,7 @@
       </c>
       <c r="F38"/>
       <c r="H38" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I38"/>
       <c r="J38"/>
@@ -23353,7 +23513,7 @@
         <v>148</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39"/>
       <c r="D39" t="s">
@@ -23364,7 +23524,7 @@
       </c>
       <c r="F39"/>
       <c r="H39" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I39"/>
       <c r="J39"/>
@@ -23386,7 +23546,7 @@
       </c>
       <c r="F40"/>
       <c r="H40" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I40"/>
       <c r="J40"/>
@@ -23408,7 +23568,7 @@
       </c>
       <c r="F41"/>
       <c r="H41" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
@@ -23419,7 +23579,7 @@
         <v>2096</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
         <v>71</v>
@@ -23432,7 +23592,7 @@
       </c>
       <c r="F42"/>
       <c r="H42" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
@@ -23454,7 +23614,7 @@
       </c>
       <c r="F43"/>
       <c r="H43" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
@@ -23476,7 +23636,7 @@
       </c>
       <c r="F44"/>
       <c r="H44" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
@@ -23487,7 +23647,7 @@
         <v>829</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
         <v>71</v>
@@ -23500,7 +23660,7 @@
       </c>
       <c r="F45"/>
       <c r="H45" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
@@ -23522,7 +23682,7 @@
       </c>
       <c r="F46"/>
       <c r="H46" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
@@ -23544,7 +23704,7 @@
       </c>
       <c r="F47"/>
       <c r="H47" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
@@ -23568,7 +23728,7 @@
         <v>1</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
@@ -23592,7 +23752,7 @@
       </c>
       <c r="F49"/>
       <c r="H49" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -23614,7 +23774,7 @@
       </c>
       <c r="F50"/>
       <c r="H50" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
@@ -23638,7 +23798,7 @@
       </c>
       <c r="F51"/>
       <c r="H51" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I51"/>
       <c r="J51"/>
@@ -23649,7 +23809,7 @@
         <v>835</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C52" t="s">
         <v>71</v>
@@ -23662,7 +23822,7 @@
       </c>
       <c r="F52"/>
       <c r="H52" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
@@ -23684,7 +23844,7 @@
       </c>
       <c r="F53"/>
       <c r="H53" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
@@ -23708,7 +23868,7 @@
       </c>
       <c r="F54"/>
       <c r="H54" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
@@ -23732,7 +23892,7 @@
       </c>
       <c r="F55"/>
       <c r="H55" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
@@ -23756,7 +23916,7 @@
       </c>
       <c r="F56"/>
       <c r="H56" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
@@ -23780,7 +23940,7 @@
       </c>
       <c r="F57"/>
       <c r="H57" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
@@ -23793,7 +23953,7 @@
         <v>847</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
         <v>71</v>
@@ -23806,7 +23966,7 @@
       </c>
       <c r="F58"/>
       <c r="H58" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
@@ -23830,7 +23990,7 @@
       </c>
       <c r="F59"/>
       <c r="H59" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I59"/>
       <c r="J59"/>
@@ -23843,7 +24003,7 @@
         <v>851</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
         <v>71</v>
@@ -23856,7 +24016,7 @@
       </c>
       <c r="F60"/>
       <c r="H60" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
@@ -23880,7 +24040,7 @@
       </c>
       <c r="F61"/>
       <c r="H61" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I61"/>
       <c r="J61"/>
@@ -23902,7 +24062,7 @@
       </c>
       <c r="F62"/>
       <c r="H62" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I62"/>
       <c r="J62"/>
@@ -23924,7 +24084,7 @@
       </c>
       <c r="F63"/>
       <c r="H63" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I63"/>
       <c r="J63"/>
@@ -23948,7 +24108,7 @@
       </c>
       <c r="F64"/>
       <c r="H64" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I64"/>
       <c r="J64"/>
@@ -23961,7 +24121,7 @@
         <v>155</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C65" t="s">
         <v>71</v>
@@ -23974,7 +24134,7 @@
       </c>
       <c r="F65"/>
       <c r="H65" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I65"/>
       <c r="J65"/>
@@ -23996,7 +24156,7 @@
       </c>
       <c r="F66"/>
       <c r="H66" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I66"/>
       <c r="J66"/>
@@ -24018,7 +24178,7 @@
       </c>
       <c r="F67"/>
       <c r="H67" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I67"/>
       <c r="J67"/>
@@ -24040,7 +24200,7 @@
       </c>
       <c r="F68"/>
       <c r="H68" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
@@ -24062,7 +24222,7 @@
       </c>
       <c r="F69"/>
       <c r="H69" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I69"/>
       <c r="J69"/>
@@ -24084,7 +24244,7 @@
       </c>
       <c r="F70"/>
       <c r="H70" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I70"/>
       <c r="J70"/>
@@ -24106,7 +24266,7 @@
       </c>
       <c r="F71"/>
       <c r="H71" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I71"/>
       <c r="J71"/>
@@ -24119,7 +24279,7 @@
         <v>2114</v>
       </c>
       <c r="B72" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C72" t="s">
         <v>71</v>
@@ -24132,7 +24292,7 @@
       </c>
       <c r="F72"/>
       <c r="H72" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I72"/>
       <c r="J72"/>
@@ -24156,7 +24316,7 @@
       </c>
       <c r="F73"/>
       <c r="H73" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I73"/>
       <c r="J73"/>
@@ -24180,7 +24340,7 @@
       </c>
       <c r="F74"/>
       <c r="H74" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I74"/>
       <c r="J74"/>
@@ -24204,7 +24364,7 @@
       </c>
       <c r="F75"/>
       <c r="H75" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I75"/>
       <c r="J75"/>
@@ -24228,7 +24388,7 @@
       </c>
       <c r="F76"/>
       <c r="H76" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I76"/>
       <c r="J76"/>
@@ -24252,7 +24412,7 @@
       </c>
       <c r="F77"/>
       <c r="H77" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
@@ -24274,7 +24434,7 @@
       </c>
       <c r="F78"/>
       <c r="H78" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
@@ -24296,7 +24456,7 @@
       </c>
       <c r="F79"/>
       <c r="H79" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
@@ -26328,10 +26488,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>12</v>
@@ -26344,13 +26510,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -26360,6 +26532,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -26379,7 +26559,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -26401,7 +26581,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -26425,7 +26605,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -26451,7 +26631,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -26475,7 +26655,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -26486,7 +26666,7 @@
         <v>2041</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>71</v>
@@ -26499,7 +26679,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -26521,7 +26701,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -26545,7 +26725,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -26569,7 +26749,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -26591,7 +26771,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -26613,7 +26793,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="17" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -27670,10 +27850,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>12</v>
@@ -27686,13 +27872,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -27702,6 +27894,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -27719,7 +27919,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -27741,7 +27941,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -27763,7 +27963,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -27774,7 +27974,7 @@
         <v>2222</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
@@ -27785,7 +27985,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -27796,7 +27996,7 @@
         <v>2224</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
@@ -27807,7 +28007,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -27831,7 +28031,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -27855,7 +28055,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -27879,7 +28079,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -27903,7 +28103,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -27927,7 +28127,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -27949,7 +28149,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -27973,7 +28173,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -27984,7 +28184,7 @@
         <v>2232</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>71</v>
@@ -27997,7 +28197,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -28021,7 +28221,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -28043,7 +28243,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -28054,7 +28254,7 @@
         <v>2238</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
         <v>71</v>
@@ -28067,7 +28267,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -28089,7 +28289,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -28100,7 +28300,7 @@
         <v>2242</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
         <v>71</v>
@@ -28113,7 +28313,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -28135,7 +28335,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -28157,7 +28357,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -28168,7 +28368,7 @@
         <v>2249</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
         <v>71</v>
@@ -28181,7 +28381,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -28192,7 +28392,7 @@
         <v>2251</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
         <v>71</v>
@@ -28205,7 +28405,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -28227,7 +28427,7 @@
       </c>
       <c r="F27"/>
       <c r="H27" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -28249,7 +28449,7 @@
       </c>
       <c r="F28"/>
       <c r="H28" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -28271,7 +28471,7 @@
       </c>
       <c r="F29"/>
       <c r="H29" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -28293,7 +28493,7 @@
       </c>
       <c r="F30"/>
       <c r="H30" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -28315,7 +28515,7 @@
       </c>
       <c r="F31"/>
       <c r="H31" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -28337,7 +28537,7 @@
       </c>
       <c r="F32"/>
       <c r="H32" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -28359,7 +28559,7 @@
       </c>
       <c r="F33"/>
       <c r="H33" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -28379,7 +28579,7 @@
       </c>
       <c r="F34"/>
       <c r="H34" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
@@ -28399,7 +28599,7 @@
       </c>
       <c r="F35"/>
       <c r="H35" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
@@ -28410,7 +28610,7 @@
         <v>2272</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
@@ -28421,7 +28621,7 @@
       </c>
       <c r="F36"/>
       <c r="H36" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
@@ -28432,7 +28632,7 @@
         <v>2274</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37"/>
       <c r="D37" t="s">
@@ -28443,7 +28643,7 @@
       </c>
       <c r="F37"/>
       <c r="H37" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I37"/>
       <c r="J37"/>
@@ -28465,7 +28665,7 @@
       </c>
       <c r="F38"/>
       <c r="H38" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I38"/>
       <c r="J38"/>
@@ -28476,7 +28676,7 @@
         <v>2279</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39" t="s">
         <v>71</v>
@@ -28489,7 +28689,7 @@
       </c>
       <c r="F39"/>
       <c r="H39" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I39"/>
       <c r="J39"/>
@@ -28511,7 +28711,7 @@
       </c>
       <c r="F40"/>
       <c r="H40" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I40"/>
       <c r="J40"/>
@@ -28533,7 +28733,7 @@
       </c>
       <c r="F41"/>
       <c r="H41" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
@@ -29538,10 +29738,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>12</v>
@@ -29554,13 +29760,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -29570,6 +29782,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -29589,7 +29809,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -29613,7 +29833,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -29633,7 +29853,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -29644,7 +29864,7 @@
         <v>2375</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
@@ -29655,7 +29875,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -29666,7 +29886,7 @@
         <v>2378</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
@@ -29677,7 +29897,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -29701,7 +29921,7 @@
         <v>1</v>
       </c>
       <c r="H10" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -29723,7 +29943,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -29734,7 +29954,7 @@
         <v>2387</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>71</v>
@@ -29747,7 +29967,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -29771,7 +29991,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -29795,7 +30015,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -29806,7 +30026,7 @@
         <v>2238</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
         <v>71</v>
@@ -29819,7 +30039,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -29845,7 +30065,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -29869,7 +30089,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -29880,7 +30100,7 @@
         <v>2399</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>71</v>
@@ -29895,7 +30115,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -29919,7 +30139,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -29941,7 +30161,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -29952,7 +30172,7 @@
         <v>2408</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
         <v>71</v>
@@ -29965,7 +30185,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -29987,7 +30207,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -30009,7 +30229,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -30033,7 +30253,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="19" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -31510,10 +31730,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
@@ -31526,13 +31752,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -31542,6 +31774,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -31559,7 +31799,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -31581,7 +31821,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -31603,7 +31843,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -31625,7 +31865,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -31636,7 +31876,7 @@
         <v>553</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>71</v>
@@ -31649,7 +31889,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -31660,7 +31900,7 @@
         <v>554</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>71</v>
@@ -31673,7 +31913,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -31684,7 +31924,7 @@
         <v>556</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>71</v>
@@ -31697,7 +31937,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -31719,7 +31959,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -31730,7 +31970,7 @@
         <v>560</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
         <v>71</v>
@@ -31743,7 +31983,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -31754,7 +31994,7 @@
         <v>562</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>71</v>
@@ -31767,7 +32007,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -31994,10 +32234,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>12</v>
@@ -32010,13 +32256,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -32026,6 +32278,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -32043,7 +32303,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -32065,7 +32325,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -32087,7 +32347,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -32109,7 +32369,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -32131,7 +32391,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -32153,7 +32413,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -32175,7 +32435,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -32197,7 +32457,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -32219,7 +32479,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -32241,7 +32501,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -32263,7 +32523,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -32285,7 +32545,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -32307,7 +32567,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -32329,7 +32589,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -32351,7 +32611,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -32373,7 +32633,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -32395,7 +32655,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -32417,7 +32677,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -32439,7 +32699,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -32461,7 +32721,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -32483,7 +32743,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -32494,7 +32754,7 @@
         <v>2497</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
@@ -32505,7 +32765,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="20" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -32652,10 +32912,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="21" t="s">
         <v>12</v>
@@ -32668,13 +32934,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -32684,6 +32956,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -32703,7 +32983,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -32725,7 +33005,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -32747,7 +33027,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -32769,7 +33049,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -32793,7 +33073,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -32815,7 +33095,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -32839,7 +33119,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -32861,7 +33141,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -32883,7 +33163,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -32905,7 +33185,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -32927,7 +33207,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -32949,7 +33229,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -32960,7 +33240,7 @@
         <v>2526</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
@@ -32971,7 +33251,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -32995,7 +33275,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -33006,7 +33286,7 @@
         <v>2530</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19"/>
       <c r="D19" t="s">
@@ -33017,7 +33297,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -33039,7 +33319,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -33061,7 +33341,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -33083,7 +33363,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="21" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -33755,10 +34035,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>12</v>
@@ -33771,13 +34057,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -33787,6 +34079,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -33804,7 +34104,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -33828,7 +34128,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -33850,7 +34150,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -33872,7 +34172,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -33894,7 +34194,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -33916,7 +34216,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -33938,7 +34238,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -33949,7 +34249,7 @@
         <v>146</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
@@ -33960,7 +34260,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -33971,7 +34271,7 @@
         <v>148</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
@@ -33982,7 +34282,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -33993,7 +34293,7 @@
         <v>2617</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
@@ -34004,7 +34304,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -34015,7 +34315,7 @@
         <v>2619</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
@@ -34028,7 +34328,7 @@
         <v>1</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -34050,7 +34350,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -34072,7 +34372,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -34094,7 +34394,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -34118,7 +34418,7 @@
         <v>1</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -34142,7 +34442,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -34164,7 +34464,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -34175,7 +34475,7 @@
         <v>2629</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
@@ -34186,7 +34486,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -34208,7 +34508,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -34230,7 +34530,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -34252,7 +34552,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -34263,7 +34563,7 @@
         <v>1151</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
@@ -34274,7 +34574,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -34285,7 +34585,7 @@
         <v>1153</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" t="s">
         <v>71</v>
@@ -34298,7 +34598,7 @@
       </c>
       <c r="F27"/>
       <c r="H27" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -34320,7 +34620,7 @@
       </c>
       <c r="F28"/>
       <c r="H28" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -34342,7 +34642,7 @@
       </c>
       <c r="F29"/>
       <c r="H29" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -34364,7 +34664,7 @@
       </c>
       <c r="F30"/>
       <c r="H30" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I30"/>
       <c r="J30"/>
@@ -34386,7 +34686,7 @@
       </c>
       <c r="F31"/>
       <c r="H31" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -34397,7 +34697,7 @@
         <v>2641</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C32"/>
       <c r="D32" t="s">
@@ -34408,7 +34708,7 @@
       </c>
       <c r="F32"/>
       <c r="H32" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -34419,7 +34719,7 @@
         <v>2643</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C33"/>
       <c r="D33" t="s">
@@ -34430,7 +34730,7 @@
       </c>
       <c r="F33"/>
       <c r="H33" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -34441,7 +34741,7 @@
         <v>2646</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C34"/>
       <c r="D34" t="s">
@@ -34452,7 +34752,7 @@
       </c>
       <c r="F34"/>
       <c r="H34" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
@@ -34463,7 +34763,7 @@
         <v>2649</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C35"/>
       <c r="D35" t="s">
@@ -34474,7 +34774,7 @@
       </c>
       <c r="F35"/>
       <c r="H35" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
@@ -34485,7 +34785,7 @@
         <v>2652</v>
       </c>
       <c r="B36" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C36"/>
       <c r="D36" t="s">
@@ -34496,7 +34796,7 @@
       </c>
       <c r="F36"/>
       <c r="H36" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I36"/>
       <c r="J36"/>
@@ -34507,7 +34807,7 @@
         <v>2654</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C37"/>
       <c r="D37" t="s">
@@ -34518,7 +34818,7 @@
       </c>
       <c r="F37"/>
       <c r="H37" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I37"/>
       <c r="J37"/>
@@ -34529,7 +34829,7 @@
         <v>2657</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38"/>
       <c r="D38" t="s">
@@ -34540,7 +34840,7 @@
       </c>
       <c r="F38"/>
       <c r="H38" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I38"/>
       <c r="J38"/>
@@ -34551,7 +34851,7 @@
         <v>2660</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C39"/>
       <c r="D39" t="s">
@@ -34562,7 +34862,7 @@
       </c>
       <c r="F39"/>
       <c r="H39" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I39"/>
       <c r="J39"/>
@@ -34584,7 +34884,7 @@
       </c>
       <c r="F40"/>
       <c r="H40" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I40"/>
       <c r="J40"/>
@@ -34595,7 +34895,7 @@
         <v>650</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41"/>
       <c r="D41" t="s">
@@ -34606,7 +34906,7 @@
       </c>
       <c r="F41"/>
       <c r="H41" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I41"/>
       <c r="J41"/>
@@ -34630,7 +34930,7 @@
       </c>
       <c r="F42"/>
       <c r="H42" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
@@ -34641,7 +34941,7 @@
         <v>2664</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C43"/>
       <c r="D43" t="s">
@@ -34652,7 +34952,7 @@
       </c>
       <c r="F43"/>
       <c r="H43" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I43"/>
       <c r="J43"/>
@@ -34674,7 +34974,7 @@
       </c>
       <c r="F44"/>
       <c r="H44" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I44"/>
       <c r="J44"/>
@@ -34696,7 +34996,7 @@
       </c>
       <c r="F45"/>
       <c r="H45" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I45"/>
       <c r="J45"/>
@@ -34718,7 +35018,7 @@
       </c>
       <c r="F46"/>
       <c r="H46" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I46"/>
       <c r="J46"/>
@@ -34740,7 +35040,7 @@
       </c>
       <c r="F47"/>
       <c r="H47" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I47"/>
       <c r="J47"/>
@@ -34762,7 +35062,7 @@
       </c>
       <c r="F48"/>
       <c r="H48" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I48"/>
       <c r="J48"/>
@@ -34784,7 +35084,7 @@
       </c>
       <c r="F49"/>
       <c r="H49" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I49"/>
       <c r="J49"/>
@@ -34808,7 +35108,7 @@
       </c>
       <c r="F50"/>
       <c r="H50" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I50"/>
       <c r="J50"/>
@@ -34832,7 +35132,7 @@
       </c>
       <c r="F51"/>
       <c r="H51" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I51"/>
       <c r="J51"/>
@@ -34856,7 +35156,7 @@
       </c>
       <c r="F52"/>
       <c r="H52" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I52"/>
       <c r="J52"/>
@@ -34880,7 +35180,7 @@
       </c>
       <c r="F53"/>
       <c r="H53" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I53"/>
       <c r="J53"/>
@@ -34902,7 +35202,7 @@
       </c>
       <c r="F54"/>
       <c r="H54" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I54"/>
       <c r="J54"/>
@@ -34926,7 +35226,7 @@
       </c>
       <c r="F55"/>
       <c r="H55" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I55"/>
       <c r="J55"/>
@@ -34948,7 +35248,7 @@
       </c>
       <c r="F56"/>
       <c r="H56" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I56"/>
       <c r="J56"/>
@@ -34972,7 +35272,7 @@
       </c>
       <c r="F57"/>
       <c r="H57" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I57"/>
       <c r="J57"/>
@@ -34994,7 +35294,7 @@
       </c>
       <c r="F58"/>
       <c r="H58" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I58"/>
       <c r="J58"/>
@@ -35005,7 +35305,7 @@
         <v>2690</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C59"/>
       <c r="D59" t="s">
@@ -35016,7 +35316,7 @@
       </c>
       <c r="F59"/>
       <c r="H59" s="22" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I59"/>
       <c r="J59"/>
@@ -37490,10 +37790,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="23" t="s">
         <v>12</v>
@@ -37506,13 +37812,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -37522,6 +37834,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -37539,7 +37859,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -37563,7 +37883,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -37587,7 +37907,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -37598,7 +37918,7 @@
         <v>2765</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>71</v>
@@ -37611,7 +37931,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -37633,7 +37953,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -37655,7 +37975,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -37677,7 +37997,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -37699,7 +38019,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -37721,7 +38041,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -37743,7 +38063,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="23" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -37825,10 +38145,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>12</v>
@@ -37841,13 +38167,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -37857,6 +38189,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -37876,7 +38216,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -37898,7 +38238,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -37920,7 +38260,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -37942,7 +38282,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -37966,7 +38306,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -37988,7 +38328,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -38010,7 +38350,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -38032,7 +38372,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -38043,7 +38383,7 @@
         <v>2778</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
@@ -38054,7 +38394,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -38065,7 +38405,7 @@
         <v>1133</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14"/>
       <c r="D14" t="s">
@@ -38076,7 +38416,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -38087,7 +38427,7 @@
         <v>2779</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
@@ -38098,7 +38438,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -38120,7 +38460,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="24" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -38537,10 +38877,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="25" t="s">
         <v>12</v>
@@ -38553,13 +38899,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -38569,13 +38921,21 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>2800</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
@@ -38586,7 +38946,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -38608,7 +38968,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -38630,7 +38990,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -38652,7 +39012,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -38663,7 +39023,7 @@
         <v>589</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
@@ -38674,7 +39034,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -38685,7 +39045,7 @@
         <v>604</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
@@ -38696,7 +39056,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -38707,7 +39067,7 @@
         <v>606</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11"/>
       <c r="D11" t="s">
@@ -38718,7 +39078,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -38729,7 +39089,7 @@
         <v>608</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
@@ -38740,7 +39100,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -38751,7 +39111,7 @@
         <v>556</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13"/>
       <c r="D13" t="s">
@@ -38762,7 +39122,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -38784,7 +39144,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -38795,7 +39155,7 @@
         <v>619</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15"/>
       <c r="D15" t="s">
@@ -38806,7 +39166,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -38817,7 +39177,7 @@
         <v>621</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
@@ -38828,7 +39188,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -38839,7 +39199,7 @@
         <v>623</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
@@ -38850,7 +39210,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -38861,7 +39221,7 @@
         <v>625</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18"/>
       <c r="D18" t="s">
@@ -38872,7 +39232,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -38894,7 +39254,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -38916,7 +39276,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -38938,7 +39298,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -38960,7 +39320,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -38982,7 +39342,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -38993,7 +39353,7 @@
         <v>818</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C24"/>
       <c r="D24" t="s">
@@ -39004,7 +39364,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="25" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -40071,10 +40431,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="26" t="s">
         <v>12</v>
@@ -40087,13 +40453,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -40103,13 +40475,21 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>2809</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
@@ -40120,7 +40500,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -40131,7 +40511,7 @@
         <v>146</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
@@ -40142,7 +40522,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -40153,7 +40533,7 @@
         <v>2811</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
@@ -40164,7 +40544,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -40175,7 +40555,7 @@
         <v>2813</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
@@ -40186,7 +40566,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -40208,7 +40588,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -40230,7 +40610,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="26" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -40312,10 +40692,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="27" t="s">
         <v>12</v>
@@ -40328,13 +40714,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -40344,13 +40736,21 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>2800</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
@@ -40361,7 +40761,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -40372,7 +40772,7 @@
         <v>2815</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
@@ -40383,7 +40783,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -40405,7 +40805,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -40427,7 +40827,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -40438,7 +40838,7 @@
         <v>818</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
@@ -40449,7 +40849,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -40471,7 +40871,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -40493,7 +40893,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="27" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -40575,10 +40975,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="28" t="s">
         <v>12</v>
@@ -40591,13 +40997,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -40607,13 +41019,21 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>2800</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
@@ -40624,7 +41044,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -40635,7 +41055,7 @@
         <v>2815</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
@@ -40646,7 +41066,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -40668,7 +41088,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -40690,7 +41110,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -40712,7 +41132,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -40723,7 +41143,7 @@
         <v>818</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
@@ -40734,7 +41154,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="28" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -40816,10 +41236,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>12</v>
@@ -40832,13 +41258,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -40848,13 +41280,21 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>2800</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5"/>
       <c r="D5" t="s">
@@ -40865,7 +41305,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="29" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -40887,7 +41327,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="29" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -40909,7 +41349,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="29" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -40931,7 +41371,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="29" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -40953,7 +41393,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="29" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -40964,7 +41404,7 @@
         <v>818</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
@@ -40975,7 +41415,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="29" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -41057,10 +41497,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -41073,13 +41519,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -41089,6 +41541,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -41106,7 +41566,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -41128,7 +41588,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -41150,7 +41610,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -41172,7 +41632,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -41194,7 +41654,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -41208,7 +41668,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
         <v>441</v>
@@ -41218,7 +41678,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -41229,10 +41689,10 @@
         <v>553</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" t="s">
         <v>588</v>
@@ -41242,7 +41702,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -41253,10 +41713,10 @@
         <v>589</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
         <v>590</v>
@@ -41266,7 +41726,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -41280,7 +41740,7 @@
         <v>592</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
         <v>593</v>
@@ -41290,7 +41750,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -41304,7 +41764,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>596</v>
@@ -41314,7 +41774,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -41328,7 +41788,7 @@
         <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
         <v>599</v>
@@ -41338,7 +41798,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -41360,7 +41820,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -41371,10 +41831,10 @@
         <v>604</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" t="s">
         <v>605</v>
@@ -41384,7 +41844,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -41395,10 +41855,10 @@
         <v>606</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
         <v>607</v>
@@ -41408,7 +41868,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -41419,10 +41879,10 @@
         <v>608</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D19" t="s">
         <v>609</v>
@@ -41432,7 +41892,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -41443,10 +41903,10 @@
         <v>556</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D20" t="s">
         <v>557</v>
@@ -41456,7 +41916,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -41478,7 +41938,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -41489,7 +41949,7 @@
         <v>613</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22"/>
       <c r="D22" t="s">
@@ -41500,7 +41960,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -41514,7 +41974,7 @@
         <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
         <v>75</v>
@@ -41524,7 +41984,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23"/>
       <c r="J23"/>
@@ -41538,7 +41998,7 @@
         <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D24" t="s">
         <v>617</v>
@@ -41548,7 +42008,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -41559,10 +42019,10 @@
         <v>618</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D25" t="s">
         <v>80</v>
@@ -41572,7 +42032,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -41583,7 +42043,7 @@
         <v>619</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C26"/>
       <c r="D26" t="s">
@@ -41594,7 +42054,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -41605,7 +42065,7 @@
         <v>621</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27"/>
       <c r="D27" t="s">
@@ -41616,7 +42076,7 @@
       </c>
       <c r="F27"/>
       <c r="H27" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27"/>
       <c r="J27"/>
@@ -41627,7 +42087,7 @@
         <v>623</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28"/>
       <c r="D28" t="s">
@@ -41638,7 +42098,7 @@
       </c>
       <c r="F28"/>
       <c r="H28" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I28"/>
       <c r="J28"/>
@@ -41649,7 +42109,7 @@
         <v>625</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C29"/>
       <c r="D29" t="s">
@@ -41660,7 +42120,7 @@
       </c>
       <c r="F29"/>
       <c r="H29" s="3" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I29"/>
       <c r="J29"/>
@@ -42905,10 +43365,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="30" t="s">
         <v>12</v>
@@ -42921,13 +43387,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -42937,6 +43409,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -42954,7 +43434,7 @@
       </c>
       <c r="F5"/>
       <c r="H5" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -42965,7 +43445,7 @@
         <v>2825</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6"/>
       <c r="D6" t="s">
@@ -42976,7 +43456,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -42984,21 +43464,21 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="30" t="s">
         <v>14</v>
       </c>
       <c r="F7"/>
       <c r="H7" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -43009,7 +43489,7 @@
         <v>24</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8"/>
       <c r="D8" t="s">
@@ -43020,7 +43500,7 @@
       </c>
       <c r="F8"/>
       <c r="H8" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -43031,7 +43511,7 @@
         <v>2827</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9"/>
       <c r="D9" t="s">
@@ -43042,7 +43522,7 @@
       </c>
       <c r="F9"/>
       <c r="H9" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I9"/>
       <c r="J9"/>
@@ -43053,7 +43533,7 @@
         <v>2828</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10"/>
       <c r="D10" t="s">
@@ -43064,7 +43544,7 @@
       </c>
       <c r="F10"/>
       <c r="H10" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -43086,7 +43566,7 @@
       </c>
       <c r="F11"/>
       <c r="H11" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -43106,7 +43586,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
@@ -43128,7 +43608,7 @@
       </c>
       <c r="F13"/>
       <c r="H13" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -43150,7 +43630,7 @@
       </c>
       <c r="F14"/>
       <c r="H14" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -43172,7 +43652,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -43194,7 +43674,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -43216,7 +43696,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -43238,7 +43718,7 @@
       </c>
       <c r="F18"/>
       <c r="H18" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18"/>
       <c r="J18"/>
@@ -43260,7 +43740,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -43282,7 +43762,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -43304,7 +43784,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21"/>
       <c r="J21"/>
@@ -43326,7 +43806,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="30" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22"/>
       <c r="J22"/>
@@ -44601,10 +45081,16 @@
         <v>14</v>
       </c>
       <c r="F2"/>
+      <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>12</v>
@@ -44617,13 +45103,19 @@
         <v>14</v>
       </c>
       <c r="F3"/>
+      <c r="H3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4"/>
       <c r="D4" t="s">
@@ -44633,6 +45125,14 @@
         <v>14</v>
       </c>
       <c r="F4"/>
+      <c r="H4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4"/>
+      <c r="K4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -44652,7 +45152,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -44674,7 +45174,7 @@
       </c>
       <c r="F6"/>
       <c r="H6" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -44685,7 +45185,7 @@
         <v>650</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7"/>
       <c r="D7" t="s">
@@ -44696,7 +45196,7 @@
       </c>
       <c r="F7"/>
       <c r="H7" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -44794,7 +45294,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I11"/>
       <c r="J11"/>
@@ -44805,7 +45305,7 @@
         <v>662</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12"/>
       <c r="D12" t="s">
@@ -44816,7 +45316,7 @@
       </c>
       <c r="F12"/>
       <c r="H12" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -44844,7 +45344,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -44870,7 +45370,7 @@
         <v>1</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -44894,7 +45394,7 @@
       </c>
       <c r="F15"/>
       <c r="H15" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -44916,7 +45416,7 @@
       </c>
       <c r="F16"/>
       <c r="H16" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I16"/>
       <c r="J16"/>
@@ -44938,7 +45438,7 @@
       </c>
       <c r="F17"/>
       <c r="H17" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -44964,7 +45464,7 @@
         <v>1</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -44988,7 +45488,7 @@
       </c>
       <c r="F19"/>
       <c r="H19" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -45012,7 +45512,7 @@
       </c>
       <c r="F20"/>
       <c r="H20" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I20"/>
       <c r="J20"/>
@@ -45036,7 +45536,7 @@
       </c>
       <c r="F21"/>
       <c r="H21" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -45060,7 +45560,7 @@
       </c>
       <c r="F22"/>
       <c r="H22" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
@@ -45073,7 +45573,7 @@
         <v>690</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="s">
         <v>71</v>
@@ -45086,7 +45586,7 @@
       </c>
       <c r="F23"/>
       <c r="H23" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -45110,7 +45610,7 @@
       </c>
       <c r="F24"/>
       <c r="H24" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I24"/>
       <c r="J24"/>
@@ -45132,7 +45632,7 @@
       </c>
       <c r="F25"/>
       <c r="H25" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I25"/>
       <c r="J25"/>
@@ -45154,7 +45654,7 @@
       </c>
       <c r="F26"/>
       <c r="H26" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I26"/>
       <c r="J26"/>
@@ -45178,7 +45678,7 @@
         <v>1</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
@@ -45202,7 +45702,7 @@
       </c>
       <c r="F28"/>
       <c r="H28" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -45226,7 +45726,7 @@
       </c>
       <c r="F29"/>
       <c r="H29" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
@@ -45250,7 +45750,7 @@
       </c>
       <c r="F30"/>
       <c r="H30" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I30" t="b">
         <v>1</v>
@@ -45274,7 +45774,7 @@
       </c>
       <c r="F31"/>
       <c r="H31" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I31"/>
       <c r="J31"/>
@@ -45285,7 +45785,7 @@
         <v>711</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C32" t="s">
         <v>71</v>
@@ -45298,7 +45798,7 @@
       </c>
       <c r="F32"/>
       <c r="H32" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I32"/>
       <c r="J32"/>
@@ -45320,7 +45820,7 @@
       </c>
       <c r="F33"/>
       <c r="H33" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I33"/>
       <c r="J33"/>
@@ -45342,7 +45842,7 @@
       </c>
       <c r="F34"/>
       <c r="H34" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I34"/>
       <c r="J34"/>
@@ -45364,7 +45864,7 @@
       </c>
       <c r="F35"/>
       <c r="H35" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I35"/>
       <c r="J35"/>
@@ -45388,7 +45888,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -45414,7 +45914,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -45430,7 +45930,7 @@
         <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D38" t="s">
         <v>441</v>
@@ -45440,7 +45940,7 @@
       </c>
       <c r="F38"/>
       <c r="H38" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -45456,7 +45956,7 @@
         <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
         <v>75</v>
@@ -45466,7 +45966,7 @@
       </c>
       <c r="F39"/>
       <c r="H39" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I39"/>
       <c r="J39"/>
@@ -45480,7 +45980,7 @@
         <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
         <v>617</v>
@@ -45492,7 +45992,7 @@
         <v>1</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -45505,10 +46005,10 @@
         <v>721</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
         <v>80</v>
@@ -45518,7 +46018,7 @@
       </c>
       <c r="F41"/>
       <c r="H41" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -45542,7 +46042,7 @@
       </c>
       <c r="F42"/>
       <c r="H42" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I42"/>
       <c r="J42"/>
@@ -45577,7 +46077,7 @@
         <v>729</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C44"/>
       <c r="D44" t="s">
@@ -45693,7 +46193,7 @@
         <v>743</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C49"/>
       <c r="D49" t="s">
@@ -45737,7 +46237,7 @@
         <v>748</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C51"/>
       <c r="D51" t="s">
@@ -45759,7 +46259,7 @@
         <v>750</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C52"/>
       <c r="D52" t="s">
@@ -45781,7 +46281,7 @@
         <v>753</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C53"/>
       <c r="D53" t="s">
@@ -45803,7 +46303,7 @@
         <v>755</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54"/>
       <c r="D54" t="s">
@@ -45825,7 +46325,7 @@
         <v>758</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C55"/>
       <c r="D55" t="s">
@@ -45847,7 +46347,7 @@
         <v>760</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C56"/>
       <c r="D56" t="s">
@@ -45928,7 +46428,7 @@
       </c>
       <c r="F59"/>
       <c r="H59" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
@@ -45941,7 +46441,7 @@
         <v>769</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C60" t="s">
         <v>71</v>
@@ -45954,7 +46454,7 @@
       </c>
       <c r="F60"/>
       <c r="H60" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I60"/>
       <c r="J60"/>
@@ -45965,7 +46465,7 @@
         <v>771</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C61" t="s">
         <v>71</v>
@@ -45978,7 +46478,7 @@
       </c>
       <c r="F61"/>
       <c r="H61" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I61"/>
       <c r="J61"/>
@@ -45989,7 +46489,7 @@
         <v>773</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C62" t="s">
         <v>71</v>
@@ -46002,7 +46502,7 @@
       </c>
       <c r="F62"/>
       <c r="H62" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I62"/>
       <c r="J62"/>
@@ -46035,7 +46535,7 @@
         <v>778</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C64" t="s">
         <v>71</v>
@@ -46072,7 +46572,7 @@
       </c>
       <c r="F65"/>
       <c r="H65" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I65"/>
       <c r="J65"/>
@@ -46096,7 +46596,7 @@
       </c>
       <c r="F66"/>
       <c r="H66" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I66"/>
       <c r="J66"/>
@@ -46120,7 +46620,7 @@
       </c>
       <c r="F67"/>
       <c r="H67" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I67"/>
       <c r="J67"/>
@@ -46142,7 +46642,7 @@
       </c>
       <c r="F68"/>
       <c r="H68" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I68"/>
       <c r="J68"/>
@@ -46164,7 +46664,7 @@
       </c>
       <c r="F69"/>
       <c r="H69" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I69"/>
       <c r="J69"/>
@@ -46186,7 +46686,7 @@
       </c>
       <c r="F70"/>
       <c r="H70" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I70"/>
       <c r="J70"/>
@@ -46208,7 +46708,7 @@
       </c>
       <c r="F71"/>
       <c r="H71" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I71"/>
       <c r="J71"/>
@@ -46230,7 +46730,7 @@
       </c>
       <c r="F72"/>
       <c r="H72" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I72"/>
       <c r="J72"/>
@@ -46252,7 +46752,7 @@
       </c>
       <c r="F73"/>
       <c r="H73" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I73"/>
       <c r="J73"/>
@@ -46274,7 +46774,7 @@
       </c>
       <c r="F74"/>
       <c r="H74" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I74"/>
       <c r="J74"/>
@@ -46285,7 +46785,7 @@
         <v>806</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C75"/>
       <c r="D75" t="s">
@@ -46296,7 +46796,7 @@
       </c>
       <c r="F75"/>
       <c r="H75" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I75"/>
       <c r="J75"/>
@@ -46320,7 +46820,7 @@
       </c>
       <c r="F76"/>
       <c r="H76" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I76"/>
       <c r="J76"/>
@@ -46342,7 +46842,7 @@
       </c>
       <c r="F77"/>
       <c r="H77" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I77"/>
       <c r="J77"/>
@@ -46356,7 +46856,7 @@
         <v>814</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
         <v>815</v>
@@ -46366,7 +46866,7 @@
       </c>
       <c r="F78"/>
       <c r="H78" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I78"/>
       <c r="J78"/>
@@ -46377,10 +46877,10 @@
         <v>816</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
         <v>817</v>
@@ -46390,7 +46890,7 @@
       </c>
       <c r="F79"/>
       <c r="H79" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I79"/>
       <c r="J79"/>
@@ -46401,7 +46901,7 @@
         <v>155</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C80" t="s">
         <v>71</v>
@@ -46414,7 +46914,7 @@
       </c>
       <c r="F80"/>
       <c r="H80" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I80"/>
       <c r="J80"/>
@@ -46425,7 +46925,7 @@
         <v>818</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C81"/>
       <c r="D81" t="s">
@@ -46436,7 +46936,7 @@
       </c>
       <c r="F81"/>
       <c r="H81" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I81"/>
       <c r="J81"/>
@@ -46449,7 +46949,7 @@
         <v>148</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C82"/>
       <c r="D82" t="s">
@@ -46460,7 +46960,7 @@
       </c>
       <c r="F82"/>
       <c r="H82" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I82"/>
       <c r="J82"/>
@@ -46482,7 +46982,7 @@
       </c>
       <c r="F83"/>
       <c r="H83" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I83"/>
       <c r="J83"/>
@@ -46504,7 +47004,7 @@
       </c>
       <c r="F84"/>
       <c r="H84" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I84"/>
       <c r="J84"/>
@@ -46528,7 +47028,7 @@
       </c>
       <c r="F85"/>
       <c r="H85" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I85"/>
       <c r="J85"/>
@@ -46552,7 +47052,7 @@
       </c>
       <c r="F86"/>
       <c r="H86" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I86"/>
       <c r="J86"/>
@@ -46563,7 +47063,7 @@
         <v>829</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C87" t="s">
         <v>71</v>
@@ -46576,7 +47076,7 @@
       </c>
       <c r="F87"/>
       <c r="H87" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I87"/>
       <c r="J87"/>
@@ -46598,7 +47098,7 @@
       </c>
       <c r="F88"/>
       <c r="H88" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I88"/>
       <c r="J88"/>
@@ -46620,7 +47120,7 @@
       </c>
       <c r="F89"/>
       <c r="H89" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I89"/>
       <c r="J89"/>
@@ -46631,7 +47131,7 @@
         <v>835</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C90" t="s">
         <v>71</v>
@@ -46644,7 +47144,7 @@
       </c>
       <c r="F90"/>
       <c r="H90" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I90"/>
       <c r="J90"/>
@@ -46666,7 +47166,7 @@
       </c>
       <c r="F91"/>
       <c r="H91" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I91"/>
       <c r="J91"/>
@@ -46690,7 +47190,7 @@
       </c>
       <c r="F92"/>
       <c r="H92" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I92"/>
       <c r="J92"/>
@@ -46714,7 +47214,7 @@
       </c>
       <c r="F93"/>
       <c r="H93" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I93"/>
       <c r="J93"/>
@@ -46738,7 +47238,7 @@
       </c>
       <c r="F94"/>
       <c r="H94" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I94"/>
       <c r="J94"/>
@@ -46762,7 +47262,7 @@
       </c>
       <c r="F95"/>
       <c r="H95" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I95"/>
       <c r="J95"/>
@@ -46775,7 +47275,7 @@
         <v>847</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C96" t="s">
         <v>71</v>
@@ -46788,7 +47288,7 @@
       </c>
       <c r="F96"/>
       <c r="H96" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I96"/>
       <c r="J96"/>
@@ -46812,7 +47312,7 @@
       </c>
       <c r="F97"/>
       <c r="H97" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I97"/>
       <c r="J97"/>
@@ -46825,7 +47325,7 @@
         <v>851</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C98" t="s">
         <v>71</v>
@@ -46838,7 +47338,7 @@
       </c>
       <c r="F98"/>
       <c r="H98" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r